--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R2358f7c912aa49df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Define" sheetId="2" r:id="Rc55efde186494c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rde2c5120e3614fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Define" sheetId="2" r:id="R6a1d7bcc80ba4528"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -12282,10 +12282,10 @@
         <x:v>EidolonText117</x:v>
       </x:c>
       <x:c r="C614" s="3" t="str">
-        <x:v>선택한 모델과 같은 계열의 LoRA를 적용합니다.</x:v>
+        <x:v>같은 계열의 LoRA를 여러 개 선택할 수 있습니다. 저장된 트리거는 생성 프롬프트에 자동 적용됩니다.</x:v>
       </x:c>
       <x:c r="D614" s="3" t="str">
-        <x:v>Apply LoRAs from the same family as the selected model.</x:v>
+        <x:v>Select multiple LoRAs from the same model family. Their saved triggers are automatically applied to the generation prompt.</x:v>
       </x:c>
     </x:row>
     <x:row r="615" ht="16.5" hidden="0" customHeight="1">
@@ -12352,10 +12352,10 @@
         <x:v>EidolonText122</x:v>
       </x:c>
       <x:c r="C619" s="3" t="str">
-        <x:v>이미지 저장</x:v>
+        <x:v>다른 이름으로 저장</x:v>
       </x:c>
       <x:c r="D619" s="3" t="str">
-        <x:v>Save image</x:v>
+        <x:v>Save a copy</x:v>
       </x:c>
     </x:row>
     <x:row r="620" ht="16.5" hidden="0" customHeight="1">
@@ -12604,10 +12604,10 @@
         <x:v>EidolonText140</x:v>
       </x:c>
       <x:c r="C637" s="3" t="str">
-        <x:v>이미지 폴더</x:v>
+        <x:v>학습할 이미지</x:v>
       </x:c>
       <x:c r="D637" s="3" t="str">
-        <x:v>Image folder</x:v>
+        <x:v>Training images</x:v>
       </x:c>
     </x:row>
     <x:row r="638" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -12632,10 +12632,10 @@
         <x:v>EidolonText142</x:v>
       </x:c>
       <x:c r="C639" s="3" t="str">
-        <x:v>선택</x:v>
+        <x:v>폴더 선택</x:v>
       </x:c>
       <x:c r="D639" s="3" t="str">
-        <x:v>Browse</x:v>
+        <x:v>Choose folder</x:v>
       </x:c>
     </x:row>
     <x:row r="640" ht="16.5" hidden="0" customHeight="1">
@@ -12758,10 +12758,10 @@
         <x:v>EidolonText151</x:v>
       </x:c>
       <x:c r="C648" s="3" t="str">
-        <x:v>작업 폴더에서 학습 로그와 결과 가중치를 확인할 수 있습니다.</x:v>
+        <x:v>완료·실패·취소한 학습을 확인합니다. 학습한 LoRA는 생성 화면에서 선택해 사용할 수 있습니다.</x:v>
       </x:c>
       <x:c r="D648" s="3" t="str">
-        <x:v>Open a job folder to find its training log and output weights.</x:v>
+        <x:v>Review completed, failed or cancelled training. Select a trained LoRA in Generate to use it.</x:v>
       </x:c>
     </x:row>
     <x:row r="649" ht="16.5" hidden="0" customHeight="1">
@@ -13136,10 +13136,10 @@
         <x:v>EidolonText178</x:v>
       </x:c>
       <x:c r="C675" s="3" t="str">
-        <x:v>긍정 프롬프트</x:v>
+        <x:v>공용 긍정 프롬프트</x:v>
       </x:c>
       <x:c r="D675" s="3" t="str">
-        <x:v>Positive prompt</x:v>
+        <x:v>Shared positive prompt</x:v>
       </x:c>
     </x:row>
     <x:row r="676" ht="16.5" hidden="0" customHeight="1">
@@ -13164,10 +13164,10 @@
         <x:v>EidolonText180</x:v>
       </x:c>
       <x:c r="C677" s="3" t="str">
-        <x:v>부정 프롬프트</x:v>
+        <x:v>공용 부정 프롬프트</x:v>
       </x:c>
       <x:c r="D677" s="3" t="str">
-        <x:v>Negative prompt</x:v>
+        <x:v>Shared negative prompt</x:v>
       </x:c>
     </x:row>
     <x:row r="678" ht="16.5" hidden="0" customHeight="1">
@@ -13262,10 +13262,10 @@
         <x:v>EidolonText187</x:v>
       </x:c>
       <x:c r="C684" s="3" t="str">
-        <x:v>기본 SDXL Base 1.0 모델 다운로드를 선택하거나 모델·LoRA 탭에서 .safetensors 파일을 가져옵니다. 설치된 모델만 표시하며 SDXL을 기본으로 선택합니다. 최초 설치에는 인터넷 연결과 여러 GB의 여유 공간이 필요합니다.</x:v>
+        <x:v>기본 SDXL Base 1.0 모델 다운로드를 선택하거나 엔진의 모델·LoRA 탭에서 .safetensors 파일을 가져옵니다. 설치된 모델만 표시하며 SDXL을 기본으로 선택합니다. 최초 설치에는 인터넷 연결과 여러 GB의 여유 공간이 필요합니다.</x:v>
       </x:c>
       <x:c r="D684" s="3" t="str">
-        <x:v>Download the default SDXL Base 1.0 model, or import a .safetensors file in Models and LoRAs. Only installed models are shown, with SDXL selected by default. Initial setup requires internet access and several GB of free space.</x:v>
+        <x:v>Download the default SDXL Base 1.0 model, or import a .safetensors file in Engine &gt; Models and LoRAs. Only installed models are shown, with SDXL selected by default. Initial setup requires internet access and several GB of free space.</x:v>
       </x:c>
     </x:row>
     <x:row r="685" ht="16.5" hidden="0" customHeight="1">
@@ -13276,10 +13276,10 @@
         <x:v>EidolonText188</x:v>
       </x:c>
       <x:c r="C685" s="3" t="str">
-        <x:v>엔진 탭에는 ComfyUI 서버 주소만 입력합니다. 실행 중인 서버가 있으면 연결하고 로컬 주소에 서버가 없으면 설치한 엔진을 실행합니다. 앱이 시작한 서버는 종료 시 함께 종료하며 기존 서버는 유지합니다.</x:v>
+        <x:v>프롬프트로 이미지 생성</x:v>
       </x:c>
       <x:c r="D685" s="3" t="str">
-        <x:v>Enter the ComfyUI server address in Engine. Connect to an existing server, or start the installed engine if no server is running at a local address. Servers started by this app stop when it closes; existing servers keep running.</x:v>
+        <x:v>Generate from a prompt</x:v>
       </x:c>
     </x:row>
     <x:row r="686" ht="105.5999984741211" hidden="0" customHeight="1">
@@ -13290,10 +13290,10 @@
         <x:v>EidolonText189</x:v>
       </x:c>
       <x:c r="C686" s="3" t="str">
-        <x:v>생성 탭에서 만들고 싶은 장면을 입력하고 대기열에 추가를 누릅니다. 설치된 모델만 선택 목록에 표시합니다. 기본 모델을 선택한 뒤에는 프롬프트만 입력하면 됩니다. 실행 중에도 다음 요청을 추가할 수 있습니다.</x:v>
+        <x:v>생성 탭에서 만들고 싶은 장면을 입력하고 대기열에 추가를 누릅니다. 설치된 모델만 선택 목록에 표시합니다. 배경 투명하게를 체크하면 최종 이미지를 투명 PNG로 저장합니다. 실행 중에도 다음 요청을 추가할 수 있습니다.</x:v>
       </x:c>
       <x:c r="D686" s="3" t="str">
-        <x:v>In Generate, describe your scene and press Add to queue. Only installed models appear in the selector. After choosing a default model, enter just a prompt. You can add more requests while a job is running.</x:v>
+        <x:v>In Generate, describe your scene and press Add to queue. Only installed models appear in the selector. Enable Transparent background to save the final image as a transparent PNG. You can add more requests while a job is running.</x:v>
       </x:c>
     </x:row>
     <x:row r="687" ht="105.5999984741211" hidden="0" customHeight="1">
@@ -13304,10 +13304,10 @@
         <x:v>EidolonText190</x:v>
       </x:c>
       <x:c r="C687" s="3" t="str">
-        <x:v>설정의 공용 긍정 프롬프트에는 반복할 스타일을, 부정 프롬프트에는 피할 표현을 입력하세요. 저장한 내용은 이후 생성에 적용됩니다. 생성 이력을 선택하면 프롬프트를 다시 사용할 수 있습니다.</x:v>
+        <x:v>설정의 공용 긍정 프롬프트에는 반복할 스타일을, 부정 프롬프트에는 피할 표현을 입력하세요. 저장한 내용은 생성 화면에도 표시되고 이후 생성에 적용됩니다. 생성 결과에서 프롬프트를 다시 사용할 수 있습니다.</x:v>
       </x:c>
       <x:c r="D687" s="3" t="str">
-        <x:v>Use the shared positive prompt in Settings for recurring styles, and the negative prompt for things to avoid. Saved prompts apply to later generations. Select a generation history entry to reuse its prompt.</x:v>
+        <x:v>Use the shared positive prompt in Settings for recurring styles, and the negative prompt for things to avoid. Saved prompts are shown in Generate and apply to later generations. Reuse a prompt from Results.</x:v>
       </x:c>
     </x:row>
     <x:row r="688" ht="16.5" hidden="0" customHeight="1">
@@ -13332,10 +13332,10 @@
         <x:v>EidolonText192</x:v>
       </x:c>
       <x:c r="C689" s="3" t="str">
-        <x:v>LoRA 학습 탭에서 기반 모델, 이미지 폴더, 이름과 트리거를 지정하고 대기열에 추가를 누릅니다. PNG·JPG·BMP와 하위 폴더, 같은 이름의 .txt 캡션을 지원합니다. 기존 LoRA 이어 학습을 켜면 저장된 가중치와 rank부터 추가 학습합니다. optimizer와 스케줄은 새로 시작하며 결과는 새 LoRA로 저장합니다. 원본 이미지와 LoRA는 보존합니다.</x:v>
+        <x:v>모델, 이미지와 LoRA 이름·트리거를 지정합니다. 단계 수를 입력하거나 빠른·기본 학습을 선택한 뒤 대기열에 추가합니다. 요청 버튼 옆에서 학습을 취소할 수 있습니다. 하단에는 진행 상태와 예상 남은 시간을 표시합니다. 학습한 LoRA를 생성에서 선택하면 트리거가 자동 적용됩니다.</x:v>
       </x:c>
       <x:c r="D689" s="3" t="str">
-        <x:v>In LoRA training, select a base model and image folder, enter a name and trigger, then add to queue. PNG, JPG, BMP, subfolders and matching .txt captions are supported. Enable Continue training an existing LoRA to start from its weights and rank. The optimizer and schedule start fresh, and a new LoRA is saved. Original images and LoRAs are preserved.</x:v>
+        <x:v>Choose a model, images, LoRA name and trigger. Enter steps or use Quick or Standard, then queue training. Cancel beside the request button. The footer shows progress and estimated time remaining. Selecting a trained LoRA applies its trigger automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="690" ht="105.5999984741211" hidden="0" customHeight="1">
@@ -13374,10 +13374,10 @@
         <x:v>EidolonText195</x:v>
       </x:c>
       <x:c r="C692" s="3" t="str">
-        <x:v>창 하단에서 현재 상태, 진행률과 대기 건수를 확인합니다. 작업 취소는 실행 중인 요청만 취소하며 다음 요청은 계속 실행합니다. 대기 작업 비우기는 아직 시작하지 않은 요청을 취소합니다. 앱을 종료하면 실행 중인 작업과 대기 요청을 취소합니다. 다운로드가 중단되면 같은 경로에 설치·복구를 다시 실행하세요.</x:v>
+        <x:v>하단에는 상태·진행률·남은 시간과 대기 건수만 표시합니다. 학습 취소는 학습 요청 버튼 옆에 있습니다. 생성·학습 화면의 대기열 목록에서 아직 시작하지 않은 요청을 비울 수 있습니다. 앱 종료 시 실행 중인 작업과 대기 요청을 정리합니다.</x:v>
       </x:c>
       <x:c r="D692" s="3" t="str">
-        <x:v>Check the current status, progress and pending count at the bottom of the window. Cancel job cancels the running request and the next request continues. Clear pending jobs cancels requests that have not started. Closing the app cancels running and pending requests. If a download stops, run install or repair at the same path.</x:v>
+        <x:v>The footer displays status, progress, time remaining and pending count. Cancel training beside the request button. Clear requests that have not started from the queue in Generate or Train. Closing the app cleans up running and pending work.</x:v>
       </x:c>
     </x:row>
     <x:row r="693" ht="118.80000305175781" hidden="0" customHeight="1">
@@ -13684,14 +13684,14 @@
       <x:c r="C714" s="3" t="str">
         <x:v>
 {0} × {1} · seed {2}
-긍정: {3}
-부정: {4}</x:v>
+생성에 사용된 프롬프트: {3}
+부정 프롬프트: {4}</x:v>
       </x:c>
       <x:c r="D714" s="3" t="str">
         <x:v>
 {0} × {1} · seed {2}
-Positive: {3}
-Negative: {4}</x:v>
+Prompt used for generation: {3}
+Negative prompt: {4}</x:v>
       </x:c>
     </x:row>
     <x:row r="715" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -14450,6 +14450,1000 @@
       </x:c>
       <x:c r="D768" s="3" t="str">
         <x:v>Connect to server</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="769" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A769" s="2" t="n">
+        <x:v>3352</x:v>
+      </x:c>
+      <x:c r="B769" s="2" t="str">
+        <x:v>EidolonText272</x:v>
+      </x:c>
+      <x:c r="C769" s="3" t="str">
+        <x:v>설치된 엔진 모듈</x:v>
+      </x:c>
+      <x:c r="D769" s="3" t="str">
+        <x:v>Installed engine modules</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="770" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A770" s="2" t="n">
+        <x:v>3353</x:v>
+      </x:c>
+      <x:c r="B770" s="2" t="str">
+        <x:v>EidolonText273</x:v>
+      </x:c>
+      <x:c r="C770" s="3" t="str">
+        <x:v>목록 새로고침</x:v>
+      </x:c>
+      <x:c r="D770" s="3" t="str">
+        <x:v>Refresh list</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="771" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A771" s="2" t="n">
+        <x:v>3354</x:v>
+      </x:c>
+      <x:c r="B771" s="2" t="str">
+        <x:v>EidolonText274</x:v>
+      </x:c>
+      <x:c r="C771" s="3" t="str">
+        <x:v>실행 구성요소</x:v>
+      </x:c>
+      <x:c r="D771" s="3" t="str">
+        <x:v>Runtime components</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="772" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A772" s="2" t="n">
+        <x:v>3355</x:v>
+      </x:c>
+      <x:c r="B772" s="2" t="str">
+        <x:v>EidolonText275</x:v>
+      </x:c>
+      <x:c r="C772" s="3" t="str">
+        <x:v>ComfyUI 커스텀 노드</x:v>
+      </x:c>
+      <x:c r="D772" s="3" t="str">
+        <x:v>ComfyUI custom nodes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="773" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A773" s="2" t="n">
+        <x:v>3356</x:v>
+      </x:c>
+      <x:c r="B773" s="2" t="str">
+        <x:v>EidolonText276</x:v>
+      </x:c>
+      <x:c r="C773" s="3" t="str">
+        <x:v>설치됨</x:v>
+      </x:c>
+      <x:c r="D773" s="3" t="str">
+        <x:v>Installed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="774" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A774" s="2" t="n">
+        <x:v>3357</x:v>
+      </x:c>
+      <x:c r="B774" s="2" t="str">
+        <x:v>EidolonText277</x:v>
+      </x:c>
+      <x:c r="C774" s="3" t="str">
+        <x:v>미설치</x:v>
+      </x:c>
+      <x:c r="D774" s="3" t="str">
+        <x:v>Not installed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="775" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A775" s="2" t="n">
+        <x:v>3358</x:v>
+      </x:c>
+      <x:c r="B775" s="2" t="str">
+        <x:v>EidolonText278</x:v>
+      </x:c>
+      <x:c r="C775" s="3" t="str">
+        <x:v>비활성화</x:v>
+      </x:c>
+      <x:c r="D775" s="3" t="str">
+        <x:v>Disabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="776" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A776" s="2" t="n">
+        <x:v>3359</x:v>
+      </x:c>
+      <x:c r="B776" s="2" t="str">
+        <x:v>EidolonText279</x:v>
+      </x:c>
+      <x:c r="C776" s="3" t="str">
+        <x:v>버전 정보 없음</x:v>
+      </x:c>
+      <x:c r="D776" s="3" t="str">
+        <x:v>Version unavailable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="777" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A777" s="2" t="n">
+        <x:v>3360</x:v>
+      </x:c>
+      <x:c r="B777" s="2" t="str">
+        <x:v>EidolonText280</x:v>
+      </x:c>
+      <x:c r="C777" s="3" t="str">
+        <x:v>설치 경로를 선택하면 구성요소를 표시합니다.</x:v>
+      </x:c>
+      <x:c r="D777" s="3" t="str">
+        <x:v>Choose an installation path to view its components.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="778" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A778" s="2" t="n">
+        <x:v>3361</x:v>
+      </x:c>
+      <x:c r="B778" s="2" t="str">
+        <x:v>EidolonText281</x:v>
+      </x:c>
+      <x:c r="C778" s="3" t="str">
+        <x:v>설치된 커스텀 노드가 없습니다.</x:v>
+      </x:c>
+      <x:c r="D778" s="3" t="str">
+        <x:v>No installed custom nodes were found.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="779" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A779" s="2" t="n">
+        <x:v>3362</x:v>
+      </x:c>
+      <x:c r="B779" s="2" t="str">
+        <x:v>EidolonText282</x:v>
+      </x:c>
+      <x:c r="C779" s="3" t="str">
+        <x:v>Python (이미지 생성)</x:v>
+      </x:c>
+      <x:c r="D779" s="3" t="str">
+        <x:v>Python (generation)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="780" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A780" s="2" t="n">
+        <x:v>3363</x:v>
+      </x:c>
+      <x:c r="B780" s="2" t="str">
+        <x:v>EidolonText283</x:v>
+      </x:c>
+      <x:c r="C780" s="3" t="str">
+        <x:v>Python (LoRA 학습)</x:v>
+      </x:c>
+      <x:c r="D780" s="3" t="str">
+        <x:v>Python (LoRA training)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="781" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A781" s="2" t="n">
+        <x:v>3364</x:v>
+      </x:c>
+      <x:c r="B781" s="2" t="str">
+        <x:v>EidolonText284</x:v>
+      </x:c>
+      <x:c r="C781" s="3" t="str">
+        <x:v>선택한 로컬 설치 폴더의 구성요소와 커스텀 노드 파일을 표시합니다.</x:v>
+      </x:c>
+      <x:c r="D781" s="3" t="str">
+        <x:v>Show components and custom node files in the selected local installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="782" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A782" s="2" t="n">
+        <x:v>3365</x:v>
+      </x:c>
+      <x:c r="B782" s="2" t="str">
+        <x:v>EidolonText285</x:v>
+      </x:c>
+      <x:c r="C782" s="3" t="str">
+        <x:v>엔진 탭에는 ComfyUI 서버 주소만 입력합니다. 실행 중인 서버가 있으면 연결하고 로컬 주소에 서버가 없으면 설치한 엔진을 실행합니다. 앱이 시작한 서버는 종료 시 함께 종료하며 기존 서버는 유지합니다.</x:v>
+      </x:c>
+      <x:c r="D782" s="3" t="str">
+        <x:v>Enter the ComfyUI server address in Engine. Connect to an existing server, or start the installed engine if no server is running at a local address. Servers started by this app stop when it closes; existing servers keep running.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="783" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A783" s="2" t="n">
+        <x:v>3366</x:v>
+      </x:c>
+      <x:c r="B783" s="2" t="str">
+        <x:v>EidolonText286</x:v>
+      </x:c>
+      <x:c r="C783" s="3" t="str">
+        <x:v>설치 목록을 불러오지 못했습니다. {0}</x:v>
+      </x:c>
+      <x:c r="D783" s="3" t="str">
+        <x:v>Could not load the installed modules. {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="784" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A784" s="2" t="n">
+        <x:v>3367</x:v>
+      </x:c>
+      <x:c r="B784" s="2" t="str">
+        <x:v>EidolonText287</x:v>
+      </x:c>
+      <x:c r="C784" s="3" t="str">
+        <x:v>기본 외곽선 추출 노드를 다운로드합니다.</x:v>
+      </x:c>
+      <x:c r="D784" s="3" t="str">
+        <x:v>Downloading the default outline extraction nodes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="785" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A785" s="2" t="n">
+        <x:v>3368</x:v>
+      </x:c>
+      <x:c r="B785" s="2" t="str">
+        <x:v>EidolonText288</x:v>
+      </x:c>
+      <x:c r="C785" s="3" t="str">
+        <x:v>외곽선 추출 노드의 실행 패키지를 설치합니다.</x:v>
+      </x:c>
+      <x:c r="D785" s="3" t="str">
+        <x:v>Installing dependencies for the outline extraction nodes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="786" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A786" s="2" t="n">
+        <x:v>3369</x:v>
+      </x:c>
+      <x:c r="B786" s="2" t="str">
+        <x:v>EidolonText289</x:v>
+      </x:c>
+      <x:c r="C786" s="3" t="str">
+        <x:v>커스텀 노드의 필수 파일이 없습니다. {0}</x:v>
+      </x:c>
+      <x:c r="D786" s="3" t="str">
+        <x:v>A required custom node file is missing. {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="787" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A787" s="2" t="n">
+        <x:v>3370</x:v>
+      </x:c>
+      <x:c r="B787" s="2" t="str">
+        <x:v>EidolonText290</x:v>
+      </x:c>
+      <x:c r="C787" s="3" t="str">
+        <x:v>외곽선 추출(Canny·Lineart) 노드도 기본 설치합니다. 기존 설치는 설치·복구를 실행해 추가하세요.</x:v>
+      </x:c>
+      <x:c r="D787" s="3" t="str">
+        <x:v>Canny and Lineart extraction nodes are installed by default. Run install or repair to add them to an existing installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="788" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A788" s="2" t="n">
+        <x:v>3371</x:v>
+      </x:c>
+      <x:c r="B788" s="2" t="str">
+        <x:v>EidolonText291</x:v>
+      </x:c>
+      <x:c r="C788" s="3" t="str">
+        <x:v>생성 결과</x:v>
+      </x:c>
+      <x:c r="D788" s="3" t="str">
+        <x:v>Results</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="789" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A789" s="2" t="n">
+        <x:v>3372</x:v>
+      </x:c>
+      <x:c r="B789" s="2" t="str">
+        <x:v>EidolonText292</x:v>
+      </x:c>
+      <x:c r="C789" s="3" t="str">
+        <x:v>입력 프롬프트</x:v>
+      </x:c>
+      <x:c r="D789" s="3" t="str">
+        <x:v>Input prompt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="790" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A790" s="2" t="n">
+        <x:v>3373</x:v>
+      </x:c>
+      <x:c r="B790" s="2" t="str">
+        <x:v>EidolonText293</x:v>
+      </x:c>
+      <x:c r="C790" s="3" t="str">
+        <x:v>실제 생성에 사용된 프롬프트</x:v>
+      </x:c>
+      <x:c r="D790" s="3" t="str">
+        <x:v>Prompt used for generation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="791" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A791" s="2" t="n">
+        <x:v>3374</x:v>
+      </x:c>
+      <x:c r="B791" s="2" t="str">
+        <x:v>EidolonText294</x:v>
+      </x:c>
+      <x:c r="C791" s="3" t="str">
+        <x:v>부정 프롬프트</x:v>
+      </x:c>
+      <x:c r="D791" s="3" t="str">
+        <x:v>Negative prompt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="792" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A792" s="2" t="n">
+        <x:v>3375</x:v>
+      </x:c>
+      <x:c r="B792" s="2" t="str">
+        <x:v>EidolonText295</x:v>
+      </x:c>
+      <x:c r="C792" s="3" t="str">
+        <x:v>이 결과로 학습</x:v>
+      </x:c>
+      <x:c r="D792" s="3" t="str">
+        <x:v>Use for training</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="793" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A793" s="2" t="n">
+        <x:v>3376</x:v>
+      </x:c>
+      <x:c r="B793" s="2" t="str">
+        <x:v>EidolonText296</x:v>
+      </x:c>
+      <x:c r="C793" s="3" t="str">
+        <x:v>이미지 폴더 열기</x:v>
+      </x:c>
+      <x:c r="D793" s="3" t="str">
+        <x:v>Open image folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="794" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A794" s="2" t="n">
+        <x:v>3377</x:v>
+      </x:c>
+      <x:c r="B794" s="2" t="str">
+        <x:v>EidolonText297</x:v>
+      </x:c>
+      <x:c r="C794" s="3" t="str">
+        <x:v>생성 이미지 저장 폴더</x:v>
+      </x:c>
+      <x:c r="D794" s="3" t="str">
+        <x:v>Generated images folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="795" ht="66" hidden="0" customHeight="1">
+      <x:c r="A795" s="2" t="n">
+        <x:v>3378</x:v>
+      </x:c>
+      <x:c r="B795" s="2" t="str">
+        <x:v>EidolonText298</x:v>
+      </x:c>
+      <x:c r="C795" s="3" t="str">
+        <x:v>새 생성의 최종 이미지만 이 폴더에 GUID.png로 저장합니다. 기본 경로는 사용자 AppData의 Eidolon\Images이며 다른 폴더를 지정할 수 있습니다. 원본은 Job 폴더에 보관하고 이전 결과는 이동하지 않습니다.</x:v>
+      </x:c>
+      <x:c r="D795" s="3" t="str">
+        <x:v>New generations save only the final image here as GUID.png. Default: Eidolon\Images under local AppData. You can choose another folder. Originals stay in job folders; previous results are not moved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="796" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A796" s="2" t="n">
+        <x:v>3379</x:v>
+      </x:c>
+      <x:c r="B796" s="2" t="str">
+        <x:v>EidolonText299</x:v>
+      </x:c>
+      <x:c r="C796" s="3" t="str">
+        <x:v>생성 이미지 저장 폴더 선택</x:v>
+      </x:c>
+      <x:c r="D796" s="3" t="str">
+        <x:v>Choose a folder for generated images</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="797" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A797" s="2" t="n">
+        <x:v>3380</x:v>
+      </x:c>
+      <x:c r="B797" s="2" t="str">
+        <x:v>EidolonText300</x:v>
+      </x:c>
+      <x:c r="C797" s="3" t="str">
+        <x:v>이미지 저장 폴더는 절대 경로를 입력하세요.</x:v>
+      </x:c>
+      <x:c r="D797" s="3" t="str">
+        <x:v>Enter an absolute path for the generated images folder.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="798" ht="66" hidden="0" customHeight="1">
+      <x:c r="A798" s="2" t="n">
+        <x:v>3381</x:v>
+      </x:c>
+      <x:c r="B798" s="2" t="str">
+        <x:v>EidolonText301</x:v>
+      </x:c>
+      <x:c r="C798" s="3" t="str">
+        <x:v>결과 이미지와 프롬프트를 가져왔습니다. 생성에 사용한 모델이 현재 목록에 없으므로 학습에 사용할 기반 모델을 선택하세요.</x:v>
+      </x:c>
+      <x:c r="D798" s="3" t="str">
+        <x:v>Loaded the result images and prompt. The model used for generation is not in the current list; select a base model for training.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="799" ht="66" hidden="0" customHeight="1">
+      <x:c r="A799" s="2" t="n">
+        <x:v>3382</x:v>
+      </x:c>
+      <x:c r="B799" s="2" t="str">
+        <x:v>EidolonText302</x:v>
+      </x:c>
+      <x:c r="C799" s="3" t="str">
+        <x:v>선택한 이미지와 생성에 사용된 프롬프트를 학습 입력으로 가져왔습니다. 이름과 트리거를 입력해 학습을 시작하세요.</x:v>
+      </x:c>
+      <x:c r="D799" s="3" t="str">
+        <x:v>Loaded the selected image and prompt used for generation into the training inputs. Enter a name and trigger to start training.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="800" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A800" s="2" t="n">
+        <x:v>3383</x:v>
+      </x:c>
+      <x:c r="B800" s="2" t="str">
+        <x:v>EidolonText303</x:v>
+      </x:c>
+      <x:c r="C800" s="3" t="str">
+        <x:v>이전 이미지와 적용된 프롬프트는 생성 결과 탭에서 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D800" s="3" t="str">
+        <x:v>View previous images and their applied prompts in Results.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="801" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A801" s="2" t="n">
+        <x:v>3384</x:v>
+      </x:c>
+      <x:c r="B801" s="2" t="str">
+        <x:v>EidolonText304</x:v>
+      </x:c>
+      <x:c r="C801" s="3" t="str">
+        <x:v>이미지를 생성하면 사용한 프롬프트와 함께 이곳에 기록됩니다.</x:v>
+      </x:c>
+      <x:c r="D801" s="3" t="str">
+        <x:v>Generated images appear here together with the prompts used.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="802" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A802" s="2" t="n">
+        <x:v>3385</x:v>
+      </x:c>
+      <x:c r="B802" s="2" t="str">
+        <x:v>EidolonText305</x:v>
+      </x:c>
+      <x:c r="C802" s="3" t="str">
+        <x:v>이 결과로 학습은 선택한 이미지 한 장과 생성에 사용된 프롬프트를 학습 입력으로 가져옵니다. 이름·트리거와 이어 학습할 LoRA는 학습 탭에서 지정하세요.</x:v>
+      </x:c>
+      <x:c r="D802" s="3" t="str">
+        <x:v>Use for training fills the selected image and prompt used for generation. In Training, enter a name and trigger, and select a LoRA to continue training.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="803" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A803" s="2" t="n">
+        <x:v>3386</x:v>
+      </x:c>
+      <x:c r="B803" s="2" t="str">
+        <x:v>EidolonText306</x:v>
+      </x:c>
+      <x:c r="C803" s="3" t="str">
+        <x:v>사용된 모델</x:v>
+      </x:c>
+      <x:c r="D803" s="3" t="str">
+        <x:v>Model used</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="804" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A804" s="2" t="n">
+        <x:v>3387</x:v>
+      </x:c>
+      <x:c r="B804" s="2" t="str">
+        <x:v>EidolonText307</x:v>
+      </x:c>
+      <x:c r="C804" s="3" t="str">
+        <x:v>표시할 결과 이미지가 없습니다.</x:v>
+      </x:c>
+      <x:c r="D804" s="3" t="str">
+        <x:v>No result image to display.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="805" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A805" s="2" t="n">
+        <x:v>3388</x:v>
+      </x:c>
+      <x:c r="B805" s="2" t="str">
+        <x:v>EidolonText308</x:v>
+      </x:c>
+      <x:c r="C805" s="3" t="str">
+        <x:v>배경 투명하게</x:v>
+      </x:c>
+      <x:c r="D805" s="3" t="str">
+        <x:v>Transparent background</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="806" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A806" s="2" t="n">
+        <x:v>3389</x:v>
+      </x:c>
+      <x:c r="B806" s="2" t="str">
+        <x:v>EidolonText309</x:v>
+      </x:c>
+      <x:c r="C806" s="3" t="str">
+        <x:v>생성 후 배경을 제거해 저장 폴더에 최종 PNG 한 장을 저장합니다. 원본은 앱의 작업 폴더에 보관하며 처음 사용할 때 배경 제거 모델을 내려받습니다.</x:v>
+      </x:c>
+      <x:c r="D806" s="3" t="str">
+        <x:v>Remove the background after generation and save one final PNG in the output folder. The original is kept in the app job folder, and the removal model is downloaded on first use.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="807" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A807" s="2" t="n">
+        <x:v>3390</x:v>
+      </x:c>
+      <x:c r="B807" s="2" t="str">
+        <x:v>EidolonText310</x:v>
+      </x:c>
+      <x:c r="C807" s="3" t="str">
+        <x:v>배경 제거 모델을 준비합니다.</x:v>
+      </x:c>
+      <x:c r="D807" s="3" t="str">
+        <x:v>Preparing the background removal model.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="808" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A808" s="2" t="n">
+        <x:v>3391</x:v>
+      </x:c>
+      <x:c r="B808" s="2" t="str">
+        <x:v>EidolonText311</x:v>
+      </x:c>
+      <x:c r="C808" s="3" t="str">
+        <x:v>이미지 배경을 제거합니다.</x:v>
+      </x:c>
+      <x:c r="D808" s="3" t="str">
+        <x:v>Removing the image background.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="809" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A809" s="2" t="n">
+        <x:v>3392</x:v>
+      </x:c>
+      <x:c r="B809" s="2" t="str">
+        <x:v>EidolonText312</x:v>
+      </x:c>
+      <x:c r="C809" s="3" t="str">
+        <x:v>배경을 제거한 투명 PNG를 저장했습니다.</x:v>
+      </x:c>
+      <x:c r="D809" s="3" t="str">
+        <x:v>Saved a transparent PNG with the background removed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="810" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A810" s="2" t="n">
+        <x:v>3393</x:v>
+      </x:c>
+      <x:c r="B810" s="2" t="str">
+        <x:v>EidolonText313</x:v>
+      </x:c>
+      <x:c r="C810" s="3" t="str">
+        <x:v>선택한 생성 기록이나 이미지가 없습니다.</x:v>
+      </x:c>
+      <x:c r="D810" s="3" t="str">
+        <x:v>The selected generation record or image is unavailable.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="811" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A811" s="2" t="n">
+        <x:v>3394</x:v>
+      </x:c>
+      <x:c r="B811" s="2" t="str">
+        <x:v>EidolonText314</x:v>
+      </x:c>
+      <x:c r="C811" s="3" t="str">
+        <x:v>실행 중인 생성 작업의 기록은 변경할 수 없습니다.</x:v>
+      </x:c>
+      <x:c r="D811" s="3" t="str">
+        <x:v>A running generation record cannot be changed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="812" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A812" s="2" t="n">
+        <x:v>3395</x:v>
+      </x:c>
+      <x:c r="B812" s="2" t="str">
+        <x:v>EidolonText315</x:v>
+      </x:c>
+      <x:c r="C812" s="3" t="str">
+        <x:v>이미지 배경을 제거하지 못했습니다. 로그를 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D812" s="3" t="str">
+        <x:v>Could not remove the image background. Check the logs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="813" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A813" s="2" t="n">
+        <x:v>3396</x:v>
+      </x:c>
+      <x:c r="B813" s="2" t="str">
+        <x:v>EidolonText316</x:v>
+      </x:c>
+      <x:c r="C813" s="3" t="str">
+        <x:v>선택 삭제</x:v>
+      </x:c>
+      <x:c r="D813" s="3" t="str">
+        <x:v>Delete selected</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="814" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A814" s="2" t="n">
+        <x:v>3397</x:v>
+      </x:c>
+      <x:c r="B814" s="2" t="str">
+        <x:v>EidolonText317</x:v>
+      </x:c>
+      <x:c r="C814" s="3" t="str">
+        <x:v>전체 삭제</x:v>
+      </x:c>
+      <x:c r="D814" s="3" t="str">
+        <x:v>Delete all</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="815" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A815" s="2" t="n">
+        <x:v>3398</x:v>
+      </x:c>
+      <x:c r="B815" s="2" t="str">
+        <x:v>EidolonText318</x:v>
+      </x:c>
+      <x:c r="C815" s="3" t="str">
+        <x:v>생성 기록 삭제</x:v>
+      </x:c>
+      <x:c r="D815" s="3" t="str">
+        <x:v>Delete generation history</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="816" ht="66" hidden="0" customHeight="1">
+      <x:c r="A816" s="2" t="n">
+        <x:v>3399</x:v>
+      </x:c>
+      <x:c r="B816" s="2" t="str">
+        <x:v>EidolonText319</x:v>
+      </x:c>
+      <x:c r="C816" s="3" t="str">
+        <x:v>선택한 생성 기록과 Job 폴더를 삭제할까요? 프롬프트·모델 정보와 Job 폴더의 원본 이미지는 삭제됩니다. 최종 저장 이미지와 학습 기록은 보존합니다.</x:v>
+      </x:c>
+      <x:c r="D816" s="3" t="str">
+        <x:v>Delete the selected generation record and job folder? Prompt and model information and original images in the job folder will be removed. Final saved images and training records are kept.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="817" ht="66" hidden="0" customHeight="1">
+      <x:c r="A817" s="2" t="n">
+        <x:v>3400</x:v>
+      </x:c>
+      <x:c r="B817" s="2" t="str">
+        <x:v>EidolonText320</x:v>
+      </x:c>
+      <x:c r="C817" s="3" t="str">
+        <x:v>생성 기록 {0}개와 해당 Job 폴더를 모두 삭제할까요? 프롬프트·모델 정보와 원본 이미지는 삭제됩니다. 최종 저장 이미지와 학습 기록은 보존합니다.</x:v>
+      </x:c>
+      <x:c r="D817" s="3" t="str">
+        <x:v>Delete all {0} generation records and their job folders? Prompt and model information and original images will be removed. Final saved images and training records are kept.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="818" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A818" s="2" t="n">
+        <x:v>3401</x:v>
+      </x:c>
+      <x:c r="B818" s="2" t="str">
+        <x:v>EidolonText321</x:v>
+      </x:c>
+      <x:c r="C818" s="3" t="str">
+        <x:v>삭제</x:v>
+      </x:c>
+      <x:c r="D818" s="3" t="str">
+        <x:v>Delete</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="819" ht="16.5" hidden="0" customHeight="1">
+      <x:c r="A819" s="2" t="n">
+        <x:v>3402</x:v>
+      </x:c>
+      <x:c r="B819" s="2" t="str">
+        <x:v>EidolonText322</x:v>
+      </x:c>
+      <x:c r="C819" s="3" t="str">
+        <x:v>취소</x:v>
+      </x:c>
+      <x:c r="D819" s="3" t="str">
+        <x:v>Cancel</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="820" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A820" s="2" t="n">
+        <x:v>3403</x:v>
+      </x:c>
+      <x:c r="B820" s="2" t="str">
+        <x:v>EidolonText323</x:v>
+      </x:c>
+      <x:c r="C820" s="3" t="str">
+        <x:v>생성 기록 {0}개와 Job 폴더를 삭제했습니다. 최종 저장 이미지는 보존했습니다.</x:v>
+      </x:c>
+      <x:c r="D820" s="3" t="str">
+        <x:v>Deleted {0} generation records and their job folders. Final saved images were kept.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="821" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A821" s="2" t="n">
+        <x:v>3404</x:v>
+      </x:c>
+      <x:c r="B821" s="2" t="str">
+        <x:v>EidolonText324</x:v>
+      </x:c>
+      <x:c r="C821" s="3" t="str">
+        <x:v>표시된 결과 이미지 한 장만 학습합니다. 폴더 열기로 위치를 확인하거나 폴더로 변경을 눌러 폴더 전체를 학습할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D821" s="3" t="str">
+        <x:v>Train only the result image shown here. Open folder shows its location. Use Switch to folder to train every image in a folder instead.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="822">
+      <x:c r="A822" s="2" t="n">
+        <x:v>3405</x:v>
+      </x:c>
+      <x:c r="B822" s="2" t="str">
+        <x:v>EidolonText325</x:v>
+      </x:c>
+      <x:c r="C822" s="3" t="str">
+        <x:v>아직 이미지가 없습니다</x:v>
+      </x:c>
+      <x:c r="D822" s="3" t="str">
+        <x:v>No images yet</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="823">
+      <x:c r="A823" s="2" t="n">
+        <x:v>3406</x:v>
+      </x:c>
+      <x:c r="B823" s="2" t="str">
+        <x:v>EidolonText326</x:v>
+      </x:c>
+      <x:c r="C823" s="3" t="str">
+        <x:v>빠른 학습</x:v>
+      </x:c>
+      <x:c r="D823" s="3" t="str">
+        <x:v>Quick training</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="824">
+      <x:c r="A824" s="2" t="n">
+        <x:v>3407</x:v>
+      </x:c>
+      <x:c r="B824" s="2" t="str">
+        <x:v>EidolonText327</x:v>
+      </x:c>
+      <x:c r="C824" s="3" t="str">
+        <x:v>학습 취소</x:v>
+      </x:c>
+      <x:c r="D824" s="3" t="str">
+        <x:v>Cancel training</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="825">
+      <x:c r="A825" s="2" t="n">
+        <x:v>3408</x:v>
+      </x:c>
+      <x:c r="B825" s="2" t="str">
+        <x:v>EidolonText328</x:v>
+      </x:c>
+      <x:c r="C825" s="3" t="str">
+        <x:v>학습 취소 중…</x:v>
+      </x:c>
+      <x:c r="D825" s="3" t="str">
+        <x:v>Cancelling training…</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="826">
+      <x:c r="A826" s="2" t="n">
+        <x:v>3409</x:v>
+      </x:c>
+      <x:c r="B826" s="2" t="str">
+        <x:v>EidolonText329</x:v>
+      </x:c>
+      <x:c r="C826" s="3" t="str">
+        <x:v>예상 남은 시간: {0}</x:v>
+      </x:c>
+      <x:c r="D826" s="3" t="str">
+        <x:v>Estimated time remaining: {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="827">
+      <x:c r="A827" s="2" t="n">
+        <x:v>3410</x:v>
+      </x:c>
+      <x:c r="B827" s="2" t="str">
+        <x:v>EidolonText330</x:v>
+      </x:c>
+      <x:c r="C827" s="3" t="str">
+        <x:v>남은 시간 계산 중…</x:v>
+      </x:c>
+      <x:c r="D827" s="3" t="str">
+        <x:v>Estimating time remaining…</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="828">
+      <x:c r="A828" s="2" t="n">
+        <x:v>3411</x:v>
+      </x:c>
+      <x:c r="B828" s="2" t="str">
+        <x:v>EidolonText331</x:v>
+      </x:c>
+      <x:c r="C828" s="3" t="str">
+        <x:v>학습 단계 수를 직접 입력할 수 있습니다. 빠른 학습은 {0}단계, 기본 학습은 {1}단계입니다. 단계를 줄이면 학습 시간과 품질이 달라질 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D828" s="3" t="str">
+        <x:v>Enter a training step count. Quick uses {0} steps and Standard uses {1}. Fewer steps change training time and may reduce quality.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="829">
+      <x:c r="A829" s="2" t="n">
+        <x:v>3412</x:v>
+      </x:c>
+      <x:c r="B829" s="2" t="str">
+        <x:v>EidolonText332</x:v>
+      </x:c>
+      <x:c r="C829" s="3" t="str">
+        <x:v>폴더 열기</x:v>
+      </x:c>
+      <x:c r="D829" s="3" t="str">
+        <x:v>Open folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="830">
+      <x:c r="A830" s="2" t="n">
+        <x:v>3413</x:v>
+      </x:c>
+      <x:c r="B830" s="2" t="str">
+        <x:v>EidolonText333</x:v>
+      </x:c>
+      <x:c r="C830" s="3" t="str">
+        <x:v>폴더로 변경</x:v>
+      </x:c>
+      <x:c r="D830" s="3" t="str">
+        <x:v>Switch to folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="831">
+      <x:c r="A831" s="2" t="n">
+        <x:v>3414</x:v>
+      </x:c>
+      <x:c r="B831" s="2" t="str">
+        <x:v>EidolonText334</x:v>
+      </x:c>
+      <x:c r="C831" s="3" t="str">
+        <x:v>선택한 폴더와 하위 폴더의 모든 이미지로 학습합니다. 이미지와 같은 이름의 .txt 파일이 있으면 설명으로 사용합니다.</x:v>
+      </x:c>
+      <x:c r="D831" s="3" t="str">
+        <x:v>Train with every image in the selected folder and its subfolders. A .txt file with the same name as an image provides its caption.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="832">
+      <x:c r="A832" s="2" t="n">
+        <x:v>3415</x:v>
+      </x:c>
+      <x:c r="B832" s="2" t="str">
+        <x:v>EidolonText335</x:v>
+      </x:c>
+      <x:c r="C832" s="3" t="str">
+        <x:v>학습 단계 수</x:v>
+      </x:c>
+      <x:c r="D832" s="3" t="str">
+        <x:v>Training steps</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="833">
+      <x:c r="A833" s="2" t="n">
+        <x:v>3416</x:v>
+      </x:c>
+      <x:c r="B833" s="2" t="str">
+        <x:v>EidolonText336</x:v>
+      </x:c>
+      <x:c r="C833" s="3" t="str">
+        <x:v>기본 학습</x:v>
+      </x:c>
+      <x:c r="D833" s="3" t="str">
+        <x:v>Standard training</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="834">
+      <x:c r="A834" s="2" t="n">
+        <x:v>3417</x:v>
+      </x:c>
+      <x:c r="B834" s="2" t="str">
+        <x:v>EidolonText337</x:v>
+      </x:c>
+      <x:c r="C834" s="3" t="str">
+        <x:v>이 단어로 LoRA를 학습합니다. 생성 화면에서 이 LoRA를 선택하면 프롬프트에 자동으로 적용됩니다.</x:v>
+      </x:c>
+      <x:c r="D834" s="3" t="str">
+        <x:v>Train this LoRA with this keyword. Selecting this LoRA in Generate automatically applies it to the prompt.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="835">
+      <x:c r="A835" s="2" t="n">
+        <x:v>3418</x:v>
+      </x:c>
+      <x:c r="B835" s="2" t="str">
+        <x:v>EidolonText338</x:v>
+      </x:c>
+      <x:c r="C835" s="3" t="str">
+        <x:v>학습 단계 수는 {0}~{1} 사이의 정수로 입력하세요.</x:v>
+      </x:c>
+      <x:c r="D835" s="3" t="str">
+        <x:v>Enter a whole number of training steps between {0} and {1}.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="836">
+      <x:c r="A836" s="2" t="n">
+        <x:v>3419</x:v>
+      </x:c>
+      <x:c r="B836" s="2" t="str">
+        <x:v>EidolonText339</x:v>
+      </x:c>
+      <x:c r="C836" s="3" t="str">
+        <x:v>학습 설정</x:v>
+      </x:c>
+      <x:c r="D836" s="3" t="str">
+        <x:v>Training settings</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="837">
+      <x:c r="A837" s="2" t="n">
+        <x:v>3420</x:v>
+      </x:c>
+      <x:c r="B837" s="2" t="str">
+        <x:v>EidolonText340</x:v>
+      </x:c>
+      <x:c r="C837" s="3" t="str">
+        <x:v>자동 적용 트리거: {0}</x:v>
+      </x:c>
+      <x:c r="D837" s="3" t="str">
+        <x:v>Automatic triggers: {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="838">
+      <x:c r="A838" s="2" t="n">
+        <x:v>3421</x:v>
+      </x:c>
+      <x:c r="B838" s="2" t="str">
+        <x:v>EidolonText341</x:v>
+      </x:c>
+      <x:c r="C838" s="3" t="str">
+        <x:v>이 모델에 사용할 수 있는 LoRA가 없습니다.</x:v>
+      </x:c>
+      <x:c r="D838" s="3" t="str">
+        <x:v>No LoRAs are available for this model.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="839">
+      <x:c r="A839" s="2" t="n">
+        <x:v>3422</x:v>
+      </x:c>
+      <x:c r="B839" s="2" t="str">
+        <x:v>EidolonText342</x:v>
+      </x:c>
+      <x:c r="C839" s="3" t="str">
+        <x:v>현재 작업이 끝난 뒤 설정을 저장할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D839" s="3" t="str">
+        <x:v>Save settings once the current work finishes.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -12380,10 +12380,10 @@
         <x:v>EidolonText124</x:v>
       </x:c>
       <x:c r="C621" s="3" t="str">
-        <x:v>현재 실행 환경에 설치된 기본 모델과 LoRA만 표시합니다.</x:v>
+        <x:v>설치된 모델과 LoRA를 관리하고 새 모델을 추가하세요.</x:v>
       </x:c>
       <x:c r="D621" s="3" t="str">
-        <x:v>Show only base models and LoRAs installed in the current runtime.</x:v>
+        <x:v>Manage installed models and LoRAs, and add new models.</x:v>
       </x:c>
     </x:row>
     <x:row r="622" ht="16.5" hidden="0" customHeight="1">
@@ -12408,10 +12408,10 @@
         <x:v>EidolonText126</x:v>
       </x:c>
       <x:c r="C623" s="3" t="str">
-        <x:v>기본 SDXL 모델 받기</x:v>
+        <x:v>선택 모델 받기</x:v>
       </x:c>
       <x:c r="D623" s="3" t="str">
-        <x:v>Download SDXL model</x:v>
+        <x:v>Download selected model</x:v>
       </x:c>
     </x:row>
     <x:row r="624" ht="16.5" hidden="0" customHeight="1">
@@ -12422,10 +12422,10 @@
         <x:v>EidolonText127</x:v>
       </x:c>
       <x:c r="C624" s="3" t="str">
-        <x:v>자산 가져오기 · 정보</x:v>
+        <x:v>모델 정보</x:v>
       </x:c>
       <x:c r="D624" s="3" t="str">
-        <x:v>Import and asset details</x:v>
+        <x:v>Model details</x:v>
       </x:c>
     </x:row>
     <x:row r="625" ht="16.5" hidden="0" customHeight="1">
@@ -12450,10 +12450,10 @@
         <x:v>EidolonText129</x:v>
       </x:c>
       <x:c r="C626" s="3" t="str">
-        <x:v>설치된 모델 계열</x:v>
+        <x:v>모델 계열</x:v>
       </x:c>
       <x:c r="D626" s="3" t="str">
-        <x:v>Installed model families</x:v>
+        <x:v>Model family</x:v>
       </x:c>
     </x:row>
     <x:row r="627" ht="16.5" hidden="0" customHeight="1">
@@ -12520,10 +12520,10 @@
         <x:v>EidolonText134</x:v>
       </x:c>
       <x:c r="C631" s="3" t="str">
-        <x:v>선택한 자산 정보 저장</x:v>
+        <x:v>변경 사항 저장</x:v>
       </x:c>
       <x:c r="D631" s="3" t="str">
-        <x:v>Save selected asset details</x:v>
+        <x:v>Save changes</x:v>
       </x:c>
     </x:row>
     <x:row r="632" ht="16.5" hidden="0" customHeight="1">
@@ -12534,10 +12534,10 @@
         <x:v>EidolonText135</x:v>
       </x:c>
       <x:c r="C632" s="3" t="str">
-        <x:v>선택한 자산 등록 해제</x:v>
+        <x:v>등록 해제</x:v>
       </x:c>
       <x:c r="D632" s="3" t="str">
-        <x:v>Unregister selected asset</x:v>
+        <x:v>Unregister</x:v>
       </x:c>
     </x:row>
     <x:row r="633" ht="66" hidden="0" customHeight="1">
@@ -12870,10 +12870,10 @@
         <x:v>EidolonText159</x:v>
       </x:c>
       <x:c r="C656" s="3" t="str">
-        <x:v>기본 SDXL 모델도 다운로드 (6.94 GB)</x:v>
+        <x:v>설치 후 받을 모델</x:v>
       </x:c>
       <x:c r="D656" s="3" t="str">
-        <x:v>Download the default SDXL model (6.94 GB)</x:v>
+        <x:v>Models to download after installation</x:v>
       </x:c>
     </x:row>
     <x:row r="657" ht="16.5" hidden="0" customHeight="1">
@@ -12898,10 +12898,10 @@
         <x:v>EidolonText161</x:v>
       </x:c>
       <x:c r="C658" s="3" t="str">
-        <x:v>선택한 경로에 설치 · 복구</x:v>
+        <x:v>설치 · 복구</x:v>
       </x:c>
       <x:c r="D658" s="3" t="str">
-        <x:v>Install or repair at selected path</x:v>
+        <x:v>Install or repair</x:v>
       </x:c>
     </x:row>
     <x:row r="659" ht="16.5" hidden="0" customHeight="1">
@@ -12912,10 +12912,10 @@
         <x:v>EidolonText162</x:v>
       </x:c>
       <x:c r="C659" s="3" t="str">
-        <x:v>설치 폴더 열기</x:v>
+        <x:v>폴더 열기</x:v>
       </x:c>
       <x:c r="D659" s="3" t="str">
-        <x:v>Open installation folder</x:v>
+        <x:v>Open folder</x:v>
       </x:c>
     </x:row>
     <x:row r="660" ht="66" hidden="0" customHeight="1">
@@ -12940,10 +12940,10 @@
         <x:v>EidolonText164</x:v>
       </x:c>
       <x:c r="C661" s="3" t="str">
-        <x:v>엔진 설정</x:v>
+        <x:v>엔진 연결</x:v>
       </x:c>
       <x:c r="D661" s="3" t="str">
-        <x:v>Engine settings</x:v>
+        <x:v>Engine connection</x:v>
       </x:c>
     </x:row>
     <x:row r="662" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -13108,10 +13108,10 @@
         <x:v>EidolonText176</x:v>
       </x:c>
       <x:c r="C673" s="3" t="str">
-        <x:v>공용 프롬프트</x:v>
+        <x:v>공통 생성 지침</x:v>
       </x:c>
       <x:c r="D673" s="3" t="str">
-        <x:v>Shared prompts</x:v>
+        <x:v>Shared generation instructions</x:v>
       </x:c>
     </x:row>
     <x:row r="674" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -13122,10 +13122,10 @@
         <x:v>EidolonText177</x:v>
       </x:c>
       <x:c r="C674" s="3" t="str">
-        <x:v>모든 이미지에 사용할 표현을 한 번 설정하세요.</x:v>
+        <x:v>모든 이미지에 반복해서 적용할 스타일·품질 조건과 제외할 요소를 설정하세요.</x:v>
       </x:c>
       <x:c r="D674" s="3" t="str">
-        <x:v>Set expressions you want to include in every image.</x:v>
+        <x:v>Set the styles, quality preferences, and elements to avoid for every image.</x:v>
       </x:c>
     </x:row>
     <x:row r="675" ht="16.5" hidden="0" customHeight="1">
@@ -13136,10 +13136,10 @@
         <x:v>EidolonText178</x:v>
       </x:c>
       <x:c r="C675" s="3" t="str">
-        <x:v>공용 긍정 프롬프트</x:v>
+        <x:v>기본 생성 지침</x:v>
       </x:c>
       <x:c r="D675" s="3" t="str">
-        <x:v>Shared positive prompt</x:v>
+        <x:v>Default generation instructions</x:v>
       </x:c>
     </x:row>
     <x:row r="676" ht="16.5" hidden="0" customHeight="1">
@@ -13164,10 +13164,10 @@
         <x:v>EidolonText180</x:v>
       </x:c>
       <x:c r="C677" s="3" t="str">
-        <x:v>공용 부정 프롬프트</x:v>
+        <x:v>제외할 요소</x:v>
       </x:c>
       <x:c r="D677" s="3" t="str">
-        <x:v>Shared negative prompt</x:v>
+        <x:v>Elements to avoid</x:v>
       </x:c>
     </x:row>
     <x:row r="678" ht="16.5" hidden="0" customHeight="1">
@@ -13206,10 +13206,10 @@
         <x:v>EidolonText183</x:v>
       </x:c>
       <x:c r="C680" s="3" t="str">
-        <x:v>기본 모델은 생성 화면에서 지정합니다. 공용 프롬프트 변경은 저장한 다음 생성부터 적용됩니다.</x:v>
+        <x:v>기본 모델은 생성 화면에서 지정합니다. 저장한 기본 생성 지침과 제외할 요소는 다음 생성부터 적용됩니다.</x:v>
       </x:c>
       <x:c r="D680" s="3" t="str">
-        <x:v>Choose the default model in Generate. Saved shared prompts apply to subsequent generations.</x:v>
+        <x:v>Choose the default model in Generate. Saved generation instructions and elements to avoid apply to subsequent generations.</x:v>
       </x:c>
     </x:row>
     <x:row r="681" ht="16.5" hidden="0" customHeight="1">
@@ -13304,10 +13304,10 @@
         <x:v>EidolonText190</x:v>
       </x:c>
       <x:c r="C687" s="3" t="str">
-        <x:v>설정의 공용 긍정 프롬프트에는 반복할 스타일을, 부정 프롬프트에는 피할 표현을 입력하세요. 저장한 내용은 생성 화면에도 표시되고 이후 생성에 적용됩니다. 생성 결과에서 프롬프트를 다시 사용할 수 있습니다.</x:v>
+        <x:v>설정의 기본 생성 지침에는 반복할 스타일·품질 조건을, 제외할 요소에는 피하고 싶은 내용을 입력하세요. 저장한 내용은 생성 화면에도 표시되고 이후 생성에 적용됩니다. 생성 결과에서 프롬프트를 다시 사용할 수 있습니다.</x:v>
       </x:c>
       <x:c r="D687" s="3" t="str">
-        <x:v>Use the shared positive prompt in Settings for recurring styles, and the negative prompt for things to avoid. Saved prompts are shown in Generate and apply to later generations. Reuse a prompt from Results.</x:v>
+        <x:v>Use default generation instructions in Settings for recurring styles and quality preferences, and Elements to avoid for unwanted content. Saved settings are shown in Generate and apply to later generations. Reuse a prompt from Results.</x:v>
       </x:c>
     </x:row>
     <x:row r="688" ht="16.5" hidden="0" customHeight="1">
@@ -13684,14 +13684,14 @@
       <x:c r="C714" s="3" t="str">
         <x:v>
 {0} × {1} · seed {2}
-생성에 사용된 프롬프트: {3}
-부정 프롬프트: {4}</x:v>
+적용된 생성 지침: {3}
+제외할 요소: {4}</x:v>
       </x:c>
       <x:c r="D714" s="3" t="str">
         <x:v>
 {0} × {1} · seed {2}
-Prompt used for generation: {3}
-Negative prompt: {4}</x:v>
+Applied generation instructions: {3}
+Elements to avoid: {4}</x:v>
       </x:c>
     </x:row>
     <x:row r="715" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -13872,10 +13872,10 @@
         <x:v>EidolonText230</x:v>
       </x:c>
       <x:c r="C727" s="3" t="str">
-        <x:v>실행 환경 설치 완료. 모델을 가져오거나 기본 SDXL 모델을 다운로드하세요.</x:v>
+        <x:v>엔진 준비가 끝났습니다. 모델을 한 개 이상 설치하거나 가져오세요.</x:v>
       </x:c>
       <x:c r="D727" s="3" t="str">
-        <x:v>Runtime installed. Import a model or download the default SDXL model.</x:v>
+        <x:v>The engine is ready. Install or import at least one model.</x:v>
       </x:c>
     </x:row>
     <x:row r="728" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -14348,10 +14348,10 @@
         <x:v>EidolonText264</x:v>
       </x:c>
       <x:c r="C761" s="3" t="str">
-        <x:v>실행 중인 ComfyUI에 연결합니다. 로컬 주소에 서버가 없으면 설치된 엔진을 실행합니다.</x:v>
+        <x:v>실행 중인 ComfyUI에 연결하거나 설치된 엔진을 실행합니다.</x:v>
       </x:c>
       <x:c r="D761" s="3" t="str">
-        <x:v>Connect to a running ComfyUI. If no server is running at a local address, start the installed engine.</x:v>
+        <x:v>Connect to a running ComfyUI or start the installed engine.</x:v>
       </x:c>
     </x:row>
     <x:row r="762" ht="16.5" hidden="0" customHeight="1">
@@ -14754,10 +14754,10 @@
         <x:v>EidolonText293</x:v>
       </x:c>
       <x:c r="C790" s="3" t="str">
-        <x:v>실제 생성에 사용된 프롬프트</x:v>
+        <x:v>적용된 생성 지침</x:v>
       </x:c>
       <x:c r="D790" s="3" t="str">
-        <x:v>Prompt used for generation</x:v>
+        <x:v>Applied generation instructions</x:v>
       </x:c>
     </x:row>
     <x:row r="791" ht="16.5" hidden="0" customHeight="1">
@@ -14768,10 +14768,10 @@
         <x:v>EidolonText294</x:v>
       </x:c>
       <x:c r="C791" s="3" t="str">
-        <x:v>부정 프롬프트</x:v>
+        <x:v>제외할 요소</x:v>
       </x:c>
       <x:c r="D791" s="3" t="str">
-        <x:v>Negative prompt</x:v>
+        <x:v>Elements to avoid</x:v>
       </x:c>
     </x:row>
     <x:row r="792" ht="16.5" hidden="0" customHeight="1">
@@ -14824,10 +14824,10 @@
         <x:v>EidolonText298</x:v>
       </x:c>
       <x:c r="C795" s="3" t="str">
-        <x:v>새 생성의 최종 이미지만 이 폴더에 GUID.png로 저장합니다. 기본 경로는 사용자 AppData의 Eidolon\Images이며 다른 폴더를 지정할 수 있습니다. 원본은 Job 폴더에 보관하고 이전 결과는 이동하지 않습니다.</x:v>
+        <x:v>생성한 이미지와 생성 정보를 함께 저장합니다. 폴더를 바꿔도 기존 이미지는 이동하지 않습니다.</x:v>
       </x:c>
       <x:c r="D795" s="3" t="str">
-        <x:v>New generations save only the final image here as GUID.png. Default: Eidolon\Images under local AppData. You can choose another folder. Originals stay in job folders; previous results are not moved.</x:v>
+        <x:v>Generated images and their generation details are saved together. Changing the folder does not move existing images.</x:v>
       </x:c>
     </x:row>
     <x:row r="796" ht="16.5" hidden="0" customHeight="1">
@@ -15090,10 +15090,10 @@
         <x:v>EidolonText317</x:v>
       </x:c>
       <x:c r="C814" s="3" t="str">
-        <x:v>전체 삭제</x:v>
+        <x:v>전체 이미지 삭제</x:v>
       </x:c>
       <x:c r="D814" s="3" t="str">
-        <x:v>Delete all</x:v>
+        <x:v>Delete all images</x:v>
       </x:c>
     </x:row>
     <x:row r="815" ht="16.5" hidden="0" customHeight="1">
@@ -15104,10 +15104,10 @@
         <x:v>EidolonText318</x:v>
       </x:c>
       <x:c r="C815" s="3" t="str">
-        <x:v>생성 기록 삭제</x:v>
+        <x:v>이미지 삭제</x:v>
       </x:c>
       <x:c r="D815" s="3" t="str">
-        <x:v>Delete generation history</x:v>
+        <x:v>Delete images</x:v>
       </x:c>
     </x:row>
     <x:row r="816" ht="66" hidden="0" customHeight="1">
@@ -15118,10 +15118,10 @@
         <x:v>EidolonText319</x:v>
       </x:c>
       <x:c r="C816" s="3" t="str">
-        <x:v>선택한 생성 기록과 Job 폴더를 삭제할까요? 프롬프트·모델 정보와 Job 폴더의 원본 이미지는 삭제됩니다. 최종 저장 이미지와 학습 기록은 보존합니다.</x:v>
+        <x:v>선택한 이미지 {0}장과 같은 이름의 프롬프트 JSON을 삭제합니다. 삭제한 파일은 복구할 수 없습니다.</x:v>
       </x:c>
       <x:c r="D816" s="3" t="str">
-        <x:v>Delete the selected generation record and job folder? Prompt and model information and original images in the job folder will be removed. Final saved images and training records are kept.</x:v>
+        <x:v>Delete {0} selected images and their matching prompt JSON files? Deleted files cannot be recovered.</x:v>
       </x:c>
     </x:row>
     <x:row r="817" ht="66" hidden="0" customHeight="1">
@@ -15132,10 +15132,10 @@
         <x:v>EidolonText320</x:v>
       </x:c>
       <x:c r="C817" s="3" t="str">
-        <x:v>생성 기록 {0}개와 해당 Job 폴더를 모두 삭제할까요? 프롬프트·모델 정보와 원본 이미지는 삭제됩니다. 최종 저장 이미지와 학습 기록은 보존합니다.</x:v>
+        <x:v>현재 출력 폴더의 이미지 {0}장과 같은 이름의 프롬프트 JSON을 모두 삭제합니다. 삭제한 파일은 복구할 수 없습니다.</x:v>
       </x:c>
       <x:c r="D817" s="3" t="str">
-        <x:v>Delete all {0} generation records and their job folders? Prompt and model information and original images will be removed. Final saved images and training records are kept.</x:v>
+        <x:v>Delete all {0} images and their matching prompt JSON files in the current output folder? Deleted files cannot be recovered.</x:v>
       </x:c>
     </x:row>
     <x:row r="818" ht="16.5" hidden="0" customHeight="1">
@@ -15174,10 +15174,10 @@
         <x:v>EidolonText323</x:v>
       </x:c>
       <x:c r="C820" s="3" t="str">
-        <x:v>생성 기록 {0}개와 Job 폴더를 삭제했습니다. 최종 저장 이미지는 보존했습니다.</x:v>
+        <x:v>이미지 {0}장과 프롬프트 JSON을 삭제했습니다.</x:v>
       </x:c>
       <x:c r="D820" s="3" t="str">
-        <x:v>Deleted {0} generation records and their job folders. Final saved images were kept.</x:v>
+        <x:v>Deleted {0} images and their prompt JSON files.</x:v>
       </x:c>
     </x:row>
     <x:row r="821" ht="52.79999923706055" hidden="0" customHeight="1">
@@ -15188,10 +15188,10 @@
         <x:v>EidolonText324</x:v>
       </x:c>
       <x:c r="C821" s="3" t="str">
-        <x:v>표시된 결과 이미지 한 장만 학습합니다. 폴더 열기로 위치를 확인하거나 폴더로 변경을 눌러 폴더 전체를 학습할 수 있습니다.</x:v>
+        <x:v>현재 선택한 이미지 한 장만 학습합니다. 여러 이미지로 학습하려면 학습 폴더 선택을 눌러주세요.</x:v>
       </x:c>
       <x:c r="D821" s="3" t="str">
-        <x:v>Train only the result image shown here. Open folder shows its location. Use Switch to folder to train every image in a folder instead.</x:v>
+        <x:v>Only the selected image will be used for training. Choose a training folder to train with multiple images.</x:v>
       </x:c>
     </x:row>
     <x:row r="822">
@@ -15202,10 +15202,10 @@
         <x:v>EidolonText325</x:v>
       </x:c>
       <x:c r="C822" s="3" t="str">
-        <x:v>아직 이미지가 없습니다</x:v>
+        <x:v>아직 생성된 이미지가 없습니다.</x:v>
       </x:c>
       <x:c r="D822" s="3" t="str">
-        <x:v>No images yet</x:v>
+        <x:v>No generated images yet.</x:v>
       </x:c>
     </x:row>
     <x:row r="823">
@@ -15314,10 +15314,10 @@
         <x:v>EidolonText333</x:v>
       </x:c>
       <x:c r="C830" s="3" t="str">
-        <x:v>폴더로 변경</x:v>
+        <x:v>학습 폴더 선택</x:v>
       </x:c>
       <x:c r="D830" s="3" t="str">
-        <x:v>Switch to folder</x:v>
+        <x:v>Choose training folder</x:v>
       </x:c>
     </x:row>
     <x:row r="831">
@@ -15412,10 +15412,10 @@
         <x:v>EidolonText340</x:v>
       </x:c>
       <x:c r="C837" s="3" t="str">
-        <x:v>자동 적용 트리거: {0}</x:v>
+        <x:v>앞에 붙는 트리거: {0}</x:v>
       </x:c>
       <x:c r="D837" s="3" t="str">
-        <x:v>Automatic triggers: {0}</x:v>
+        <x:v>Prepended trigger: {0}</x:v>
       </x:c>
     </x:row>
     <x:row r="838">
@@ -15446,6 +15446,1662 @@
         <x:v>Save settings once the current work finishes.</x:v>
       </x:c>
     </x:row>
+    <x:row r="840">
+      <x:c r="A840" t="n" s="2">
+        <x:v>3423</x:v>
+      </x:c>
+      <x:c r="B840" t="str" s="2">
+        <x:v>EidolonText343</x:v>
+      </x:c>
+      <x:c r="C840" t="str" s="3">
+        <x:v>사용할 모델을 골라 설치하세요. 삭제하면 모델 파일도 제거됩니다.</x:v>
+      </x:c>
+      <x:c r="D840" t="str" s="3">
+        <x:v>Choose a model to install. Deleting also removes its file.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="841">
+      <x:c r="A841" t="n" s="2">
+        <x:v>3424</x:v>
+      </x:c>
+      <x:c r="B841" t="str" s="2">
+        <x:v>EidolonText344</x:v>
+      </x:c>
+      <x:c r="C841" t="str" s="3">
+        <x:v>새 모델 설치</x:v>
+      </x:c>
+      <x:c r="D841" t="str" s="3">
+        <x:v>Install a new model</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="842">
+      <x:c r="A842" t="n" s="2">
+        <x:v>3425</x:v>
+      </x:c>
+      <x:c r="B842" t="str" s="2">
+        <x:v>EidolonText345</x:v>
+      </x:c>
+      <x:c r="C842" t="str" s="3">
+        <x:v>다양한 이미지 생성과 LoRA 학습에 사용하는 기본 모델</x:v>
+      </x:c>
+      <x:c r="D842" t="str" s="3">
+        <x:v>Base model for general image generation and LoRA training</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="843">
+      <x:c r="A843" t="n" s="2">
+        <x:v>3426</x:v>
+      </x:c>
+      <x:c r="B843" t="str" s="2">
+        <x:v>EidolonText346</x:v>
+      </x:c>
+      <x:c r="C843" t="str" s="3">
+        <x:v>SD 1.5 기반 생성과 기존 LoRA 사용을 위한 기본 모델</x:v>
+      </x:c>
+      <x:c r="D843" t="str" s="3">
+        <x:v>Base model for SD 1.5 generation and compatible LoRAs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="844">
+      <x:c r="A844" t="n" s="2">
+        <x:v>3427</x:v>
+      </x:c>
+      <x:c r="B844" t="str" s="2">
+        <x:v>EidolonText347</x:v>
+      </x:c>
+      <x:c r="C844" t="str" s="3">
+        <x:v>인물·사진 스타일의 실사 이미지 생성에 맞춘 모델</x:v>
+      </x:c>
+      <x:c r="D844" t="str" s="3">
+        <x:v>Model for photorealistic portraits and photographic images</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="845">
+      <x:c r="A845" t="n" s="2">
+        <x:v>3428</x:v>
+      </x:c>
+      <x:c r="B845" t="str" s="2">
+        <x:v>EidolonText348</x:v>
+      </x:c>
+      <x:c r="C845" t="str" s="3">
+        <x:v>사용 가능</x:v>
+      </x:c>
+      <x:c r="D845" t="str" s="3">
+        <x:v>Ready to use</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="846">
+      <x:c r="A846" t="n" s="2">
+        <x:v>3429</x:v>
+      </x:c>
+      <x:c r="B846" t="str" s="2">
+        <x:v>EidolonText349</x:v>
+      </x:c>
+      <x:c r="C846" t="str" s="3">
+        <x:v>{0} 모델 준비 완료</x:v>
+      </x:c>
+      <x:c r="D846" t="str" s="3">
+        <x:v>{0} model ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="847">
+      <x:c r="A847" t="n" s="2">
+        <x:v>3430</x:v>
+      </x:c>
+      <x:c r="B847" t="str" s="2">
+        <x:v>EidolonText350</x:v>
+      </x:c>
+      <x:c r="C847" t="str" s="3">
+        <x:v>일러스트·애니메이션 스타일의 SDXL 기반 모델</x:v>
+      </x:c>
+      <x:c r="D847" t="str" s="3">
+        <x:v>SDXL-based model for illustration and anime styles</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="848">
+      <x:c r="A848" t="n" s="2">
+        <x:v>3431</x:v>
+      </x:c>
+      <x:c r="B848" t="str" s="2">
+        <x:v>EidolonText351</x:v>
+      </x:c>
+      <x:c r="C848" t="str" s="3">
+        <x:v>설치</x:v>
+      </x:c>
+      <x:c r="D848" t="str" s="3">
+        <x:v>Install</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="849">
+      <x:c r="A849" t="n" s="2">
+        <x:v>3432</x:v>
+      </x:c>
+      <x:c r="B849" t="str" s="2">
+        <x:v>EidolonText352</x:v>
+      </x:c>
+      <x:c r="C849" t="str" s="3">
+        <x:v>모델 설치와 삭제는 로컬 엔진에서 사용할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D849" t="str" s="3">
+        <x:v>Model installation and deletion are available for the local engine.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="850">
+      <x:c r="A850" t="n" s="2">
+        <x:v>3433</x:v>
+      </x:c>
+      <x:c r="B850" t="str" s="2">
+        <x:v>EidolonText353</x:v>
+      </x:c>
+      <x:c r="C850" t="str" s="3">
+        <x:v>먼저 선택한 경로에 엔진을 설치하세요. 완료 후 각 모델의 설치 버튼을 사용할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D850" t="str" s="3">
+        <x:v>Install the engine at the selected path first. Then use the install button for each model.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="851">
+      <x:c r="A851" t="n" s="2">
+        <x:v>3434</x:v>
+      </x:c>
+      <x:c r="B851" t="str" s="2">
+        <x:v>EidolonText354</x:v>
+      </x:c>
+      <x:c r="C851" t="str" s="3">
+        <x:v>설치 중…</x:v>
+      </x:c>
+      <x:c r="D851" t="str" s="3">
+        <x:v>Installing…</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="852">
+      <x:c r="A852" t="n" s="2">
+        <x:v>3435</x:v>
+      </x:c>
+      <x:c r="B852" t="str" s="2">
+        <x:v>EidolonText355</x:v>
+      </x:c>
+      <x:c r="C852" t="str" s="3">
+        <x:v>삭제</x:v>
+      </x:c>
+      <x:c r="D852" t="str" s="3">
+        <x:v>Delete</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="853">
+      <x:c r="A853" t="n" s="2">
+        <x:v>3436</x:v>
+      </x:c>
+      <x:c r="B853" t="str" s="2">
+        <x:v>EidolonText356</x:v>
+      </x:c>
+      <x:c r="C853" t="str" s="3">
+        <x:v>모델 삭제</x:v>
+      </x:c>
+      <x:c r="D853" t="str" s="3">
+        <x:v>Delete model</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="854">
+      <x:c r="A854" t="n" s="2">
+        <x:v>3437</x:v>
+      </x:c>
+      <x:c r="B854" t="str" s="2">
+        <x:v>EidolonText357</x:v>
+      </x:c>
+      <x:c r="C854" t="str" s="3">
+        <x:v>{0} 모델 파일을 삭제할까요?
+{1}
+다시 사용하려면 모델을 다시 다운로드해야 합니다.</x:v>
+      </x:c>
+      <x:c r="D854" t="str" s="3">
+        <x:v>Delete the {0} model file?
+{1}
+You will need to download the model again to use it.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="855">
+      <x:c r="A855" t="n" s="2">
+        <x:v>3438</x:v>
+      </x:c>
+      <x:c r="B855" t="str" s="2">
+        <x:v>EidolonText358</x:v>
+      </x:c>
+      <x:c r="C855" t="str" s="3">
+        <x:v>{0} 모델 파일을 삭제했습니다.</x:v>
+      </x:c>
+      <x:c r="D855" t="str" s="3">
+        <x:v>Deleted the {0} model file.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="856">
+      <x:c r="A856" t="n" s="2">
+        <x:v>3439</x:v>
+      </x:c>
+      <x:c r="B856" t="str" s="2">
+        <x:v>EidolonText359</x:v>
+      </x:c>
+      <x:c r="C856" t="str" s="3">
+        <x:v>모델·체크포인트</x:v>
+      </x:c>
+      <x:c r="D856" t="str" s="3">
+        <x:v>Model and checkpoint</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="857">
+      <x:c r="A857" t="n" s="2">
+        <x:v>3440</x:v>
+      </x:c>
+      <x:c r="B857" t="str" s="2">
+        <x:v>EidolonText360</x:v>
+      </x:c>
+      <x:c r="C857" t="str" s="3">
+        <x:v>설치한 모델과 체크포인트 폴더에 직접 넣은 .safetensors 모델을 선택합니다. 파일을 추가했다면 새로고침하세요.</x:v>
+      </x:c>
+      <x:c r="D857" t="str" s="3">
+        <x:v>Choose an installed model or a .safetensors model placed in the checkpoint folder. Refresh after adding files.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="858">
+      <x:c r="A858" t="n" s="2">
+        <x:v>3441</x:v>
+      </x:c>
+      <x:c r="B858" t="str" s="2">
+        <x:v>EidolonText361</x:v>
+      </x:c>
+      <x:c r="C858" t="str" s="3">
+        <x:v>선택할 모델이 없습니다. 엔진 탭에서 모델을 설치하거나 가져온 뒤 새로고침하세요.</x:v>
+      </x:c>
+      <x:c r="D858" t="str" s="3">
+        <x:v>No models are available. Install or import a model in the Engine tab, then refresh.</x:v>
+      </x:c>
+    </x:row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="859" spans="1:4">
+      <c r="A859" s="2" t="n">
+        <v>3442</v>
+      </c>
+      <c r="B859" s="2" t="str">
+        <v>EidolonText362</v>
+      </c>
+      <c r="C859" s="3" t="str">
+        <v>생성 지침</v>
+      </c>
+      <c r="D859" s="3" t="str">
+        <v>Generation instructions</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="860" spans="1:4">
+      <c r="A860" s="2" t="n">
+        <v>3443</v>
+      </c>
+      <c r="B860" s="2" t="str">
+        <v>EidolonText363</v>
+      </c>
+      <c r="C860" s="3" t="str">
+        <v>여기서 바꾼 지침은 이번 요청에만 적용됩니다. 설정의 기본값은 유지됩니다.</v>
+      </c>
+      <c r="D860" s="3" t="str">
+        <v>Changes here apply to this request. Your saved defaults stay the same.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="861" spans="1:4">
+      <c r="A861" s="2" t="n">
+        <v>3444</v>
+      </c>
+      <c r="B861" s="2" t="str">
+        <v>EidolonText364</v>
+      </c>
+      <c r="C861" s="3" t="str">
+        <v>기본값 불러오기</v>
+      </c>
+      <c r="D861" s="3" t="str">
+        <v>Load defaults</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="862" spans="1:4">
+      <c r="A862" s="2" t="n">
+        <v>3445</v>
+      </c>
+      <c r="B862" s="2" t="str">
+        <v>EidolonText365</v>
+      </c>
+      <c r="C862" s="3" t="str">
+        <v>생성 정보</v>
+      </c>
+      <c r="D862" s="3" t="str">
+        <v>Generation details</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="863" spans="1:4">
+      <c r="A863" s="2" t="n">
+        <v>3446</v>
+      </c>
+      <c r="B863" s="2" t="str">
+        <v>EidolonText366</v>
+      </c>
+      <c r="C863" s="3" t="str">
+        <v>상태</v>
+      </c>
+      <c r="D863" s="3" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="864" spans="1:4">
+      <c r="A864" s="2" t="n">
+        <v>3447</v>
+      </c>
+      <c r="B864" s="2" t="str">
+        <v>EidolonText367</v>
+      </c>
+      <c r="C864" s="3" t="str">
+        <v>생성 시각</v>
+      </c>
+      <c r="D864" s="3" t="str">
+        <v>Created</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="865" spans="1:4">
+      <c r="A865" s="2" t="n">
+        <v>3448</v>
+      </c>
+      <c r="B865" s="2" t="str">
+        <v>EidolonText368</v>
+      </c>
+      <c r="C865" s="3" t="str">
+        <v>해상도</v>
+      </c>
+      <c r="D865" s="3" t="str">
+        <v>Resolution</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="866" spans="1:4">
+      <c r="A866" s="2" t="n">
+        <v>3449</v>
+      </c>
+      <c r="B866" s="2" t="str">
+        <v>EidolonText369</v>
+      </c>
+      <c r="C866" s="3" t="str">
+        <v>시드</v>
+      </c>
+      <c r="D866" s="3" t="str">
+        <v>Seed</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="867" spans="1:4">
+      <c r="A867" s="2" t="n">
+        <v>3450</v>
+      </c>
+      <c r="B867" s="2" t="str">
+        <v>EidolonText370</v>
+      </c>
+      <c r="C867" s="3" t="str">
+        <v>이 결과의 모델 또는 LoRA 일부가 현재 목록에 없습니다. 생성 전에 선택을 확인해 주세요.</v>
+      </c>
+      <c r="D867" s="3" t="str">
+        <v>Some models or LoRAs used for this result are unavailable. Check your selection before generating.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="868" spans="1:4">
+      <c r="A868" s="2" t="n">
+        <v>3451</v>
+      </c>
+      <c r="B868" s="2" t="str">
+        <v>EidolonText371</v>
+      </c>
+      <c r="C868" s="3" t="str">
+        <v>이번 요청의 지침</v>
+      </c>
+      <c r="D868" s="3" t="str">
+        <v>Instructions for this request</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="869" spans="1:4">
+      <c r="A869" s="2" t="n">
+        <v>3452</v>
+      </c>
+      <c r="B869" s="2" t="str">
+        <v>EidolonText372</v>
+      </c>
+      <c r="C869" s="3" t="str">
+        <v>결과 갤러리</v>
+      </c>
+      <c r="D869" s="3" t="str">
+        <v>Results gallery</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="870" spans="1:4">
+      <c r="A870" s="2" t="n">
+        <v>3453</v>
+      </c>
+      <c r="B870" s="2" t="str">
+        <v>EidolonText373</v>
+      </c>
+      <c r="C870" s="3" t="str">
+        <v>클릭하면 오른쪽에 이미지·프롬프트 표시 · Ctrl+클릭으로 다중 선택 · Shift+클릭으로 범위 선택</v>
+      </c>
+      <c r="D870" s="3" t="str">
+        <v>Click to preview on the right · Ctrl+click for multiple selection · Shift+click to select a range</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="871" spans="1:4">
+      <c r="A871" s="2" t="n">
+        <v>3454</v>
+      </c>
+      <c r="B871" s="2" t="str">
+        <v>EidolonText374</v>
+      </c>
+      <c r="C871" s="3" t="str">
+        <v>이전</v>
+      </c>
+      <c r="D871" s="3" t="str">
+        <v>Previous</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="872" spans="1:4">
+      <c r="A872" s="2" t="n">
+        <v>3455</v>
+      </c>
+      <c r="B872" s="2" t="str">
+        <v>EidolonText375</v>
+      </c>
+      <c r="C872" s="3" t="str">
+        <v>다음</v>
+      </c>
+      <c r="D872" s="3" t="str">
+        <v>Next</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="873" spans="1:4">
+      <c r="A873" s="2" t="n">
+        <v>3456</v>
+      </c>
+      <c r="B873" s="2" t="str">
+        <v>EidolonText376</v>
+      </c>
+      <c r="C873" s="3" t="str">
+        <v>{0} / {1} 페이지</v>
+      </c>
+      <c r="D873" s="3" t="str">
+        <v>Page {0} of {1}</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="874" spans="1:4">
+      <c r="A874" s="2" t="n">
+        <v>3457</v>
+      </c>
+      <c r="B874" s="2" t="str">
+        <v>EidolonText377</v>
+      </c>
+      <c r="C874" s="3" t="str">
+        <v>이미지 {0}장</v>
+      </c>
+      <c r="D874" s="3" t="str">
+        <v>{0} images</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="875" spans="1:4">
+      <c r="A875" s="2" t="n">
+        <v>3458</v>
+      </c>
+      <c r="B875" s="2" t="str">
+        <v>EidolonText378</v>
+      </c>
+      <c r="C875" s="3" t="str">
+        <v>결과 불러오는 중…</v>
+      </c>
+      <c r="D875" s="3" t="str">
+        <v>Loading results…</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="876" spans="1:4">
+      <c r="A876" s="2" t="n">
+        <v>3459</v>
+      </c>
+      <c r="B876" s="2" t="str">
+        <v>EidolonText379</v>
+      </c>
+      <c r="C876" s="3" t="str">
+        <v>닫기</v>
+      </c>
+      <c r="D876" s="3" t="str">
+        <v>Close</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="877" spans="1:4">
+      <c r="A877" s="2" t="n">
+        <v>3460</v>
+      </c>
+      <c r="B877" s="2" t="str">
+        <v>EidolonText380</v>
+      </c>
+      <c r="C877" s="3" t="str">
+        <v>결과를 불러오지 못했습니다. 새로고침해 주세요.</v>
+      </c>
+      <c r="D877" s="3" t="str">
+        <v>Could not load results. Please refresh.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="878" spans="1:4">
+      <c r="A878" s="2" t="n">
+        <v>3461</v>
+      </c>
+      <c r="B878" s="2" t="str">
+        <v>EidolonText381</v>
+      </c>
+      <c r="C878" s="3" t="str">
+        <v>미리보기 없음</v>
+      </c>
+      <c r="D878" s="3" t="str">
+        <v>No preview</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="879" spans="1:4">
+      <c r="A879" s="2" t="n">
+        <v>3462</v>
+      </c>
+      <c r="B879" s="2" t="str">
+        <v>EidolonText382</v>
+      </c>
+      <c r="C879" s="3" t="str">
+        <v>{0}장</v>
+      </c>
+      <c r="D879" s="3" t="str">
+        <v>{0} images</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="880" spans="1:4">
+      <c r="A880" s="2" t="n">
+        <v>3463</v>
+      </c>
+      <c r="B880" s="2" t="str">
+        <v>EidolonText383</v>
+      </c>
+      <c r="C880" s="3" t="str">
+        <v>프롬프트 정보 없음</v>
+      </c>
+      <c r="D880" s="3" t="str">
+        <v>No prompt data</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="881" spans="1:4">
+      <c r="A881" s="2" t="n">
+        <v>3464</v>
+      </c>
+      <c r="B881" s="2" t="str">
+        <v>EidolonText384</v>
+      </c>
+      <c r="C881" s="3" t="str">
+        <v>프롬프트 JSON을 읽을 수 없습니다. 이미지는 계속 사용할 수 있습니다.</v>
+      </c>
+      <c r="D881" s="3" t="str">
+        <v>Cannot read the prompt JSON. The image is still available.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="882" spans="1:4">
+      <c r="A882" s="2" t="n">
+        <v>3465</v>
+      </c>
+      <c r="B882" s="2" t="str">
+        <v>EidolonText385</v>
+      </c>
+      <c r="C882" s="3" t="str">
+        <v>{0}장 선택됨</v>
+      </c>
+      <c r="D882" s="3" t="str">
+        <v>{0} selected</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="883" spans="1:4">
+      <c r="A883" s="2" t="n">
+        <v>3466</v>
+      </c>
+      <c r="B883" s="2" t="str">
+        <v>EidolonText386</v>
+      </c>
+      <c r="C883" s="3" t="str">
+        <v>크게 보기</v>
+      </c>
+      <c r="D883" s="3" t="str">
+        <v>View image</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="884" spans="1:4">
+      <c r="A884" s="2" t="n">
+        <v>3467</v>
+      </c>
+      <c r="B884" s="2" t="str">
+        <v>EidolonText387</v>
+      </c>
+      <c r="C884" s="3" t="str">
+        <v>선택 해제</v>
+      </c>
+      <c r="D884" s="3" t="str">
+        <v>Clear selection</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="885" spans="1:4">
+      <c r="A885" s="2" t="n">
+        <v>3468</v>
+      </c>
+      <c r="B885" s="2" t="str">
+        <v>EidolonText388</v>
+      </c>
+      <c r="C885" s="3" t="str">
+        <v>같은 이름의 유효한 프롬프트 JSON이 있어야 생성 지침을 다시 사용할 수 있습니다.</v>
+      </c>
+      <c r="D885" s="3" t="str">
+        <v>Reusing instructions requires a valid prompt JSON file with the same name.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="886" spans="1:4">
+      <c r="A886" s="2" t="n">
+        <v>3469</v>
+      </c>
+      <c r="B886" s="2" t="str">
+        <v>EidolonText389</v>
+      </c>
+      <c r="C886" s="3" t="str">
+        <v>1. 엔진 준비</v>
+      </c>
+      <c r="D886" s="3" t="str">
+        <v>1. Prepare engine</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="887" spans="1:4">
+      <c r="A887" s="2" t="n">
+        <v>3470</v>
+      </c>
+      <c r="B887" s="2" t="str">
+        <v>EidolonText390</v>
+      </c>
+      <c r="C887" s="3" t="str">
+        <v>2. 생성 모델 준비</v>
+      </c>
+      <c r="D887" s="3" t="str">
+        <v>2. Prepare generation model</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="888" spans="1:4">
+      <c r="A888" s="2" t="n">
+        <v>3471</v>
+      </c>
+      <c r="B888" s="2" t="str">
+        <v>EidolonText391</v>
+      </c>
+      <c r="C888" s="3" t="str">
+        <v>모델 설치가 필요합니다</v>
+      </c>
+      <c r="D888" s="3" t="str">
+        <v>Install a generation model</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="889" spans="1:4">
+      <c r="A889" s="2" t="n">
+        <v>3472</v>
+      </c>
+      <c r="B889" s="2" t="str">
+        <v>EidolonText392</v>
+      </c>
+      <c r="C889" s="3" t="str">
+        <v>이미지를 생성하려면 모델을 한 개 이상 준비해야 합니다. 모델 · LoRA에서 설치하거나 모델 파일을 가져오세요.</v>
+      </c>
+      <c r="D889" s="3" t="str">
+        <v>You need at least one model to generate images. Install or import a model in Models · LoRA.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="890" spans="1:4">
+      <c r="A890" s="2" t="n">
+        <v>3473</v>
+      </c>
+      <c r="B890" s="2" t="str">
+        <v>EidolonText393</v>
+      </c>
+      <c r="C890" s="3" t="str">
+        <v>모델 설치하기</v>
+      </c>
+      <c r="D890" s="3" t="str">
+        <v>Install a model</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="891" spans="1:4">
+      <c r="A891" s="2" t="n">
+        <v>3474</v>
+      </c>
+      <c r="B891" s="2" t="str">
+        <v>EidolonText394</v>
+      </c>
+      <c r="C891" s="3" t="str">
+        <v>모델 설치 중</v>
+      </c>
+      <c r="D891" s="3" t="str">
+        <v>Installing a model</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="892" spans="1:4">
+      <c r="A892" s="2" t="n">
+        <v>3475</v>
+      </c>
+      <c r="B892" s="2" t="str">
+        <v>EidolonText395</v>
+      </c>
+      <c r="C892" s="3" t="str">
+        <v>{0} 설치 중입니다. 완료되면 생성 화면에서 선택할 수 있습니다.</v>
+      </c>
+      <c r="D892" s="3" t="str">
+        <v>{0} is installing. Once complete, you can select it in Generate.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="893" spans="1:4">
+      <c r="A893" s="2" t="n">
+        <v>3476</v>
+      </c>
+      <c r="B893" s="2" t="str">
+        <v>EidolonText396</v>
+      </c>
+      <c r="C893" s="3" t="str">
+        <v>모델 준비 완료</v>
+      </c>
+      <c r="D893" s="3" t="str">
+        <v>Models ready</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="894" spans="1:4">
+      <c r="A894" s="2" t="n">
+        <v>3477</v>
+      </c>
+      <c r="B894" s="2" t="str">
+        <v>EidolonText397</v>
+      </c>
+      <c r="C894" s="3" t="str">
+        <v>{0}개 모델을 사용할 수 있습니다.</v>
+      </c>
+      <c r="D894" s="3" t="str">
+        <v>{0} models available.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="895" spans="1:4">
+      <c r="A895" s="2" t="n">
+        <v>3478</v>
+      </c>
+      <c r="B895" s="2" t="str">
+        <v>EidolonText398</v>
+      </c>
+      <c r="C895" s="3" t="str">
+        <v>모델 관리</v>
+      </c>
+      <c r="D895" s="3" t="str">
+        <v>Manage models</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="896" spans="1:4">
+      <c r="A896" s="2" t="n">
+        <v>3479</v>
+      </c>
+      <c r="B896" s="2" t="str">
+        <v>EidolonText399</v>
+      </c>
+      <c r="C896" s="3" t="str">
+        <v>설치 상태 보기</v>
+      </c>
+      <c r="D896" s="3" t="str">
+        <v>View installation</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="897" spans="1:4">
+      <c r="A897" s="2" t="n">
+        <v>3480</v>
+      </c>
+      <c r="B897" s="2" t="str">
+        <v>EidolonText400</v>
+      </c>
+      <c r="C897" s="3" t="str">
+        <v>엔진 준비 완료</v>
+      </c>
+      <c r="D897" s="3" t="str">
+        <v>Engine ready</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="898" spans="1:4">
+      <c r="A898" s="2" t="n">
+        <v>3481</v>
+      </c>
+      <c r="B898" s="2" t="str">
+        <v>EidolonText401</v>
+      </c>
+      <c r="C898" s="3" t="str">
+        <v>엔진 설치 또는 서버 연결 필요</v>
+      </c>
+      <c r="D898" s="3" t="str">
+        <v>Install an engine or connect to a server</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="899" spans="1:4">
+      <c r="A899" s="2" t="n">
+        <v>3482</v>
+      </c>
+      <c r="B899" s="2" t="str">
+        <v>EidolonText402</v>
+      </c>
+      <c r="C899" s="3" t="str">
+        <v>준비 상태 확인 중…</v>
+      </c>
+      <c r="D899" s="3" t="str">
+        <v>Checking setup…</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="900" spans="1:4">
+      <c r="A900" s="2" t="n">
+        <v>3483</v>
+      </c>
+      <c r="B900" s="2" t="str">
+        <v>EidolonText403</v>
+      </c>
+      <c r="C900" s="3" t="str">
+        <v>연결한 서버의 모델을 준비한 뒤 모델 목록을 새로고침해 주세요.</v>
+      </c>
+      <c r="D900" s="3" t="str">
+        <v>Prepare a model on your connected server, then refresh the model list.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="901" spans="1:4">
+      <c r="A901" s="2" t="n">
+        <v>3484</v>
+      </c>
+      <c r="B901" s="2" t="str">
+        <v>EidolonText404</v>
+      </c>
+      <c r="C901" s="3" t="str">
+        <v>모델 목록 확인</v>
+      </c>
+      <c r="D901" s="3" t="str">
+        <v>View models</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="902" spans="1:4">
+      <c r="A902" s="2" t="n">
+        <v>3485</v>
+      </c>
+      <c r="B902" s="2" t="str">
+        <v>EidolonText405</v>
+      </c>
+      <c r="C902" s="3" t="str">
+        <v>먼저 엔진 설치 또는 서버 연결을 완료해 주세요.</v>
+      </c>
+      <c r="D902" s="3" t="str">
+        <v>First install the engine or connect to a server.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="903" spans="1:4">
+      <c r="A903" s="2" t="n">
+        <v>3486</v>
+      </c>
+      <c r="B903" s="2" t="str">
+        <v>EidolonText406</v>
+      </c>
+      <c r="C903" s="3" t="str">
+        <v>엔진 설치 완료 · 연결 필요</v>
+      </c>
+      <c r="D903" s="3" t="str">
+        <v>Engine installed · connect to continue</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="904" spans="1:4">
+      <c r="A904" s="2" t="n">
+        <v>3487</v>
+      </c>
+      <c r="B904" s="2" t="str">
+        <v>EidolonText407</v>
+      </c>
+      <c r="C904" s="3" t="str">
+        <v>엔진 준비하기</v>
+      </c>
+      <c r="D904" s="3" t="str">
+        <v>Prepare engine</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="905" spans="1:4">
+      <c r="A905" s="2" t="n">
+        <v>3488</v>
+      </c>
+      <c r="B905" s="2" t="str">
+        <v>EidolonText408</v>
+      </c>
+      <c r="C905" s="3" t="str">
+        <v>이미지 생성과 LoRA 학습에 필요한 실행 환경을 준비합니다.</v>
+      </c>
+      <c r="D905" s="3" t="str">
+        <v>Prepare the runtime for image generation and LoRA training.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="906" spans="1:4">
+      <c r="A906" s="2" t="n">
+        <v>3489</v>
+      </c>
+      <c r="B906" s="2" t="str">
+        <v>EidolonText409</v>
+      </c>
+      <c r="C906" s="3" t="str">
+        <v>파일 가져오기</v>
+      </c>
+      <c r="D906" s="3" t="str">
+        <v>Import file</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="907" spans="1:4">
+      <c r="A907" s="2" t="n">
+        <v>3490</v>
+      </c>
+      <c r="B907" s="2" t="str">
+        <v>EidolonText410</v>
+      </c>
+      <c r="C907" s="3" t="str">
+        <v>새로고침</v>
+      </c>
+      <c r="D907" s="3" t="str">
+        <v>Refresh</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="908" spans="1:4">
+      <c r="A908" s="2" t="n">
+        <v>3491</v>
+      </c>
+      <c r="B908" s="2" t="str">
+        <v>EidolonText411</v>
+      </c>
+      <c r="C908" s="3" t="str">
+        <v>내 모델 · LoRA</v>
+      </c>
+      <c r="D908" s="3" t="str">
+        <v>My models · LoRA</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="909" spans="1:4">
+      <c r="A909" s="2" t="n">
+        <v>3492</v>
+      </c>
+      <c r="B909" s="2" t="str">
+        <v>EidolonText412</v>
+      </c>
+      <c r="C909" s="3" t="str">
+        <v>상세 설정</v>
+      </c>
+      <c r="D909" s="3" t="str">
+        <v>Advanced settings</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="910" spans="1:4">
+      <c r="A910" s="2" t="n">
+        <v>3493</v>
+      </c>
+      <c r="B910" s="2" t="str">
+        <v>EidolonText413</v>
+      </c>
+      <c r="C910" s="3" t="str">
+        <v>계열은 자동 판별합니다. 판별되지 않은 모델만 직접 지정하세요.</v>
+      </c>
+      <c r="D910" s="3" t="str">
+        <v>The family is detected automatically. Set it manually only if detection is unavailable.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="911" spans="1:4">
+      <c r="A911" s="2" t="n">
+        <v>3494</v>
+      </c>
+      <c r="B911" s="2" t="str">
+        <v>EidolonText414</v>
+      </c>
+      <c r="C911" s="3" t="str">
+        <v>모델 계열을 확인해 주세요.</v>
+      </c>
+      <c r="D911" s="3" t="str">
+        <v>Check this model's family.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="912" spans="1:4">
+      <c r="A912" s="2" t="n">
+        <v>3495</v>
+      </c>
+      <c r="B912" s="2" t="str">
+        <v>EidolonText415</v>
+      </c>
+      <c r="C912" s="3" t="str">
+        <v>모델 파일은 삭제되지 않습니다.</v>
+      </c>
+      <c r="D912" s="3" t="str">
+        <v>The model file is kept.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="913" spans="1:4">
+      <c r="A913" s="2" t="n">
+        <v>3496</v>
+      </c>
+      <c r="B913" s="2" t="str">
+        <v>EidolonText416</v>
+      </c>
+      <c r="C913" s="3" t="str">
+        <v>설치 안내</v>
+      </c>
+      <c r="D913" s="3" t="str">
+        <v>Installation details</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="914" spans="1:4">
+      <c r="A914" s="2" t="n">
+        <v>3497</v>
+      </c>
+      <c r="B914" s="2" t="str">
+        <v>EidolonText417</v>
+      </c>
+      <c r="C914" s="3" t="str">
+        <v>연결 안내</v>
+      </c>
+      <c r="D914" s="3" t="str">
+        <v>Connection details</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="915" spans="1:4">
+      <c r="A915" s="2" t="n">
+        <v>3498</v>
+      </c>
+      <c r="B915" s="2" t="str">
+        <v>EidolonText418</v>
+      </c>
+      <c r="C915" s="3" t="str">
+        <v>설치하거나 가져온 모델이 여기에 표시됩니다.</v>
+      </c>
+      <c r="D915" s="3" t="str">
+        <v>Installed and imported models appear here.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="916" spans="1:4">
+      <c r="A916" s="2" t="n">
+        <v>3499</v>
+      </c>
+      <c r="B916" s="2" t="str">
+        <v>EidolonText419</v>
+      </c>
+      <c r="C916" s="3" t="str">
+        <v>자동 생성</v>
+      </c>
+      <c r="D916" s="3" t="str">
+        <v>Random seed</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="917" spans="1:4">
+      <c r="A917" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="B917" s="2" t="str">
+        <v>EidolonText420</v>
+      </c>
+      <c r="C917" s="3" t="str">
+        <v>요청마다 새로운 시드로 생성합니다.</v>
+      </c>
+      <c r="D917" s="3" t="str">
+        <v>Each request uses a new random seed.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="918" spans="1:4">
+      <c r="A918" s="2" t="n">
+        <v>3501</v>
+      </c>
+      <c r="B918" s="2" t="str">
+        <v>EidolonText421</v>
+      </c>
+      <c r="C918" s="3" t="str">
+        <v>시드는 {0}~{1} 사이의 정수를 입력하세요.</v>
+      </c>
+      <c r="D918" s="3" t="str">
+        <v>Enter an integer seed between {0} and {1}.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="919" spans="1:4">
+      <c r="A919" s="2" t="n">
+        <v>3502</v>
+      </c>
+      <c r="B919" s="2" t="str">
+        <v>EidolonText422</v>
+      </c>
+      <c r="C919" s="3" t="str">
+        <v>최근 요청 시드: {0}</v>
+      </c>
+      <c r="D919" s="3" t="str">
+        <v>Latest requested seed: {0}</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="920" spans="1:4">
+      <c r="A920" s="2" t="n">
+        <v>3503</v>
+      </c>
+      <c r="B920" s="2" t="str">
+        <v>EidolonText423</v>
+      </c>
+      <c r="C920" s="3" t="str">
+        <v>LoRA (선택)</v>
+      </c>
+      <c r="D920" s="3" t="str">
+        <v>LoRA (optional)</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="921" spans="1:4">
+      <c r="A921" s="2" t="n">
+        <v>3504</v>
+      </c>
+      <c r="B921" s="2" t="str">
+        <v>EidolonText424</v>
+      </c>
+      <c r="C921" s="3" t="str">
+        <v>왼쪽에서 이미지를 선택하면 크게 볼 수 있습니다.</v>
+      </c>
+      <c r="D921" s="3" t="str">
+        <v>Select an image on the left to view it here.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="922" spans="1:4">
+      <c r="A922" s="2" t="n">
+        <v>3505</v>
+      </c>
+      <c r="B922" s="2" t="str">
+        <v>EidolonText425</v>
+      </c>
+      <c r="C922" s="3" t="str">
+        <v>학습 이미지 배경</v>
+      </c>
+      <c r="D922" s="3" t="str">
+        <v>Training image background</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="923" spans="1:4">
+      <c r="A923" s="2" t="n">
+        <v>3506</v>
+      </c>
+      <c r="B923" s="2" t="str">
+        <v>EidolonText426</v>
+      </c>
+      <c r="C923" s="3" t="str">
+        <v>원본 유지</v>
+      </c>
+      <c r="D923" s="3" t="str">
+        <v>Keep original</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="924" spans="1:4">
+      <c r="A924" s="2" t="n">
+        <v>3507</v>
+      </c>
+      <c r="B924" s="2" t="str">
+        <v>EidolonText427</v>
+      </c>
+      <c r="C924" s="3" t="str">
+        <v>흰색</v>
+      </c>
+      <c r="D924" s="3" t="str">
+        <v>White</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="925" spans="1:4">
+      <c r="A925" s="2" t="n">
+        <v>3508</v>
+      </c>
+      <c r="B925" s="2" t="str">
+        <v>EidolonText428</v>
+      </c>
+      <c r="C925" s="3" t="str">
+        <v>검정색</v>
+      </c>
+      <c r="D925" s="3" t="str">
+        <v>Black</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="926" spans="1:4">
+      <c r="A926" s="2" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B926" s="2" t="str">
+        <v>EidolonText429</v>
+      </c>
+      <c r="C926" s="3" t="str">
+        <v>투명 영역을 선택한 색으로 채웁니다. 이미 있는 배경과 원본 이미지·설명은 유지합니다.</v>
+      </c>
+      <c r="D926" s="3" t="str">
+        <v>Fill transparent areas with the selected color. Existing backgrounds, original images and captions are preserved.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="927" spans="1:4">
+      <c r="A927" s="2" t="n">
+        <v>3510</v>
+      </c>
+      <c r="B927" s="2" t="str">
+        <v>EidolonText430</v>
+      </c>
+      <c r="C927" s="3" t="str">
+        <v>학습 이미지 배경을 선택하세요.</v>
+      </c>
+      <c r="D927" s="3" t="str">
+        <v>Select a training image background.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="928" spans="1:4">
+      <c r="A928" s="2" t="n">
+        <v>3511</v>
+      </c>
+      <c r="B928" s="2" t="str">
+        <v>EidolonText431</v>
+      </c>
+      <c r="C928" s="3" t="str">
+        <v>학습 이미지 배경을 처리하지 못했습니다: {0}</v>
+      </c>
+      <c r="D928" s="3" t="str">
+        <v>Could not prepare the training image background: {0}</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="929" spans="1:4">
+      <c r="A929" s="2" t="n">
+        <v>3512</v>
+      </c>
+      <c r="B929" s="2" t="str">
+        <v>EidolonText432</v>
+      </c>
+      <c r="C929" s="3" t="str">
+        <v>LoRA 이름·파일명·트리거 검색</v>
+      </c>
+      <c r="D929" s="3" t="str">
+        <v>Search LoRA name, filename or trigger</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="930" spans="1:4">
+      <c r="A930" s="2" t="n">
+        <v>3513</v>
+      </c>
+      <c r="B930" s="2" t="str">
+        <v>EidolonText433</v>
+      </c>
+      <c r="C930" s="3" t="str">
+        <v>검색한 LoRA가 없습니다.</v>
+      </c>
+      <c r="D930" s="3" t="str">
+        <v>No matching LoRAs.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="931" spans="1:4">
+      <c r="A931" s="2" t="n">
+        <v>3514</v>
+      </c>
+      <c r="B931" s="2" t="str">
+        <v>EidolonText434</v>
+      </c>
+      <c r="C931" s="3" t="str">
+        <v>{0}개 LoRA 적용 중</v>
+      </c>
+      <c r="D931" s="3" t="str">
+        <v>{0} LoRAs applied</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="932" spans="1:4">
+      <c r="A932" s="2" t="n">
+        <v>3515</v>
+      </c>
+      <c r="B932" s="2" t="str">
+        <v>EidolonText435</v>
+      </c>
+      <c r="C932" s="3" t="str">
+        <v>적용 중</v>
+      </c>
+      <c r="D932" s="3" t="str">
+        <v>Applied</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="933" spans="1:4">
+      <c r="A933" s="2" t="n">
+        <v>3516</v>
+      </c>
+      <c r="B933" s="2" t="str">
+        <v>EidolonText436</v>
+      </c>
+      <c r="C933" s="3" t="str">
+        <v>설정의 생성 지침</v>
+      </c>
+      <c r="D933" s="3" t="str">
+        <v>Generation instructions from settings</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="934" spans="1:4">
+      <c r="A934" s="2" t="n">
+        <v>3517</v>
+      </c>
+      <c r="B934" s="2" t="str">
+        <v>EidolonText437</v>
+      </c>
+      <c r="C934" s="3" t="str">
+        <v>설정에 저장한 생성 지침과 제외할 요소가 적용됩니다.</v>
+      </c>
+      <c r="D934" s="3" t="str">
+        <v>The generation instructions and elements to avoid saved in settings are applied.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="935" spans="1:4">
+      <c r="A935" s="2" t="n">
+        <v>3518</v>
+      </c>
+      <c r="B935" s="2" t="str">
+        <v>EidolonText438</v>
+      </c>
+      <c r="C935" s="3" t="str">
+        <v>생성하기</v>
+      </c>
+      <c r="D935" s="3" t="str">
+        <v>Generate</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="936" spans="1:4">
+      <c r="A936" s="2" t="n">
+        <v>3519</v>
+      </c>
+      <c r="B936" s="2" t="str">
+        <v>EidolonText439</v>
+      </c>
+      <c r="C936" s="3" t="str">
+        <v>미리보기</v>
+      </c>
+      <c r="D936" s="3" t="str">
+        <v>Preview</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="937" spans="1:4">
+      <c r="A937" s="2" t="n">
+        <v>3520</v>
+      </c>
+      <c r="B937" s="2" t="str">
+        <v>EidolonText440</v>
+      </c>
+      <c r="C937" s="3" t="str">
+        <v>참고 이미지</v>
+      </c>
+      <c r="D937" s="3" t="str">
+        <v>Reference image</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="938" spans="1:4">
+      <c r="A938" s="2" t="n">
+        <v>3521</v>
+      </c>
+      <c r="B938" s="2" t="str">
+        <v>EidolonText441</v>
+      </c>
+      <c r="C938" s="3" t="str">
+        <v>참고 이미지 추가</v>
+      </c>
+      <c r="D938" s="3" t="str">
+        <v>Add reference image</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="939" spans="1:4">
+      <c r="A939" s="2" t="n">
+        <v>3522</v>
+      </c>
+      <c r="B939" s="2" t="str">
+        <v>EidolonText442</v>
+      </c>
+      <c r="C939" s="3" t="str">
+        <v>이미지 변경</v>
+      </c>
+      <c r="D939" s="3" t="str">
+        <v>Change image</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="940" spans="1:4">
+      <c r="A940" s="2" t="n">
+        <v>3523</v>
+      </c>
+      <c r="B940" s="2" t="str">
+        <v>EidolonText443</v>
+      </c>
+      <c r="C940" s="3" t="str">
+        <v>제거</v>
+      </c>
+      <c r="D940" s="3" t="str">
+        <v>Remove</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="941" spans="1:4">
+      <c r="A941" s="2" t="n">
+        <v>3524</v>
+      </c>
+      <c r="B941" s="2" t="str">
+        <v>EidolonText444</v>
+      </c>
+      <c r="C941" s="3" t="str">
+        <v>참고해 새로 생성</v>
+      </c>
+      <c r="D941" s="3" t="str">
+        <v>Reimagine from image</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="942" spans="1:4">
+      <c r="A942" s="2" t="n">
+        <v>3525</v>
+      </c>
+      <c r="B942" s="2" t="str">
+        <v>EidolonText445</v>
+      </c>
+      <c r="C942" s="3" t="str">
+        <v>그림체 변경</v>
+      </c>
+      <c r="D942" s="3" t="str">
+        <v>Change style</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="943" spans="1:4">
+      <c r="A943" s="2" t="n">
+        <v>3526</v>
+      </c>
+      <c r="B943" s="2" t="str">
+        <v>EidolonText446</v>
+      </c>
+      <c r="C943" s="3" t="str">
+        <v>원본 이미지를 바탕으로 설명에 맞는 새로운 이미지를 만듭니다.</v>
+      </c>
+      <c r="D943" s="3" t="str">
+        <v>Create a new image based on the reference and your description.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="944" spans="1:4">
+      <c r="A944" s="2" t="n">
+        <v>3527</v>
+      </c>
+      <c r="B944" s="2" t="str">
+        <v>EidolonText447</v>
+      </c>
+      <c r="C944" s="3" t="str">
+        <v>대상과 구도를 최대한 유지하며 원하는 그림체를 적용합니다. 설명에 바꿀 스타일을 적어주세요.</v>
+      </c>
+      <c r="D944" s="3" t="str">
+        <v>Keep the subject and composition as closely as possible while applying the style described in your prompt.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="945" spans="1:4">
+      <c r="A945" s="2" t="n">
+        <v>3528</v>
+      </c>
+      <c r="B945" s="2" t="str">
+        <v>EidolonText448</v>
+      </c>
+      <c r="C945" s="3" t="str">
+        <v>변경 강도</v>
+      </c>
+      <c r="D945" s="3" t="str">
+        <v>Change strength</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="946" spans="1:4">
+      <c r="A946" s="2" t="n">
+        <v>3529</v>
+      </c>
+      <c r="B946" s="2" t="str">
+        <v>EidolonText449</v>
+      </c>
+      <c r="C946" s="3" t="str">
+        <v>낮을수록 원본 유지 · 높을수록 큰 변화</v>
+      </c>
+      <c r="D946" s="3" t="str">
+        <v>Lower preserves the original · higher makes larger changes</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="947" spans="1:4">
+      <c r="A947" s="2" t="n">
+        <v>3530</v>
+      </c>
+      <c r="B947" s="2" t="str">
+        <v>EidolonText450</v>
+      </c>
+      <c r="C947" s="3" t="str">
+        <v>이미지를 읽을 수 없습니다. 32 MB·4천만 픽셀 이하의 PNG, JPG, WebP 파일을 선택해주세요.</v>
+      </c>
+      <c r="D947" s="3" t="str">
+        <v>Cannot read this image. Choose a PNG, JPG, or WebP file up to 32 MB and 40 million pixels.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="948" spans="1:4">
+      <c r="A948" s="2" t="n">
+        <v>3531</v>
+      </c>
+      <c r="B948" s="2" t="str">
+        <v>EidolonText451</v>
+      </c>
+      <c r="C948" s="3" t="str">
+        <v>참고 이미지의 모드와 변경 강도를 확인해주세요. 변경 강도는 5~95%로 설정할 수 있습니다.</v>
+      </c>
+      <c r="D948" s="3" t="str">
+        <v>Check the reference mode and change strength. Strength must be between 5% and 95%.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="949" spans="1:4">
+      <c r="A949" s="2" t="n">
+        <v>3532</v>
+      </c>
+      <c r="B949" s="2" t="str">
+        <v>EidolonText452</v>
+      </c>
+      <c r="C949" s="3" t="str">
+        <v>참고 이미지 준비 중</v>
+      </c>
+      <c r="D949" s="3" t="str">
+        <v>Preparing reference image</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="950" spans="1:4">
+      <c r="A950" s="2" t="n">
+        <v>3533</v>
+      </c>
+      <c r="B950" s="2" t="str">
+        <v>EidolonText453</v>
+      </c>
+      <c r="C950" s="3" t="str">
+        <v>참고 이미지를 생성 엔진에 전송 중</v>
+      </c>
+      <c r="D950" s="3" t="str">
+        <v>Uploading reference image to the generation engine</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="951" spans="1:4">
+      <c r="A951" s="2" t="n">
+        <v>3534</v>
+      </c>
+      <c r="B951" s="2" t="str">
+        <v>EidolonText454</v>
+      </c>
+      <c r="C951" s="3" t="str">
+        <v>이 결과의 참고 이미지를 찾거나 읽을 수 없습니다. 이미지를 다시 선택해주세요.</v>
+      </c>
+      <c r="D951" s="3" t="str">
+        <v>The reference image for this result cannot be found or read. Select an image again.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="952" spans="1:4">
+      <c r="A952" s="2" t="n">
+        <v>3535</v>
+      </c>
+      <c r="B952" s="2" t="str">
+        <v>EidolonText455</v>
+      </c>
+      <c r="C952" s="3" t="str">
+        <v>이 이미지로 편집</v>
+      </c>
+      <c r="D952" s="3" t="str">
+        <v>Edit from this image</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="953" spans="1:4">
+      <c r="A953" s="2" t="n">
+        <v>3536</v>
+      </c>
+      <c r="B953" s="2" t="str">
+        <v>EidolonText456</v>
+      </c>
+      <c r="C953" s="3" t="str">
+        <v>이미지 편집</v>
+      </c>
+      <c r="D953" s="3" t="str">
+        <v>Image editing</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="954" spans="1:4">
+      <c r="A954" s="2" t="n">
+        <v>3537</v>
+      </c>
+      <c r="B954" s="2" t="str">
+        <v>EidolonText457</v>
+      </c>
+      <c r="C954" s="3" t="str">
+        <v>어떻게 바꿀까요?</v>
+      </c>
+      <c r="D954" s="3" t="str">
+        <v>How should it change?</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="955" spans="1:4">
+      <c r="A955" s="2" t="n">
+        <v>3538</v>
+      </c>
+      <c r="B955" s="2" t="str">
+        <v>EidolonText458</v>
+      </c>
+      <c r="C955" s="3" t="str">
+        <v>예: 대상과 구도를 유지하고 수채화풍으로 바꿔줘</v>
+      </c>
+      <c r="D955" s="3" t="str">
+        <v>Example: Keep the subject and composition, and change it to a watercolor illustration</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="956" spans="1:4">
+      <c r="A956" s="2" t="n">
+        <v>3539</v>
+      </c>
+      <c r="B956" s="2" t="str">
+        <v>EidolonText459</v>
+      </c>
+      <c r="C956" s="3" t="str">
+        <v>편집할 이미지를 먼저 선택해주세요.</v>
+      </c>
+      <c r="D956" s="3" t="str">
+        <v>Select the image you want to edit first.</v>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="957" spans="1:4">
+      <c r="A957" s="2" t="n">
+        <v>3540</v>
+      </c>
+      <c r="B957" s="2" t="str">
+        <v>EidolonText460</v>
+      </c>
+      <c r="C957" s="3" t="str">
+        <v>저장 폴더 선택</v>
+      </c>
+      <c r="D957" s="3" t="str">
+        <v>Choose output folder</v>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -13332,10 +13332,10 @@
         <x:v>EidolonText192</x:v>
       </x:c>
       <x:c r="C689" s="3" t="str">
-        <x:v>모델, 이미지와 LoRA 이름·트리거를 지정합니다. 단계 수를 입력하거나 빠른·기본 학습을 선택한 뒤 대기열에 추가합니다. 요청 버튼 옆에서 학습을 취소할 수 있습니다. 하단에는 진행 상태와 예상 남은 시간을 표시합니다. 학습한 LoRA를 생성에서 선택하면 트리거가 자동 적용됩니다.</x:v>
+        <x:v>이미지 선택 → 이름과 트리거 → 학습 폴더 준비 → 설명 확인 → 학습 순서로 진행합니다. 흰색·검정색 목록에 고른 이미지는 함께 학습해 LoRA 하나를 만듭니다. 학습 폴더의 .txt 설명을 수정하고 저장한 뒤 모델과 단계 수를 정해 학습하기를 누르세요.</x:v>
       </x:c>
       <x:c r="D689" s="3" t="str">
-        <x:v>Choose a model, images, LoRA name and trigger. Enter steps or use Quick or Standard, then queue training. Cancel beside the request button. The footer shows progress and estimated time remaining. Selecting a trained LoRA applies its trigger automatically.</x:v>
+        <x:v>Follow the steps: select images, set a name and trigger, prepare a training folder, review captions, and train. Images from the white and black lists are combined into one LoRA. Edit and save the caption .txt files, choose the model and step count, then select Train.</x:v>
       </x:c>
     </x:row>
     <x:row r="690" ht="105.5999984741211" hidden="0" customHeight="1">
@@ -13346,10 +13346,10 @@
         <x:v>EidolonText193</x:v>
       </x:c>
       <x:c r="C690" s="3" t="str">
-        <x:v>학습에는 NVIDIA GPU 환경이 필요합니다. 트리거는 공백과 쉼표가 없는 단어를 사용하세요. 완료한 LoRA는 자동으로 등록되며 이미지 생성 탭에서 선택해 사용할 수 있습니다. 기본 모델과 같은 계열의 LoRA만 표시합니다.</x:v>
+        <x:v>학습에는 NVIDIA GPU가 필요합니다. 트리거는 공백과 쉼표 없는 단어를 사용하세요. 완료된 LoRA는 생성 화면에서 선택할 수 있으며, 트리거가 프롬프트 맨 앞에 자동으로 적용됩니다. 기반 모델과 같은 계열의 LoRA만 표시합니다.</x:v>
       </x:c>
       <x:c r="D690" s="3" t="str">
-        <x:v>Training requires an NVIDIA GPU environment. Use a trigger word without spaces or commas. Completed LoRAs are registered automatically and can be selected in Generate. Only LoRAs matching the base model family are shown.</x:v>
+        <x:v>Training requires an NVIDIA GPU. Use a trigger without spaces or commas. Completed LoRAs are available in the generation tab, where their triggers are added to the beginning of the prompt. Only LoRAs compatible with the selected model family are shown.</x:v>
       </x:c>
     </x:row>
     <x:row r="691" ht="16.5" hidden="0" customHeight="1">
@@ -17102,6 +17102,846 @@
         <v>Choose output folder</v>
       </c>
     </row>
+    <x:row r="958" spans="1:4">
+      <x:c r="A958" s="2" t="n">
+        <x:v>3541</x:v>
+      </x:c>
+      <x:c r="B958" s="2" t="str">
+        <x:v>EidolonText461</x:v>
+      </x:c>
+      <x:c r="C958" s="3" t="str">
+        <x:v>흰색 배경</x:v>
+      </x:c>
+      <x:c r="D958" s="3" t="str">
+        <x:v>White background</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="959" spans="1:4">
+      <x:c r="A959" s="2" t="n">
+        <x:v>3542</x:v>
+      </x:c>
+      <x:c r="B959" s="2" t="str">
+        <x:v>EidolonText462</x:v>
+      </x:c>
+      <x:c r="C959" s="3" t="str">
+        <x:v>검정색 배경</x:v>
+      </x:c>
+      <x:c r="D959" s="3" t="str">
+        <x:v>Black background</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="960" spans="1:4">
+      <x:c r="A960" s="2" t="n">
+        <x:v>3543</x:v>
+      </x:c>
+      <x:c r="B960" s="2" t="str">
+        <x:v>EidolonText463</x:v>
+      </x:c>
+      <x:c r="C960" s="3" t="str">
+        <x:v>이미지 추가</x:v>
+      </x:c>
+      <x:c r="D960" s="3" t="str">
+        <x:v>Add images</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="961" spans="1:4">
+      <x:c r="A961" s="2" t="n">
+        <x:v>3544</x:v>
+      </x:c>
+      <x:c r="B961" s="2" t="str">
+        <x:v>EidolonText464</x:v>
+      </x:c>
+      <x:c r="C961" s="3" t="str">
+        <x:v>폴더 추가</x:v>
+      </x:c>
+      <x:c r="D961" s="3" t="str">
+        <x:v>Add folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="962" spans="1:4">
+      <x:c r="A962" s="2" t="n">
+        <x:v>3545</x:v>
+      </x:c>
+      <x:c r="B962" s="2" t="str">
+        <x:v>EidolonText465</x:v>
+      </x:c>
+      <x:c r="C962" s="3" t="str">
+        <x:v>{0}장</x:v>
+      </x:c>
+      <x:c r="D962" s="3" t="str">
+        <x:v>{0} images</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="963" spans="1:4">
+      <x:c r="A963" s="2" t="n">
+        <x:v>3546</x:v>
+      </x:c>
+      <x:c r="B963" s="2" t="str">
+        <x:v>EidolonText466</x:v>
+      </x:c>
+      <x:c r="C963" s="3" t="str">
+        <x:v>총 {0}장 · LoRA 하나로 학습</x:v>
+      </x:c>
+      <x:c r="D963" s="3" t="str">
+        <x:v>{0} images · One LoRA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="964" spans="1:4">
+      <x:c r="A964" s="2" t="n">
+        <x:v>3547</x:v>
+      </x:c>
+      <x:c r="B964" s="2" t="str">
+        <x:v>EidolonText467</x:v>
+      </x:c>
+      <x:c r="C964" s="3" t="str">
+        <x:v>이미지를 추가해주세요.</x:v>
+      </x:c>
+      <x:c r="D964" s="3" t="str">
+        <x:v>Add images to begin.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="965" spans="1:4">
+      <x:c r="A965" s="2" t="n">
+        <x:v>3548</x:v>
+      </x:c>
+      <x:c r="B965" s="2" t="str">
+        <x:v>EidolonText468</x:v>
+      </x:c>
+      <x:c r="C965" s="3" t="str">
+        <x:v>두 목록의 이미지를 함께 학습해 LoRA 하나를 만듭니다. 투명한 영역만 선택한 배경색으로 채우며, 이미 있는 배경과 원본은 유지합니다.</x:v>
+      </x:c>
+      <x:c r="D965" s="3" t="str">
+        <x:v>Both lists are trained together into one LoRA. Only transparent areas are filled with the selected background color. Existing backgrounds and source files are preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="966" spans="1:4">
+      <x:c r="A966" s="2" t="n">
+        <x:v>3549</x:v>
+      </x:c>
+      <x:c r="B966" s="2" t="str">
+        <x:v>EidolonText469</x:v>
+      </x:c>
+      <x:c r="C966" s="3" t="str">
+        <x:v>목록 비우기</x:v>
+      </x:c>
+      <x:c r="D966" s="3" t="str">
+        <x:v>Clear list</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="967" spans="1:4">
+      <x:c r="A967" s="2" t="n">
+        <x:v>3550</x:v>
+      </x:c>
+      <x:c r="B967" s="2" t="str">
+        <x:v>EidolonText470</x:v>
+      </x:c>
+      <x:c r="C967" s="3" t="str">
+        <x:v>학습할 이미지를 추가해주세요.</x:v>
+      </x:c>
+      <x:c r="D967" s="3" t="str">
+        <x:v>Add training images.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="968" spans="1:4">
+      <x:c r="A968" s="2" t="n">
+        <x:v>3551</x:v>
+      </x:c>
+      <x:c r="B968" s="2" t="str">
+        <x:v>EidolonText471</x:v>
+      </x:c>
+      <x:c r="C968" s="3" t="str">
+        <x:v>학습 폴더 만들기</x:v>
+      </x:c>
+      <x:c r="D968" s="3" t="str">
+        <x:v>Create training folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="969" spans="1:4">
+      <x:c r="A969" s="2" t="n">
+        <x:v>3552</x:v>
+      </x:c>
+      <x:c r="B969" s="2" t="str">
+        <x:v>EidolonText472</x:v>
+      </x:c>
+      <x:c r="C969" s="3" t="str">
+        <x:v>학습 폴더를 저장할 위치 선택</x:v>
+      </x:c>
+      <x:c r="D969" s="3" t="str">
+        <x:v>Choose where to save the training folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="970" spans="1:4">
+      <x:c r="A970" s="2" t="n">
+        <x:v>3553</x:v>
+      </x:c>
+      <x:c r="B970" s="2" t="str">
+        <x:v>EidolonText473</x:v>
+      </x:c>
+      <x:c r="C970" s="3" t="str">
+        <x:v>{0}장의 이미지와 설명 파일을 준비했습니다.</x:v>
+      </x:c>
+      <x:c r="D970" s="3" t="str">
+        <x:v>Prepared {0} images and caption files.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="971" spans="1:4">
+      <x:c r="A971" s="2" t="n">
+        <x:v>3554</x:v>
+      </x:c>
+      <x:c r="B971" s="2" t="str">
+        <x:v>EidolonText474</x:v>
+      </x:c>
+      <x:c r="C971" s="3" t="str">
+        <x:v>학습하기</x:v>
+      </x:c>
+      <x:c r="D971" s="3" t="str">
+        <x:v>Train</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="972" spans="1:4">
+      <x:c r="A972" s="2" t="n">
+        <x:v>3555</x:v>
+      </x:c>
+      <x:c r="B972" s="2" t="str">
+        <x:v>EidolonText475</x:v>
+      </x:c>
+      <x:c r="C972" s="3" t="str">
+        <x:v>이미지를 불러오는 중입니다.</x:v>
+      </x:c>
+      <x:c r="D972" s="3" t="str">
+        <x:v>Loading images.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="973" spans="1:4">
+      <x:c r="A973" s="2" t="n">
+        <x:v>3556</x:v>
+      </x:c>
+      <x:c r="B973" s="2" t="str">
+        <x:v>EidolonText476</x:v>
+      </x:c>
+      <x:c r="C973" s="3" t="str">
+        <x:v>기존 이미지의 그림체 바꾸기</x:v>
+      </x:c>
+      <x:c r="D973" s="3" t="str">
+        <x:v>Change an image style</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="974" spans="1:4">
+      <x:c r="A974" s="2" t="n">
+        <x:v>3557</x:v>
+      </x:c>
+      <x:c r="B974" s="2" t="str">
+        <x:v>EidolonText477</x:v>
+      </x:c>
+      <x:c r="C974" s="3" t="str">
+        <x:v>이미지 편집 탭에서 참고 이미지를 선택하고 원하는 그림체를 설명합니다. 모델과 LoRA를 고른 뒤 대기열에 추가하세요. 생성 결과에서도 이미지 편집 버튼으로 시작할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D974" s="3" t="str">
+        <x:v>Select a reference image in the image editing tab and describe the style you want. Choose a model and LoRAs, then add the request to the queue. You can also start with the image editing action in the result gallery.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="975" spans="1:4">
+      <x:c r="A975" s="2" t="n">
+        <x:v>3559</x:v>
+      </x:c>
+      <x:c r="B975" s="2" t="str">
+        <x:v>EidolonText479</x:v>
+      </x:c>
+      <x:c r="C975" s="3" t="str">
+        <x:v>변경 강도가 낮을수록 원본을 더 유지하고, 높을수록 새 그림체와 설명을 더 반영합니다. 형태나 구도를 정확히 고정하지는 않습니다. 원본 파일은 변경하지 않습니다.</x:v>
+      </x:c>
+      <x:c r="D975" s="3" t="str">
+        <x:v>Lower change strength retains more of the original; higher strength applies more of the new style and description. Exact shape or composition is not guaranteed. The source file is preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="976" spans="1:4">
+      <x:c r="A976" s="2" t="n">
+        <x:v>3560</x:v>
+      </x:c>
+      <x:c r="B976" s="2" t="str">
+        <x:v>EidolonText480</x:v>
+      </x:c>
+      <x:c r="C976" s="3" t="str">
+        <x:v>생성 탭에서도 참고 이미지를 선택할 수 있습니다. 설명과 참고 이미지를 바탕으로 새 이미지를 생성하며, 참고 이미지를 제거하면 설명만으로 생성합니다.</x:v>
+      </x:c>
+      <x:c r="D976" s="3" t="str">
+        <x:v>You can also add a reference image in the generation tab to create a new image from your description and reference. Remove the reference to generate from text alone.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="977" spans="1:4">
+      <x:c r="A977" s="2" t="n">
+        <x:v>3561</x:v>
+      </x:c>
+      <x:c r="B977" s="2" t="str">
+        <x:v>EidolonText481</x:v>
+      </x:c>
+      <x:c r="C977" s="3" t="str">
+        <x:v>빠른 학습 {0}단계 · 기본 학습 {1}단계</x:v>
+      </x:c>
+      <x:c r="D977" s="3" t="str">
+        <x:v>Quick: {0} steps · Standard: {1} steps</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="978" spans="1:4">
+      <x:c r="A978" s="2" t="n">
+        <x:v>3562</x:v>
+      </x:c>
+      <x:c r="B978" s="2" t="str">
+        <x:v>EidolonText482</x:v>
+      </x:c>
+      <x:c r="C978" s="3" t="str">
+        <x:v>이미지에서 배경과 대상을 구분하지 못했습니다. 배경 투명화를 끄거나 다른 이미지로 시도해주세요.</x:v>
+      </x:c>
+      <x:c r="D978" s="3" t="str">
+        <x:v>Could not distinguish the subject from the background. Turn off background removal or try another image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="979" spans="1:4">
+      <x:c r="A979" s="2" t="n">
+        <x:v>3563</x:v>
+      </x:c>
+      <x:c r="B979" s="2" t="str">
+        <x:v>EidolonText483</x:v>
+      </x:c>
+      <x:c r="C979" s="3" t="str">
+        <x:v>이미지 선택</x:v>
+      </x:c>
+      <x:c r="D979" s="3" t="str">
+        <x:v>Select images</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="980" spans="1:4">
+      <x:c r="A980" s="2" t="n">
+        <x:v>3564</x:v>
+      </x:c>
+      <x:c r="B980" s="2" t="str">
+        <x:v>EidolonText484</x:v>
+      </x:c>
+      <x:c r="C980" s="3" t="str">
+        <x:v>이름과 트리거</x:v>
+      </x:c>
+      <x:c r="D980" s="3" t="str">
+        <x:v>Name and trigger</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="981" spans="1:4">
+      <x:c r="A981" s="2" t="n">
+        <x:v>3565</x:v>
+      </x:c>
+      <x:c r="B981" s="2" t="str">
+        <x:v>EidolonText485</x:v>
+      </x:c>
+      <x:c r="C981" s="3" t="str">
+        <x:v>학습 폴더 준비</x:v>
+      </x:c>
+      <x:c r="D981" s="3" t="str">
+        <x:v>Prepare folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="982" spans="1:4">
+      <x:c r="A982" s="2" t="n">
+        <x:v>3566</x:v>
+      </x:c>
+      <x:c r="B982" s="2" t="str">
+        <x:v>EidolonText486</x:v>
+      </x:c>
+      <x:c r="C982" s="3" t="str">
+        <x:v>설명 확인</x:v>
+      </x:c>
+      <x:c r="D982" s="3" t="str">
+        <x:v>Review captions</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="983" spans="1:4">
+      <x:c r="A983" s="2" t="n">
+        <x:v>3567</x:v>
+      </x:c>
+      <x:c r="B983" s="2" t="str">
+        <x:v>EidolonText487</x:v>
+      </x:c>
+      <x:c r="C983" s="3" t="str">
+        <x:v>학습</x:v>
+      </x:c>
+      <x:c r="D983" s="3" t="str">
+        <x:v>Train</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="984" spans="1:4">
+      <x:c r="A984" s="2" t="n">
+        <x:v>3568</x:v>
+      </x:c>
+      <x:c r="B984" s="2" t="str">
+        <x:v>EidolonText488</x:v>
+      </x:c>
+      <x:c r="C984" s="3" t="str">
+        <x:v>{0} / {1} 단계</x:v>
+      </x:c>
+      <x:c r="D984" s="3" t="str">
+        <x:v>Step {0} of {1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="985" spans="1:4">
+      <x:c r="A985" s="2" t="n">
+        <x:v>3569</x:v>
+      </x:c>
+      <x:c r="B985" s="2" t="str">
+        <x:v>EidolonText489</x:v>
+      </x:c>
+      <x:c r="C985" s="3" t="str">
+        <x:v>이전</x:v>
+      </x:c>
+      <x:c r="D985" s="3" t="str">
+        <x:v>Previous</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="986" spans="1:4">
+      <x:c r="A986" s="2" t="n">
+        <x:v>3570</x:v>
+      </x:c>
+      <x:c r="B986" s="2" t="str">
+        <x:v>EidolonText490</x:v>
+      </x:c>
+      <x:c r="C986" s="3" t="str">
+        <x:v>다음</x:v>
+      </x:c>
+      <x:c r="D986" s="3" t="str">
+        <x:v>Next</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="987" spans="1:4">
+      <x:c r="A987" s="2" t="n">
+        <x:v>3571</x:v>
+      </x:c>
+      <x:c r="B987" s="2" t="str">
+        <x:v>EidolonText491</x:v>
+      </x:c>
+      <x:c r="C987" s="3" t="str">
+        <x:v>학습 폴더 열기</x:v>
+      </x:c>
+      <x:c r="D987" s="3" t="str">
+        <x:v>Open training folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="988" spans="1:4">
+      <x:c r="A988" s="2" t="n">
+        <x:v>3572</x:v>
+      </x:c>
+      <x:c r="B988" s="2" t="str">
+        <x:v>EidolonText492</x:v>
+      </x:c>
+      <x:c r="C988" s="3" t="str">
+        <x:v>같은 그림체나 대상을 담은 이미지를 고르세요. 투명한 부분을 흰색으로 채울 이미지와 검정색으로 채울 이미지를 각각 추가합니다.</x:v>
+      </x:c>
+      <x:c r="D988" s="3" t="str">
+        <x:v>Choose images of the same style or subject. Add images to each list according to whether their transparent areas should be filled with white or black.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="989" spans="1:4">
+      <x:c r="A989" s="2" t="n">
+        <x:v>3573</x:v>
+      </x:c>
+      <x:c r="B989" s="2" t="str">
+        <x:v>EidolonText493</x:v>
+      </x:c>
+      <x:c r="C989" s="3" t="str">
+        <x:v>LoRA를 알아볼 수 있는 이름과 생성할 때 사용할 트리거 단어를 정해주세요. 트리거는 이 LoRA를 선택하면 프롬프트 맨 앞에 자동으로 붙습니다.</x:v>
+      </x:c>
+      <x:c r="D989" s="3" t="str">
+        <x:v>Choose a recognizable LoRA name and a trigger word for generation. Selecting this LoRA automatically adds its trigger to the beginning of the prompt.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="990" spans="1:4">
+      <x:c r="A990" s="2" t="n">
+        <x:v>3574</x:v>
+      </x:c>
+      <x:c r="B990" s="2" t="str">
+        <x:v>EidolonText494</x:v>
+      </x:c>
+      <x:c r="C990" s="3" t="str">
+        <x:v>원본 이미지에 같은 이름의 .txt가 있으면 그 설명을 먼저 사용합니다. 없는 이미지는 공통 설명과 트리거로 설명 파일을 만듭니다.</x:v>
+      </x:c>
+      <x:c r="D990" s="3" t="str">
+        <x:v>An existing .txt file with the same name as an image takes priority. Images without one receive a caption from the common description and trigger.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="991" spans="1:4">
+      <x:c r="A991" s="2" t="n">
+        <x:v>3575</x:v>
+      </x:c>
+      <x:c r="B991" s="2" t="str">
+        <x:v>EidolonText495</x:v>
+      </x:c>
+      <x:c r="C991" s="3" t="str">
+        <x:v>이 이름과 트리거로 학습 폴더를 준비합니다.</x:v>
+      </x:c>
+      <x:c r="D991" s="3" t="str">
+        <x:v>The training folder will use this name and trigger.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="992" spans="1:4">
+      <x:c r="A992" s="2" t="n">
+        <x:v>3576</x:v>
+      </x:c>
+      <x:c r="B992" s="2" t="str">
+        <x:v>EidolonText496</x:v>
+      </x:c>
+      <x:c r="C992" s="3" t="str">
+        <x:v>선택한 이미지를 한 폴더에 모으고 이미지별 .txt 설명을 만듭니다. 저장할 위치를 선택하면 새 하위 폴더를 만들며, 원본 파일은 유지합니다.</x:v>
+      </x:c>
+      <x:c r="D992" s="3" t="str">
+        <x:v>Combine the selected images and create a .txt caption for each one. Choose a save location to create a new subfolder. Source files are preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="993" spans="1:4">
+      <x:c r="A993" s="2" t="n">
+        <x:v>3577</x:v>
+      </x:c>
+      <x:c r="B993" s="2" t="str">
+        <x:v>EidolonText497</x:v>
+      </x:c>
+      <x:c r="C993" s="3" t="str">
+        <x:v>학습 폴더를 먼저 준비해주세요.</x:v>
+      </x:c>
+      <x:c r="D993" s="3" t="str">
+        <x:v>Prepare the training folder first.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="994" spans="1:4">
+      <x:c r="A994" s="2" t="n">
+        <x:v>3578</x:v>
+      </x:c>
+      <x:c r="B994" s="2" t="str">
+        <x:v>EidolonText498</x:v>
+      </x:c>
+      <x:c r="C994" s="3" t="str">
+        <x:v>폴더가 준비됐습니다. 다음 단계에서 설명 파일을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D994" s="3" t="str">
+        <x:v>The folder is ready. Review its caption files in the next step.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="995" spans="1:4">
+      <x:c r="A995" s="2" t="n">
+        <x:v>3579</x:v>
+      </x:c>
+      <x:c r="B995" s="2" t="str">
+        <x:v>EidolonText499</x:v>
+      </x:c>
+      <x:c r="C995" s="3" t="str">
+        <x:v>학습 폴더를 준비하고 있습니다.</x:v>
+      </x:c>
+      <x:c r="D995" s="3" t="str">
+        <x:v>Preparing the training folder.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="996" spans="1:4">
+      <x:c r="A996" s="2" t="n">
+        <x:v>3580</x:v>
+      </x:c>
+      <x:c r="B996" s="2" t="str">
+        <x:v>EidolonText500</x:v>
+      </x:c>
+      <x:c r="C996" s="3" t="str">
+        <x:v>이미지나 이름·트리거·설명을 바꿨습니다. 학습 폴더를 다시 만들어주세요.</x:v>
+      </x:c>
+      <x:c r="D996" s="3" t="str">
+        <x:v>The images, name, trigger, or description have changed. Create a new training folder.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="997" spans="1:4">
+      <x:c r="A997" s="2" t="n">
+        <x:v>3581</x:v>
+      </x:c>
+      <x:c r="B997" s="2" t="str">
+        <x:v>EidolonText501</x:v>
+      </x:c>
+      <x:c r="C997" s="3" t="str">
+        <x:v>설명 파일을 확인했다면 다음 단계로 이동하세요.</x:v>
+      </x:c>
+      <x:c r="D997" s="3" t="str">
+        <x:v>Continue when you have reviewed the caption files.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="998" spans="1:4">
+      <x:c r="A998" s="2" t="n">
+        <x:v>3582</x:v>
+      </x:c>
+      <x:c r="B998" s="2" t="str">
+        <x:v>EidolonText502</x:v>
+      </x:c>
+      <x:c r="C998" s="3" t="str">
+        <x:v>a sword with a golden hilt</x:v>
+      </x:c>
+      <x:c r="D998" s="3" t="str">
+        <x:v>a sword with a golden hilt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="999" spans="1:4">
+      <x:c r="A999" s="2" t="n">
+        <x:v>3583</x:v>
+      </x:c>
+      <x:c r="B999" s="2" t="str">
+        <x:v>EidolonText503</x:v>
+      </x:c>
+      <x:c r="C999" s="3" t="str">
+        <x:v>설명 파일 예시</x:v>
+      </x:c>
+      <x:c r="D999" s="3" t="str">
+        <x:v>Caption example</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1000" spans="1:4">
+      <x:c r="A1000" s="2" t="n">
+        <x:v>3584</x:v>
+      </x:c>
+      <x:c r="B1000" s="2" t="str">
+        <x:v>EidolonText504</x:v>
+      </x:c>
+      <x:c r="C1000" s="3" t="str">
+        <x:v>이미지 선택부터 설명 확인까지, 순서대로 LoRA 하나를 준비합니다.</x:v>
+      </x:c>
+      <x:c r="D1000" s="3" t="str">
+        <x:v>Prepare one LoRA, from selecting images to reviewing captions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1001" spans="1:4">
+      <x:c r="A1001" s="2" t="n">
+        <x:v>3585</x:v>
+      </x:c>
+      <x:c r="B1001" s="2" t="str">
+        <x:v>EidolonText505</x:v>
+      </x:c>
+      <x:c r="C1001" s="3" t="str">
+        <x:v>학습 폴더를 열고 이미지 옆의 .txt를 메모장 등으로 수정한 뒤 저장하세요. 트리거 뒤에 각 이미지의 물체·색·특징을 적으면 됩니다.</x:v>
+      </x:c>
+      <x:c r="D1001" s="3" t="str">
+        <x:v>Open the training folder, edit the .txt file beside each image in a text editor, and save it. Describe the objects, colors, and features after the trigger.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1002" spans="1:4">
+      <x:c r="A1002" s="2" t="n">
+        <x:v>3586</x:v>
+      </x:c>
+      <x:c r="B1002" s="2" t="str">
+        <x:v>EidolonText506</x:v>
+      </x:c>
+      <x:c r="C1002" s="3" t="str">
+        <x:v>저장한 설명으로 학습합니다. 이미지 선택이나 이름·트리거·공통 설명을 바꾸면 새 학습 폴더를 준비해야 합니다.</x:v>
+      </x:c>
+      <x:c r="D1002" s="3" t="str">
+        <x:v>Training uses the saved captions. Changing the selected images, name, trigger, or common description requires preparing a new folder.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1003" spans="1:4">
+      <x:c r="A1003" s="2" t="n">
+        <x:v>3587</x:v>
+      </x:c>
+      <x:c r="B1003" s="2" t="str">
+        <x:v>EidolonText507</x:v>
+      </x:c>
+      <x:c r="C1003" s="3" t="str">
+        <x:v>생성에 사용할 모델과 같은 계열의 모델을 선택하세요.</x:v>
+      </x:c>
+      <x:c r="D1003" s="3" t="str">
+        <x:v>Select a model from the same family as the model you will use for generation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1004" spans="1:4">
+      <x:c r="A1004" s="2" t="n">
+        <x:v>3588</x:v>
+      </x:c>
+      <x:c r="B1004" s="2" t="str">
+        <x:v>EidolonText508</x:v>
+      </x:c>
+      <x:c r="C1004" s="3" t="str">
+        <x:v>이어 학습 (선택)</x:v>
+      </x:c>
+      <x:c r="D1004" s="3" t="str">
+        <x:v>Continue training (optional)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1005" spans="1:4">
+      <x:c r="A1005" s="2" t="n">
+        <x:v>3589</x:v>
+      </x:c>
+      <x:c r="B1005" s="2" t="str">
+        <x:v>EidolonText509</x:v>
+      </x:c>
+      <x:c r="C1005" s="3" t="str">
+        <x:v>프롬프트 프리셋</x:v>
+      </x:c>
+      <x:c r="D1005" s="3" t="str">
+        <x:v>Prompt presets</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1006" spans="1:4">
+      <x:c r="A1006" s="2" t="n">
+        <x:v>3590</x:v>
+      </x:c>
+      <x:c r="B1006" s="2" t="str">
+        <x:v>EidolonText510</x:v>
+      </x:c>
+      <x:c r="C1006" s="3" t="str">
+        <x:v>저장한 프리셋 선택</x:v>
+      </x:c>
+      <x:c r="D1006" s="3" t="str">
+        <x:v>Select a saved preset</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1007" spans="1:4">
+      <x:c r="A1007" s="2" t="n">
+        <x:v>3591</x:v>
+      </x:c>
+      <x:c r="B1007" s="2" t="str">
+        <x:v>EidolonText511</x:v>
+      </x:c>
+      <x:c r="C1007" s="3" t="str">
+        <x:v>프리셋을 선택하면 생성 지침과 제외할 요소를 불러옵니다. 설정을 저장한 뒤 생성·편집에 적용됩니다.</x:v>
+      </x:c>
+      <x:c r="D1007" s="3" t="str">
+        <x:v>Selecting a preset loads its generation instructions and exclusions. Save settings to apply them to generation and editing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1008" spans="1:4">
+      <x:c r="A1008" s="2" t="n">
+        <x:v>3592</x:v>
+      </x:c>
+      <x:c r="B1008" s="2" t="str">
+        <x:v>EidolonText512</x:v>
+      </x:c>
+      <x:c r="C1008" s="3" t="str">
+        <x:v>프리셋 이름</x:v>
+      </x:c>
+      <x:c r="D1008" s="3" t="str">
+        <x:v>Preset name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1009" spans="1:4">
+      <x:c r="A1009" s="2" t="n">
+        <x:v>3593</x:v>
+      </x:c>
+      <x:c r="B1009" s="2" t="str">
+        <x:v>EidolonText513</x:v>
+      </x:c>
+      <x:c r="C1009" s="3" t="str">
+        <x:v>예: 게임 아이콘, 수채화</x:v>
+      </x:c>
+      <x:c r="D1009" s="3" t="str">
+        <x:v>Example: game icons, watercolor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1010" spans="1:4">
+      <x:c r="A1010" s="2" t="n">
+        <x:v>3594</x:v>
+      </x:c>
+      <x:c r="B1010" s="2" t="str">
+        <x:v>EidolonText514</x:v>
+      </x:c>
+      <x:c r="C1010" s="3" t="str">
+        <x:v>새 프리셋 추가</x:v>
+      </x:c>
+      <x:c r="D1010" s="3" t="str">
+        <x:v>Add new preset</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1011" spans="1:4">
+      <x:c r="A1011" s="2" t="n">
+        <x:v>3595</x:v>
+      </x:c>
+      <x:c r="B1011" s="2" t="str">
+        <x:v>EidolonText515</x:v>
+      </x:c>
+      <x:c r="C1011" s="3" t="str">
+        <x:v>선택 프리셋 수정</x:v>
+      </x:c>
+      <x:c r="D1011" s="3" t="str">
+        <x:v>Update selected preset</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1012" spans="1:4">
+      <x:c r="A1012" s="2" t="n">
+        <x:v>3596</x:v>
+      </x:c>
+      <x:c r="B1012" s="2" t="str">
+        <x:v>EidolonText516</x:v>
+      </x:c>
+      <x:c r="C1012" s="3" t="str">
+        <x:v>프리셋 삭제</x:v>
+      </x:c>
+      <x:c r="D1012" s="3" t="str">
+        <x:v>Delete preset</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1013" spans="1:4">
+      <x:c r="A1013" s="2" t="n">
+        <x:v>3599</x:v>
+      </x:c>
+      <x:c r="B1013" s="2" t="str">
+        <x:v>EidolonText519</x:v>
+      </x:c>
+      <x:c r="C1013" s="3" t="str">
+        <x:v>현재 지침에 이름을 붙이면 새 프리셋으로 추가할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D1013" s="3" t="str">
+        <x:v>Name the current instructions to add them as a new preset.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1014" spans="1:4">
+      <x:c r="A1014" s="2" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="B1014" s="2" t="str">
+        <x:v>EidolonText520</x:v>
+      </x:c>
+      <x:c r="C1014" s="3" t="str">
+        <x:v>같은 이름의 프리셋이 있습니다. 다른 이름을 입력해주세요.</x:v>
+      </x:c>
+      <x:c r="D1014" s="3" t="str">
+        <x:v>A preset with this name already exists. Enter a different name.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1015" spans="1:4">
+      <x:c r="A1015" s="2" t="n">
+        <x:v>3601</x:v>
+      </x:c>
+      <x:c r="B1015" s="2" t="str">
+        <x:v>EidolonText521</x:v>
+      </x:c>
+      <x:c r="C1015" s="3" t="str">
+        <x:v>선택한 프리셋과 내용이 다릅니다. 선택 프리셋을 수정하거나 다른 이름으로 추가하세요.</x:v>
+      </x:c>
+      <x:c r="D1015" s="3" t="str">
+        <x:v>The selected preset has been edited. Update it or add a new preset with a different name.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1016" spans="1:4">
+      <x:c r="A1016" s="2" t="n">
+        <x:v>3602</x:v>
+      </x:c>
+      <x:c r="B1016" s="2" t="str">
+        <x:v>EidolonText522</x:v>
+      </x:c>
+      <x:c r="C1016" s="3" t="str">
+        <x:v>프리셋 목록과 현재 지침은 설정 저장을 누르면 함께 저장됩니다.</x:v>
+      </x:c>
+      <x:c r="D1016" s="3" t="str">
+        <x:v>Save settings to store both the preset list and the current instructions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1017" spans="1:4">
+      <x:c r="A1017" s="2" t="n">
+        <x:v>3605</x:v>
+      </x:c>
+      <x:c r="B1017" s="2" t="str">
+        <x:v>EidolonText525</x:v>
+      </x:c>
+      <x:c r="C1017" s="3" t="str">
+        <x:v>프롬프트 프리셋 설정에 누락되거나 중복된 정보가 있습니다.</x:v>
+      </x:c>
+      <x:c r="D1017" s="3" t="str">
+        <x:v>Prompt preset settings contain missing or duplicate information.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rde2c5120e3614fd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Define" sheetId="2" r:id="R6a1d7bcc80ba4528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R7a3f3334b94f4df9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Define" sheetId="2" r:id="Rb6e07b3774574c7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13234,10 +13234,10 @@
         <x:v>EidolonText185</x:v>
       </x:c>
       <x:c r="C682" s="3" t="str">
-        <x:v>1. 엔진과 모델 준비</x:v>
+        <x:v>1. 생성 환경 선택</x:v>
       </x:c>
       <x:c r="D682" s="3" t="str">
-        <x:v>1. Prepare the engine and model</x:v>
+        <x:v>1. Choose a generation environment</x:v>
       </x:c>
     </x:row>
     <x:row r="683" ht="92.4000015258789" hidden="0" customHeight="1">
@@ -13248,10 +13248,10 @@
         <x:v>EidolonText186</x:v>
       </x:c>
       <x:c r="C683" s="3" t="str">
-        <x:v>엔진 탭에서 설치 폴더를 선택하고 설치·복구를 실행합니다. NVIDIA GPU가 있으면 기본 옵션을 유지하고, GPU가 없으면 CPU 환경을 선택하세요. CPU는 이미지 생성만 지원합니다.</x:v>
+        <x:v>생성 환경의 생성 방식·지침에서 ComfyUI 또는 Codex와 공통 생성 지침·제외할 요소·프리셋을 저장합니다. 이미지 저장 폴더·언어·테마는 설정에서 별도로 저장합니다.</x:v>
       </x:c>
       <x:c r="D683" s="3" t="str">
-        <x:v>In Engine, choose an installation folder and run install or repair. Keep the default options for an NVIDIA GPU, or select CPU if you have no GPU. CPU supports image generation only.</x:v>
+        <x:v>Save ComfyUI or Codex, shared guidelines, excluded elements and presets in Generation environment &gt; Generation method and guidelines. Save the output folder, language and theme separately in Settings.</x:v>
       </x:c>
     </x:row>
     <x:row r="684" ht="92.4000015258789" hidden="0" customHeight="1">
@@ -13262,10 +13262,10 @@
         <x:v>EidolonText187</x:v>
       </x:c>
       <x:c r="C684" s="3" t="str">
-        <x:v>기본 SDXL Base 1.0 모델 다운로드를 선택하거나 엔진의 모델·LoRA 탭에서 .safetensors 파일을 가져옵니다. 설치된 모델만 표시하며 SDXL을 기본으로 선택합니다. 최초 설치에는 인터넷 연결과 여러 GB의 여유 공간이 필요합니다.</x:v>
+        <x:v>ComfyUI는 엔진 설치에서 실행 환경을 준비하고 모델·LoRA에서 기반 모델을 설치하거나 모델 폴더에 넣고 새로고침합니다. NVIDIA GPU가 없으면 CPU 환경으로 이미지 생성만 지원합니다.</x:v>
       </x:c>
       <x:c r="D684" s="3" t="str">
-        <x:v>Download the default SDXL Base 1.0 model, or import a .safetensors file in Engine &gt; Models and LoRAs. Only installed models are shown, with SDXL selected by default. Initial setup requires internet access and several GB of free space.</x:v>
+        <x:v>For ComfyUI, prepare the runtime in Engine setup, then install a base model or place it in Model folder and refresh. CPU supports image generation only.</x:v>
       </x:c>
     </x:row>
     <x:row r="685" ht="16.5" hidden="0" customHeight="1">
@@ -13290,10 +13290,10 @@
         <x:v>EidolonText189</x:v>
       </x:c>
       <x:c r="C686" s="3" t="str">
-        <x:v>생성 탭에서 만들고 싶은 장면을 입력하고 대기열에 추가를 누릅니다. 설치된 모델만 선택 목록에 표시합니다. 배경 투명하게를 체크하면 최종 이미지를 투명 PNG로 저장합니다. 실행 중에도 다음 요청을 추가할 수 있습니다.</x:v>
+        <x:v>설명을 입력하고 생성 요청을 추가합니다. ComfyUI에서는 모델과 선택할 LoRA를 지정합니다. Codex에서는 저장된 실행 모델을 사용합니다. 배경 투명하게를 켜면 투명 PNG를 요청하며 실행 중에도 다음 요청을 추가할 수 있습니다.</x:v>
       </x:c>
       <x:c r="D686" s="3" t="str">
-        <x:v>In Generate, describe your scene and press Add to queue. Only installed models appear in the selector. Enable Transparent background to save the final image as a transparent PNG. You can add more requests while a job is running.</x:v>
+        <x:v>Describe the image and submit a request. ComfyUI uses your selected model and LoRAs; Codex uses the saved agent model. Enable Transparent background for a transparent PNG. More requests can be queued while running.</x:v>
       </x:c>
     </x:row>
     <x:row r="687" ht="105.5999984741211" hidden="0" customHeight="1">
@@ -13304,10 +13304,10 @@
         <x:v>EidolonText190</x:v>
       </x:c>
       <x:c r="C687" s="3" t="str">
-        <x:v>설정의 기본 생성 지침에는 반복할 스타일·품질 조건을, 제외할 요소에는 피하고 싶은 내용을 입력하세요. 저장한 내용은 생성 화면에도 표시되고 이후 생성에 적용됩니다. 생성 결과에서 프롬프트를 다시 사용할 수 있습니다.</x:v>
+        <x:v>생성 환경에서 공통 생성 지침과 제외할 요소를 편집하고 프리셋을 선택하거나 추가·수정합니다. 생성 환경 저장을 누르면 이후 생성·편집 요청에 적용하며 대기 중인 요청은 기존 설정을 유지합니다.</x:v>
       </x:c>
       <x:c r="D687" s="3" t="str">
-        <x:v>Use default generation instructions in Settings for recurring styles and quality preferences, and Elements to avoid for unwanted content. Saved settings are shown in Generate and apply to later generations. Reuse a prompt from Results.</x:v>
+        <x:v>Edit shared guidelines and exclusions, and select, add or update presets in Generation environment. Save the generation environment to apply them to new generation and editing requests. Queued requests retain their settings.</x:v>
       </x:c>
     </x:row>
     <x:row r="688" ht="16.5" hidden="0" customHeight="1">
@@ -13332,10 +13332,10 @@
         <x:v>EidolonText192</x:v>
       </x:c>
       <x:c r="C689" s="3" t="str">
-        <x:v>이미지 선택 → 이름과 트리거 → 학습 폴더 준비 → 설명 확인 → 학습 순서로 진행합니다. 흰색·검정색 목록에 고른 이미지는 함께 학습해 LoRA 하나를 만듭니다. 학습 폴더의 .txt 설명을 수정하고 저장한 뒤 모델과 단계 수를 정해 학습하기를 누르세요.</x:v>
+        <x:v>이미지 선택 → 이름·트리거 → 학습 설정 순서로 진행합니다. 첫 이미지의 설명을 자동으로 채우고 이름·트리거는 기본값을 제공합니다. 확인하거나 수정한 뒤 학습하세요. 학습 폴더는 엔진 경로 아래 작업별로 자동 준비하며 엔진 설치에서 열거나 비울 수 있습니다.</x:v>
       </x:c>
       <x:c r="D689" s="3" t="str">
-        <x:v>Follow the steps: select images, set a name and trigger, prepare a training folder, review captions, and train. Images from the white and black lists are combined into one LoRA. Edit and save the caption .txt files, choose the model and step count, then select Train.</x:v>
+        <x:v>Select images, review the name and trigger, then configure training. The first image fills the description; a name and trigger are provided. Review or edit them before training. Datasets are prepared per job under the engine path and can be opened or cleared in Engine setup.</x:v>
       </x:c>
     </x:row>
     <x:row r="690" ht="105.5999984741211" hidden="0" customHeight="1">
@@ -13346,10 +13346,10 @@
         <x:v>EidolonText193</x:v>
       </x:c>
       <x:c r="C690" s="3" t="str">
-        <x:v>학습에는 NVIDIA GPU가 필요합니다. 트리거는 공백과 쉼표 없는 단어를 사용하세요. 완료된 LoRA는 생성 화면에서 선택할 수 있으며, 트리거가 프롬프트 맨 앞에 자동으로 적용됩니다. 기반 모델과 같은 계열의 LoRA만 표시합니다.</x:v>
+        <x:v>LoRA 학습에는 로컬 ComfyUI 환경·기반 모델과 NVIDIA GPU가 필요합니다. 생성에서 호환 LoRA를 선택하면 저장된 트리거가 자동 적용됩니다. Codex 생성에는 LoRA를 적용하지 않습니다.</x:v>
       </x:c>
       <x:c r="D690" s="3" t="str">
-        <x:v>Training requires an NVIDIA GPU. Use a trigger without spaces or commas. Completed LoRAs are available in the generation tab, where their triggers are added to the beginning of the prompt. Only LoRAs compatible with the selected model family are shown.</x:v>
+        <x:v>LoRA training requires a local ComfyUI runtime, base model and NVIDIA GPU. Selecting a compatible LoRA applies its saved trigger. LoRAs do not apply to Codex generation.</x:v>
       </x:c>
     </x:row>
     <x:row r="691" ht="16.5" hidden="0" customHeight="1">
@@ -13872,10 +13872,10 @@
         <x:v>EidolonText230</x:v>
       </x:c>
       <x:c r="C727" s="3" t="str">
-        <x:v>엔진 준비가 끝났습니다. 모델을 한 개 이상 설치하거나 가져오세요.</x:v>
+        <x:v>엔진 준비가 끝났습니다. 모델을 설치하거나 모델 폴더에 넣고 새로고침하세요.</x:v>
       </x:c>
       <x:c r="D727" s="3" t="str">
-        <x:v>The engine is ready. Install or import at least one model.</x:v>
+        <x:v>The engine is ready. Install a model or place one in Model folder and refresh.</x:v>
       </x:c>
     </x:row>
     <x:row r="728" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -14642,10 +14642,10 @@
         <x:v>EidolonText285</x:v>
       </x:c>
       <x:c r="C782" s="3" t="str">
-        <x:v>엔진 탭에는 ComfyUI 서버 주소만 입력합니다. 실행 중인 서버가 있으면 연결하고 로컬 주소에 서버가 없으면 설치한 엔진을 실행합니다. 앱이 시작한 서버는 종료 시 함께 종료하며 기존 서버는 유지합니다.</x:v>
+        <x:v>ComfyUI 서버 주소는 엔진 설치에서 입력합니다. 기존 서버에 연결하거나 로컬 설치 엔진을 실행합니다. Codex는 ComfyUI 설치와 서버 연결 없이 설치된 Codex의 로그인으로 사용합니다.</x:v>
       </x:c>
       <x:c r="D782" s="3" t="str">
-        <x:v>Enter the ComfyUI server address in Engine. Connect to an existing server, or start the installed engine if no server is running at a local address. Servers started by this app stop when it closes; existing servers keep running.</x:v>
+        <x:v>Set the ComfyUI server address in Engine setup. Connect to an existing server or start the installed local engine. Codex uses its own sign-in without ComfyUI setup.</x:v>
       </x:c>
     </x:row>
     <x:row r="783" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -15447,1662 +15447,1662 @@
       </x:c>
     </x:row>
     <x:row r="840">
-      <x:c r="A840" t="n" s="2">
+      <x:c r="A840" s="2" t="n">
         <x:v>3423</x:v>
       </x:c>
-      <x:c r="B840" t="str" s="2">
+      <x:c r="B840" s="2" t="str">
         <x:v>EidolonText343</x:v>
       </x:c>
-      <x:c r="C840" t="str" s="3">
+      <x:c r="C840" s="3" t="str">
         <x:v>사용할 모델을 골라 설치하세요. 삭제하면 모델 파일도 제거됩니다.</x:v>
       </x:c>
-      <x:c r="D840" t="str" s="3">
+      <x:c r="D840" s="3" t="str">
         <x:v>Choose a model to install. Deleting also removes its file.</x:v>
       </x:c>
     </x:row>
     <x:row r="841">
-      <x:c r="A841" t="n" s="2">
+      <x:c r="A841" s="2" t="n">
         <x:v>3424</x:v>
       </x:c>
-      <x:c r="B841" t="str" s="2">
+      <x:c r="B841" s="2" t="str">
         <x:v>EidolonText344</x:v>
       </x:c>
-      <x:c r="C841" t="str" s="3">
+      <x:c r="C841" s="3" t="str">
         <x:v>새 모델 설치</x:v>
       </x:c>
-      <x:c r="D841" t="str" s="3">
+      <x:c r="D841" s="3" t="str">
         <x:v>Install a new model</x:v>
       </x:c>
     </x:row>
     <x:row r="842">
-      <x:c r="A842" t="n" s="2">
+      <x:c r="A842" s="2" t="n">
         <x:v>3425</x:v>
       </x:c>
-      <x:c r="B842" t="str" s="2">
+      <x:c r="B842" s="2" t="str">
         <x:v>EidolonText345</x:v>
       </x:c>
-      <x:c r="C842" t="str" s="3">
+      <x:c r="C842" s="3" t="str">
         <x:v>다양한 이미지 생성과 LoRA 학습에 사용하는 기본 모델</x:v>
       </x:c>
-      <x:c r="D842" t="str" s="3">
+      <x:c r="D842" s="3" t="str">
         <x:v>Base model for general image generation and LoRA training</x:v>
       </x:c>
     </x:row>
     <x:row r="843">
-      <x:c r="A843" t="n" s="2">
+      <x:c r="A843" s="2" t="n">
         <x:v>3426</x:v>
       </x:c>
-      <x:c r="B843" t="str" s="2">
+      <x:c r="B843" s="2" t="str">
         <x:v>EidolonText346</x:v>
       </x:c>
-      <x:c r="C843" t="str" s="3">
+      <x:c r="C843" s="3" t="str">
         <x:v>SD 1.5 기반 생성과 기존 LoRA 사용을 위한 기본 모델</x:v>
       </x:c>
-      <x:c r="D843" t="str" s="3">
+      <x:c r="D843" s="3" t="str">
         <x:v>Base model for SD 1.5 generation and compatible LoRAs</x:v>
       </x:c>
     </x:row>
     <x:row r="844">
-      <x:c r="A844" t="n" s="2">
+      <x:c r="A844" s="2" t="n">
         <x:v>3427</x:v>
       </x:c>
-      <x:c r="B844" t="str" s="2">
+      <x:c r="B844" s="2" t="str">
         <x:v>EidolonText347</x:v>
       </x:c>
-      <x:c r="C844" t="str" s="3">
+      <x:c r="C844" s="3" t="str">
         <x:v>인물·사진 스타일의 실사 이미지 생성에 맞춘 모델</x:v>
       </x:c>
-      <x:c r="D844" t="str" s="3">
+      <x:c r="D844" s="3" t="str">
         <x:v>Model for photorealistic portraits and photographic images</x:v>
       </x:c>
     </x:row>
     <x:row r="845">
-      <x:c r="A845" t="n" s="2">
+      <x:c r="A845" s="2" t="n">
         <x:v>3428</x:v>
       </x:c>
-      <x:c r="B845" t="str" s="2">
+      <x:c r="B845" s="2" t="str">
         <x:v>EidolonText348</x:v>
       </x:c>
-      <x:c r="C845" t="str" s="3">
+      <x:c r="C845" s="3" t="str">
         <x:v>사용 가능</x:v>
       </x:c>
-      <x:c r="D845" t="str" s="3">
+      <x:c r="D845" s="3" t="str">
         <x:v>Ready to use</x:v>
       </x:c>
     </x:row>
     <x:row r="846">
-      <x:c r="A846" t="n" s="2">
+      <x:c r="A846" s="2" t="n">
         <x:v>3429</x:v>
       </x:c>
-      <x:c r="B846" t="str" s="2">
+      <x:c r="B846" s="2" t="str">
         <x:v>EidolonText349</x:v>
       </x:c>
-      <x:c r="C846" t="str" s="3">
+      <x:c r="C846" s="3" t="str">
         <x:v>{0} 모델 준비 완료</x:v>
       </x:c>
-      <x:c r="D846" t="str" s="3">
+      <x:c r="D846" s="3" t="str">
         <x:v>{0} model ready</x:v>
       </x:c>
     </x:row>
     <x:row r="847">
-      <x:c r="A847" t="n" s="2">
+      <x:c r="A847" s="2" t="n">
         <x:v>3430</x:v>
       </x:c>
-      <x:c r="B847" t="str" s="2">
+      <x:c r="B847" s="2" t="str">
         <x:v>EidolonText350</x:v>
       </x:c>
-      <x:c r="C847" t="str" s="3">
+      <x:c r="C847" s="3" t="str">
         <x:v>일러스트·애니메이션 스타일의 SDXL 기반 모델</x:v>
       </x:c>
-      <x:c r="D847" t="str" s="3">
+      <x:c r="D847" s="3" t="str">
         <x:v>SDXL-based model for illustration and anime styles</x:v>
       </x:c>
     </x:row>
     <x:row r="848">
-      <x:c r="A848" t="n" s="2">
+      <x:c r="A848" s="2" t="n">
         <x:v>3431</x:v>
       </x:c>
-      <x:c r="B848" t="str" s="2">
+      <x:c r="B848" s="2" t="str">
         <x:v>EidolonText351</x:v>
       </x:c>
-      <x:c r="C848" t="str" s="3">
+      <x:c r="C848" s="3" t="str">
         <x:v>설치</x:v>
       </x:c>
-      <x:c r="D848" t="str" s="3">
+      <x:c r="D848" s="3" t="str">
         <x:v>Install</x:v>
       </x:c>
     </x:row>
     <x:row r="849">
-      <x:c r="A849" t="n" s="2">
+      <x:c r="A849" s="2" t="n">
         <x:v>3432</x:v>
       </x:c>
-      <x:c r="B849" t="str" s="2">
+      <x:c r="B849" s="2" t="str">
         <x:v>EidolonText352</x:v>
       </x:c>
-      <x:c r="C849" t="str" s="3">
+      <x:c r="C849" s="3" t="str">
         <x:v>모델 설치와 삭제는 로컬 엔진에서 사용할 수 있습니다.</x:v>
       </x:c>
-      <x:c r="D849" t="str" s="3">
+      <x:c r="D849" s="3" t="str">
         <x:v>Model installation and deletion are available for the local engine.</x:v>
       </x:c>
     </x:row>
     <x:row r="850">
-      <x:c r="A850" t="n" s="2">
+      <x:c r="A850" s="2" t="n">
         <x:v>3433</x:v>
       </x:c>
-      <x:c r="B850" t="str" s="2">
+      <x:c r="B850" s="2" t="str">
         <x:v>EidolonText353</x:v>
       </x:c>
-      <x:c r="C850" t="str" s="3">
+      <x:c r="C850" s="3" t="str">
         <x:v>먼저 선택한 경로에 엔진을 설치하세요. 완료 후 각 모델의 설치 버튼을 사용할 수 있습니다.</x:v>
       </x:c>
-      <x:c r="D850" t="str" s="3">
+      <x:c r="D850" s="3" t="str">
         <x:v>Install the engine at the selected path first. Then use the install button for each model.</x:v>
       </x:c>
     </x:row>
     <x:row r="851">
-      <x:c r="A851" t="n" s="2">
+      <x:c r="A851" s="2" t="n">
         <x:v>3434</x:v>
       </x:c>
-      <x:c r="B851" t="str" s="2">
+      <x:c r="B851" s="2" t="str">
         <x:v>EidolonText354</x:v>
       </x:c>
-      <x:c r="C851" t="str" s="3">
+      <x:c r="C851" s="3" t="str">
         <x:v>설치 중…</x:v>
       </x:c>
-      <x:c r="D851" t="str" s="3">
+      <x:c r="D851" s="3" t="str">
         <x:v>Installing…</x:v>
       </x:c>
     </x:row>
     <x:row r="852">
-      <x:c r="A852" t="n" s="2">
+      <x:c r="A852" s="2" t="n">
         <x:v>3435</x:v>
       </x:c>
-      <x:c r="B852" t="str" s="2">
+      <x:c r="B852" s="2" t="str">
         <x:v>EidolonText355</x:v>
       </x:c>
-      <x:c r="C852" t="str" s="3">
+      <x:c r="C852" s="3" t="str">
         <x:v>삭제</x:v>
       </x:c>
-      <x:c r="D852" t="str" s="3">
+      <x:c r="D852" s="3" t="str">
         <x:v>Delete</x:v>
       </x:c>
     </x:row>
     <x:row r="853">
-      <x:c r="A853" t="n" s="2">
+      <x:c r="A853" s="2" t="n">
         <x:v>3436</x:v>
       </x:c>
-      <x:c r="B853" t="str" s="2">
+      <x:c r="B853" s="2" t="str">
         <x:v>EidolonText356</x:v>
       </x:c>
-      <x:c r="C853" t="str" s="3">
+      <x:c r="C853" s="3" t="str">
         <x:v>모델 삭제</x:v>
       </x:c>
-      <x:c r="D853" t="str" s="3">
+      <x:c r="D853" s="3" t="str">
         <x:v>Delete model</x:v>
       </x:c>
     </x:row>
     <x:row r="854">
-      <x:c r="A854" t="n" s="2">
+      <x:c r="A854" s="2" t="n">
         <x:v>3437</x:v>
       </x:c>
-      <x:c r="B854" t="str" s="2">
+      <x:c r="B854" s="2" t="str">
         <x:v>EidolonText357</x:v>
       </x:c>
-      <x:c r="C854" t="str" s="3">
+      <x:c r="C854" s="3" t="str">
         <x:v>{0} 모델 파일을 삭제할까요?
 {1}
 다시 사용하려면 모델을 다시 다운로드해야 합니다.</x:v>
       </x:c>
-      <x:c r="D854" t="str" s="3">
+      <x:c r="D854" s="3" t="str">
         <x:v>Delete the {0} model file?
 {1}
 You will need to download the model again to use it.</x:v>
       </x:c>
     </x:row>
     <x:row r="855">
-      <x:c r="A855" t="n" s="2">
+      <x:c r="A855" s="2" t="n">
         <x:v>3438</x:v>
       </x:c>
-      <x:c r="B855" t="str" s="2">
+      <x:c r="B855" s="2" t="str">
         <x:v>EidolonText358</x:v>
       </x:c>
-      <x:c r="C855" t="str" s="3">
+      <x:c r="C855" s="3" t="str">
         <x:v>{0} 모델 파일을 삭제했습니다.</x:v>
       </x:c>
-      <x:c r="D855" t="str" s="3">
+      <x:c r="D855" s="3" t="str">
         <x:v>Deleted the {0} model file.</x:v>
       </x:c>
     </x:row>
     <x:row r="856">
-      <x:c r="A856" t="n" s="2">
+      <x:c r="A856" s="2" t="n">
         <x:v>3439</x:v>
       </x:c>
-      <x:c r="B856" t="str" s="2">
+      <x:c r="B856" s="2" t="str">
         <x:v>EidolonText359</x:v>
       </x:c>
-      <x:c r="C856" t="str" s="3">
+      <x:c r="C856" s="3" t="str">
         <x:v>모델·체크포인트</x:v>
       </x:c>
-      <x:c r="D856" t="str" s="3">
+      <x:c r="D856" s="3" t="str">
         <x:v>Model and checkpoint</x:v>
       </x:c>
     </x:row>
     <x:row r="857">
-      <x:c r="A857" t="n" s="2">
+      <x:c r="A857" s="2" t="n">
         <x:v>3440</x:v>
       </x:c>
-      <x:c r="B857" t="str" s="2">
+      <x:c r="B857" s="2" t="str">
         <x:v>EidolonText360</x:v>
       </x:c>
-      <x:c r="C857" t="str" s="3">
+      <x:c r="C857" s="3" t="str">
         <x:v>설치한 모델과 체크포인트 폴더에 직접 넣은 .safetensors 모델을 선택합니다. 파일을 추가했다면 새로고침하세요.</x:v>
       </x:c>
-      <x:c r="D857" t="str" s="3">
+      <x:c r="D857" s="3" t="str">
         <x:v>Choose an installed model or a .safetensors model placed in the checkpoint folder. Refresh after adding files.</x:v>
       </x:c>
     </x:row>
     <x:row r="858">
-      <x:c r="A858" t="n" s="2">
+      <x:c r="A858" s="2" t="n">
         <x:v>3441</x:v>
       </x:c>
-      <x:c r="B858" t="str" s="2">
+      <x:c r="B858" s="2" t="str">
         <x:v>EidolonText361</x:v>
       </x:c>
-      <x:c r="C858" t="str" s="3">
+      <x:c r="C858" s="3" t="str">
         <x:v>선택할 모델이 없습니다. 엔진 탭에서 모델을 설치하거나 가져온 뒤 새로고침하세요.</x:v>
       </x:c>
-      <x:c r="D858" t="str" s="3">
+      <x:c r="D858" s="3" t="str">
         <x:v>No models are available. Install or import a model in the Engine tab, then refresh.</x:v>
       </x:c>
     </x:row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="859" spans="1:4">
-      <c r="A859" s="2" t="n">
-        <v>3442</v>
-      </c>
-      <c r="B859" s="2" t="str">
-        <v>EidolonText362</v>
-      </c>
-      <c r="C859" s="3" t="str">
-        <v>생성 지침</v>
-      </c>
-      <c r="D859" s="3" t="str">
-        <v>Generation instructions</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="860" spans="1:4">
-      <c r="A860" s="2" t="n">
-        <v>3443</v>
-      </c>
-      <c r="B860" s="2" t="str">
-        <v>EidolonText363</v>
-      </c>
-      <c r="C860" s="3" t="str">
-        <v>여기서 바꾼 지침은 이번 요청에만 적용됩니다. 설정의 기본값은 유지됩니다.</v>
-      </c>
-      <c r="D860" s="3" t="str">
-        <v>Changes here apply to this request. Your saved defaults stay the same.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="861" spans="1:4">
-      <c r="A861" s="2" t="n">
-        <v>3444</v>
-      </c>
-      <c r="B861" s="2" t="str">
-        <v>EidolonText364</v>
-      </c>
-      <c r="C861" s="3" t="str">
-        <v>기본값 불러오기</v>
-      </c>
-      <c r="D861" s="3" t="str">
-        <v>Load defaults</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="862" spans="1:4">
-      <c r="A862" s="2" t="n">
-        <v>3445</v>
-      </c>
-      <c r="B862" s="2" t="str">
-        <v>EidolonText365</v>
-      </c>
-      <c r="C862" s="3" t="str">
-        <v>생성 정보</v>
-      </c>
-      <c r="D862" s="3" t="str">
-        <v>Generation details</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="863" spans="1:4">
-      <c r="A863" s="2" t="n">
-        <v>3446</v>
-      </c>
-      <c r="B863" s="2" t="str">
-        <v>EidolonText366</v>
-      </c>
-      <c r="C863" s="3" t="str">
-        <v>상태</v>
-      </c>
-      <c r="D863" s="3" t="str">
-        <v>Status</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="864" spans="1:4">
-      <c r="A864" s="2" t="n">
-        <v>3447</v>
-      </c>
-      <c r="B864" s="2" t="str">
-        <v>EidolonText367</v>
-      </c>
-      <c r="C864" s="3" t="str">
-        <v>생성 시각</v>
-      </c>
-      <c r="D864" s="3" t="str">
-        <v>Created</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="865" spans="1:4">
-      <c r="A865" s="2" t="n">
-        <v>3448</v>
-      </c>
-      <c r="B865" s="2" t="str">
-        <v>EidolonText368</v>
-      </c>
-      <c r="C865" s="3" t="str">
-        <v>해상도</v>
-      </c>
-      <c r="D865" s="3" t="str">
-        <v>Resolution</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="866" spans="1:4">
-      <c r="A866" s="2" t="n">
-        <v>3449</v>
-      </c>
-      <c r="B866" s="2" t="str">
-        <v>EidolonText369</v>
-      </c>
-      <c r="C866" s="3" t="str">
-        <v>시드</v>
-      </c>
-      <c r="D866" s="3" t="str">
-        <v>Seed</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="867" spans="1:4">
-      <c r="A867" s="2" t="n">
-        <v>3450</v>
-      </c>
-      <c r="B867" s="2" t="str">
-        <v>EidolonText370</v>
-      </c>
-      <c r="C867" s="3" t="str">
-        <v>이 결과의 모델 또는 LoRA 일부가 현재 목록에 없습니다. 생성 전에 선택을 확인해 주세요.</v>
-      </c>
-      <c r="D867" s="3" t="str">
-        <v>Some models or LoRAs used for this result are unavailable. Check your selection before generating.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="868" spans="1:4">
-      <c r="A868" s="2" t="n">
-        <v>3451</v>
-      </c>
-      <c r="B868" s="2" t="str">
-        <v>EidolonText371</v>
-      </c>
-      <c r="C868" s="3" t="str">
-        <v>이번 요청의 지침</v>
-      </c>
-      <c r="D868" s="3" t="str">
-        <v>Instructions for this request</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="869" spans="1:4">
-      <c r="A869" s="2" t="n">
-        <v>3452</v>
-      </c>
-      <c r="B869" s="2" t="str">
-        <v>EidolonText372</v>
-      </c>
-      <c r="C869" s="3" t="str">
-        <v>결과 갤러리</v>
-      </c>
-      <c r="D869" s="3" t="str">
-        <v>Results gallery</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="870" spans="1:4">
-      <c r="A870" s="2" t="n">
-        <v>3453</v>
-      </c>
-      <c r="B870" s="2" t="str">
-        <v>EidolonText373</v>
-      </c>
-      <c r="C870" s="3" t="str">
-        <v>클릭하면 오른쪽에 이미지·프롬프트 표시 · Ctrl+클릭으로 다중 선택 · Shift+클릭으로 범위 선택</v>
-      </c>
-      <c r="D870" s="3" t="str">
-        <v>Click to preview on the right · Ctrl+click for multiple selection · Shift+click to select a range</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="871" spans="1:4">
-      <c r="A871" s="2" t="n">
-        <v>3454</v>
-      </c>
-      <c r="B871" s="2" t="str">
-        <v>EidolonText374</v>
-      </c>
-      <c r="C871" s="3" t="str">
-        <v>이전</v>
-      </c>
-      <c r="D871" s="3" t="str">
-        <v>Previous</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="872" spans="1:4">
-      <c r="A872" s="2" t="n">
-        <v>3455</v>
-      </c>
-      <c r="B872" s="2" t="str">
-        <v>EidolonText375</v>
-      </c>
-      <c r="C872" s="3" t="str">
-        <v>다음</v>
-      </c>
-      <c r="D872" s="3" t="str">
-        <v>Next</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="873" spans="1:4">
-      <c r="A873" s="2" t="n">
-        <v>3456</v>
-      </c>
-      <c r="B873" s="2" t="str">
-        <v>EidolonText376</v>
-      </c>
-      <c r="C873" s="3" t="str">
-        <v>{0} / {1} 페이지</v>
-      </c>
-      <c r="D873" s="3" t="str">
-        <v>Page {0} of {1}</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="874" spans="1:4">
-      <c r="A874" s="2" t="n">
-        <v>3457</v>
-      </c>
-      <c r="B874" s="2" t="str">
-        <v>EidolonText377</v>
-      </c>
-      <c r="C874" s="3" t="str">
-        <v>이미지 {0}장</v>
-      </c>
-      <c r="D874" s="3" t="str">
-        <v>{0} images</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="875" spans="1:4">
-      <c r="A875" s="2" t="n">
-        <v>3458</v>
-      </c>
-      <c r="B875" s="2" t="str">
-        <v>EidolonText378</v>
-      </c>
-      <c r="C875" s="3" t="str">
-        <v>결과 불러오는 중…</v>
-      </c>
-      <c r="D875" s="3" t="str">
-        <v>Loading results…</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="876" spans="1:4">
-      <c r="A876" s="2" t="n">
-        <v>3459</v>
-      </c>
-      <c r="B876" s="2" t="str">
-        <v>EidolonText379</v>
-      </c>
-      <c r="C876" s="3" t="str">
-        <v>닫기</v>
-      </c>
-      <c r="D876" s="3" t="str">
-        <v>Close</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="877" spans="1:4">
-      <c r="A877" s="2" t="n">
-        <v>3460</v>
-      </c>
-      <c r="B877" s="2" t="str">
-        <v>EidolonText380</v>
-      </c>
-      <c r="C877" s="3" t="str">
-        <v>결과를 불러오지 못했습니다. 새로고침해 주세요.</v>
-      </c>
-      <c r="D877" s="3" t="str">
-        <v>Could not load results. Please refresh.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="878" spans="1:4">
-      <c r="A878" s="2" t="n">
-        <v>3461</v>
-      </c>
-      <c r="B878" s="2" t="str">
-        <v>EidolonText381</v>
-      </c>
-      <c r="C878" s="3" t="str">
-        <v>미리보기 없음</v>
-      </c>
-      <c r="D878" s="3" t="str">
-        <v>No preview</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="879" spans="1:4">
-      <c r="A879" s="2" t="n">
-        <v>3462</v>
-      </c>
-      <c r="B879" s="2" t="str">
-        <v>EidolonText382</v>
-      </c>
-      <c r="C879" s="3" t="str">
-        <v>{0}장</v>
-      </c>
-      <c r="D879" s="3" t="str">
-        <v>{0} images</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="880" spans="1:4">
-      <c r="A880" s="2" t="n">
-        <v>3463</v>
-      </c>
-      <c r="B880" s="2" t="str">
-        <v>EidolonText383</v>
-      </c>
-      <c r="C880" s="3" t="str">
-        <v>프롬프트 정보 없음</v>
-      </c>
-      <c r="D880" s="3" t="str">
-        <v>No prompt data</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="881" spans="1:4">
-      <c r="A881" s="2" t="n">
-        <v>3464</v>
-      </c>
-      <c r="B881" s="2" t="str">
-        <v>EidolonText384</v>
-      </c>
-      <c r="C881" s="3" t="str">
-        <v>프롬프트 JSON을 읽을 수 없습니다. 이미지는 계속 사용할 수 있습니다.</v>
-      </c>
-      <c r="D881" s="3" t="str">
-        <v>Cannot read the prompt JSON. The image is still available.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="882" spans="1:4">
-      <c r="A882" s="2" t="n">
-        <v>3465</v>
-      </c>
-      <c r="B882" s="2" t="str">
-        <v>EidolonText385</v>
-      </c>
-      <c r="C882" s="3" t="str">
-        <v>{0}장 선택됨</v>
-      </c>
-      <c r="D882" s="3" t="str">
-        <v>{0} selected</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="883" spans="1:4">
-      <c r="A883" s="2" t="n">
-        <v>3466</v>
-      </c>
-      <c r="B883" s="2" t="str">
-        <v>EidolonText386</v>
-      </c>
-      <c r="C883" s="3" t="str">
-        <v>크게 보기</v>
-      </c>
-      <c r="D883" s="3" t="str">
-        <v>View image</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="884" spans="1:4">
-      <c r="A884" s="2" t="n">
-        <v>3467</v>
-      </c>
-      <c r="B884" s="2" t="str">
-        <v>EidolonText387</v>
-      </c>
-      <c r="C884" s="3" t="str">
-        <v>선택 해제</v>
-      </c>
-      <c r="D884" s="3" t="str">
-        <v>Clear selection</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="885" spans="1:4">
-      <c r="A885" s="2" t="n">
-        <v>3468</v>
-      </c>
-      <c r="B885" s="2" t="str">
-        <v>EidolonText388</v>
-      </c>
-      <c r="C885" s="3" t="str">
-        <v>같은 이름의 유효한 프롬프트 JSON이 있어야 생성 지침을 다시 사용할 수 있습니다.</v>
-      </c>
-      <c r="D885" s="3" t="str">
-        <v>Reusing instructions requires a valid prompt JSON file with the same name.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="886" spans="1:4">
-      <c r="A886" s="2" t="n">
-        <v>3469</v>
-      </c>
-      <c r="B886" s="2" t="str">
-        <v>EidolonText389</v>
-      </c>
-      <c r="C886" s="3" t="str">
-        <v>1. 엔진 준비</v>
-      </c>
-      <c r="D886" s="3" t="str">
-        <v>1. Prepare engine</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="887" spans="1:4">
-      <c r="A887" s="2" t="n">
-        <v>3470</v>
-      </c>
-      <c r="B887" s="2" t="str">
-        <v>EidolonText390</v>
-      </c>
-      <c r="C887" s="3" t="str">
-        <v>2. 생성 모델 준비</v>
-      </c>
-      <c r="D887" s="3" t="str">
-        <v>2. Prepare generation model</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="888" spans="1:4">
-      <c r="A888" s="2" t="n">
-        <v>3471</v>
-      </c>
-      <c r="B888" s="2" t="str">
-        <v>EidolonText391</v>
-      </c>
-      <c r="C888" s="3" t="str">
-        <v>모델 설치가 필요합니다</v>
-      </c>
-      <c r="D888" s="3" t="str">
-        <v>Install a generation model</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="889" spans="1:4">
-      <c r="A889" s="2" t="n">
-        <v>3472</v>
-      </c>
-      <c r="B889" s="2" t="str">
-        <v>EidolonText392</v>
-      </c>
-      <c r="C889" s="3" t="str">
-        <v>이미지를 생성하려면 모델을 한 개 이상 준비해야 합니다. 모델 · LoRA에서 설치하거나 모델 파일을 가져오세요.</v>
-      </c>
-      <c r="D889" s="3" t="str">
-        <v>You need at least one model to generate images. Install or import a model in Models · LoRA.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="890" spans="1:4">
-      <c r="A890" s="2" t="n">
-        <v>3473</v>
-      </c>
-      <c r="B890" s="2" t="str">
-        <v>EidolonText393</v>
-      </c>
-      <c r="C890" s="3" t="str">
-        <v>모델 설치하기</v>
-      </c>
-      <c r="D890" s="3" t="str">
-        <v>Install a model</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="891" spans="1:4">
-      <c r="A891" s="2" t="n">
-        <v>3474</v>
-      </c>
-      <c r="B891" s="2" t="str">
-        <v>EidolonText394</v>
-      </c>
-      <c r="C891" s="3" t="str">
-        <v>모델 설치 중</v>
-      </c>
-      <c r="D891" s="3" t="str">
-        <v>Installing a model</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="892" spans="1:4">
-      <c r="A892" s="2" t="n">
-        <v>3475</v>
-      </c>
-      <c r="B892" s="2" t="str">
-        <v>EidolonText395</v>
-      </c>
-      <c r="C892" s="3" t="str">
-        <v>{0} 설치 중입니다. 완료되면 생성 화면에서 선택할 수 있습니다.</v>
-      </c>
-      <c r="D892" s="3" t="str">
-        <v>{0} is installing. Once complete, you can select it in Generate.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="893" spans="1:4">
-      <c r="A893" s="2" t="n">
-        <v>3476</v>
-      </c>
-      <c r="B893" s="2" t="str">
-        <v>EidolonText396</v>
-      </c>
-      <c r="C893" s="3" t="str">
-        <v>모델 준비 완료</v>
-      </c>
-      <c r="D893" s="3" t="str">
-        <v>Models ready</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="894" spans="1:4">
-      <c r="A894" s="2" t="n">
-        <v>3477</v>
-      </c>
-      <c r="B894" s="2" t="str">
-        <v>EidolonText397</v>
-      </c>
-      <c r="C894" s="3" t="str">
-        <v>{0}개 모델을 사용할 수 있습니다.</v>
-      </c>
-      <c r="D894" s="3" t="str">
-        <v>{0} models available.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="895" spans="1:4">
-      <c r="A895" s="2" t="n">
-        <v>3478</v>
-      </c>
-      <c r="B895" s="2" t="str">
-        <v>EidolonText398</v>
-      </c>
-      <c r="C895" s="3" t="str">
-        <v>모델 관리</v>
-      </c>
-      <c r="D895" s="3" t="str">
-        <v>Manage models</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="896" spans="1:4">
-      <c r="A896" s="2" t="n">
-        <v>3479</v>
-      </c>
-      <c r="B896" s="2" t="str">
-        <v>EidolonText399</v>
-      </c>
-      <c r="C896" s="3" t="str">
-        <v>설치 상태 보기</v>
-      </c>
-      <c r="D896" s="3" t="str">
-        <v>View installation</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="897" spans="1:4">
-      <c r="A897" s="2" t="n">
-        <v>3480</v>
-      </c>
-      <c r="B897" s="2" t="str">
-        <v>EidolonText400</v>
-      </c>
-      <c r="C897" s="3" t="str">
-        <v>엔진 준비 완료</v>
-      </c>
-      <c r="D897" s="3" t="str">
-        <v>Engine ready</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="898" spans="1:4">
-      <c r="A898" s="2" t="n">
-        <v>3481</v>
-      </c>
-      <c r="B898" s="2" t="str">
-        <v>EidolonText401</v>
-      </c>
-      <c r="C898" s="3" t="str">
-        <v>엔진 설치 또는 서버 연결 필요</v>
-      </c>
-      <c r="D898" s="3" t="str">
-        <v>Install an engine or connect to a server</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="899" spans="1:4">
-      <c r="A899" s="2" t="n">
-        <v>3482</v>
-      </c>
-      <c r="B899" s="2" t="str">
-        <v>EidolonText402</v>
-      </c>
-      <c r="C899" s="3" t="str">
-        <v>준비 상태 확인 중…</v>
-      </c>
-      <c r="D899" s="3" t="str">
-        <v>Checking setup…</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="900" spans="1:4">
-      <c r="A900" s="2" t="n">
-        <v>3483</v>
-      </c>
-      <c r="B900" s="2" t="str">
-        <v>EidolonText403</v>
-      </c>
-      <c r="C900" s="3" t="str">
-        <v>연결한 서버의 모델을 준비한 뒤 모델 목록을 새로고침해 주세요.</v>
-      </c>
-      <c r="D900" s="3" t="str">
-        <v>Prepare a model on your connected server, then refresh the model list.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="901" spans="1:4">
-      <c r="A901" s="2" t="n">
-        <v>3484</v>
-      </c>
-      <c r="B901" s="2" t="str">
-        <v>EidolonText404</v>
-      </c>
-      <c r="C901" s="3" t="str">
-        <v>모델 목록 확인</v>
-      </c>
-      <c r="D901" s="3" t="str">
-        <v>View models</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="902" spans="1:4">
-      <c r="A902" s="2" t="n">
-        <v>3485</v>
-      </c>
-      <c r="B902" s="2" t="str">
-        <v>EidolonText405</v>
-      </c>
-      <c r="C902" s="3" t="str">
-        <v>먼저 엔진 설치 또는 서버 연결을 완료해 주세요.</v>
-      </c>
-      <c r="D902" s="3" t="str">
-        <v>First install the engine or connect to a server.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="903" spans="1:4">
-      <c r="A903" s="2" t="n">
-        <v>3486</v>
-      </c>
-      <c r="B903" s="2" t="str">
-        <v>EidolonText406</v>
-      </c>
-      <c r="C903" s="3" t="str">
-        <v>엔진 설치 완료 · 연결 필요</v>
-      </c>
-      <c r="D903" s="3" t="str">
-        <v>Engine installed · connect to continue</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="904" spans="1:4">
-      <c r="A904" s="2" t="n">
-        <v>3487</v>
-      </c>
-      <c r="B904" s="2" t="str">
-        <v>EidolonText407</v>
-      </c>
-      <c r="C904" s="3" t="str">
-        <v>엔진 준비하기</v>
-      </c>
-      <c r="D904" s="3" t="str">
-        <v>Prepare engine</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="905" spans="1:4">
-      <c r="A905" s="2" t="n">
-        <v>3488</v>
-      </c>
-      <c r="B905" s="2" t="str">
-        <v>EidolonText408</v>
-      </c>
-      <c r="C905" s="3" t="str">
-        <v>이미지 생성과 LoRA 학습에 필요한 실행 환경을 준비합니다.</v>
-      </c>
-      <c r="D905" s="3" t="str">
-        <v>Prepare the runtime for image generation and LoRA training.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="906" spans="1:4">
-      <c r="A906" s="2" t="n">
-        <v>3489</v>
-      </c>
-      <c r="B906" s="2" t="str">
-        <v>EidolonText409</v>
-      </c>
-      <c r="C906" s="3" t="str">
-        <v>파일 가져오기</v>
-      </c>
-      <c r="D906" s="3" t="str">
-        <v>Import file</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="907" spans="1:4">
-      <c r="A907" s="2" t="n">
-        <v>3490</v>
-      </c>
-      <c r="B907" s="2" t="str">
-        <v>EidolonText410</v>
-      </c>
-      <c r="C907" s="3" t="str">
-        <v>새로고침</v>
-      </c>
-      <c r="D907" s="3" t="str">
-        <v>Refresh</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="908" spans="1:4">
-      <c r="A908" s="2" t="n">
-        <v>3491</v>
-      </c>
-      <c r="B908" s="2" t="str">
-        <v>EidolonText411</v>
-      </c>
-      <c r="C908" s="3" t="str">
-        <v>내 모델 · LoRA</v>
-      </c>
-      <c r="D908" s="3" t="str">
-        <v>My models · LoRA</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="909" spans="1:4">
-      <c r="A909" s="2" t="n">
-        <v>3492</v>
-      </c>
-      <c r="B909" s="2" t="str">
-        <v>EidolonText412</v>
-      </c>
-      <c r="C909" s="3" t="str">
-        <v>상세 설정</v>
-      </c>
-      <c r="D909" s="3" t="str">
-        <v>Advanced settings</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="910" spans="1:4">
-      <c r="A910" s="2" t="n">
-        <v>3493</v>
-      </c>
-      <c r="B910" s="2" t="str">
-        <v>EidolonText413</v>
-      </c>
-      <c r="C910" s="3" t="str">
-        <v>계열은 자동 판별합니다. 판별되지 않은 모델만 직접 지정하세요.</v>
-      </c>
-      <c r="D910" s="3" t="str">
-        <v>The family is detected automatically. Set it manually only if detection is unavailable.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="911" spans="1:4">
-      <c r="A911" s="2" t="n">
-        <v>3494</v>
-      </c>
-      <c r="B911" s="2" t="str">
-        <v>EidolonText414</v>
-      </c>
-      <c r="C911" s="3" t="str">
-        <v>모델 계열을 확인해 주세요.</v>
-      </c>
-      <c r="D911" s="3" t="str">
-        <v>Check this model's family.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="912" spans="1:4">
-      <c r="A912" s="2" t="n">
-        <v>3495</v>
-      </c>
-      <c r="B912" s="2" t="str">
-        <v>EidolonText415</v>
-      </c>
-      <c r="C912" s="3" t="str">
-        <v>모델 파일은 삭제되지 않습니다.</v>
-      </c>
-      <c r="D912" s="3" t="str">
-        <v>The model file is kept.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="913" spans="1:4">
-      <c r="A913" s="2" t="n">
-        <v>3496</v>
-      </c>
-      <c r="B913" s="2" t="str">
-        <v>EidolonText416</v>
-      </c>
-      <c r="C913" s="3" t="str">
-        <v>설치 안내</v>
-      </c>
-      <c r="D913" s="3" t="str">
-        <v>Installation details</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="914" spans="1:4">
-      <c r="A914" s="2" t="n">
-        <v>3497</v>
-      </c>
-      <c r="B914" s="2" t="str">
-        <v>EidolonText417</v>
-      </c>
-      <c r="C914" s="3" t="str">
-        <v>연결 안내</v>
-      </c>
-      <c r="D914" s="3" t="str">
-        <v>Connection details</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="915" spans="1:4">
-      <c r="A915" s="2" t="n">
-        <v>3498</v>
-      </c>
-      <c r="B915" s="2" t="str">
-        <v>EidolonText418</v>
-      </c>
-      <c r="C915" s="3" t="str">
-        <v>설치하거나 가져온 모델이 여기에 표시됩니다.</v>
-      </c>
-      <c r="D915" s="3" t="str">
-        <v>Installed and imported models appear here.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="916" spans="1:4">
-      <c r="A916" s="2" t="n">
-        <v>3499</v>
-      </c>
-      <c r="B916" s="2" t="str">
-        <v>EidolonText419</v>
-      </c>
-      <c r="C916" s="3" t="str">
-        <v>자동 생성</v>
-      </c>
-      <c r="D916" s="3" t="str">
-        <v>Random seed</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="917" spans="1:4">
-      <c r="A917" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="B917" s="2" t="str">
-        <v>EidolonText420</v>
-      </c>
-      <c r="C917" s="3" t="str">
-        <v>요청마다 새로운 시드로 생성합니다.</v>
-      </c>
-      <c r="D917" s="3" t="str">
-        <v>Each request uses a new random seed.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="918" spans="1:4">
-      <c r="A918" s="2" t="n">
-        <v>3501</v>
-      </c>
-      <c r="B918" s="2" t="str">
-        <v>EidolonText421</v>
-      </c>
-      <c r="C918" s="3" t="str">
-        <v>시드는 {0}~{1} 사이의 정수를 입력하세요.</v>
-      </c>
-      <c r="D918" s="3" t="str">
-        <v>Enter an integer seed between {0} and {1}.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="919" spans="1:4">
-      <c r="A919" s="2" t="n">
-        <v>3502</v>
-      </c>
-      <c r="B919" s="2" t="str">
-        <v>EidolonText422</v>
-      </c>
-      <c r="C919" s="3" t="str">
-        <v>최근 요청 시드: {0}</v>
-      </c>
-      <c r="D919" s="3" t="str">
-        <v>Latest requested seed: {0}</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="920" spans="1:4">
-      <c r="A920" s="2" t="n">
-        <v>3503</v>
-      </c>
-      <c r="B920" s="2" t="str">
-        <v>EidolonText423</v>
-      </c>
-      <c r="C920" s="3" t="str">
-        <v>LoRA (선택)</v>
-      </c>
-      <c r="D920" s="3" t="str">
-        <v>LoRA (optional)</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="921" spans="1:4">
-      <c r="A921" s="2" t="n">
-        <v>3504</v>
-      </c>
-      <c r="B921" s="2" t="str">
-        <v>EidolonText424</v>
-      </c>
-      <c r="C921" s="3" t="str">
-        <v>왼쪽에서 이미지를 선택하면 크게 볼 수 있습니다.</v>
-      </c>
-      <c r="D921" s="3" t="str">
-        <v>Select an image on the left to view it here.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="922" spans="1:4">
-      <c r="A922" s="2" t="n">
-        <v>3505</v>
-      </c>
-      <c r="B922" s="2" t="str">
-        <v>EidolonText425</v>
-      </c>
-      <c r="C922" s="3" t="str">
-        <v>학습 이미지 배경</v>
-      </c>
-      <c r="D922" s="3" t="str">
-        <v>Training image background</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="923" spans="1:4">
-      <c r="A923" s="2" t="n">
-        <v>3506</v>
-      </c>
-      <c r="B923" s="2" t="str">
-        <v>EidolonText426</v>
-      </c>
-      <c r="C923" s="3" t="str">
-        <v>원본 유지</v>
-      </c>
-      <c r="D923" s="3" t="str">
-        <v>Keep original</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="924" spans="1:4">
-      <c r="A924" s="2" t="n">
-        <v>3507</v>
-      </c>
-      <c r="B924" s="2" t="str">
-        <v>EidolonText427</v>
-      </c>
-      <c r="C924" s="3" t="str">
-        <v>흰색</v>
-      </c>
-      <c r="D924" s="3" t="str">
-        <v>White</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="925" spans="1:4">
-      <c r="A925" s="2" t="n">
-        <v>3508</v>
-      </c>
-      <c r="B925" s="2" t="str">
-        <v>EidolonText428</v>
-      </c>
-      <c r="C925" s="3" t="str">
-        <v>검정색</v>
-      </c>
-      <c r="D925" s="3" t="str">
-        <v>Black</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="926" spans="1:4">
-      <c r="A926" s="2" t="n">
-        <v>3509</v>
-      </c>
-      <c r="B926" s="2" t="str">
-        <v>EidolonText429</v>
-      </c>
-      <c r="C926" s="3" t="str">
-        <v>투명 영역을 선택한 색으로 채웁니다. 이미 있는 배경과 원본 이미지·설명은 유지합니다.</v>
-      </c>
-      <c r="D926" s="3" t="str">
-        <v>Fill transparent areas with the selected color. Existing backgrounds, original images and captions are preserved.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="927" spans="1:4">
-      <c r="A927" s="2" t="n">
-        <v>3510</v>
-      </c>
-      <c r="B927" s="2" t="str">
-        <v>EidolonText430</v>
-      </c>
-      <c r="C927" s="3" t="str">
-        <v>학습 이미지 배경을 선택하세요.</v>
-      </c>
-      <c r="D927" s="3" t="str">
-        <v>Select a training image background.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="928" spans="1:4">
-      <c r="A928" s="2" t="n">
-        <v>3511</v>
-      </c>
-      <c r="B928" s="2" t="str">
-        <v>EidolonText431</v>
-      </c>
-      <c r="C928" s="3" t="str">
-        <v>학습 이미지 배경을 처리하지 못했습니다: {0}</v>
-      </c>
-      <c r="D928" s="3" t="str">
-        <v>Could not prepare the training image background: {0}</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="929" spans="1:4">
-      <c r="A929" s="2" t="n">
-        <v>3512</v>
-      </c>
-      <c r="B929" s="2" t="str">
-        <v>EidolonText432</v>
-      </c>
-      <c r="C929" s="3" t="str">
-        <v>LoRA 이름·파일명·트리거 검색</v>
-      </c>
-      <c r="D929" s="3" t="str">
-        <v>Search LoRA name, filename or trigger</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="930" spans="1:4">
-      <c r="A930" s="2" t="n">
-        <v>3513</v>
-      </c>
-      <c r="B930" s="2" t="str">
-        <v>EidolonText433</v>
-      </c>
-      <c r="C930" s="3" t="str">
-        <v>검색한 LoRA가 없습니다.</v>
-      </c>
-      <c r="D930" s="3" t="str">
-        <v>No matching LoRAs.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="931" spans="1:4">
-      <c r="A931" s="2" t="n">
-        <v>3514</v>
-      </c>
-      <c r="B931" s="2" t="str">
-        <v>EidolonText434</v>
-      </c>
-      <c r="C931" s="3" t="str">
-        <v>{0}개 LoRA 적용 중</v>
-      </c>
-      <c r="D931" s="3" t="str">
-        <v>{0} LoRAs applied</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="932" spans="1:4">
-      <c r="A932" s="2" t="n">
-        <v>3515</v>
-      </c>
-      <c r="B932" s="2" t="str">
-        <v>EidolonText435</v>
-      </c>
-      <c r="C932" s="3" t="str">
-        <v>적용 중</v>
-      </c>
-      <c r="D932" s="3" t="str">
-        <v>Applied</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="933" spans="1:4">
-      <c r="A933" s="2" t="n">
-        <v>3516</v>
-      </c>
-      <c r="B933" s="2" t="str">
-        <v>EidolonText436</v>
-      </c>
-      <c r="C933" s="3" t="str">
-        <v>설정의 생성 지침</v>
-      </c>
-      <c r="D933" s="3" t="str">
-        <v>Generation instructions from settings</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="934" spans="1:4">
-      <c r="A934" s="2" t="n">
-        <v>3517</v>
-      </c>
-      <c r="B934" s="2" t="str">
-        <v>EidolonText437</v>
-      </c>
-      <c r="C934" s="3" t="str">
-        <v>설정에 저장한 생성 지침과 제외할 요소가 적용됩니다.</v>
-      </c>
-      <c r="D934" s="3" t="str">
-        <v>The generation instructions and elements to avoid saved in settings are applied.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="935" spans="1:4">
-      <c r="A935" s="2" t="n">
-        <v>3518</v>
-      </c>
-      <c r="B935" s="2" t="str">
-        <v>EidolonText438</v>
-      </c>
-      <c r="C935" s="3" t="str">
-        <v>생성하기</v>
-      </c>
-      <c r="D935" s="3" t="str">
-        <v>Generate</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="936" spans="1:4">
-      <c r="A936" s="2" t="n">
-        <v>3519</v>
-      </c>
-      <c r="B936" s="2" t="str">
-        <v>EidolonText439</v>
-      </c>
-      <c r="C936" s="3" t="str">
-        <v>미리보기</v>
-      </c>
-      <c r="D936" s="3" t="str">
-        <v>Preview</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="937" spans="1:4">
-      <c r="A937" s="2" t="n">
-        <v>3520</v>
-      </c>
-      <c r="B937" s="2" t="str">
-        <v>EidolonText440</v>
-      </c>
-      <c r="C937" s="3" t="str">
-        <v>참고 이미지</v>
-      </c>
-      <c r="D937" s="3" t="str">
-        <v>Reference image</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="938" spans="1:4">
-      <c r="A938" s="2" t="n">
-        <v>3521</v>
-      </c>
-      <c r="B938" s="2" t="str">
-        <v>EidolonText441</v>
-      </c>
-      <c r="C938" s="3" t="str">
-        <v>참고 이미지 추가</v>
-      </c>
-      <c r="D938" s="3" t="str">
-        <v>Add reference image</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="939" spans="1:4">
-      <c r="A939" s="2" t="n">
-        <v>3522</v>
-      </c>
-      <c r="B939" s="2" t="str">
-        <v>EidolonText442</v>
-      </c>
-      <c r="C939" s="3" t="str">
-        <v>이미지 변경</v>
-      </c>
-      <c r="D939" s="3" t="str">
-        <v>Change image</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="940" spans="1:4">
-      <c r="A940" s="2" t="n">
-        <v>3523</v>
-      </c>
-      <c r="B940" s="2" t="str">
-        <v>EidolonText443</v>
-      </c>
-      <c r="C940" s="3" t="str">
-        <v>제거</v>
-      </c>
-      <c r="D940" s="3" t="str">
-        <v>Remove</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="941" spans="1:4">
-      <c r="A941" s="2" t="n">
-        <v>3524</v>
-      </c>
-      <c r="B941" s="2" t="str">
-        <v>EidolonText444</v>
-      </c>
-      <c r="C941" s="3" t="str">
-        <v>참고해 새로 생성</v>
-      </c>
-      <c r="D941" s="3" t="str">
-        <v>Reimagine from image</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="942" spans="1:4">
-      <c r="A942" s="2" t="n">
-        <v>3525</v>
-      </c>
-      <c r="B942" s="2" t="str">
-        <v>EidolonText445</v>
-      </c>
-      <c r="C942" s="3" t="str">
-        <v>그림체 변경</v>
-      </c>
-      <c r="D942" s="3" t="str">
-        <v>Change style</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="943" spans="1:4">
-      <c r="A943" s="2" t="n">
-        <v>3526</v>
-      </c>
-      <c r="B943" s="2" t="str">
-        <v>EidolonText446</v>
-      </c>
-      <c r="C943" s="3" t="str">
-        <v>원본 이미지를 바탕으로 설명에 맞는 새로운 이미지를 만듭니다.</v>
-      </c>
-      <c r="D943" s="3" t="str">
-        <v>Create a new image based on the reference and your description.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="944" spans="1:4">
-      <c r="A944" s="2" t="n">
-        <v>3527</v>
-      </c>
-      <c r="B944" s="2" t="str">
-        <v>EidolonText447</v>
-      </c>
-      <c r="C944" s="3" t="str">
-        <v>대상과 구도를 최대한 유지하며 원하는 그림체를 적용합니다. 설명에 바꿀 스타일을 적어주세요.</v>
-      </c>
-      <c r="D944" s="3" t="str">
-        <v>Keep the subject and composition as closely as possible while applying the style described in your prompt.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="945" spans="1:4">
-      <c r="A945" s="2" t="n">
-        <v>3528</v>
-      </c>
-      <c r="B945" s="2" t="str">
-        <v>EidolonText448</v>
-      </c>
-      <c r="C945" s="3" t="str">
-        <v>변경 강도</v>
-      </c>
-      <c r="D945" s="3" t="str">
-        <v>Change strength</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="946" spans="1:4">
-      <c r="A946" s="2" t="n">
-        <v>3529</v>
-      </c>
-      <c r="B946" s="2" t="str">
-        <v>EidolonText449</v>
-      </c>
-      <c r="C946" s="3" t="str">
-        <v>낮을수록 원본 유지 · 높을수록 큰 변화</v>
-      </c>
-      <c r="D946" s="3" t="str">
-        <v>Lower preserves the original · higher makes larger changes</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="947" spans="1:4">
-      <c r="A947" s="2" t="n">
-        <v>3530</v>
-      </c>
-      <c r="B947" s="2" t="str">
-        <v>EidolonText450</v>
-      </c>
-      <c r="C947" s="3" t="str">
-        <v>이미지를 읽을 수 없습니다. 32 MB·4천만 픽셀 이하의 PNG, JPG, WebP 파일을 선택해주세요.</v>
-      </c>
-      <c r="D947" s="3" t="str">
-        <v>Cannot read this image. Choose a PNG, JPG, or WebP file up to 32 MB and 40 million pixels.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="948" spans="1:4">
-      <c r="A948" s="2" t="n">
-        <v>3531</v>
-      </c>
-      <c r="B948" s="2" t="str">
-        <v>EidolonText451</v>
-      </c>
-      <c r="C948" s="3" t="str">
-        <v>참고 이미지의 모드와 변경 강도를 확인해주세요. 변경 강도는 5~95%로 설정할 수 있습니다.</v>
-      </c>
-      <c r="D948" s="3" t="str">
-        <v>Check the reference mode and change strength. Strength must be between 5% and 95%.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="949" spans="1:4">
-      <c r="A949" s="2" t="n">
-        <v>3532</v>
-      </c>
-      <c r="B949" s="2" t="str">
-        <v>EidolonText452</v>
-      </c>
-      <c r="C949" s="3" t="str">
-        <v>참고 이미지 준비 중</v>
-      </c>
-      <c r="D949" s="3" t="str">
-        <v>Preparing reference image</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="950" spans="1:4">
-      <c r="A950" s="2" t="n">
-        <v>3533</v>
-      </c>
-      <c r="B950" s="2" t="str">
-        <v>EidolonText453</v>
-      </c>
-      <c r="C950" s="3" t="str">
-        <v>참고 이미지를 생성 엔진에 전송 중</v>
-      </c>
-      <c r="D950" s="3" t="str">
-        <v>Uploading reference image to the generation engine</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="951" spans="1:4">
-      <c r="A951" s="2" t="n">
-        <v>3534</v>
-      </c>
-      <c r="B951" s="2" t="str">
-        <v>EidolonText454</v>
-      </c>
-      <c r="C951" s="3" t="str">
-        <v>이 결과의 참고 이미지를 찾거나 읽을 수 없습니다. 이미지를 다시 선택해주세요.</v>
-      </c>
-      <c r="D951" s="3" t="str">
-        <v>The reference image for this result cannot be found or read. Select an image again.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="952" spans="1:4">
-      <c r="A952" s="2" t="n">
-        <v>3535</v>
-      </c>
-      <c r="B952" s="2" t="str">
-        <v>EidolonText455</v>
-      </c>
-      <c r="C952" s="3" t="str">
-        <v>이 이미지로 편집</v>
-      </c>
-      <c r="D952" s="3" t="str">
-        <v>Edit from this image</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="953" spans="1:4">
-      <c r="A953" s="2" t="n">
-        <v>3536</v>
-      </c>
-      <c r="B953" s="2" t="str">
-        <v>EidolonText456</v>
-      </c>
-      <c r="C953" s="3" t="str">
-        <v>이미지 편집</v>
-      </c>
-      <c r="D953" s="3" t="str">
-        <v>Image editing</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="954" spans="1:4">
-      <c r="A954" s="2" t="n">
-        <v>3537</v>
-      </c>
-      <c r="B954" s="2" t="str">
-        <v>EidolonText457</v>
-      </c>
-      <c r="C954" s="3" t="str">
-        <v>어떻게 바꿀까요?</v>
-      </c>
-      <c r="D954" s="3" t="str">
-        <v>How should it change?</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="955" spans="1:4">
-      <c r="A955" s="2" t="n">
-        <v>3538</v>
-      </c>
-      <c r="B955" s="2" t="str">
-        <v>EidolonText458</v>
-      </c>
-      <c r="C955" s="3" t="str">
-        <v>예: 대상과 구도를 유지하고 수채화풍으로 바꿔줘</v>
-      </c>
-      <c r="D955" s="3" t="str">
-        <v>Example: Keep the subject and composition, and change it to a watercolor illustration</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="956" spans="1:4">
-      <c r="A956" s="2" t="n">
-        <v>3539</v>
-      </c>
-      <c r="B956" s="2" t="str">
-        <v>EidolonText459</v>
-      </c>
-      <c r="C956" s="3" t="str">
-        <v>편집할 이미지를 먼저 선택해주세요.</v>
-      </c>
-      <c r="D956" s="3" t="str">
-        <v>Select the image you want to edit first.</v>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="957" spans="1:4">
-      <c r="A957" s="2" t="n">
-        <v>3540</v>
-      </c>
-      <c r="B957" s="2" t="str">
-        <v>EidolonText460</v>
-      </c>
-      <c r="C957" s="3" t="str">
-        <v>저장 폴더 선택</v>
-      </c>
-      <c r="D957" s="3" t="str">
-        <v>Choose output folder</v>
-      </c>
-    </row>
-    <x:row r="958" spans="1:4">
+    <x:row r="859">
+      <x:c r="A859" s="2" t="n">
+        <x:v>3442</x:v>
+      </x:c>
+      <x:c r="B859" s="2" t="str">
+        <x:v>EidolonText362</x:v>
+      </x:c>
+      <x:c r="C859" s="3" t="str">
+        <x:v>생성 지침</x:v>
+      </x:c>
+      <x:c r="D859" s="3" t="str">
+        <x:v>Generation instructions</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="860">
+      <x:c r="A860" s="2" t="n">
+        <x:v>3443</x:v>
+      </x:c>
+      <x:c r="B860" s="2" t="str">
+        <x:v>EidolonText363</x:v>
+      </x:c>
+      <x:c r="C860" s="3" t="str">
+        <x:v>여기서 바꾼 지침은 이번 요청에만 적용됩니다. 설정의 기본값은 유지됩니다.</x:v>
+      </x:c>
+      <x:c r="D860" s="3" t="str">
+        <x:v>Changes here apply to this request. Your saved defaults stay the same.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="861">
+      <x:c r="A861" s="2" t="n">
+        <x:v>3444</x:v>
+      </x:c>
+      <x:c r="B861" s="2" t="str">
+        <x:v>EidolonText364</x:v>
+      </x:c>
+      <x:c r="C861" s="3" t="str">
+        <x:v>기본값 불러오기</x:v>
+      </x:c>
+      <x:c r="D861" s="3" t="str">
+        <x:v>Load defaults</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="862">
+      <x:c r="A862" s="2" t="n">
+        <x:v>3445</x:v>
+      </x:c>
+      <x:c r="B862" s="2" t="str">
+        <x:v>EidolonText365</x:v>
+      </x:c>
+      <x:c r="C862" s="3" t="str">
+        <x:v>생성 정보</x:v>
+      </x:c>
+      <x:c r="D862" s="3" t="str">
+        <x:v>Generation details</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="863">
+      <x:c r="A863" s="2" t="n">
+        <x:v>3446</x:v>
+      </x:c>
+      <x:c r="B863" s="2" t="str">
+        <x:v>EidolonText366</x:v>
+      </x:c>
+      <x:c r="C863" s="3" t="str">
+        <x:v>상태</x:v>
+      </x:c>
+      <x:c r="D863" s="3" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="864">
+      <x:c r="A864" s="2" t="n">
+        <x:v>3447</x:v>
+      </x:c>
+      <x:c r="B864" s="2" t="str">
+        <x:v>EidolonText367</x:v>
+      </x:c>
+      <x:c r="C864" s="3" t="str">
+        <x:v>생성 시각</x:v>
+      </x:c>
+      <x:c r="D864" s="3" t="str">
+        <x:v>Created</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="865">
+      <x:c r="A865" s="2" t="n">
+        <x:v>3448</x:v>
+      </x:c>
+      <x:c r="B865" s="2" t="str">
+        <x:v>EidolonText368</x:v>
+      </x:c>
+      <x:c r="C865" s="3" t="str">
+        <x:v>해상도</x:v>
+      </x:c>
+      <x:c r="D865" s="3" t="str">
+        <x:v>Resolution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="866">
+      <x:c r="A866" s="2" t="n">
+        <x:v>3449</x:v>
+      </x:c>
+      <x:c r="B866" s="2" t="str">
+        <x:v>EidolonText369</x:v>
+      </x:c>
+      <x:c r="C866" s="3" t="str">
+        <x:v>시드</x:v>
+      </x:c>
+      <x:c r="D866" s="3" t="str">
+        <x:v>Seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="867">
+      <x:c r="A867" s="2" t="n">
+        <x:v>3450</x:v>
+      </x:c>
+      <x:c r="B867" s="2" t="str">
+        <x:v>EidolonText370</x:v>
+      </x:c>
+      <x:c r="C867" s="3" t="str">
+        <x:v>이 결과의 모델 또는 LoRA 일부가 현재 목록에 없습니다. 생성 전에 선택을 확인해 주세요.</x:v>
+      </x:c>
+      <x:c r="D867" s="3" t="str">
+        <x:v>Some models or LoRAs used for this result are unavailable. Check your selection before generating.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="868">
+      <x:c r="A868" s="2" t="n">
+        <x:v>3451</x:v>
+      </x:c>
+      <x:c r="B868" s="2" t="str">
+        <x:v>EidolonText371</x:v>
+      </x:c>
+      <x:c r="C868" s="3" t="str">
+        <x:v>이번 요청의 지침</x:v>
+      </x:c>
+      <x:c r="D868" s="3" t="str">
+        <x:v>Instructions for this request</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="869">
+      <x:c r="A869" s="2" t="n">
+        <x:v>3452</x:v>
+      </x:c>
+      <x:c r="B869" s="2" t="str">
+        <x:v>EidolonText372</x:v>
+      </x:c>
+      <x:c r="C869" s="3" t="str">
+        <x:v>결과 갤러리</x:v>
+      </x:c>
+      <x:c r="D869" s="3" t="str">
+        <x:v>Results gallery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="870">
+      <x:c r="A870" s="2" t="n">
+        <x:v>3453</x:v>
+      </x:c>
+      <x:c r="B870" s="2" t="str">
+        <x:v>EidolonText373</x:v>
+      </x:c>
+      <x:c r="C870" s="3" t="str">
+        <x:v>클릭하면 오른쪽에 이미지·프롬프트 표시 · Ctrl+클릭으로 다중 선택 · Shift+클릭으로 범위 선택</x:v>
+      </x:c>
+      <x:c r="D870" s="3" t="str">
+        <x:v>Click to preview on the right · Ctrl+click for multiple selection · Shift+click to select a range</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="871">
+      <x:c r="A871" s="2" t="n">
+        <x:v>3454</x:v>
+      </x:c>
+      <x:c r="B871" s="2" t="str">
+        <x:v>EidolonText374</x:v>
+      </x:c>
+      <x:c r="C871" s="3" t="str">
+        <x:v>이전</x:v>
+      </x:c>
+      <x:c r="D871" s="3" t="str">
+        <x:v>Previous</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="872">
+      <x:c r="A872" s="2" t="n">
+        <x:v>3455</x:v>
+      </x:c>
+      <x:c r="B872" s="2" t="str">
+        <x:v>EidolonText375</x:v>
+      </x:c>
+      <x:c r="C872" s="3" t="str">
+        <x:v>다음</x:v>
+      </x:c>
+      <x:c r="D872" s="3" t="str">
+        <x:v>Next</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="873">
+      <x:c r="A873" s="2" t="n">
+        <x:v>3456</x:v>
+      </x:c>
+      <x:c r="B873" s="2" t="str">
+        <x:v>EidolonText376</x:v>
+      </x:c>
+      <x:c r="C873" s="3" t="str">
+        <x:v>{0} / {1} 페이지</x:v>
+      </x:c>
+      <x:c r="D873" s="3" t="str">
+        <x:v>Page {0} of {1}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="874">
+      <x:c r="A874" s="2" t="n">
+        <x:v>3457</x:v>
+      </x:c>
+      <x:c r="B874" s="2" t="str">
+        <x:v>EidolonText377</x:v>
+      </x:c>
+      <x:c r="C874" s="3" t="str">
+        <x:v>이미지 {0}장</x:v>
+      </x:c>
+      <x:c r="D874" s="3" t="str">
+        <x:v>{0} images</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="875">
+      <x:c r="A875" s="2" t="n">
+        <x:v>3458</x:v>
+      </x:c>
+      <x:c r="B875" s="2" t="str">
+        <x:v>EidolonText378</x:v>
+      </x:c>
+      <x:c r="C875" s="3" t="str">
+        <x:v>결과 불러오는 중…</x:v>
+      </x:c>
+      <x:c r="D875" s="3" t="str">
+        <x:v>Loading results…</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="876">
+      <x:c r="A876" s="2" t="n">
+        <x:v>3459</x:v>
+      </x:c>
+      <x:c r="B876" s="2" t="str">
+        <x:v>EidolonText379</x:v>
+      </x:c>
+      <x:c r="C876" s="3" t="str">
+        <x:v>닫기</x:v>
+      </x:c>
+      <x:c r="D876" s="3" t="str">
+        <x:v>Close</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="877">
+      <x:c r="A877" s="2" t="n">
+        <x:v>3460</x:v>
+      </x:c>
+      <x:c r="B877" s="2" t="str">
+        <x:v>EidolonText380</x:v>
+      </x:c>
+      <x:c r="C877" s="3" t="str">
+        <x:v>결과를 불러오지 못했습니다. 새로고침해 주세요.</x:v>
+      </x:c>
+      <x:c r="D877" s="3" t="str">
+        <x:v>Could not load results. Please refresh.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="878">
+      <x:c r="A878" s="2" t="n">
+        <x:v>3461</x:v>
+      </x:c>
+      <x:c r="B878" s="2" t="str">
+        <x:v>EidolonText381</x:v>
+      </x:c>
+      <x:c r="C878" s="3" t="str">
+        <x:v>미리보기 없음</x:v>
+      </x:c>
+      <x:c r="D878" s="3" t="str">
+        <x:v>No preview</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="879">
+      <x:c r="A879" s="2" t="n">
+        <x:v>3462</x:v>
+      </x:c>
+      <x:c r="B879" s="2" t="str">
+        <x:v>EidolonText382</x:v>
+      </x:c>
+      <x:c r="C879" s="3" t="str">
+        <x:v>{0}장</x:v>
+      </x:c>
+      <x:c r="D879" s="3" t="str">
+        <x:v>{0} images</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="880">
+      <x:c r="A880" s="2" t="n">
+        <x:v>3463</x:v>
+      </x:c>
+      <x:c r="B880" s="2" t="str">
+        <x:v>EidolonText383</x:v>
+      </x:c>
+      <x:c r="C880" s="3" t="str">
+        <x:v>프롬프트 정보 없음</x:v>
+      </x:c>
+      <x:c r="D880" s="3" t="str">
+        <x:v>No prompt data</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="881">
+      <x:c r="A881" s="2" t="n">
+        <x:v>3464</x:v>
+      </x:c>
+      <x:c r="B881" s="2" t="str">
+        <x:v>EidolonText384</x:v>
+      </x:c>
+      <x:c r="C881" s="3" t="str">
+        <x:v>프롬프트 JSON을 읽을 수 없습니다. 이미지는 계속 사용할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D881" s="3" t="str">
+        <x:v>Cannot read the prompt JSON. The image is still available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="882">
+      <x:c r="A882" s="2" t="n">
+        <x:v>3465</x:v>
+      </x:c>
+      <x:c r="B882" s="2" t="str">
+        <x:v>EidolonText385</x:v>
+      </x:c>
+      <x:c r="C882" s="3" t="str">
+        <x:v>{0}장 선택됨</x:v>
+      </x:c>
+      <x:c r="D882" s="3" t="str">
+        <x:v>{0} selected</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="883">
+      <x:c r="A883" s="2" t="n">
+        <x:v>3466</x:v>
+      </x:c>
+      <x:c r="B883" s="2" t="str">
+        <x:v>EidolonText386</x:v>
+      </x:c>
+      <x:c r="C883" s="3" t="str">
+        <x:v>크게 보기</x:v>
+      </x:c>
+      <x:c r="D883" s="3" t="str">
+        <x:v>View image</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="884">
+      <x:c r="A884" s="2" t="n">
+        <x:v>3467</x:v>
+      </x:c>
+      <x:c r="B884" s="2" t="str">
+        <x:v>EidolonText387</x:v>
+      </x:c>
+      <x:c r="C884" s="3" t="str">
+        <x:v>선택 해제</x:v>
+      </x:c>
+      <x:c r="D884" s="3" t="str">
+        <x:v>Clear selection</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="885">
+      <x:c r="A885" s="2" t="n">
+        <x:v>3468</x:v>
+      </x:c>
+      <x:c r="B885" s="2" t="str">
+        <x:v>EidolonText388</x:v>
+      </x:c>
+      <x:c r="C885" s="3" t="str">
+        <x:v>같은 이름의 유효한 프롬프트 JSON이 있어야 생성 지침을 다시 사용할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D885" s="3" t="str">
+        <x:v>Reusing instructions requires a valid prompt JSON file with the same name.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="886">
+      <x:c r="A886" s="2" t="n">
+        <x:v>3469</x:v>
+      </x:c>
+      <x:c r="B886" s="2" t="str">
+        <x:v>EidolonText389</x:v>
+      </x:c>
+      <x:c r="C886" s="3" t="str">
+        <x:v>1. 엔진 준비</x:v>
+      </x:c>
+      <x:c r="D886" s="3" t="str">
+        <x:v>1. Prepare engine</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="887">
+      <x:c r="A887" s="2" t="n">
+        <x:v>3470</x:v>
+      </x:c>
+      <x:c r="B887" s="2" t="str">
+        <x:v>EidolonText390</x:v>
+      </x:c>
+      <x:c r="C887" s="3" t="str">
+        <x:v>2. 생성 모델 준비</x:v>
+      </x:c>
+      <x:c r="D887" s="3" t="str">
+        <x:v>2. Prepare generation model</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="888">
+      <x:c r="A888" s="2" t="n">
+        <x:v>3471</x:v>
+      </x:c>
+      <x:c r="B888" s="2" t="str">
+        <x:v>EidolonText391</x:v>
+      </x:c>
+      <x:c r="C888" s="3" t="str">
+        <x:v>모델 설치가 필요합니다</x:v>
+      </x:c>
+      <x:c r="D888" s="3" t="str">
+        <x:v>Install a generation model</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="889">
+      <x:c r="A889" s="2" t="n">
+        <x:v>3472</x:v>
+      </x:c>
+      <x:c r="B889" s="2" t="str">
+        <x:v>EidolonText392</x:v>
+      </x:c>
+      <x:c r="C889" s="3" t="str">
+        <x:v>이미지를 생성하려면 모델을 한 개 이상 준비해야 합니다. 모델·LoRA에서 설치하거나 모델 폴더에 넣고 새로고침하세요.</x:v>
+      </x:c>
+      <x:c r="D889" s="3" t="str">
+        <x:v>Prepare at least one model to generate images. Install it in Models and LoRAs or place it in Model folder and refresh.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="890">
+      <x:c r="A890" s="2" t="n">
+        <x:v>3473</x:v>
+      </x:c>
+      <x:c r="B890" s="2" t="str">
+        <x:v>EidolonText393</x:v>
+      </x:c>
+      <x:c r="C890" s="3" t="str">
+        <x:v>모델 설치하기</x:v>
+      </x:c>
+      <x:c r="D890" s="3" t="str">
+        <x:v>Install a model</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="891">
+      <x:c r="A891" s="2" t="n">
+        <x:v>3474</x:v>
+      </x:c>
+      <x:c r="B891" s="2" t="str">
+        <x:v>EidolonText394</x:v>
+      </x:c>
+      <x:c r="C891" s="3" t="str">
+        <x:v>모델 설치 중</x:v>
+      </x:c>
+      <x:c r="D891" s="3" t="str">
+        <x:v>Installing a model</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="892">
+      <x:c r="A892" s="2" t="n">
+        <x:v>3475</x:v>
+      </x:c>
+      <x:c r="B892" s="2" t="str">
+        <x:v>EidolonText395</x:v>
+      </x:c>
+      <x:c r="C892" s="3" t="str">
+        <x:v>{0} 설치 중입니다. 완료되면 생성 화면에서 선택할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D892" s="3" t="str">
+        <x:v>{0} is installing. Once complete, you can select it in Generate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="893">
+      <x:c r="A893" s="2" t="n">
+        <x:v>3476</x:v>
+      </x:c>
+      <x:c r="B893" s="2" t="str">
+        <x:v>EidolonText396</x:v>
+      </x:c>
+      <x:c r="C893" s="3" t="str">
+        <x:v>모델 준비 완료</x:v>
+      </x:c>
+      <x:c r="D893" s="3" t="str">
+        <x:v>Models ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="894">
+      <x:c r="A894" s="2" t="n">
+        <x:v>3477</x:v>
+      </x:c>
+      <x:c r="B894" s="2" t="str">
+        <x:v>EidolonText397</x:v>
+      </x:c>
+      <x:c r="C894" s="3" t="str">
+        <x:v>{0}개 모델을 사용할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D894" s="3" t="str">
+        <x:v>{0} models available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="895">
+      <x:c r="A895" s="2" t="n">
+        <x:v>3478</x:v>
+      </x:c>
+      <x:c r="B895" s="2" t="str">
+        <x:v>EidolonText398</x:v>
+      </x:c>
+      <x:c r="C895" s="3" t="str">
+        <x:v>모델 관리</x:v>
+      </x:c>
+      <x:c r="D895" s="3" t="str">
+        <x:v>Manage models</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="896">
+      <x:c r="A896" s="2" t="n">
+        <x:v>3479</x:v>
+      </x:c>
+      <x:c r="B896" s="2" t="str">
+        <x:v>EidolonText399</x:v>
+      </x:c>
+      <x:c r="C896" s="3" t="str">
+        <x:v>설치 상태 보기</x:v>
+      </x:c>
+      <x:c r="D896" s="3" t="str">
+        <x:v>View installation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="897">
+      <x:c r="A897" s="2" t="n">
+        <x:v>3480</x:v>
+      </x:c>
+      <x:c r="B897" s="2" t="str">
+        <x:v>EidolonText400</x:v>
+      </x:c>
+      <x:c r="C897" s="3" t="str">
+        <x:v>엔진 준비 완료</x:v>
+      </x:c>
+      <x:c r="D897" s="3" t="str">
+        <x:v>Engine ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="898">
+      <x:c r="A898" s="2" t="n">
+        <x:v>3481</x:v>
+      </x:c>
+      <x:c r="B898" s="2" t="str">
+        <x:v>EidolonText401</x:v>
+      </x:c>
+      <x:c r="C898" s="3" t="str">
+        <x:v>엔진 설치 또는 서버 연결 필요</x:v>
+      </x:c>
+      <x:c r="D898" s="3" t="str">
+        <x:v>Install an engine or connect to a server</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="899">
+      <x:c r="A899" s="2" t="n">
+        <x:v>3482</x:v>
+      </x:c>
+      <x:c r="B899" s="2" t="str">
+        <x:v>EidolonText402</x:v>
+      </x:c>
+      <x:c r="C899" s="3" t="str">
+        <x:v>준비 상태 확인 중…</x:v>
+      </x:c>
+      <x:c r="D899" s="3" t="str">
+        <x:v>Checking setup…</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="900">
+      <x:c r="A900" s="2" t="n">
+        <x:v>3483</x:v>
+      </x:c>
+      <x:c r="B900" s="2" t="str">
+        <x:v>EidolonText403</x:v>
+      </x:c>
+      <x:c r="C900" s="3" t="str">
+        <x:v>연결한 서버의 모델을 준비한 뒤 모델 목록을 새로고침해 주세요.</x:v>
+      </x:c>
+      <x:c r="D900" s="3" t="str">
+        <x:v>Prepare a model on your connected server, then refresh the model list.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="901">
+      <x:c r="A901" s="2" t="n">
+        <x:v>3484</x:v>
+      </x:c>
+      <x:c r="B901" s="2" t="str">
+        <x:v>EidolonText404</x:v>
+      </x:c>
+      <x:c r="C901" s="3" t="str">
+        <x:v>모델 목록 확인</x:v>
+      </x:c>
+      <x:c r="D901" s="3" t="str">
+        <x:v>View models</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="902">
+      <x:c r="A902" s="2" t="n">
+        <x:v>3485</x:v>
+      </x:c>
+      <x:c r="B902" s="2" t="str">
+        <x:v>EidolonText405</x:v>
+      </x:c>
+      <x:c r="C902" s="3" t="str">
+        <x:v>먼저 엔진 설치 또는 서버 연결을 완료해 주세요.</x:v>
+      </x:c>
+      <x:c r="D902" s="3" t="str">
+        <x:v>First install the engine or connect to a server.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="903">
+      <x:c r="A903" s="2" t="n">
+        <x:v>3486</x:v>
+      </x:c>
+      <x:c r="B903" s="2" t="str">
+        <x:v>EidolonText406</x:v>
+      </x:c>
+      <x:c r="C903" s="3" t="str">
+        <x:v>엔진 설치 완료 · 연결 필요</x:v>
+      </x:c>
+      <x:c r="D903" s="3" t="str">
+        <x:v>Engine installed · connect to continue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="904">
+      <x:c r="A904" s="2" t="n">
+        <x:v>3487</x:v>
+      </x:c>
+      <x:c r="B904" s="2" t="str">
+        <x:v>EidolonText407</x:v>
+      </x:c>
+      <x:c r="C904" s="3" t="str">
+        <x:v>엔진 준비하기</x:v>
+      </x:c>
+      <x:c r="D904" s="3" t="str">
+        <x:v>Prepare engine</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="905">
+      <x:c r="A905" s="2" t="n">
+        <x:v>3488</x:v>
+      </x:c>
+      <x:c r="B905" s="2" t="str">
+        <x:v>EidolonText408</x:v>
+      </x:c>
+      <x:c r="C905" s="3" t="str">
+        <x:v>이미지 생성과 LoRA 학습에 필요한 실행 환경을 준비합니다.</x:v>
+      </x:c>
+      <x:c r="D905" s="3" t="str">
+        <x:v>Prepare the runtime for image generation and LoRA training.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="906">
+      <x:c r="A906" s="2" t="n">
+        <x:v>3489</x:v>
+      </x:c>
+      <x:c r="B906" s="2" t="str">
+        <x:v>EidolonText409</x:v>
+      </x:c>
+      <x:c r="C906" s="3" t="str">
+        <x:v>파일 가져오기</x:v>
+      </x:c>
+      <x:c r="D906" s="3" t="str">
+        <x:v>Import file</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="907">
+      <x:c r="A907" s="2" t="n">
+        <x:v>3490</x:v>
+      </x:c>
+      <x:c r="B907" s="2" t="str">
+        <x:v>EidolonText410</x:v>
+      </x:c>
+      <x:c r="C907" s="3" t="str">
+        <x:v>새로고침</x:v>
+      </x:c>
+      <x:c r="D907" s="3" t="str">
+        <x:v>Refresh</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="908">
+      <x:c r="A908" s="2" t="n">
+        <x:v>3491</x:v>
+      </x:c>
+      <x:c r="B908" s="2" t="str">
+        <x:v>EidolonText411</x:v>
+      </x:c>
+      <x:c r="C908" s="3" t="str">
+        <x:v>내 모델 · LoRA</x:v>
+      </x:c>
+      <x:c r="D908" s="3" t="str">
+        <x:v>My models · LoRA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="909">
+      <x:c r="A909" s="2" t="n">
+        <x:v>3492</x:v>
+      </x:c>
+      <x:c r="B909" s="2" t="str">
+        <x:v>EidolonText412</x:v>
+      </x:c>
+      <x:c r="C909" s="3" t="str">
+        <x:v>상세 설정</x:v>
+      </x:c>
+      <x:c r="D909" s="3" t="str">
+        <x:v>Advanced settings</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="910">
+      <x:c r="A910" s="2" t="n">
+        <x:v>3493</x:v>
+      </x:c>
+      <x:c r="B910" s="2" t="str">
+        <x:v>EidolonText413</x:v>
+      </x:c>
+      <x:c r="C910" s="3" t="str">
+        <x:v>계열은 자동 판별합니다. 판별되지 않은 모델만 직접 지정하세요.</x:v>
+      </x:c>
+      <x:c r="D910" s="3" t="str">
+        <x:v>The family is detected automatically. Set it manually only if detection is unavailable.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="911">
+      <x:c r="A911" s="2" t="n">
+        <x:v>3494</x:v>
+      </x:c>
+      <x:c r="B911" s="2" t="str">
+        <x:v>EidolonText414</x:v>
+      </x:c>
+      <x:c r="C911" s="3" t="str">
+        <x:v>모델 계열을 확인해 주세요.</x:v>
+      </x:c>
+      <x:c r="D911" s="3" t="str">
+        <x:v>Check this model's family.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="912">
+      <x:c r="A912" s="2" t="n">
+        <x:v>3495</x:v>
+      </x:c>
+      <x:c r="B912" s="2" t="str">
+        <x:v>EidolonText415</x:v>
+      </x:c>
+      <x:c r="C912" s="3" t="str">
+        <x:v>모델 파일은 삭제되지 않습니다.</x:v>
+      </x:c>
+      <x:c r="D912" s="3" t="str">
+        <x:v>The model file is kept.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="913">
+      <x:c r="A913" s="2" t="n">
+        <x:v>3496</x:v>
+      </x:c>
+      <x:c r="B913" s="2" t="str">
+        <x:v>EidolonText416</x:v>
+      </x:c>
+      <x:c r="C913" s="3" t="str">
+        <x:v>설치 안내</x:v>
+      </x:c>
+      <x:c r="D913" s="3" t="str">
+        <x:v>Installation details</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="914">
+      <x:c r="A914" s="2" t="n">
+        <x:v>3497</x:v>
+      </x:c>
+      <x:c r="B914" s="2" t="str">
+        <x:v>EidolonText417</x:v>
+      </x:c>
+      <x:c r="C914" s="3" t="str">
+        <x:v>연결 안내</x:v>
+      </x:c>
+      <x:c r="D914" s="3" t="str">
+        <x:v>Connection details</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="915">
+      <x:c r="A915" s="2" t="n">
+        <x:v>3498</x:v>
+      </x:c>
+      <x:c r="B915" s="2" t="str">
+        <x:v>EidolonText418</x:v>
+      </x:c>
+      <x:c r="C915" s="3" t="str">
+        <x:v>모델이나 LoRA 파일을 해당 폴더에 넣고 새로고침하면 여기에 표시됩니다.</x:v>
+      </x:c>
+      <x:c r="D915" s="3" t="str">
+        <x:v>Place model or LoRA files in the corresponding folder and refresh to see them here.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="916">
+      <x:c r="A916" s="2" t="n">
+        <x:v>3499</x:v>
+      </x:c>
+      <x:c r="B916" s="2" t="str">
+        <x:v>EidolonText419</x:v>
+      </x:c>
+      <x:c r="C916" s="3" t="str">
+        <x:v>자동 생성</x:v>
+      </x:c>
+      <x:c r="D916" s="3" t="str">
+        <x:v>Random seed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="917">
+      <x:c r="A917" s="2" t="n">
+        <x:v>3500</x:v>
+      </x:c>
+      <x:c r="B917" s="2" t="str">
+        <x:v>EidolonText420</x:v>
+      </x:c>
+      <x:c r="C917" s="3" t="str">
+        <x:v>요청마다 새로운 시드로 생성합니다.</x:v>
+      </x:c>
+      <x:c r="D917" s="3" t="str">
+        <x:v>Each request uses a new random seed.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="918">
+      <x:c r="A918" s="2" t="n">
+        <x:v>3501</x:v>
+      </x:c>
+      <x:c r="B918" s="2" t="str">
+        <x:v>EidolonText421</x:v>
+      </x:c>
+      <x:c r="C918" s="3" t="str">
+        <x:v>시드는 {0}~{1} 사이의 정수를 입력하세요.</x:v>
+      </x:c>
+      <x:c r="D918" s="3" t="str">
+        <x:v>Enter an integer seed between {0} and {1}.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="919">
+      <x:c r="A919" s="2" t="n">
+        <x:v>3502</x:v>
+      </x:c>
+      <x:c r="B919" s="2" t="str">
+        <x:v>EidolonText422</x:v>
+      </x:c>
+      <x:c r="C919" s="3" t="str">
+        <x:v>최근 요청 시드: {0}</x:v>
+      </x:c>
+      <x:c r="D919" s="3" t="str">
+        <x:v>Latest requested seed: {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="920">
+      <x:c r="A920" s="2" t="n">
+        <x:v>3503</x:v>
+      </x:c>
+      <x:c r="B920" s="2" t="str">
+        <x:v>EidolonText423</x:v>
+      </x:c>
+      <x:c r="C920" s="3" t="str">
+        <x:v>LoRA (선택)</x:v>
+      </x:c>
+      <x:c r="D920" s="3" t="str">
+        <x:v>LoRA (optional)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="921">
+      <x:c r="A921" s="2" t="n">
+        <x:v>3504</x:v>
+      </x:c>
+      <x:c r="B921" s="2" t="str">
+        <x:v>EidolonText424</x:v>
+      </x:c>
+      <x:c r="C921" s="3" t="str">
+        <x:v>왼쪽에서 이미지를 선택하면 크게 볼 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D921" s="3" t="str">
+        <x:v>Select an image on the left to view it here.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="922">
+      <x:c r="A922" s="2" t="n">
+        <x:v>3505</x:v>
+      </x:c>
+      <x:c r="B922" s="2" t="str">
+        <x:v>EidolonText425</x:v>
+      </x:c>
+      <x:c r="C922" s="3" t="str">
+        <x:v>학습 이미지 배경</x:v>
+      </x:c>
+      <x:c r="D922" s="3" t="str">
+        <x:v>Training image background</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="923">
+      <x:c r="A923" s="2" t="n">
+        <x:v>3506</x:v>
+      </x:c>
+      <x:c r="B923" s="2" t="str">
+        <x:v>EidolonText426</x:v>
+      </x:c>
+      <x:c r="C923" s="3" t="str">
+        <x:v>원본 유지</x:v>
+      </x:c>
+      <x:c r="D923" s="3" t="str">
+        <x:v>Keep original</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="924">
+      <x:c r="A924" s="2" t="n">
+        <x:v>3507</x:v>
+      </x:c>
+      <x:c r="B924" s="2" t="str">
+        <x:v>EidolonText427</x:v>
+      </x:c>
+      <x:c r="C924" s="3" t="str">
+        <x:v>흰색</x:v>
+      </x:c>
+      <x:c r="D924" s="3" t="str">
+        <x:v>White</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="925">
+      <x:c r="A925" s="2" t="n">
+        <x:v>3508</x:v>
+      </x:c>
+      <x:c r="B925" s="2" t="str">
+        <x:v>EidolonText428</x:v>
+      </x:c>
+      <x:c r="C925" s="3" t="str">
+        <x:v>검정색</x:v>
+      </x:c>
+      <x:c r="D925" s="3" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="926">
+      <x:c r="A926" s="2" t="n">
+        <x:v>3509</x:v>
+      </x:c>
+      <x:c r="B926" s="2" t="str">
+        <x:v>EidolonText429</x:v>
+      </x:c>
+      <x:c r="C926" s="3" t="str">
+        <x:v>투명 영역을 선택한 색으로 채웁니다. 이미 있는 배경과 원본 이미지·설명은 유지합니다.</x:v>
+      </x:c>
+      <x:c r="D926" s="3" t="str">
+        <x:v>Fill transparent areas with the selected color. Existing backgrounds, original images and captions are preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="927">
+      <x:c r="A927" s="2" t="n">
+        <x:v>3510</x:v>
+      </x:c>
+      <x:c r="B927" s="2" t="str">
+        <x:v>EidolonText430</x:v>
+      </x:c>
+      <x:c r="C927" s="3" t="str">
+        <x:v>학습 이미지 배경을 선택하세요.</x:v>
+      </x:c>
+      <x:c r="D927" s="3" t="str">
+        <x:v>Select a training image background.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="928">
+      <x:c r="A928" s="2" t="n">
+        <x:v>3511</x:v>
+      </x:c>
+      <x:c r="B928" s="2" t="str">
+        <x:v>EidolonText431</x:v>
+      </x:c>
+      <x:c r="C928" s="3" t="str">
+        <x:v>학습 이미지 배경을 처리하지 못했습니다: {0}</x:v>
+      </x:c>
+      <x:c r="D928" s="3" t="str">
+        <x:v>Could not prepare the training image background: {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="929">
+      <x:c r="A929" s="2" t="n">
+        <x:v>3512</x:v>
+      </x:c>
+      <x:c r="B929" s="2" t="str">
+        <x:v>EidolonText432</x:v>
+      </x:c>
+      <x:c r="C929" s="3" t="str">
+        <x:v>LoRA 이름·파일명·트리거 검색</x:v>
+      </x:c>
+      <x:c r="D929" s="3" t="str">
+        <x:v>Search LoRA name, filename or trigger</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="930">
+      <x:c r="A930" s="2" t="n">
+        <x:v>3513</x:v>
+      </x:c>
+      <x:c r="B930" s="2" t="str">
+        <x:v>EidolonText433</x:v>
+      </x:c>
+      <x:c r="C930" s="3" t="str">
+        <x:v>검색한 LoRA가 없습니다.</x:v>
+      </x:c>
+      <x:c r="D930" s="3" t="str">
+        <x:v>No matching LoRAs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="931">
+      <x:c r="A931" s="2" t="n">
+        <x:v>3514</x:v>
+      </x:c>
+      <x:c r="B931" s="2" t="str">
+        <x:v>EidolonText434</x:v>
+      </x:c>
+      <x:c r="C931" s="3" t="str">
+        <x:v>{0}개 LoRA 적용 중</x:v>
+      </x:c>
+      <x:c r="D931" s="3" t="str">
+        <x:v>{0} LoRAs applied</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="932">
+      <x:c r="A932" s="2" t="n">
+        <x:v>3515</x:v>
+      </x:c>
+      <x:c r="B932" s="2" t="str">
+        <x:v>EidolonText435</x:v>
+      </x:c>
+      <x:c r="C932" s="3" t="str">
+        <x:v>적용 중</x:v>
+      </x:c>
+      <x:c r="D932" s="3" t="str">
+        <x:v>Applied</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="933">
+      <x:c r="A933" s="2" t="n">
+        <x:v>3516</x:v>
+      </x:c>
+      <x:c r="B933" s="2" t="str">
+        <x:v>EidolonText436</x:v>
+      </x:c>
+      <x:c r="C933" s="3" t="str">
+        <x:v>공통 생성 지침</x:v>
+      </x:c>
+      <x:c r="D933" s="3" t="str">
+        <x:v>Shared generation guidelines</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="934">
+      <x:c r="A934" s="2" t="n">
+        <x:v>3517</x:v>
+      </x:c>
+      <x:c r="B934" s="2" t="str">
+        <x:v>EidolonText437</x:v>
+      </x:c>
+      <x:c r="C934" s="3" t="str">
+        <x:v>설정에 저장한 생성 지침과 제외할 요소가 적용됩니다.</x:v>
+      </x:c>
+      <x:c r="D934" s="3" t="str">
+        <x:v>The generation instructions and elements to avoid saved in settings are applied.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="935">
+      <x:c r="A935" s="2" t="n">
+        <x:v>3518</x:v>
+      </x:c>
+      <x:c r="B935" s="2" t="str">
+        <x:v>EidolonText438</x:v>
+      </x:c>
+      <x:c r="C935" s="3" t="str">
+        <x:v>생성하기</x:v>
+      </x:c>
+      <x:c r="D935" s="3" t="str">
+        <x:v>Generate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="936">
+      <x:c r="A936" s="2" t="n">
+        <x:v>3519</x:v>
+      </x:c>
+      <x:c r="B936" s="2" t="str">
+        <x:v>EidolonText439</x:v>
+      </x:c>
+      <x:c r="C936" s="3" t="str">
+        <x:v>미리보기</x:v>
+      </x:c>
+      <x:c r="D936" s="3" t="str">
+        <x:v>Preview</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="937">
+      <x:c r="A937" s="2" t="n">
+        <x:v>3520</x:v>
+      </x:c>
+      <x:c r="B937" s="2" t="str">
+        <x:v>EidolonText440</x:v>
+      </x:c>
+      <x:c r="C937" s="3" t="str">
+        <x:v>참고 이미지</x:v>
+      </x:c>
+      <x:c r="D937" s="3" t="str">
+        <x:v>Reference image</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="938">
+      <x:c r="A938" s="2" t="n">
+        <x:v>3521</x:v>
+      </x:c>
+      <x:c r="B938" s="2" t="str">
+        <x:v>EidolonText441</x:v>
+      </x:c>
+      <x:c r="C938" s="3" t="str">
+        <x:v>참고 이미지 추가</x:v>
+      </x:c>
+      <x:c r="D938" s="3" t="str">
+        <x:v>Add reference image</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="939">
+      <x:c r="A939" s="2" t="n">
+        <x:v>3522</x:v>
+      </x:c>
+      <x:c r="B939" s="2" t="str">
+        <x:v>EidolonText442</x:v>
+      </x:c>
+      <x:c r="C939" s="3" t="str">
+        <x:v>이미지 변경</x:v>
+      </x:c>
+      <x:c r="D939" s="3" t="str">
+        <x:v>Change image</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="940">
+      <x:c r="A940" s="2" t="n">
+        <x:v>3523</x:v>
+      </x:c>
+      <x:c r="B940" s="2" t="str">
+        <x:v>EidolonText443</x:v>
+      </x:c>
+      <x:c r="C940" s="3" t="str">
+        <x:v>제거</x:v>
+      </x:c>
+      <x:c r="D940" s="3" t="str">
+        <x:v>Remove</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="941">
+      <x:c r="A941" s="2" t="n">
+        <x:v>3524</x:v>
+      </x:c>
+      <x:c r="B941" s="2" t="str">
+        <x:v>EidolonText444</x:v>
+      </x:c>
+      <x:c r="C941" s="3" t="str">
+        <x:v>참고해 새로 생성</x:v>
+      </x:c>
+      <x:c r="D941" s="3" t="str">
+        <x:v>Reimagine from image</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="942">
+      <x:c r="A942" s="2" t="n">
+        <x:v>3525</x:v>
+      </x:c>
+      <x:c r="B942" s="2" t="str">
+        <x:v>EidolonText445</x:v>
+      </x:c>
+      <x:c r="C942" s="3" t="str">
+        <x:v>그림체 변경</x:v>
+      </x:c>
+      <x:c r="D942" s="3" t="str">
+        <x:v>Change style</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="943">
+      <x:c r="A943" s="2" t="n">
+        <x:v>3526</x:v>
+      </x:c>
+      <x:c r="B943" s="2" t="str">
+        <x:v>EidolonText446</x:v>
+      </x:c>
+      <x:c r="C943" s="3" t="str">
+        <x:v>원본 이미지를 바탕으로 설명에 맞는 새로운 이미지를 만듭니다.</x:v>
+      </x:c>
+      <x:c r="D943" s="3" t="str">
+        <x:v>Create a new image based on the reference and your description.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="944">
+      <x:c r="A944" s="2" t="n">
+        <x:v>3527</x:v>
+      </x:c>
+      <x:c r="B944" s="2" t="str">
+        <x:v>EidolonText447</x:v>
+      </x:c>
+      <x:c r="C944" s="3" t="str">
+        <x:v>대상과 구도를 최대한 유지하며 원하는 그림체를 적용합니다. 설명에 바꿀 스타일을 적어주세요.</x:v>
+      </x:c>
+      <x:c r="D944" s="3" t="str">
+        <x:v>Keep the subject and composition as closely as possible while applying the style described in your prompt.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="945">
+      <x:c r="A945" s="2" t="n">
+        <x:v>3528</x:v>
+      </x:c>
+      <x:c r="B945" s="2" t="str">
+        <x:v>EidolonText448</x:v>
+      </x:c>
+      <x:c r="C945" s="3" t="str">
+        <x:v>변경 강도</x:v>
+      </x:c>
+      <x:c r="D945" s="3" t="str">
+        <x:v>Change strength</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="946">
+      <x:c r="A946" s="2" t="n">
+        <x:v>3529</x:v>
+      </x:c>
+      <x:c r="B946" s="2" t="str">
+        <x:v>EidolonText449</x:v>
+      </x:c>
+      <x:c r="C946" s="3" t="str">
+        <x:v>낮을수록 원본 유지 · 높을수록 큰 변화</x:v>
+      </x:c>
+      <x:c r="D946" s="3" t="str">
+        <x:v>Lower preserves the original · higher makes larger changes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="947">
+      <x:c r="A947" s="2" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="B947" s="2" t="str">
+        <x:v>EidolonText450</x:v>
+      </x:c>
+      <x:c r="C947" s="3" t="str">
+        <x:v>이미지를 읽을 수 없습니다. 32 MB·4천만 픽셀 이하의 PNG, JPG, WebP 파일을 선택해주세요.</x:v>
+      </x:c>
+      <x:c r="D947" s="3" t="str">
+        <x:v>Cannot read this image. Choose a PNG, JPG, or WebP file up to 32 MB and 40 million pixels.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="948">
+      <x:c r="A948" s="2" t="n">
+        <x:v>3531</x:v>
+      </x:c>
+      <x:c r="B948" s="2" t="str">
+        <x:v>EidolonText451</x:v>
+      </x:c>
+      <x:c r="C948" s="3" t="str">
+        <x:v>참고 이미지의 모드와 변경 강도를 확인해주세요. 변경 강도는 5~95%로 설정할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D948" s="3" t="str">
+        <x:v>Check the reference mode and change strength. Strength must be between 5% and 95%.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="949">
+      <x:c r="A949" s="2" t="n">
+        <x:v>3532</x:v>
+      </x:c>
+      <x:c r="B949" s="2" t="str">
+        <x:v>EidolonText452</x:v>
+      </x:c>
+      <x:c r="C949" s="3" t="str">
+        <x:v>참고 이미지 준비 중</x:v>
+      </x:c>
+      <x:c r="D949" s="3" t="str">
+        <x:v>Preparing reference image</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="950">
+      <x:c r="A950" s="2" t="n">
+        <x:v>3533</x:v>
+      </x:c>
+      <x:c r="B950" s="2" t="str">
+        <x:v>EidolonText453</x:v>
+      </x:c>
+      <x:c r="C950" s="3" t="str">
+        <x:v>참고 이미지를 생성 엔진에 전송 중</x:v>
+      </x:c>
+      <x:c r="D950" s="3" t="str">
+        <x:v>Uploading reference image to the generation engine</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="951">
+      <x:c r="A951" s="2" t="n">
+        <x:v>3534</x:v>
+      </x:c>
+      <x:c r="B951" s="2" t="str">
+        <x:v>EidolonText454</x:v>
+      </x:c>
+      <x:c r="C951" s="3" t="str">
+        <x:v>이 결과의 참고 이미지를 찾거나 읽을 수 없습니다. 이미지를 다시 선택해주세요.</x:v>
+      </x:c>
+      <x:c r="D951" s="3" t="str">
+        <x:v>The reference image for this result cannot be found or read. Select an image again.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="952">
+      <x:c r="A952" s="2" t="n">
+        <x:v>3535</x:v>
+      </x:c>
+      <x:c r="B952" s="2" t="str">
+        <x:v>EidolonText455</x:v>
+      </x:c>
+      <x:c r="C952" s="3" t="str">
+        <x:v>이 이미지로 편집</x:v>
+      </x:c>
+      <x:c r="D952" s="3" t="str">
+        <x:v>Edit from this image</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="953">
+      <x:c r="A953" s="2" t="n">
+        <x:v>3536</x:v>
+      </x:c>
+      <x:c r="B953" s="2" t="str">
+        <x:v>EidolonText456</x:v>
+      </x:c>
+      <x:c r="C953" s="3" t="str">
+        <x:v>이미지 편집</x:v>
+      </x:c>
+      <x:c r="D953" s="3" t="str">
+        <x:v>Image editing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="954">
+      <x:c r="A954" s="2" t="n">
+        <x:v>3537</x:v>
+      </x:c>
+      <x:c r="B954" s="2" t="str">
+        <x:v>EidolonText457</x:v>
+      </x:c>
+      <x:c r="C954" s="3" t="str">
+        <x:v>어떻게 바꿀까요?</x:v>
+      </x:c>
+      <x:c r="D954" s="3" t="str">
+        <x:v>How should it change?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="955">
+      <x:c r="A955" s="2" t="n">
+        <x:v>3538</x:v>
+      </x:c>
+      <x:c r="B955" s="2" t="str">
+        <x:v>EidolonText458</x:v>
+      </x:c>
+      <x:c r="C955" s="3" t="str">
+        <x:v>예: 대상과 구도를 유지하고 수채화풍으로 바꿔줘</x:v>
+      </x:c>
+      <x:c r="D955" s="3" t="str">
+        <x:v>Example: Keep the subject and composition, and change it to a watercolor illustration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="956">
+      <x:c r="A956" s="2" t="n">
+        <x:v>3539</x:v>
+      </x:c>
+      <x:c r="B956" s="2" t="str">
+        <x:v>EidolonText459</x:v>
+      </x:c>
+      <x:c r="C956" s="3" t="str">
+        <x:v>편집할 이미지를 먼저 선택해주세요.</x:v>
+      </x:c>
+      <x:c r="D956" s="3" t="str">
+        <x:v>Select the image you want to edit first.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="957">
+      <x:c r="A957" s="2" t="n">
+        <x:v>3540</x:v>
+      </x:c>
+      <x:c r="B957" s="2" t="str">
+        <x:v>EidolonText460</x:v>
+      </x:c>
+      <x:c r="C957" s="3" t="str">
+        <x:v>저장 폴더 선택</x:v>
+      </x:c>
+      <x:c r="D957" s="3" t="str">
+        <x:v>Choose output folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="958">
       <x:c r="A958" s="2" t="n">
         <x:v>3541</x:v>
       </x:c>
@@ -17116,7 +17116,7 @@
         <x:v>White background</x:v>
       </x:c>
     </x:row>
-    <x:row r="959" spans="1:4">
+    <x:row r="959">
       <x:c r="A959" s="2" t="n">
         <x:v>3542</x:v>
       </x:c>
@@ -17130,7 +17130,7 @@
         <x:v>Black background</x:v>
       </x:c>
     </x:row>
-    <x:row r="960" spans="1:4">
+    <x:row r="960">
       <x:c r="A960" s="2" t="n">
         <x:v>3543</x:v>
       </x:c>
@@ -17144,7 +17144,7 @@
         <x:v>Add images</x:v>
       </x:c>
     </x:row>
-    <x:row r="961" spans="1:4">
+    <x:row r="961">
       <x:c r="A961" s="2" t="n">
         <x:v>3544</x:v>
       </x:c>
@@ -17158,7 +17158,7 @@
         <x:v>Add folder</x:v>
       </x:c>
     </x:row>
-    <x:row r="962" spans="1:4">
+    <x:row r="962">
       <x:c r="A962" s="2" t="n">
         <x:v>3545</x:v>
       </x:c>
@@ -17172,7 +17172,7 @@
         <x:v>{0} images</x:v>
       </x:c>
     </x:row>
-    <x:row r="963" spans="1:4">
+    <x:row r="963">
       <x:c r="A963" s="2" t="n">
         <x:v>3546</x:v>
       </x:c>
@@ -17186,7 +17186,7 @@
         <x:v>{0} images · One LoRA</x:v>
       </x:c>
     </x:row>
-    <x:row r="964" spans="1:4">
+    <x:row r="964">
       <x:c r="A964" s="2" t="n">
         <x:v>3547</x:v>
       </x:c>
@@ -17200,7 +17200,7 @@
         <x:v>Add images to begin.</x:v>
       </x:c>
     </x:row>
-    <x:row r="965" spans="1:4">
+    <x:row r="965">
       <x:c r="A965" s="2" t="n">
         <x:v>3548</x:v>
       </x:c>
@@ -17214,7 +17214,7 @@
         <x:v>Both lists are trained together into one LoRA. Only transparent areas are filled with the selected background color. Existing backgrounds and source files are preserved.</x:v>
       </x:c>
     </x:row>
-    <x:row r="966" spans="1:4">
+    <x:row r="966">
       <x:c r="A966" s="2" t="n">
         <x:v>3549</x:v>
       </x:c>
@@ -17228,7 +17228,7 @@
         <x:v>Clear list</x:v>
       </x:c>
     </x:row>
-    <x:row r="967" spans="1:4">
+    <x:row r="967">
       <x:c r="A967" s="2" t="n">
         <x:v>3550</x:v>
       </x:c>
@@ -17242,7 +17242,7 @@
         <x:v>Add training images.</x:v>
       </x:c>
     </x:row>
-    <x:row r="968" spans="1:4">
+    <x:row r="968">
       <x:c r="A968" s="2" t="n">
         <x:v>3551</x:v>
       </x:c>
@@ -17256,7 +17256,7 @@
         <x:v>Create training folder</x:v>
       </x:c>
     </x:row>
-    <x:row r="969" spans="1:4">
+    <x:row r="969">
       <x:c r="A969" s="2" t="n">
         <x:v>3552</x:v>
       </x:c>
@@ -17270,7 +17270,7 @@
         <x:v>Choose where to save the training folder</x:v>
       </x:c>
     </x:row>
-    <x:row r="970" spans="1:4">
+    <x:row r="970">
       <x:c r="A970" s="2" t="n">
         <x:v>3553</x:v>
       </x:c>
@@ -17284,7 +17284,7 @@
         <x:v>Prepared {0} images and caption files.</x:v>
       </x:c>
     </x:row>
-    <x:row r="971" spans="1:4">
+    <x:row r="971">
       <x:c r="A971" s="2" t="n">
         <x:v>3554</x:v>
       </x:c>
@@ -17298,7 +17298,7 @@
         <x:v>Train</x:v>
       </x:c>
     </x:row>
-    <x:row r="972" spans="1:4">
+    <x:row r="972">
       <x:c r="A972" s="2" t="n">
         <x:v>3555</x:v>
       </x:c>
@@ -17312,7 +17312,7 @@
         <x:v>Loading images.</x:v>
       </x:c>
     </x:row>
-    <x:row r="973" spans="1:4">
+    <x:row r="973">
       <x:c r="A973" s="2" t="n">
         <x:v>3556</x:v>
       </x:c>
@@ -17326,7 +17326,7 @@
         <x:v>Change an image style</x:v>
       </x:c>
     </x:row>
-    <x:row r="974" spans="1:4">
+    <x:row r="974">
       <x:c r="A974" s="2" t="n">
         <x:v>3557</x:v>
       </x:c>
@@ -17334,13 +17334,13 @@
         <x:v>EidolonText477</x:v>
       </x:c>
       <x:c r="C974" s="3" t="str">
-        <x:v>이미지 편집 탭에서 참고 이미지를 선택하고 원하는 그림체를 설명합니다. 모델과 LoRA를 고른 뒤 대기열에 추가하세요. 생성 결과에서도 이미지 편집 버튼으로 시작할 수 있습니다.</x:v>
+        <x:v>원본 이미지와 수정 설명을 입력해 편집을 요청합니다. ComfyUI는 선택 모델·LoRA와 변경 강도를 사용하고, Codex는 원본과 수정 설명을 함께 전달합니다. 원본은 보존하고 결과는 새 이미지로 저장합니다.</x:v>
       </x:c>
       <x:c r="D974" s="3" t="str">
-        <x:v>Select a reference image in the image editing tab and describe the style you want. Choose a model and LoRAs, then add the request to the queue. You can also start with the image editing action in the result gallery.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="975" spans="1:4">
+        <x:v>Provide a source image and edit instructions. ComfyUI uses the selected model, LoRAs and change strength; Codex receives the image and instructions. The source is preserved and the result is saved as a new image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="975">
       <x:c r="A975" s="2" t="n">
         <x:v>3559</x:v>
       </x:c>
@@ -17354,7 +17354,7 @@
         <x:v>Lower change strength retains more of the original; higher strength applies more of the new style and description. Exact shape or composition is not guaranteed. The source file is preserved.</x:v>
       </x:c>
     </x:row>
-    <x:row r="976" spans="1:4">
+    <x:row r="976">
       <x:c r="A976" s="2" t="n">
         <x:v>3560</x:v>
       </x:c>
@@ -17368,7 +17368,7 @@
         <x:v>You can also add a reference image in the generation tab to create a new image from your description and reference. Remove the reference to generate from text alone.</x:v>
       </x:c>
     </x:row>
-    <x:row r="977" spans="1:4">
+    <x:row r="977">
       <x:c r="A977" s="2" t="n">
         <x:v>3561</x:v>
       </x:c>
@@ -17382,7 +17382,7 @@
         <x:v>Quick: {0} steps · Standard: {1} steps</x:v>
       </x:c>
     </x:row>
-    <x:row r="978" spans="1:4">
+    <x:row r="978">
       <x:c r="A978" s="2" t="n">
         <x:v>3562</x:v>
       </x:c>
@@ -17396,7 +17396,7 @@
         <x:v>Could not distinguish the subject from the background. Turn off background removal or try another image.</x:v>
       </x:c>
     </x:row>
-    <x:row r="979" spans="1:4">
+    <x:row r="979">
       <x:c r="A979" s="2" t="n">
         <x:v>3563</x:v>
       </x:c>
@@ -17410,7 +17410,7 @@
         <x:v>Select images</x:v>
       </x:c>
     </x:row>
-    <x:row r="980" spans="1:4">
+    <x:row r="980">
       <x:c r="A980" s="2" t="n">
         <x:v>3564</x:v>
       </x:c>
@@ -17424,7 +17424,7 @@
         <x:v>Name and trigger</x:v>
       </x:c>
     </x:row>
-    <x:row r="981" spans="1:4">
+    <x:row r="981">
       <x:c r="A981" s="2" t="n">
         <x:v>3565</x:v>
       </x:c>
@@ -17438,7 +17438,7 @@
         <x:v>Prepare folder</x:v>
       </x:c>
     </x:row>
-    <x:row r="982" spans="1:4">
+    <x:row r="982">
       <x:c r="A982" s="2" t="n">
         <x:v>3566</x:v>
       </x:c>
@@ -17452,7 +17452,7 @@
         <x:v>Review captions</x:v>
       </x:c>
     </x:row>
-    <x:row r="983" spans="1:4">
+    <x:row r="983">
       <x:c r="A983" s="2" t="n">
         <x:v>3567</x:v>
       </x:c>
@@ -17466,7 +17466,7 @@
         <x:v>Train</x:v>
       </x:c>
     </x:row>
-    <x:row r="984" spans="1:4">
+    <x:row r="984">
       <x:c r="A984" s="2" t="n">
         <x:v>3568</x:v>
       </x:c>
@@ -17480,7 +17480,7 @@
         <x:v>Step {0} of {1}</x:v>
       </x:c>
     </x:row>
-    <x:row r="985" spans="1:4">
+    <x:row r="985">
       <x:c r="A985" s="2" t="n">
         <x:v>3569</x:v>
       </x:c>
@@ -17494,7 +17494,7 @@
         <x:v>Previous</x:v>
       </x:c>
     </x:row>
-    <x:row r="986" spans="1:4">
+    <x:row r="986">
       <x:c r="A986" s="2" t="n">
         <x:v>3570</x:v>
       </x:c>
@@ -17508,7 +17508,7 @@
         <x:v>Next</x:v>
       </x:c>
     </x:row>
-    <x:row r="987" spans="1:4">
+    <x:row r="987">
       <x:c r="A987" s="2" t="n">
         <x:v>3571</x:v>
       </x:c>
@@ -17522,7 +17522,7 @@
         <x:v>Open training folder</x:v>
       </x:c>
     </x:row>
-    <x:row r="988" spans="1:4">
+    <x:row r="988">
       <x:c r="A988" s="2" t="n">
         <x:v>3572</x:v>
       </x:c>
@@ -17536,7 +17536,7 @@
         <x:v>Choose images of the same style or subject. Add images to each list according to whether their transparent areas should be filled with white or black.</x:v>
       </x:c>
     </x:row>
-    <x:row r="989" spans="1:4">
+    <x:row r="989">
       <x:c r="A989" s="2" t="n">
         <x:v>3573</x:v>
       </x:c>
@@ -17550,7 +17550,7 @@
         <x:v>Choose a recognizable LoRA name and a trigger word for generation. Selecting this LoRA automatically adds its trigger to the beginning of the prompt.</x:v>
       </x:c>
     </x:row>
-    <x:row r="990" spans="1:4">
+    <x:row r="990">
       <x:c r="A990" s="2" t="n">
         <x:v>3574</x:v>
       </x:c>
@@ -17558,13 +17558,13 @@
         <x:v>EidolonText494</x:v>
       </x:c>
       <x:c r="C990" s="3" t="str">
-        <x:v>원본 이미지에 같은 이름의 .txt가 있으면 그 설명을 먼저 사용합니다. 없는 이미지는 공통 설명과 트리거로 설명 파일을 만듭니다.</x:v>
+        <x:v>이미지별 .txt 설명 → 이미지 옆 프롬프트 JSON → 공통 설명 → 직접 붙인 파일명 순서로 사용합니다. 자동 시각·GUID 파일명은 설명에서 제외하고 트리거는 자동 추가합니다.</x:v>
       </x:c>
       <x:c r="D990" s="3" t="str">
-        <x:v>An existing .txt file with the same name as an image takes priority. Images without one receive a caption from the common description and trigger.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="991" spans="1:4">
+        <x:v>Caption priority is a matching .txt, prompt JSON beside the image, shared description, then a descriptive filename. Automatic timestamp and GUID names are excluded. The trigger is added automatically.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="991">
       <x:c r="A991" s="2" t="n">
         <x:v>3575</x:v>
       </x:c>
@@ -17572,13 +17572,13 @@
         <x:v>EidolonText495</x:v>
       </x:c>
       <x:c r="C991" s="3" t="str">
-        <x:v>이 이름과 트리거로 학습 폴더를 준비합니다.</x:v>
+        <x:v>이름·트리거와 자동 입력한 설명을 확인하고 다음으로 진행하세요.</x:v>
       </x:c>
       <x:c r="D991" s="3" t="str">
-        <x:v>The training folder will use this name and trigger.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="992" spans="1:4">
+        <x:v>Review the name, trigger and automatically filled description, then continue.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="992">
       <x:c r="A992" s="2" t="n">
         <x:v>3576</x:v>
       </x:c>
@@ -17592,7 +17592,7 @@
         <x:v>Combine the selected images and create a .txt caption for each one. Choose a save location to create a new subfolder. Source files are preserved.</x:v>
       </x:c>
     </x:row>
-    <x:row r="993" spans="1:4">
+    <x:row r="993">
       <x:c r="A993" s="2" t="n">
         <x:v>3577</x:v>
       </x:c>
@@ -17606,7 +17606,7 @@
         <x:v>Prepare the training folder first.</x:v>
       </x:c>
     </x:row>
-    <x:row r="994" spans="1:4">
+    <x:row r="994">
       <x:c r="A994" s="2" t="n">
         <x:v>3578</x:v>
       </x:c>
@@ -17620,7 +17620,7 @@
         <x:v>The folder is ready. Review its caption files in the next step.</x:v>
       </x:c>
     </x:row>
-    <x:row r="995" spans="1:4">
+    <x:row r="995">
       <x:c r="A995" s="2" t="n">
         <x:v>3579</x:v>
       </x:c>
@@ -17634,7 +17634,7 @@
         <x:v>Preparing the training folder.</x:v>
       </x:c>
     </x:row>
-    <x:row r="996" spans="1:4">
+    <x:row r="996">
       <x:c r="A996" s="2" t="n">
         <x:v>3580</x:v>
       </x:c>
@@ -17648,7 +17648,7 @@
         <x:v>The images, name, trigger, or description have changed. Create a new training folder.</x:v>
       </x:c>
     </x:row>
-    <x:row r="997" spans="1:4">
+    <x:row r="997">
       <x:c r="A997" s="2" t="n">
         <x:v>3581</x:v>
       </x:c>
@@ -17662,7 +17662,7 @@
         <x:v>Continue when you have reviewed the caption files.</x:v>
       </x:c>
     </x:row>
-    <x:row r="998" spans="1:4">
+    <x:row r="998">
       <x:c r="A998" s="2" t="n">
         <x:v>3582</x:v>
       </x:c>
@@ -17676,7 +17676,7 @@
         <x:v>a sword with a golden hilt</x:v>
       </x:c>
     </x:row>
-    <x:row r="999" spans="1:4">
+    <x:row r="999">
       <x:c r="A999" s="2" t="n">
         <x:v>3583</x:v>
       </x:c>
@@ -17690,7 +17690,7 @@
         <x:v>Caption example</x:v>
       </x:c>
     </x:row>
-    <x:row r="1000" spans="1:4">
+    <x:row r="1000">
       <x:c r="A1000" s="2" t="n">
         <x:v>3584</x:v>
       </x:c>
@@ -17698,13 +17698,13 @@
         <x:v>EidolonText504</x:v>
       </x:c>
       <x:c r="C1000" s="3" t="str">
-        <x:v>이미지 선택부터 설명 확인까지, 순서대로 LoRA 하나를 준비합니다.</x:v>
+        <x:v>이미지를 고르면 설명을 채우고 학습 데이터는 내부에서 자동 준비합니다. 완료된 LoRA는 생성에서 선택하세요.</x:v>
       </x:c>
       <x:c r="D1000" s="3" t="str">
-        <x:v>Prepare one LoRA, from selecting images to reviewing captions.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1001" spans="1:4">
+        <x:v>Selecting images fills the description, and training data is prepared automatically. Select the completed LoRA when generating.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1001">
       <x:c r="A1001" s="2" t="n">
         <x:v>3585</x:v>
       </x:c>
@@ -17718,7 +17718,7 @@
         <x:v>Open the training folder, edit the .txt file beside each image in a text editor, and save it. Describe the objects, colors, and features after the trigger.</x:v>
       </x:c>
     </x:row>
-    <x:row r="1002" spans="1:4">
+    <x:row r="1002">
       <x:c r="A1002" s="2" t="n">
         <x:v>3586</x:v>
       </x:c>
@@ -17732,7 +17732,7 @@
         <x:v>Training uses the saved captions. Changing the selected images, name, trigger, or common description requires preparing a new folder.</x:v>
       </x:c>
     </x:row>
-    <x:row r="1003" spans="1:4">
+    <x:row r="1003">
       <x:c r="A1003" s="2" t="n">
         <x:v>3587</x:v>
       </x:c>
@@ -17746,7 +17746,7 @@
         <x:v>Select a model from the same family as the model you will use for generation.</x:v>
       </x:c>
     </x:row>
-    <x:row r="1004" spans="1:4">
+    <x:row r="1004">
       <x:c r="A1004" s="2" t="n">
         <x:v>3588</x:v>
       </x:c>
@@ -17760,7 +17760,7 @@
         <x:v>Continue training (optional)</x:v>
       </x:c>
     </x:row>
-    <x:row r="1005" spans="1:4">
+    <x:row r="1005">
       <x:c r="A1005" s="2" t="n">
         <x:v>3589</x:v>
       </x:c>
@@ -17774,7 +17774,7 @@
         <x:v>Prompt presets</x:v>
       </x:c>
     </x:row>
-    <x:row r="1006" spans="1:4">
+    <x:row r="1006">
       <x:c r="A1006" s="2" t="n">
         <x:v>3590</x:v>
       </x:c>
@@ -17788,7 +17788,7 @@
         <x:v>Select a saved preset</x:v>
       </x:c>
     </x:row>
-    <x:row r="1007" spans="1:4">
+    <x:row r="1007">
       <x:c r="A1007" s="2" t="n">
         <x:v>3591</x:v>
       </x:c>
@@ -17796,13 +17796,13 @@
         <x:v>EidolonText511</x:v>
       </x:c>
       <x:c r="C1007" s="3" t="str">
-        <x:v>프리셋을 선택하면 생성 지침과 제외할 요소를 불러옵니다. 설정을 저장한 뒤 생성·편집에 적용됩니다.</x:v>
+        <x:v>프리셋을 선택하면 생성 지침과 제외할 요소를 불러옵니다. 생성 환경을 저장한 뒤 생성·편집에 적용됩니다.</x:v>
       </x:c>
       <x:c r="D1007" s="3" t="str">
-        <x:v>Selecting a preset loads its generation instructions and exclusions. Save settings to apply them to generation and editing.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1008" spans="1:4">
+        <x:v>Selecting a preset loads its guidelines and exclusions. Save the generation environment to apply them to generation and editing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1008">
       <x:c r="A1008" s="2" t="n">
         <x:v>3592</x:v>
       </x:c>
@@ -17816,7 +17816,7 @@
         <x:v>Preset name</x:v>
       </x:c>
     </x:row>
-    <x:row r="1009" spans="1:4">
+    <x:row r="1009">
       <x:c r="A1009" s="2" t="n">
         <x:v>3593</x:v>
       </x:c>
@@ -17830,7 +17830,7 @@
         <x:v>Example: game icons, watercolor</x:v>
       </x:c>
     </x:row>
-    <x:row r="1010" spans="1:4">
+    <x:row r="1010">
       <x:c r="A1010" s="2" t="n">
         <x:v>3594</x:v>
       </x:c>
@@ -17844,7 +17844,7 @@
         <x:v>Add new preset</x:v>
       </x:c>
     </x:row>
-    <x:row r="1011" spans="1:4">
+    <x:row r="1011">
       <x:c r="A1011" s="2" t="n">
         <x:v>3595</x:v>
       </x:c>
@@ -17858,7 +17858,7 @@
         <x:v>Update selected preset</x:v>
       </x:c>
     </x:row>
-    <x:row r="1012" spans="1:4">
+    <x:row r="1012">
       <x:c r="A1012" s="2" t="n">
         <x:v>3596</x:v>
       </x:c>
@@ -17872,7 +17872,7 @@
         <x:v>Delete preset</x:v>
       </x:c>
     </x:row>
-    <x:row r="1013" spans="1:4">
+    <x:row r="1013">
       <x:c r="A1013" s="2" t="n">
         <x:v>3599</x:v>
       </x:c>
@@ -17886,7 +17886,7 @@
         <x:v>Name the current instructions to add them as a new preset.</x:v>
       </x:c>
     </x:row>
-    <x:row r="1014" spans="1:4">
+    <x:row r="1014">
       <x:c r="A1014" s="2" t="n">
         <x:v>3600</x:v>
       </x:c>
@@ -17900,7 +17900,7 @@
         <x:v>A preset with this name already exists. Enter a different name.</x:v>
       </x:c>
     </x:row>
-    <x:row r="1015" spans="1:4">
+    <x:row r="1015">
       <x:c r="A1015" s="2" t="n">
         <x:v>3601</x:v>
       </x:c>
@@ -17914,7 +17914,7 @@
         <x:v>The selected preset has been edited. Update it or add a new preset with a different name.</x:v>
       </x:c>
     </x:row>
-    <x:row r="1016" spans="1:4">
+    <x:row r="1016">
       <x:c r="A1016" s="2" t="n">
         <x:v>3602</x:v>
       </x:c>
@@ -17922,13 +17922,13 @@
         <x:v>EidolonText522</x:v>
       </x:c>
       <x:c r="C1016" s="3" t="str">
-        <x:v>프리셋 목록과 현재 지침은 설정 저장을 누르면 함께 저장됩니다.</x:v>
+        <x:v>프리셋 목록과 현재 지침은 생성 환경 저장을 누르면 함께 저장됩니다.</x:v>
       </x:c>
       <x:c r="D1016" s="3" t="str">
-        <x:v>Save settings to store both the preset list and the current instructions.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1017" spans="1:4">
+        <x:v>Save the generation environment to store the preset list and current guidelines together.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1017">
       <x:c r="A1017" s="2" t="n">
         <x:v>3605</x:v>
       </x:c>
@@ -17940,6 +17940,770 @@
       </x:c>
       <x:c r="D1017" s="3" t="str">
         <x:v>Prompt preset settings contain missing or duplicate information.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1018">
+      <x:c r="A1018" s="2" t="n">
+        <x:v>3606</x:v>
+      </x:c>
+      <x:c r="B1018" s="2" t="str">
+        <x:v>EidolonText526</x:v>
+      </x:c>
+      <x:c r="C1018" s="3" t="str">
+        <x:v>이미지 생성 방식</x:v>
+      </x:c>
+      <x:c r="D1018" s="3" t="str">
+        <x:v>Image generation method</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1019">
+      <x:c r="A1019" s="2" t="n">
+        <x:v>3607</x:v>
+      </x:c>
+      <x:c r="B1019" s="2" t="str">
+        <x:v>EidolonText527</x:v>
+      </x:c>
+      <x:c r="C1019" s="3" t="str">
+        <x:v>ComfyUI</x:v>
+      </x:c>
+      <x:c r="D1019" s="3" t="str">
+        <x:v>ComfyUI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1020">
+      <x:c r="A1020" s="2" t="n">
+        <x:v>3608</x:v>
+      </x:c>
+      <x:c r="B1020" s="2" t="str">
+        <x:v>EidolonText528</x:v>
+      </x:c>
+      <x:c r="C1020" s="3" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+      <x:c r="D1020" s="3" t="str">
+        <x:v>Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1021">
+      <x:c r="A1021" s="2" t="n">
+        <x:v>3609</x:v>
+      </x:c>
+      <x:c r="B1021" s="2" t="str">
+        <x:v>EidolonText529</x:v>
+      </x:c>
+      <x:c r="C1021" s="3" t="str">
+        <x:v>Codex 실행 파일</x:v>
+      </x:c>
+      <x:c r="D1021" s="3" t="str">
+        <x:v>Codex executable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1022">
+      <x:c r="A1022" s="2" t="n">
+        <x:v>3610</x:v>
+      </x:c>
+      <x:c r="B1022" s="2" t="str">
+        <x:v>EidolonText530</x:v>
+      </x:c>
+      <x:c r="C1022" s="3" t="str">
+        <x:v>비워 두면 설치 경로 또는 PATH에서 자동 찾기</x:v>
+      </x:c>
+      <x:c r="D1022" s="3" t="str">
+        <x:v>Leave blank to find Codex in its installation directory or PATH</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1023">
+      <x:c r="A1023" s="2" t="n">
+        <x:v>3611</x:v>
+      </x:c>
+      <x:c r="B1023" s="2" t="str">
+        <x:v>EidolonText531</x:v>
+      </x:c>
+      <x:c r="C1023" s="3" t="str">
+        <x:v>설치된 Codex에 로그인한 계정으로 이미지를 생성합니다. 입력한 이미지 설명과 공통 생성 지침·제외할 요소를 함께 전달하며 Codex 사용 한도가 적용됩니다. 먼저 Codex에서 로그인하세요.</x:v>
+      </x:c>
+      <x:c r="D1023" s="3" t="str">
+        <x:v>Generate images with the account signed in to your installed Codex. Your description, shared guidelines and exclusions are sent together. Codex usage limits apply. Sign in to Codex first.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1024">
+      <x:c r="A1024" s="2" t="n">
+        <x:v>3612</x:v>
+      </x:c>
+      <x:c r="B1024" s="2" t="str">
+        <x:v>EidolonText532</x:v>
+      </x:c>
+      <x:c r="C1024" s="3" t="str">
+        <x:v>실행 파일 선택</x:v>
+      </x:c>
+      <x:c r="D1024" s="3" t="str">
+        <x:v>Choose executable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1025">
+      <x:c r="A1025" s="2" t="n">
+        <x:v>3613</x:v>
+      </x:c>
+      <x:c r="B1025" s="2" t="str">
+        <x:v>EidolonText533</x:v>
+      </x:c>
+      <x:c r="C1025" s="3" t="str">
+        <x:v>Codex의 내장 이미지 생성을 사용합니다. ComfyUI 모델·LoRA·시드·변경 강도는 적용하지 않으며 결과는 같은 이미지 저장 폴더와 갤러리에 표시합니다.</x:v>
+      </x:c>
+      <x:c r="D1025" s="3" t="str">
+        <x:v>Uses built-in Codex image generation. ComfyUI models, LoRAs, seeds and change strength do not apply. Results use the same image output folder and gallery.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1026">
+      <x:c r="A1026" s="2" t="n">
+        <x:v>3614</x:v>
+      </x:c>
+      <x:c r="B1026" s="2" t="str">
+        <x:v>EidolonText534</x:v>
+      </x:c>
+      <x:c r="C1026" s="3" t="str">
+        <x:v>Codex 실행 파일을 찾을 수 없습니다. Codex를 설치하고 로그인한 뒤 생성 환경에서 codex.exe 경로를 지정하세요.</x:v>
+      </x:c>
+      <x:c r="D1026" s="3" t="str">
+        <x:v>Codex executable was not found. Install and sign in to Codex, then select codex.exe in Generation environment.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1027">
+      <x:c r="A1027" s="2" t="n">
+        <x:v>3615</x:v>
+      </x:c>
+      <x:c r="B1027" s="2" t="str">
+        <x:v>EidolonText535</x:v>
+      </x:c>
+      <x:c r="C1027" s="3" t="str">
+        <x:v>Codex로 이미지를 생성하는 중</x:v>
+      </x:c>
+      <x:c r="D1027" s="3" t="str">
+        <x:v>Generating an image with Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1028">
+      <x:c r="A1028" s="2" t="n">
+        <x:v>3616</x:v>
+      </x:c>
+      <x:c r="B1028" s="2" t="str">
+        <x:v>EidolonText536</x:v>
+      </x:c>
+      <x:c r="C1028" s="3" t="str">
+        <x:v>Codex가 이미지 파일을 저장하지 않았습니다. 로그인·이미지 생성 지원·사용 한도를 확인하세요. 로그: {0}</x:v>
+      </x:c>
+      <x:c r="D1028" s="3" t="str">
+        <x:v>Codex did not save an image. Check sign-in, image-generation support and usage limits. Log: {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1029">
+      <x:c r="A1029" s="2" t="n">
+        <x:v>3617</x:v>
+      </x:c>
+      <x:c r="B1029" s="2" t="str">
+        <x:v>EidolonText537</x:v>
+      </x:c>
+      <x:c r="C1029" s="3" t="str">
+        <x:v>지원하지 않는 이미지 생성 방식입니다.</x:v>
+      </x:c>
+      <x:c r="D1029" s="3" t="str">
+        <x:v>Unsupported image generation method.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1030">
+      <x:c r="A1030" s="2" t="n">
+        <x:v>3618</x:v>
+      </x:c>
+      <x:c r="B1030" s="2" t="str">
+        <x:v>EidolonText538</x:v>
+      </x:c>
+      <x:c r="C1030" s="3" t="str">
+        <x:v>Codex 결과가 유효한 PNG가 아니거나 요청한 투명 배경이 없습니다. 로그: {0}</x:v>
+      </x:c>
+      <x:c r="D1030" s="3" t="str">
+        <x:v>The Codex result is not a valid PNG or lacks the requested transparency. Log: {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1031">
+      <x:c r="A1031" s="2" t="n">
+        <x:v>3619</x:v>
+      </x:c>
+      <x:c r="B1031" s="2" t="str">
+        <x:v>EidolonText539</x:v>
+      </x:c>
+      <x:c r="C1031" s="3" t="str">
+        <x:v>참고 이미지를 Codex에 함께 전달합니다. 생성에서는 참고하여 새 이미지를 만들고 편집에서는 대상·구도를 유지하며 그림체 변경을 요청합니다.</x:v>
+      </x:c>
+      <x:c r="D1031" s="3" t="str">
+        <x:v>Send the reference image to Codex. Generate uses it as visual guidance for a new image. Edit requests a style change while preserving the subject and composition.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1032">
+      <x:c r="A1032" s="2" t="n">
+        <x:v>3620</x:v>
+      </x:c>
+      <x:c r="B1032" s="2" t="str">
+        <x:v>EidolonText540</x:v>
+      </x:c>
+      <x:c r="C1032" s="3" t="str">
+        <x:v>현재 생성 방식: {0}</x:v>
+      </x:c>
+      <x:c r="D1032" s="3" t="str">
+        <x:v>Current generation method: {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1033">
+      <x:c r="A1033" s="2" t="n">
+        <x:v>3621</x:v>
+      </x:c>
+      <x:c r="B1033" s="2" t="str">
+        <x:v>EidolonText541</x:v>
+      </x:c>
+      <x:c r="C1033" s="3" t="str">
+        <x:v>생성 환경 변경이 아직 적용되지 않았습니다. 생성 환경을 저장해 주세요.</x:v>
+      </x:c>
+      <x:c r="D1033" s="3" t="str">
+        <x:v>Generation setup changes are not applied yet. Save the generation environment to apply them.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1034">
+      <x:c r="A1034" s="2" t="n">
+        <x:v>3622</x:v>
+      </x:c>
+      <x:c r="B1034" s="2" t="str">
+        <x:v>EidolonText542</x:v>
+      </x:c>
+      <x:c r="C1034" s="3" t="str">
+        <x:v>저장하면 다음 생성·편집 요청부터 적용됩니다. 대기 중인 요청은 기존 설정을 사용합니다.</x:v>
+      </x:c>
+      <x:c r="D1034" s="3" t="str">
+        <x:v>Saved settings apply to new generation and editing requests. Queued requests keep their original settings.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1035">
+      <x:c r="A1035" s="2" t="n">
+        <x:v>3623</x:v>
+      </x:c>
+      <x:c r="B1035" s="2" t="str">
+        <x:v>EidolonText543</x:v>
+      </x:c>
+      <x:c r="C1035" s="3" t="str">
+        <x:v>ComfyUI와 Codex 모두 이 지침과 제외할 요소를 사용합니다.</x:v>
+      </x:c>
+      <x:c r="D1035" s="3" t="str">
+        <x:v>Both ComfyUI and Codex use these guidelines and excluded elements.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1036">
+      <x:c r="A1036" s="2" t="n">
+        <x:v>3624</x:v>
+      </x:c>
+      <x:c r="B1036" s="2" t="str">
+        <x:v>EidolonText544</x:v>
+      </x:c>
+      <x:c r="C1036" s="3" t="str">
+        <x:v>설치한 모델과 LoRA로 생성합니다. 엔진 설치에서 서버를 연결하고 모델·LoRA에서 자산을 관리하세요.</x:v>
+      </x:c>
+      <x:c r="D1036" s="3" t="str">
+        <x:v>Generate with installed models and LoRAs. Connect the server in Engine setup and manage assets in Models and LoRAs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1037">
+      <x:c r="A1037" s="2" t="n">
+        <x:v>3625</x:v>
+      </x:c>
+      <x:c r="B1037" s="2" t="str">
+        <x:v>EidolonText545</x:v>
+      </x:c>
+      <x:c r="C1037" s="3" t="str">
+        <x:v>이미지 설명과 공통 생성 지침으로 Codex에 생성을 요청합니다.</x:v>
+      </x:c>
+      <x:c r="D1037" s="3" t="str">
+        <x:v>Request an image from Codex with your image description and shared generation guidelines.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1038">
+      <x:c r="A1038" s="2" t="n">
+        <x:v>3626</x:v>
+      </x:c>
+      <x:c r="B1038" s="2" t="str">
+        <x:v>EidolonText546</x:v>
+      </x:c>
+      <x:c r="C1038" s="3" t="str">
+        <x:v>이미지 저장</x:v>
+      </x:c>
+      <x:c r="D1038" s="3" t="str">
+        <x:v>Image output</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1039">
+      <x:c r="A1039" s="2" t="n">
+        <x:v>3627</x:v>
+      </x:c>
+      <x:c r="B1039" s="2" t="str">
+        <x:v>EidolonText547</x:v>
+      </x:c>
+      <x:c r="C1039" s="3" t="str">
+        <x:v>프리셋 관리</x:v>
+      </x:c>
+      <x:c r="D1039" s="3" t="str">
+        <x:v>Manage presets</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1040">
+      <x:c r="A1040" s="2" t="n">
+        <x:v>3628</x:v>
+      </x:c>
+      <x:c r="B1040" s="2" t="str">
+        <x:v>EidolonText548</x:v>
+      </x:c>
+      <x:c r="C1040" s="3" t="str">
+        <x:v>Codex 실행 모델</x:v>
+      </x:c>
+      <x:c r="D1040" s="3" t="str">
+        <x:v>Codex agent model</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1041">
+      <x:c r="A1041" s="2" t="n">
+        <x:v>3629</x:v>
+      </x:c>
+      <x:c r="B1041" s="2" t="str">
+        <x:v>EidolonText549</x:v>
+      </x:c>
+      <x:c r="C1041" s="3" t="str">
+        <x:v>비워 두면 Codex 기본 모델 사용</x:v>
+      </x:c>
+      <x:c r="D1041" s="3" t="str">
+        <x:v>Leave blank to use the Codex default model</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1042">
+      <x:c r="A1042" s="2" t="n">
+        <x:v>3630</x:v>
+      </x:c>
+      <x:c r="B1042" s="2" t="str">
+        <x:v>EidolonText550</x:v>
+      </x:c>
+      <x:c r="C1042" s="3" t="str">
+        <x:v>요청을 처리하는 Codex 모델입니다. 내장 이미지 생성 모델과는 별개입니다.</x:v>
+      </x:c>
+      <x:c r="D1042" s="3" t="str">
+        <x:v>The Codex model handling your request, separate from the built-in image generation model.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1043">
+      <x:c r="A1043" s="2" t="n">
+        <x:v>3631</x:v>
+      </x:c>
+      <x:c r="B1043" s="2" t="str">
+        <x:v>EidolonText551</x:v>
+      </x:c>
+      <x:c r="C1043" s="3" t="str">
+        <x:v>Codex 기본 모델</x:v>
+      </x:c>
+      <x:c r="D1043" s="3" t="str">
+        <x:v>Codex default model</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1044">
+      <x:c r="A1044" s="2" t="n">
+        <x:v>3632</x:v>
+      </x:c>
+      <x:c r="B1044" s="2" t="str">
+        <x:v>EidolonText552</x:v>
+      </x:c>
+      <x:c r="C1044" s="3" t="str">
+        <x:v>설치된 Codex에서 모델 목록을 가져옵니다. 기본 모델을 선택하면 Codex의 기본값을 사용합니다.</x:v>
+      </x:c>
+      <x:c r="D1044" s="3" t="str">
+        <x:v>Models are retrieved from your installed Codex. Select the default model to use the Codex default.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1045">
+      <x:c r="A1045" s="2" t="n">
+        <x:v>3633</x:v>
+      </x:c>
+      <x:c r="B1045" s="2" t="str">
+        <x:v>EidolonText553</x:v>
+      </x:c>
+      <x:c r="C1045" s="3" t="str">
+        <x:v>Codex 모델 목록을 가져오는 중...</x:v>
+      </x:c>
+      <x:c r="D1045" s="3" t="str">
+        <x:v>Retrieving Codex models...</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1046">
+      <x:c r="A1046" s="2" t="n">
+        <x:v>3634</x:v>
+      </x:c>
+      <x:c r="B1046" s="2" t="str">
+        <x:v>EidolonText554</x:v>
+      </x:c>
+      <x:c r="C1046" s="3" t="str">
+        <x:v>모델 목록을 가져오지 못했습니다. 기본 모델로 진행하거나 다시 새로고침하세요. {0}</x:v>
+      </x:c>
+      <x:c r="D1046" s="3" t="str">
+        <x:v>Could not retrieve models. Use the default model or refresh again. {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1047">
+      <x:c r="A1047" s="2" t="n">
+        <x:v>3635</x:v>
+      </x:c>
+      <x:c r="B1047" s="2" t="str">
+        <x:v>EidolonText556</x:v>
+      </x:c>
+      <x:c r="C1047" s="3" t="str">
+        <x:v>모델·LoRA 삭제</x:v>
+      </x:c>
+      <x:c r="D1047" s="3" t="str">
+        <x:v>Delete model or LoRA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1048">
+      <x:c r="A1048" s="2" t="n">
+        <x:v>3636</x:v>
+      </x:c>
+      <x:c r="B1048" s="2" t="str">
+        <x:v>EidolonText557</x:v>
+      </x:c>
+      <x:c r="C1048" s="3" t="str">
+        <x:v>{0} 가중치 파일을 삭제할까요?
+{1}
+다시 사용하려면 설치하거나 해당 모델·LoRA 폴더에 파일을 넣어야 합니다.</x:v>
+      </x:c>
+      <x:c r="D1048" s="3" t="str">
+        <x:v>Delete the {0} weights file?
+{1}
+Install it again or place the file in its model or LoRA folder to use it.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1049">
+      <x:c r="A1049" s="2" t="n">
+        <x:v>3637</x:v>
+      </x:c>
+      <x:c r="B1049" s="2" t="str">
+        <x:v>EidolonText558</x:v>
+      </x:c>
+      <x:c r="C1049" s="3" t="str">
+        <x:v>{0} 파일을 삭제했습니다.</x:v>
+      </x:c>
+      <x:c r="D1049" s="3" t="str">
+        <x:v>Deleted the {0} file.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1050">
+      <x:c r="A1050" s="2" t="n">
+        <x:v>3638</x:v>
+      </x:c>
+      <x:c r="B1050" s="2" t="str">
+        <x:v>EidolonText559</x:v>
+      </x:c>
+      <x:c r="C1050" s="3" t="str">
+        <x:v>삭제하면 설치된 가중치 파일도 제거됩니다.</x:v>
+      </x:c>
+      <x:c r="D1050" s="3" t="str">
+        <x:v>Deleting also removes the installed weights file.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1051">
+      <x:c r="A1051" s="2" t="n">
+        <x:v>3639</x:v>
+      </x:c>
+      <x:c r="B1051" s="2" t="str">
+        <x:v>EidolonText560</x:v>
+      </x:c>
+      <x:c r="C1051" s="3" t="str">
+        <x:v>생성 환경</x:v>
+      </x:c>
+      <x:c r="D1051" s="3" t="str">
+        <x:v>Generation environment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1052">
+      <x:c r="A1052" s="2" t="n">
+        <x:v>3640</x:v>
+      </x:c>
+      <x:c r="B1052" s="2" t="str">
+        <x:v>EidolonText561</x:v>
+      </x:c>
+      <x:c r="C1052" s="3" t="str">
+        <x:v>생성 환경 저장</x:v>
+      </x:c>
+      <x:c r="D1052" s="3" t="str">
+        <x:v>Save generation environment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1053">
+      <x:c r="A1053" s="2" t="n">
+        <x:v>3641</x:v>
+      </x:c>
+      <x:c r="B1053" s="2" t="str">
+        <x:v>EidolonText562</x:v>
+      </x:c>
+      <x:c r="C1053" s="3" t="str">
+        <x:v>공통 지침·제외할 요소와 프리셋은 설정에서 관리합니다. 두 생성 방식 모두 저장된 지침을 사용합니다.</x:v>
+      </x:c>
+      <x:c r="D1053" s="3" t="str">
+        <x:v>Manage shared guidelines, excluded elements and presets in Settings. Both generation methods use the saved guidelines.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1054">
+      <x:c r="A1054" s="2" t="n">
+        <x:v>3642</x:v>
+      </x:c>
+      <x:c r="B1054" s="2" t="str">
+        <x:v>EidolonText563</x:v>
+      </x:c>
+      <x:c r="C1054" s="3" t="str">
+        <x:v>Codex 이미지 생성과 편집</x:v>
+      </x:c>
+      <x:c r="D1054" s="3" t="str">
+        <x:v>Generate and edit with Codex</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1055">
+      <x:c r="A1055" s="2" t="n">
+        <x:v>3643</x:v>
+      </x:c>
+      <x:c r="B1055" s="2" t="str">
+        <x:v>EidolonText564</x:v>
+      </x:c>
+      <x:c r="C1055" s="3" t="str">
+        <x:v>선택 항목 삭제</x:v>
+      </x:c>
+      <x:c r="D1055" s="3" t="str">
+        <x:v>Delete selected asset</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1056">
+      <x:c r="A1056" s="2" t="n">
+        <x:v>3644</x:v>
+      </x:c>
+      <x:c r="B1056" s="2" t="str">
+        <x:v>EidolonText565</x:v>
+      </x:c>
+      <x:c r="C1056" s="3" t="str">
+        <x:v>설치된 Codex에서 로그인한 뒤 생성 환경에서 Codex를 선택하세요. 실행 모델은 가져온 목록에서 선택하고 생성 환경 저장을 누릅니다. 기본 모델은 Codex의 기본값을 사용합니다.</x:v>
+      </x:c>
+      <x:c r="D1056" s="3" t="str">
+        <x:v>Sign in to your installed Codex, choose Codex in Generation environment, select an agent model and save. The default option uses the Codex default.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1057">
+      <x:c r="A1057" s="2" t="n">
+        <x:v>3645</x:v>
+      </x:c>
+      <x:c r="B1057" s="2" t="str">
+        <x:v>EidolonText566</x:v>
+      </x:c>
+      <x:c r="C1057" s="3" t="str">
+        <x:v>생성은 이미지 설명과 선택적 참고 이미지를, 편집은 원본 이미지와 수정 설명을 전달합니다. 두 요청 모두 생성 환경의 공통 지침·제외할 요소를 사용합니다. 배경 투명하게는 투명 PNG를 요청합니다.</x:v>
+      </x:c>
+      <x:c r="D1057" s="3" t="str">
+        <x:v>Generate sends your description and optional reference. Edit sends the source image and edit instructions. Both use the shared guidelines and exclusions in Generation environment. Transparent background requests a transparent PNG.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1058">
+      <x:c r="A1058" s="2" t="n">
+        <x:v>3646</x:v>
+      </x:c>
+      <x:c r="B1058" s="2" t="str">
+        <x:v>EidolonText567</x:v>
+      </x:c>
+      <x:c r="C1058" s="3" t="str">
+        <x:v>최종 이미지와 프롬프트 JSON은 설정의 이미지 저장 폴더에 저장합니다. 기본은 사용자 데이터의 Images 폴더입니다. 원본과 실행 로그는 Job 폴더에 보관합니다.</x:v>
+      </x:c>
+      <x:c r="D1058" s="3" t="str">
+        <x:v>Final images and prompt JSON use the image output folder in Settings, defaulting to Images in app data. Originals and execution logs are kept in the job folder.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1059">
+      <x:c r="A1059" s="2" t="n">
+        <x:v>3647</x:v>
+      </x:c>
+      <x:c r="B1059" s="2" t="str">
+        <x:v>EidolonText568</x:v>
+      </x:c>
+      <x:c r="C1059" s="3" t="str">
+        <x:v>모델·LoRA 관리</x:v>
+      </x:c>
+      <x:c r="D1059" s="3" t="str">
+        <x:v>Manage models and LoRAs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1060">
+      <x:c r="A1060" s="2" t="n">
+        <x:v>3648</x:v>
+      </x:c>
+      <x:c r="B1060" s="2" t="str">
+        <x:v>EidolonText569</x:v>
+      </x:c>
+      <x:c r="C1060" s="3" t="str">
+        <x:v>생성 환경의 모델·LoRA에서 모델 폴더나 LoRA 폴더를 열어 파일을 넣고 새로고침합니다. 기본 모델은 설치 목록에서도 받을 수 있습니다. 보유 항목을 누르면 아래에서 계열·트리거를 수정하거나 삭제합니다. 외부 서버 파일은 해당 ComfyUI에서 관리하며 Codex 생성에는 이 자산을 사용하지 않습니다.</x:v>
+      </x:c>
+      <x:c r="D1060" s="3" t="str">
+        <x:v>Open Model folder or LoRA folder in Generation environment &gt; Models and LoRAs, place files there and refresh. Base models can also be installed from the list. Select an asset to edit its family and trigger or delete it. Manage external files in their ComfyUI installation. Codex generation does not use these assets.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1061">
+      <x:c r="A1061" s="2" t="n">
+        <x:v>3649</x:v>
+      </x:c>
+      <x:c r="B1061" s="2" t="str">
+        <x:v>EidolonText570</x:v>
+      </x:c>
+      <x:c r="C1061" s="3" t="str">
+        <x:v>생성 방식·지침</x:v>
+      </x:c>
+      <x:c r="D1061" s="3" t="str">
+        <x:v>Generation method and guidelines</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1062">
+      <x:c r="A1062" s="2" t="n">
+        <x:v>3650</x:v>
+      </x:c>
+      <x:c r="B1062" s="2" t="str">
+        <x:v>EidolonText571</x:v>
+      </x:c>
+      <x:c r="C1062" s="3" t="str">
+        <x:v>모델 폴더</x:v>
+      </x:c>
+      <x:c r="D1062" s="3" t="str">
+        <x:v>Model folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1063">
+      <x:c r="A1063" s="2" t="n">
+        <x:v>3651</x:v>
+      </x:c>
+      <x:c r="B1063" s="2" t="str">
+        <x:v>EidolonText572</x:v>
+      </x:c>
+      <x:c r="C1063" s="3" t="str">
+        <x:v>LoRA 폴더</x:v>
+      </x:c>
+      <x:c r="D1063" s="3" t="str">
+        <x:v>LoRA folder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1064">
+      <x:c r="A1064" s="2" t="n">
+        <x:v>3652</x:v>
+      </x:c>
+      <x:c r="B1064" s="2" t="str">
+        <x:v>EidolonText573</x:v>
+      </x:c>
+      <x:c r="C1064" s="3" t="str">
+        <x:v>모델은 모델 폴더에, LoRA는 LoRA 폴더에 넣고 새로고침하세요. 두 폴더는 ComfyUI에 연결되어 있습니다.</x:v>
+      </x:c>
+      <x:c r="D1064" s="3" t="str">
+        <x:v>Place checkpoints in Model folder and LoRAs in LoRA folder, then refresh. Both folders are connected to ComfyUI.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1065">
+      <x:c r="A1065" s="2" t="n">
+        <x:v>3653</x:v>
+      </x:c>
+      <x:c r="B1065" s="2" t="str">
+        <x:v>EidolonText574</x:v>
+      </x:c>
+      <x:c r="C1065" s="3" t="str">
+        <x:v>학습을 시작하면 엔진 경로 아래에 학습 폴더를 자동으로 준비합니다. 원본 이미지는 보존합니다.</x:v>
+      </x:c>
+      <x:c r="D1065" s="3" t="str">
+        <x:v>Starting training automatically prepares a dataset under the engine path. Source images are preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1066">
+      <x:c r="A1066" s="2" t="n">
+        <x:v>3654</x:v>
+      </x:c>
+      <x:c r="B1066" s="2" t="str">
+        <x:v>EidolonText575</x:v>
+      </x:c>
+      <x:c r="C1066" s="3" t="str">
+        <x:v>학습 데이터</x:v>
+      </x:c>
+      <x:c r="D1066" s="3" t="str">
+        <x:v>Training data</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1067">
+      <x:c r="A1067" s="2" t="n">
+        <x:v>3655</x:v>
+      </x:c>
+      <x:c r="B1067" s="2" t="str">
+        <x:v>EidolonText576</x:v>
+      </x:c>
+      <x:c r="C1067" s="3" t="str">
+        <x:v>학습마다 작업별 하위 폴더를 자동으로 만듭니다. 학습 데이터 비우기는 준비한 이미지와 설명만 삭제하며 원본 이미지·LoRA·작업 로그는 보존합니다.</x:v>
+      </x:c>
+      <x:c r="D1067" s="3" t="str">
+        <x:v>Each training job gets its own dataset folder. Clearing training data removes prepared images and captions, while preserving source images, LoRAs and job logs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1068">
+      <x:c r="A1068" s="2" t="n">
+        <x:v>3656</x:v>
+      </x:c>
+      <x:c r="B1068" s="2" t="str">
+        <x:v>EidolonText577</x:v>
+      </x:c>
+      <x:c r="C1068" s="3" t="str">
+        <x:v>학습 데이터 비우기</x:v>
+      </x:c>
+      <x:c r="D1068" s="3" t="str">
+        <x:v>Clear training data</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1069">
+      <x:c r="A1069" s="2" t="n">
+        <x:v>3657</x:v>
+      </x:c>
+      <x:c r="B1069" s="2" t="str">
+        <x:v>EidolonText578</x:v>
+      </x:c>
+      <x:c r="C1069" s="3" t="str">
+        <x:v>학습 데이터 삭제</x:v>
+      </x:c>
+      <x:c r="D1069" s="3" t="str">
+        <x:v>Delete training data</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1070">
+      <x:c r="A1070" s="2" t="n">
+        <x:v>3658</x:v>
+      </x:c>
+      <x:c r="B1070" s="2" t="str">
+        <x:v>EidolonText579</x:v>
+      </x:c>
+      <x:c r="C1070" s="3" t="str">
+        <x:v>아래 경로에 자동으로 만든 학습 폴더를 모두 삭제할까요?
+{0}
+원본 이미지·완료된 LoRA·작업 로그는 보존합니다.</x:v>
+      </x:c>
+      <x:c r="D1070" s="3" t="str">
+        <x:v>Delete all automatically prepared dataset folders at this path?
+{0}
+Source images, completed LoRAs and job logs are preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1071">
+      <x:c r="A1071" s="2" t="n">
+        <x:v>3659</x:v>
+      </x:c>
+      <x:c r="B1071" s="2" t="str">
+        <x:v>EidolonText580</x:v>
+      </x:c>
+      <x:c r="C1071" s="3" t="str">
+        <x:v>학습 데이터 폴더 {0}개를 삭제했습니다.</x:v>
+      </x:c>
+      <x:c r="D1071" s="3" t="str">
+        <x:v>Deleted {0} training dataset folders.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -18706,6 +18706,1506 @@
         <x:v>Deleted {0} training dataset folders.</x:v>
       </x:c>
     </x:row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1072">
+      <c r="A1072" s="2">
+        <v>3660</v>
+      </c>
+      <c r="B1072" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText581</t>
+        </is>
+      </c>
+      <c r="C1072" s="2" t="inlineStr">
+        <is>
+          <t>생성 환경</t>
+        </is>
+      </c>
+      <c r="D1072" s="2" t="inlineStr">
+        <is>
+          <t>Generation environment</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1073">
+      <c r="A1073" s="2">
+        <v>3661</v>
+      </c>
+      <c r="B1073" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText582</t>
+        </is>
+      </c>
+      <c r="C1073" s="2" t="inlineStr">
+        <is>
+          <t>생성 방식과 사용할 모델, 모든 이미지에 적용할 공통 지침을 관리합니다.</t>
+        </is>
+      </c>
+      <c r="D1073" s="2" t="inlineStr">
+        <is>
+          <t>Manage generation methods, models, and instructions shared by all images.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1074">
+      <c r="A1074" s="2">
+        <v>3662</v>
+      </c>
+      <c r="B1074" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText583</t>
+        </is>
+      </c>
+      <c r="C1074" s="2" t="inlineStr">
+        <is>
+          <t>생성 방식</t>
+        </is>
+      </c>
+      <c r="D1074" s="2" t="inlineStr">
+        <is>
+          <t>Generation methods</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1075">
+      <c r="A1075" s="2">
+        <v>3663</v>
+      </c>
+      <c r="B1075" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText584</t>
+        </is>
+      </c>
+      <c r="C1075" s="2" t="inlineStr">
+        <is>
+          <t>학습 데이터</t>
+        </is>
+      </c>
+      <c r="D1075" s="2" t="inlineStr">
+        <is>
+          <t>Training data</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1076">
+      <c r="A1076" s="2">
+        <v>3664</v>
+      </c>
+      <c r="B1076" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText585</t>
+        </is>
+      </c>
+      <c r="C1076" s="2" t="inlineStr">
+        <is>
+          <t>준비한 학습 데이터로 LoRA를 학습합니다. 데이터 준비와 수정은 설정에서 진행하세요.</t>
+        </is>
+      </c>
+      <c r="D1076" s="2" t="inlineStr">
+        <is>
+          <t>Train a LoRA with the prepared dataset. Prepare and edit training data in Settings.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1077">
+      <c r="A1077" s="2">
+        <v>3665</v>
+      </c>
+      <c r="B1077" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText586</t>
+        </is>
+      </c>
+      <c r="C1077" s="2" t="inlineStr">
+        <is>
+          <t>화면과 저장 위치, 엔진 설치·연결, 학습 데이터 준비를 관리합니다.</t>
+        </is>
+      </c>
+      <c r="D1077" s="2" t="inlineStr">
+        <is>
+          <t>Manage appearance, storage, engine setup and connections, and training data.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1078">
+      <c r="A1078" s="2">
+        <v>3666</v>
+      </c>
+      <c r="B1078" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText587</t>
+        </is>
+      </c>
+      <c r="C1078" s="2" t="inlineStr">
+        <is>
+          <t>학습 데이터가 아직 없습니다. 위의 학습 데이터를 눌러 이미지와 설명을 준비하세요.</t>
+        </is>
+      </c>
+      <c r="D1078" s="2" t="inlineStr">
+        <is>
+          <t>No training data is ready. Select Training data above to prepare images and captions.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1079">
+      <c r="A1079" s="2">
+        <v>3667</v>
+      </c>
+      <c r="B1079" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText588</t>
+        </is>
+      </c>
+      <c r="C1079" s="2" t="inlineStr">
+        <is>
+          <t>설명으로 새로운 이미지를 만듭니다. 참고 이미지를 추가하면 기존 이미지의 구도와 내용을 바탕으로 생성할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D1079" s="2" t="inlineStr">
+        <is>
+          <t>Create a new image from a description. Add a reference image to guide its composition and content.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1080">
+      <c r="A1080" s="2">
+        <v>3668</v>
+      </c>
+      <c r="B1080" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText589</t>
+        </is>
+      </c>
+      <c r="C1080" s="2" t="inlineStr">
+        <is>
+          <t>이미지와 원하는 그림체를 지정해 편집합니다. 변경 강도로 기존 이미지가 유지되는 정도를 조절합니다.</t>
+        </is>
+      </c>
+      <c r="D1080" s="2" t="inlineStr">
+        <is>
+          <t>Choose an image and describe the desired style. Change strength controls how much of the original image is preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1081">
+      <c r="A1081" s="2">
+        <v>3669</v>
+      </c>
+      <c r="B1081" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText590</t>
+        </is>
+      </c>
+      <c r="C1081" s="2" t="inlineStr">
+        <is>
+          <t>생성으로 이동</t>
+        </is>
+      </c>
+      <c r="D1081" s="2" t="inlineStr">
+        <is>
+          <t>Open Generate</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1082">
+      <c r="A1082" s="2">
+        <v>3670</v>
+      </c>
+      <c r="B1082" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText591</t>
+        </is>
+      </c>
+      <c r="C1082" s="2" t="inlineStr">
+        <is>
+          <t>편집으로 이동</t>
+        </is>
+      </c>
+      <c r="D1082" s="2" t="inlineStr">
+        <is>
+          <t>Open Edit</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1083">
+      <c r="A1083" s="2">
+        <v>3671</v>
+      </c>
+      <c r="B1083" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText592</t>
+        </is>
+      </c>
+      <c r="C1083" s="2" t="inlineStr">
+        <is>
+          <t>저장 위치</t>
+        </is>
+      </c>
+      <c r="D1083" s="2" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1084">
+      <c r="A1084" s="2">
+        <v>3672</v>
+      </c>
+      <c r="B1084" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText593</t>
+        </is>
+      </c>
+      <c r="C1084" s="2" t="inlineStr">
+        <is>
+          <t>엔진 설치·연결</t>
+        </is>
+      </c>
+      <c r="D1084" s="2" t="inlineStr">
+        <is>
+          <t>Engine setup and connection</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1085">
+      <c r="A1085" s="2">
+        <v>3673</v>
+      </c>
+      <c r="B1085" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText594</t>
+        </is>
+      </c>
+      <c r="C1085" s="2" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D1085" s="2" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1086">
+      <c r="A1086" s="2">
+        <v>3674</v>
+      </c>
+      <c r="B1086" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText595</t>
+        </is>
+      </c>
+      <c r="C1086" s="2" t="inlineStr">
+        <is>
+          <t>MCP 연결</t>
+        </is>
+      </c>
+      <c r="D1086" s="2" t="inlineStr">
+        <is>
+          <t>MCP connection</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1087">
+      <c r="A1087" s="2">
+        <v>3675</v>
+      </c>
+      <c r="B1087" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText596</t>
+        </is>
+      </c>
+      <c r="C1087" s="2" t="inlineStr">
+        <is>
+          <t>외부 AI 도구에서 이미지 생성·편집과 결과 조회를 사용할 수 있습니다. 사용할 때 서버를 켜세요.</t>
+        </is>
+      </c>
+      <c r="D1087" s="2" t="inlineStr">
+        <is>
+          <t>Use image generation, editing and result lookup from external AI tools. Start the server when you need it.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1088">
+      <c r="A1088" s="2">
+        <v>3676</v>
+      </c>
+      <c r="B1088" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText597</t>
+        </is>
+      </c>
+      <c r="C1088" s="2" t="inlineStr">
+        <is>
+          <t>생성 지침은 MCP 요청별로 바꿀 수 있습니다. 저장한 설정은 유지되며 같은 PC에서만 연결합니다.</t>
+        </is>
+      </c>
+      <c r="D1088" s="2" t="inlineStr">
+        <is>
+          <t>Override generation instructions per MCP request. Saved settings are preserved. Connections are limited to this PC.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1089">
+      <c r="A1089" s="2">
+        <v>3677</v>
+      </c>
+      <c r="B1089" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText598</t>
+        </is>
+      </c>
+      <c r="C1089" s="2" t="inlineStr">
+        <is>
+          <t>연결 대기 중</t>
+        </is>
+      </c>
+      <c r="D1089" s="2" t="inlineStr">
+        <is>
+          <t>Listening</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1090">
+      <c r="A1090" s="2">
+        <v>3678</v>
+      </c>
+      <c r="B1090" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText599</t>
+        </is>
+      </c>
+      <c r="C1090" s="2" t="inlineStr">
+        <is>
+          <t>서버 꺼짐</t>
+        </is>
+      </c>
+      <c r="D1090" s="2" t="inlineStr">
+        <is>
+          <t>Server stopped</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1091">
+      <c r="A1091" s="2">
+        <v>3679</v>
+      </c>
+      <c r="B1091" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText600</t>
+        </is>
+      </c>
+      <c r="C1091" s="2" t="inlineStr">
+        <is>
+          <t>서버 켜기</t>
+        </is>
+      </c>
+      <c r="D1091" s="2" t="inlineStr">
+        <is>
+          <t>Start server</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1092">
+      <c r="A1092" s="2">
+        <v>3680</v>
+      </c>
+      <c r="B1092" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText601</t>
+        </is>
+      </c>
+      <c r="C1092" s="2" t="inlineStr">
+        <is>
+          <t>서버 끄기</t>
+        </is>
+      </c>
+      <c r="D1092" s="2" t="inlineStr">
+        <is>
+          <t>Stop server</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1093">
+      <c r="A1093" s="2">
+        <v>3681</v>
+      </c>
+      <c r="B1093" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText602</t>
+        </is>
+      </c>
+      <c r="C1093" s="2" t="inlineStr">
+        <is>
+          <t>MCP 주소의 수신 권한이 없습니다. 사용법 문서의 HTTP URL 예약 안내를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D1093" s="2" t="inlineStr">
+        <is>
+          <t>The MCP address has no listener permission. See the HTTP URL reservation instructions in the usage document.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1094">
+      <c r="A1094" s="2">
+        <v>3682</v>
+      </c>
+      <c r="B1094" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText603</t>
+        </is>
+      </c>
+      <c r="C1094" s="2" t="inlineStr">
+        <is>
+          <t>에셋 제작</t>
+        </is>
+      </c>
+      <c r="D1094" s="2" t="inlineStr">
+        <is>
+          <t>Asset creation</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1095">
+      <c r="A1095" s="2">
+        <v>3683</v>
+      </c>
+      <c r="B1095" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText604</t>
+        </is>
+      </c>
+      <c r="C1095" s="2" t="inlineStr">
+        <is>
+          <t>기준 이미지로 스프라이트 프레임이나 모델링 참고 이미지를 만듭니다.</t>
+        </is>
+      </c>
+      <c r="D1095" s="2" t="inlineStr">
+        <is>
+          <t>Create sprite frames or modeling-reference views from a reference image.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1096">
+      <c r="A1096" s="2">
+        <v>3684</v>
+      </c>
+      <c r="B1096" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText605</t>
+        </is>
+      </c>
+      <c r="C1096" s="2" t="inlineStr">
+        <is>
+          <t>스프라이트 애니메이션</t>
+        </is>
+      </c>
+      <c r="D1096" s="2" t="inlineStr">
+        <is>
+          <t>Sprite animation</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1097">
+      <c r="A1097" s="2">
+        <v>3685</v>
+      </c>
+      <c r="B1097" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText606</t>
+        </is>
+      </c>
+      <c r="C1097" s="2" t="inlineStr">
+        <is>
+          <t>캐릭터 삼면도</t>
+        </is>
+      </c>
+      <c r="D1097" s="2" t="inlineStr">
+        <is>
+          <t>Character views</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1098">
+      <c r="A1098" s="2">
+        <v>3686</v>
+      </c>
+      <c r="B1098" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText607</t>
+        </is>
+      </c>
+      <c r="C1098" s="2" t="inlineStr">
+        <is>
+          <t>물체 삼면도</t>
+        </is>
+      </c>
+      <c r="D1098" s="2" t="inlineStr">
+        <is>
+          <t>Object views</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1099">
+      <c r="A1099" s="2">
+        <v>3687</v>
+      </c>
+      <c r="B1099" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText608</t>
+        </is>
+      </c>
+      <c r="C1099" s="2" t="inlineStr">
+        <is>
+          <t>1. 기준 이미지</t>
+        </is>
+      </c>
+      <c r="D1099" s="2" t="inlineStr">
+        <is>
+          <t>1. Reference image</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1100">
+      <c r="A1100" s="2">
+        <v>3688</v>
+      </c>
+      <c r="B1100" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText609</t>
+        </is>
+      </c>
+      <c r="C1100" s="2" t="inlineStr">
+        <is>
+          <t>2. 제작 설정</t>
+        </is>
+      </c>
+      <c r="D1100" s="2" t="inlineStr">
+        <is>
+          <t>2. Creation settings</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1101">
+      <c r="A1101" s="2">
+        <v>3689</v>
+      </c>
+      <c r="B1101" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText610</t>
+        </is>
+      </c>
+      <c r="C1101" s="2" t="inlineStr">
+        <is>
+          <t>동작 설명</t>
+        </is>
+      </c>
+      <c r="D1101" s="2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1102">
+      <c r="A1102" s="2">
+        <v>3690</v>
+      </c>
+      <c r="B1102" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText611</t>
+        </is>
+      </c>
+      <c r="C1102" s="2" t="inlineStr">
+        <is>
+          <t>프레임 수</t>
+        </is>
+      </c>
+      <c r="D1102" s="2" t="inlineStr">
+        <is>
+          <t>Frame count</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1103">
+      <c r="A1103" s="2">
+        <v>3691</v>
+      </c>
+      <c r="B1103" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText612</t>
+        </is>
+      </c>
+      <c r="C1103" s="2" t="inlineStr">
+        <is>
+          <t>재생 속도 (FPS)</t>
+        </is>
+      </c>
+      <c r="D1103" s="2" t="inlineStr">
+        <is>
+          <t>Playback speed (FPS)</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1104">
+      <c r="A1104" s="2">
+        <v>3692</v>
+      </c>
+      <c r="B1104" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText613</t>
+        </is>
+      </c>
+      <c r="C1104" s="2" t="inlineStr">
+        <is>
+          <t>참고 이미지 변경 강도</t>
+        </is>
+      </c>
+      <c r="D1104" s="2" t="inlineStr">
+        <is>
+          <t>Reference change strength</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1105">
+      <c r="A1105" s="2">
+        <v>3693</v>
+      </c>
+      <c r="B1105" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText614</t>
+        </is>
+      </c>
+      <c r="C1105" s="2" t="inlineStr">
+        <is>
+          <t>픽셀 아트</t>
+        </is>
+      </c>
+      <c r="D1105" s="2" t="inlineStr">
+        <is>
+          <t>Pixel art</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1106">
+      <c r="A1106" s="2">
+        <v>3694</v>
+      </c>
+      <c r="B1106" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText615</t>
+        </is>
+      </c>
+      <c r="C1106" s="2" t="inlineStr">
+        <is>
+          <t>출력 프레임 크기 (px)</t>
+        </is>
+      </c>
+      <c r="D1106" s="2" t="inlineStr">
+        <is>
+          <t>Export frame size (px)</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1107">
+      <c r="A1107" s="2">
+        <v>3695</v>
+      </c>
+      <c r="B1107" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText616</t>
+        </is>
+      </c>
+      <c r="C1107" s="2" t="inlineStr">
+        <is>
+          <t>시트 열 수</t>
+        </is>
+      </c>
+      <c r="D1107" s="2" t="inlineStr">
+        <is>
+          <t>Sheet columns</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1108">
+      <c r="A1108" s="2">
+        <v>3696</v>
+      </c>
+      <c r="B1108" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText617</t>
+        </is>
+      </c>
+      <c r="C1108" s="2" t="inlineStr">
+        <is>
+          <t>묶음 만들기</t>
+        </is>
+      </c>
+      <c r="D1108" s="2" t="inlineStr">
+        <is>
+          <t>Create collection</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1109">
+      <c r="A1109" s="2">
+        <v>3697</v>
+      </c>
+      <c r="B1109" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText618</t>
+        </is>
+      </c>
+      <c r="C1109" s="2" t="inlineStr">
+        <is>
+          <t>재생</t>
+        </is>
+      </c>
+      <c r="D1109" s="2" t="inlineStr">
+        <is>
+          <t>Play</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1110">
+      <c r="A1110" s="2">
+        <v>3698</v>
+      </c>
+      <c r="B1110" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText619</t>
+        </is>
+      </c>
+      <c r="C1110" s="2" t="inlineStr">
+        <is>
+          <t>일시 정지</t>
+        </is>
+      </c>
+      <c r="D1110" s="2" t="inlineStr">
+        <is>
+          <t>Pause</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1111">
+      <c r="A1111" s="2">
+        <v>3699</v>
+      </c>
+      <c r="B1111" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText620</t>
+        </is>
+      </c>
+      <c r="C1111" s="2" t="inlineStr">
+        <is>
+          <t>프레임 {0}</t>
+        </is>
+      </c>
+      <c r="D1111" s="2" t="inlineStr">
+        <is>
+          <t>Frame {0}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1112">
+      <c r="A1112" s="2">
+        <v>3700</v>
+      </c>
+      <c r="B1112" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText621</t>
+        </is>
+      </c>
+      <c r="C1112" s="2" t="inlineStr">
+        <is>
+          <t>기준 이미지를 선택하고 제작 설명을 입력하세요.</t>
+        </is>
+      </c>
+      <c r="D1112" s="2" t="inlineStr">
+        <is>
+          <t>Select a reference image and describe the asset.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1113">
+      <c r="A1113" s="2">
+        <v>3701</v>
+      </c>
+      <c r="B1113" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText622</t>
+        </is>
+      </c>
+      <c r="C1113" s="2" t="inlineStr">
+        <is>
+          <t>3. 결과 확인</t>
+        </is>
+      </c>
+      <c r="D1113" s="2" t="inlineStr">
+        <is>
+          <t>3. Review results</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1114">
+      <c r="A1114" s="2">
+        <v>3702</v>
+      </c>
+      <c r="B1114" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText623</t>
+        </is>
+      </c>
+      <c r="C1114" s="2" t="inlineStr">
+        <is>
+          <t>이전 제작 묶음</t>
+        </is>
+      </c>
+      <c r="D1114" s="2" t="inlineStr">
+        <is>
+          <t>Previous collections</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1115">
+      <c r="A1115" s="2">
+        <v>3703</v>
+      </c>
+      <c r="B1115" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText624</t>
+        </is>
+      </c>
+      <c r="C1115" s="2" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="D1115" s="2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1116">
+      <c r="A1116" s="2">
+        <v>3704</v>
+      </c>
+      <c r="B1116" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText625</t>
+        </is>
+      </c>
+      <c r="C1116" s="2" t="inlineStr">
+        <is>
+          <t>생성 중</t>
+        </is>
+      </c>
+      <c r="D1116" s="2" t="inlineStr">
+        <is>
+          <t>Generating</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1117">
+      <c r="A1117" s="2">
+        <v>3705</v>
+      </c>
+      <c r="B1117" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText626</t>
+        </is>
+      </c>
+      <c r="C1117" s="2" t="inlineStr">
+        <is>
+          <t>다시 만들기 필요</t>
+        </is>
+      </c>
+      <c r="D1117" s="2" t="inlineStr">
+        <is>
+          <t>Needs regeneration</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1118">
+      <c r="A1118" s="2">
+        <v>3706</v>
+      </c>
+      <c r="B1118" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText627</t>
+        </is>
+      </c>
+      <c r="C1118" s="2" t="inlineStr">
+        <is>
+          <t>에셋 내보내기 폴더 선택</t>
+        </is>
+      </c>
+      <c r="D1118" s="2" t="inlineStr">
+        <is>
+          <t>Choose an asset export folder</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1119">
+      <c r="A1119" s="2">
+        <v>3707</v>
+      </c>
+      <c r="B1119" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText628</t>
+        </is>
+      </c>
+      <c r="C1119" s="2" t="inlineStr">
+        <is>
+          <t>선택 항목의 생성 설명</t>
+        </is>
+      </c>
+      <c r="D1119" s="2" t="inlineStr">
+        <is>
+          <t>Selected frame prompt</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1120">
+      <c r="A1120" s="2">
+        <v>3708</v>
+      </c>
+      <c r="B1120" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText629</t>
+        </is>
+      </c>
+      <c r="C1120" s="2" t="inlineStr">
+        <is>
+          <t>참고 생성으로 만드는 초안입니다. 외형·동작·시점의 일관성을 보장하지 않으므로 결과를 확인하고 필요한 항목을 다시 만드세요.</t>
+        </is>
+      </c>
+      <c r="D1120" s="2" t="inlineStr">
+        <is>
+          <t>These are reference-based drafts. Identity, motion and view consistency are not guaranteed. Review the results and regenerate individual items as needed.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1121">
+      <c r="A1121" s="2">
+        <v>3709</v>
+      </c>
+      <c r="B1121" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText630</t>
+        </is>
+      </c>
+      <c r="C1121" s="2" t="inlineStr">
+        <is>
+          <t>선택 항목 다시 만들기</t>
+        </is>
+      </c>
+      <c r="D1121" s="2" t="inlineStr">
+        <is>
+          <t>Regenerate selected</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1122">
+      <c r="A1122" s="2">
+        <v>3710</v>
+      </c>
+      <c r="B1122" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText631</t>
+        </is>
+      </c>
+      <c r="C1122" s="2" t="inlineStr">
+        <is>
+          <t>제작 취소</t>
+        </is>
+      </c>
+      <c r="D1122" s="2" t="inlineStr">
+        <is>
+          <t>Cancel creation</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1123">
+      <c r="A1123" s="2">
+        <v>3711</v>
+      </c>
+      <c r="B1123" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText632</t>
+        </is>
+      </c>
+      <c r="C1123" s="2" t="inlineStr">
+        <is>
+          <t>이미지 교체</t>
+        </is>
+      </c>
+      <c r="D1123" s="2" t="inlineStr">
+        <is>
+          <t>Replace image</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1124">
+      <c r="A1124" s="2">
+        <v>3712</v>
+      </c>
+      <c r="B1124" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText633</t>
+        </is>
+      </c>
+      <c r="C1124" s="2" t="inlineStr">
+        <is>
+          <t>미완성 이어 만들기</t>
+        </is>
+      </c>
+      <c r="D1124" s="2" t="inlineStr">
+        <is>
+          <t>Resume unfinished</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1125">
+      <c r="A1125" s="2">
+        <v>3713</v>
+      </c>
+      <c r="B1125" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText634</t>
+        </is>
+      </c>
+      <c r="C1125" s="2" t="inlineStr">
+        <is>
+          <t>에셋 제작 입력이나 묶음 기록이 올바르지 않습니다.</t>
+        </is>
+      </c>
+      <c r="D1125" s="2" t="inlineStr">
+        <is>
+          <t>The asset creation input or collection record is invalid.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1126">
+      <c r="A1126" s="2">
+        <v>3714</v>
+      </c>
+      <c r="B1126" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText635</t>
+        </is>
+      </c>
+      <c r="C1126" s="2" t="inlineStr">
+        <is>
+          <t>{0}/{1} 항목 생성 중</t>
+        </is>
+      </c>
+      <c r="D1126" s="2" t="inlineStr">
+        <is>
+          <t>Generating item {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1127">
+      <c r="A1127" s="2">
+        <v>3715</v>
+      </c>
+      <c r="B1127" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText636</t>
+        </is>
+      </c>
+      <c r="C1127" s="2" t="inlineStr">
+        <is>
+          <t>에셋 제작에 실패했습니다. 완성된 이미지는 유지됩니다.</t>
+        </is>
+      </c>
+      <c r="D1127" s="2" t="inlineStr">
+        <is>
+          <t>Asset creation failed. Completed images are preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1128">
+      <c r="A1128" s="2">
+        <v>3716</v>
+      </c>
+      <c r="B1128" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText637</t>
+        </is>
+      </c>
+      <c r="C1128" s="2" t="inlineStr">
+        <is>
+          <t>정면</t>
+        </is>
+      </c>
+      <c r="D1128" s="2" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1129">
+      <c r="A1129" s="2">
+        <v>3717</v>
+      </c>
+      <c r="B1129" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText638</t>
+        </is>
+      </c>
+      <c r="C1129" s="2" t="inlineStr">
+        <is>
+          <t>측면</t>
+        </is>
+      </c>
+      <c r="D1129" s="2" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1130">
+      <c r="A1130" s="2">
+        <v>3718</v>
+      </c>
+      <c r="B1130" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText639</t>
+        </is>
+      </c>
+      <c r="C1130" s="2" t="inlineStr">
+        <is>
+          <t>후면</t>
+        </is>
+      </c>
+      <c r="D1130" s="2" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1131">
+      <c r="A1131" s="2">
+        <v>3719</v>
+      </c>
+      <c r="B1131" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText640</t>
+        </is>
+      </c>
+      <c r="C1131" s="2" t="inlineStr">
+        <is>
+          <t>윗면</t>
+        </is>
+      </c>
+      <c r="D1131" s="2" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1132">
+      <c r="A1132" s="2">
+        <v>3720</v>
+      </c>
+      <c r="B1132" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText641</t>
+        </is>
+      </c>
+      <c r="C1132" s="2" t="inlineStr">
+        <is>
+          <t>예: 파란 망토를 입은 작은 기사</t>
+        </is>
+      </c>
+      <c r="D1132" s="2" t="inlineStr">
+        <is>
+          <t>e.g. a small knight wearing a blue cape</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1133">
+      <c r="A1133" s="2">
+        <v>3721</v>
+      </c>
+      <c r="B1133" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText642</t>
+        </is>
+      </c>
+      <c r="C1133" s="2" t="inlineStr">
+        <is>
+          <t>예: 오른쪽으로 걷기</t>
+        </is>
+      </c>
+      <c r="D1133" s="2" t="inlineStr">
+        <is>
+          <t>e.g. walking to the right</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1134">
+      <c r="A1134" s="2">
+        <v>3722</v>
+      </c>
+      <c r="B1134" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText643</t>
+        </is>
+      </c>
+      <c r="C1134" s="2" t="inlineStr">
+        <is>
+          <t>프레임별 포즈 설명 (선택)</t>
+        </is>
+      </c>
+      <c r="D1134" s="2" t="inlineStr">
+        <is>
+          <t>Per-frame poses (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1135">
+      <c r="A1135" s="2">
+        <v>3723</v>
+      </c>
+      <c r="B1135" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText644</t>
+        </is>
+      </c>
+      <c r="C1135" s="2" t="inlineStr">
+        <is>
+          <t>프레임 수만큼 한 줄씩 입력합니다. 비우면 공통 동작을 단계별 초안으로 만듭니다.</t>
+        </is>
+      </c>
+      <c r="D1135" s="2" t="inlineStr">
+        <is>
+          <t>Enter one pose per frame, one per line. Leave blank to draft phases of the shared action.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1136">
+      <c r="A1136" s="2">
+        <v>3724</v>
+      </c>
+      <c r="B1136" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText645</t>
+        </is>
+      </c>
+      <c r="C1136" s="2" t="inlineStr">
+        <is>
+          <t>모델·LoRA·출력 설정</t>
+        </is>
+      </c>
+      <c r="D1136" s="2" t="inlineStr">
+        <is>
+          <t>Model, LoRA and output</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1137">
+      <c r="A1137" s="2">
+        <v>3725</v>
+      </c>
+      <c r="B1137" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText646</t>
+        </is>
+      </c>
+      <c r="C1137" s="2" t="inlineStr">
+        <is>
+          <t>앞으로 이동</t>
+        </is>
+      </c>
+      <c r="D1137" s="2" t="inlineStr">
+        <is>
+          <t>Move earlier</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1138">
+      <c r="A1138" s="2">
+        <v>3726</v>
+      </c>
+      <c r="B1138" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText647</t>
+        </is>
+      </c>
+      <c r="C1138" s="2" t="inlineStr">
+        <is>
+          <t>뒤로 이동</t>
+        </is>
+      </c>
+      <c r="D1138" s="2" t="inlineStr">
+        <is>
+          <t>Move later</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1139">
+      <c r="A1139" s="2">
+        <v>3727</v>
+      </c>
+      <c r="B1139" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText648</t>
+        </is>
+      </c>
+      <c r="C1139" s="2" t="inlineStr">
+        <is>
+          <t>4. 공통 크기·하단 중앙 기준점으로 PNG와 시트를 저장합니다.</t>
+        </is>
+      </c>
+      <c r="D1139" s="2" t="inlineStr">
+        <is>
+          <t>4. Export PNG frames and a sheet at a common size with a bottom-center pivot.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1140">
+      <c r="A1140" s="2">
+        <v>3728</v>
+      </c>
+      <c r="B1140" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText649</t>
+        </is>
+      </c>
+      <c r="C1140" s="2" t="inlineStr">
+        <is>
+          <t>시트·PNG 내보내기</t>
+        </is>
+      </c>
+      <c r="D1140" s="2" t="inlineStr">
+        <is>
+          <t>Export sheet and PNGs</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1141">
+      <c r="A1141" s="2">
+        <v>3729</v>
+      </c>
+      <c r="B1141" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText650</t>
+        </is>
+      </c>
+      <c r="C1141" s="2" t="inlineStr">
+        <is>
+          <t>모든 항목에 이미지가 있어야 내보낼 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="D1141" s="2" t="inlineStr">
+        <is>
+          <t>All items need an image before export.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1142">
+      <c r="A1142" s="2">
+        <v>3730</v>
+      </c>
+      <c r="B1142" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText651</t>
+        </is>
+      </c>
+      <c r="C1142" s="2" t="inlineStr">
+        <is>
+          <t>출력 시트가 너무 큽니다. 프레임 크기를 줄이세요.</t>
+        </is>
+      </c>
+      <c r="D1142" s="2" t="inlineStr">
+        <is>
+          <t>The output sheet is too large. Reduce the frame size.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1143">
+      <c r="A1143" s="2">
+        <v>3731</v>
+      </c>
+      <c r="B1143" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText652</t>
+        </is>
+      </c>
+      <c r="C1143" s="2" t="inlineStr">
+        <is>
+          <t>스프라이트·삼면도 제작</t>
+        </is>
+      </c>
+      <c r="D1143" s="2" t="inlineStr">
+        <is>
+          <t>Create sprites and views</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1144">
+      <c r="A1144" s="2">
+        <v>3732</v>
+      </c>
+      <c r="B1144" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText653</t>
+        </is>
+      </c>
+      <c r="C1144" s="2" t="inlineStr">
+        <is>
+          <t>생성 결과의 큰 이미지에서 우클릭 메뉴의 에셋 제작을 선택하면 이미지와 기존 설명을 가져옵니다. 에셋 제작에서 기준 이미지와 대상 설명을 입력하고 스프라이트 또는 삼면도를 선택합니다. 스프라이트는 동작·프레임 수·재생 속도를 지정합니다. 캐릭터는 정면·측면·후면, 물체는 정면·측면·윗면을 만듭니다. 결과에서 항목을 선택해 다시 만들거나 이미지로 교체할 수 있고, 스프라이트는 순서 변경과 반복 재생을 지원합니다. 취소·실패한 묶음은 미완성 이어 만들기로 남은 항목만 생성합니다. 내보내면 새 폴더에 개별 PNG, 시트, 좌표·기준점·FPS JSON과 원본 사본을 저장합니다. 참고 생성 기반 초안이므로 동작 연결이나 삼면도의 형태가 정확히 맞는지 직접 확인하세요.</t>
+        </is>
+      </c>
+      <c r="D1144" s="2" t="inlineStr">
+        <is>
+          <t>Right-click a large result preview and choose Asset creation to use its image and existing description. In Asset creation, select a reference, describe the subject and choose sprites or views. For sprites, enter an action, frame count and playback speed. Character views include front, side and back; object views include front, side and top. Regenerate or replace selected items, and reorder or loop sprite frames. Resume unfinished collections after cancellation or failure. Export creates a new folder with individual PNGs, a sheet, rectangle/pivot/FPS JSON and source copies. These reference-based drafts require review of motion continuity and view consistency.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1145">
+      <c r="A1145" s="2">
+        <v>3733</v>
+      </c>
+      <c r="B1145" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText654</t>
+        </is>
+      </c>
+      <c r="C1145" s="2" t="inlineStr">
+        <is>
+          <t>공통 시드: {0}</t>
+        </is>
+      </c>
+      <c r="D1145" s="2" t="inlineStr">
+        <is>
+          <t>Common seed: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1146">
+      <c r="A1146" s="2">
+        <v>3734</v>
+      </c>
+      <c r="B1146" s="2" t="inlineStr">
+        <is>
+          <t>EidolonText655</t>
+        </is>
+      </c>
+      <c r="C1146" s="2" t="inlineStr">
+        <is>
+          <t>에셋 제작은 ComfyUI 생성 방식에서 사용할 수 있습니다. 생성 환경에서 방식을 변경하세요.</t>
+        </is>
+      </c>
+      <c r="D1146" s="2" t="inlineStr">
+        <is>
+          <t>Asset creation uses ComfyUI. Change the backend in Generation environment to create assets.</t>
+        </is>
+      </c>
+    </row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R7a3f3334b94f4df9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Define" sheetId="2" r:id="Rb6e07b3774574c7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R0fd105b852534051"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Define" sheetId="2" r:id="R9c10a561ab2d4882"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1773,7 +1773,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
@@ -1784,6 +1784,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -13234,10 +13237,10 @@
         <x:v>EidolonText185</x:v>
       </x:c>
       <x:c r="C682" s="3" t="str">
-        <x:v>1. 생성 환경 선택</x:v>
+        <x:v>처음 시작하기</x:v>
       </x:c>
       <x:c r="D682" s="3" t="str">
-        <x:v>1. Choose a generation environment</x:v>
+        <x:v>Getting started</x:v>
       </x:c>
     </x:row>
     <x:row r="683" ht="92.4000015258789" hidden="0" customHeight="1">
@@ -13248,10 +13251,14 @@
         <x:v>EidolonText186</x:v>
       </x:c>
       <x:c r="C683" s="3" t="str">
-        <x:v>생성 환경의 생성 방식·지침에서 ComfyUI 또는 Codex와 공통 생성 지침·제외할 요소·프리셋을 저장합니다. 이미지 저장 폴더·언어·테마는 설정에서 별도로 저장합니다.</x:v>
+        <x:v>1. 생성 환경 → 생성 방식·지침에서 ComfyUI 또는 Codex를 선택합니다.
+2. Codex를 사용하려면 설치된 Codex에서 먼저 로그인하고 실행 모델을 선택합니다. 기본 모델은 Codex의 기본값을 사용합니다.
+3. 공통 생성 지침·제외할 요소와 프리셋을 정하고 생성 환경 저장을 누릅니다.</x:v>
       </x:c>
       <x:c r="D683" s="3" t="str">
-        <x:v>Save ComfyUI or Codex, shared guidelines, excluded elements and presets in Generation environment &gt; Generation method and guidelines. Save the output folder, language and theme separately in Settings.</x:v>
+        <x:v>1. Open Generation environment &gt; Generation method and guidelines and choose ComfyUI or Codex.
+2. For Codex, sign in to your installed Codex and select an execution model. Default model uses the CLI default.
+3. Set shared guidelines, exclusions and presets, then save the generation environment.</x:v>
       </x:c>
     </x:row>
     <x:row r="684" ht="92.4000015258789" hidden="0" customHeight="1">
@@ -13262,10 +13269,10 @@
         <x:v>EidolonText187</x:v>
       </x:c>
       <x:c r="C684" s="3" t="str">
-        <x:v>ComfyUI는 엔진 설치에서 실행 환경을 준비하고 모델·LoRA에서 기반 모델을 설치하거나 모델 폴더에 넣고 새로고침합니다. NVIDIA GPU가 없으면 CPU 환경으로 이미지 생성만 지원합니다.</x:v>
+        <x:v>ComfyUI는 설정 → 엔진 설치·연결에서 실행 환경을 준비합니다. 생성 환경 → 모델·LoRA에서 모델을 설치하거나 모델 폴더·LoRA 폴더에 .safetensors를 넣고 새로고침합니다. CPU 환경은 이미지 생성만 지원합니다.</x:v>
       </x:c>
       <x:c r="D684" s="3" t="str">
-        <x:v>For ComfyUI, prepare the runtime in Engine setup, then install a base model or place it in Model folder and refresh. CPU supports image generation only.</x:v>
+        <x:v>For ComfyUI, prepare the runtime in Settings &gt; Engine setup and connection. Install a model in Generation environment &gt; Models and LoRAs, or put .safetensors files in Model folder or LoRA folder and refresh. CPU mode supports image generation only.</x:v>
       </x:c>
     </x:row>
     <x:row r="685" ht="16.5" hidden="0" customHeight="1">
@@ -13276,10 +13283,10 @@
         <x:v>EidolonText188</x:v>
       </x:c>
       <x:c r="C685" s="3" t="str">
-        <x:v>프롬프트로 이미지 생성</x:v>
+        <x:v>이미지 생성</x:v>
       </x:c>
       <x:c r="D685" s="3" t="str">
-        <x:v>Generate from a prompt</x:v>
+        <x:v>Generate images</x:v>
       </x:c>
     </x:row>
     <x:row r="686" ht="105.5999984741211" hidden="0" customHeight="1">
@@ -13290,10 +13297,14 @@
         <x:v>EidolonText189</x:v>
       </x:c>
       <x:c r="C686" s="3" t="str">
-        <x:v>설명을 입력하고 생성 요청을 추가합니다. ComfyUI에서는 모델과 선택할 LoRA를 지정합니다. Codex에서는 저장된 실행 모델을 사용합니다. 배경 투명하게를 켜면 투명 PNG를 요청하며 실행 중에도 다음 요청을 추가할 수 있습니다.</x:v>
+        <x:v>1. 이미지 생성에서 만들고 싶은 대상을 설명합니다. ComfyUI는 모델과 호환 LoRA를 선택하고 Codex는 저장한 실행 모델을 사용합니다.
+2. 필요한 경우 참고 이미지를 추가하거나 배경 투명하게를 켭니다.
+3. 생성 요청을 추가합니다. 실행 중에도 다음 요청을 작성할 수 있습니다.</x:v>
       </x:c>
       <x:c r="D686" s="3" t="str">
-        <x:v>Describe the image and submit a request. ComfyUI uses your selected model and LoRAs; Codex uses the saved agent model. Enable Transparent background for a transparent PNG. More requests can be queued while running.</x:v>
+        <x:v>1. In Generate, describe the image. For ComfyUI, choose a model and compatible LoRAs. Codex uses the saved execution model.
+2. Add a reference image or enable Transparent background if needed.
+3. Submit the request. You can prepare more requests while a job is running.</x:v>
       </x:c>
     </x:row>
     <x:row r="687" ht="105.5999984741211" hidden="0" customHeight="1">
@@ -13304,10 +13315,10 @@
         <x:v>EidolonText190</x:v>
       </x:c>
       <x:c r="C687" s="3" t="str">
-        <x:v>생성 환경에서 공통 생성 지침과 제외할 요소를 편집하고 프리셋을 선택하거나 추가·수정합니다. 생성 환경 저장을 누르면 이후 생성·편집 요청에 적용하며 대기 중인 요청은 기존 설정을 유지합니다.</x:v>
+        <x:v>생성 환경의 지침은 새 생성·편집 요청에 공통으로 적용합니다. 저장 전에 대기열에 넣은 요청은 기존 설정을 유지합니다.</x:v>
       </x:c>
       <x:c r="D687" s="3" t="str">
-        <x:v>Edit shared guidelines and exclusions, and select, add or update presets in Generation environment. Save the generation environment to apply them to new generation and editing requests. Queued requests retain their settings.</x:v>
+        <x:v>Shared guidelines apply to new generation and editing requests. Requests queued before saving retain their previous settings.</x:v>
       </x:c>
     </x:row>
     <x:row r="688" ht="16.5" hidden="0" customHeight="1">
@@ -13318,10 +13329,10 @@
         <x:v>EidolonText191</x:v>
       </x:c>
       <x:c r="C688" s="3" t="str">
-        <x:v>3. 내 이미지로 LoRA 학습</x:v>
+        <x:v>LoRA 학습</x:v>
       </x:c>
       <x:c r="D688" s="3" t="str">
-        <x:v>3. Train a LoRA with your images</x:v>
+        <x:v>Train a LoRA</x:v>
       </x:c>
     </x:row>
     <x:row r="689" ht="118.80000305175781" hidden="0" customHeight="1">
@@ -13332,10 +13343,16 @@
         <x:v>EidolonText192</x:v>
       </x:c>
       <x:c r="C689" s="3" t="str">
-        <x:v>이미지 선택 → 이름·트리거 → 학습 설정 순서로 진행합니다. 첫 이미지의 설명을 자동으로 채우고 이름·트리거는 기본값을 제공합니다. 확인하거나 수정한 뒤 학습하세요. 학습 폴더는 엔진 경로 아래 작업별로 자동 준비하며 엔진 설치에서 열거나 비울 수 있습니다.</x:v>
+        <x:v>1. 학습할 이미지를 흰색·검정색 배경 목록에 추가합니다.
+2. 자동 입력된 설명과 LoRA 이름·트리거를 확인하거나 수정합니다.
+3. 학습 설정을 확인하고 학습을 시작합니다. 학습 데이터는 엔진 경로 아래 작업별 폴더에 자동 준비합니다.
+4. 완료된 LoRA를 이미지 생성에서 선택하면 저장한 트리거가 자동으로 적용됩니다.</x:v>
       </x:c>
       <x:c r="D689" s="3" t="str">
-        <x:v>Select images, review the name and trigger, then configure training. The first image fills the description; a name and trigger are provided. Review or edit them before training. Datasets are prepared per job under the engine path and can be opened or cleared in Engine setup.</x:v>
+        <x:v>1. Add training images to the white or black background lists.
+2. Review or edit the suggested description, LoRA name and trigger.
+3. Review training settings and start. A dataset is prepared automatically in a per-job folder under the engine path.
+4. Select the completed LoRA when generating to apply its saved trigger automatically.</x:v>
       </x:c>
     </x:row>
     <x:row r="690" ht="105.5999984741211" hidden="0" customHeight="1">
@@ -13346,10 +13363,10 @@
         <x:v>EidolonText193</x:v>
       </x:c>
       <x:c r="C690" s="3" t="str">
-        <x:v>LoRA 학습에는 로컬 ComfyUI 환경·기반 모델과 NVIDIA GPU가 필요합니다. 생성에서 호환 LoRA를 선택하면 저장된 트리거가 자동 적용됩니다. Codex 생성에는 LoRA를 적용하지 않습니다.</x:v>
+        <x:v>학습에는 앱이 관리하는 로컬 ComfyUI 환경·기반 모델과 NVIDIA GPU가 필요합니다. 기존 LoRA를 이어 학습해 새 가중치를 만들 수 있습니다. Codex 생성에는 LoRA를 적용하지 않습니다.</x:v>
       </x:c>
       <x:c r="D690" s="3" t="str">
-        <x:v>LoRA training requires a local ComfyUI runtime, base model and NVIDIA GPU. Selecting a compatible LoRA applies its saved trigger. LoRAs do not apply to Codex generation.</x:v>
+        <x:v>Training requires a local ComfyUI runtime managed by this app, a base model and an NVIDIA GPU. You can continue training an existing LoRA to produce new weights. LoRAs do not apply to Codex generation.</x:v>
       </x:c>
     </x:row>
     <x:row r="691" ht="16.5" hidden="0" customHeight="1">
@@ -13374,10 +13391,10 @@
         <x:v>EidolonText195</x:v>
       </x:c>
       <x:c r="C692" s="3" t="str">
-        <x:v>하단에는 상태·진행률·남은 시간과 대기 건수만 표시합니다. 학습 취소는 학습 요청 버튼 옆에 있습니다. 생성·학습 화면의 대기열 목록에서 아직 시작하지 않은 요청을 비울 수 있습니다. 앱 종료 시 실행 중인 작업과 대기 요청을 정리합니다.</x:v>
+        <x:v>생성·편집·학습과 에셋 요청은 순서대로 실행합니다. 하단은 상태·진행률·학습 예상 남은 시간·대기 건수만 표시합니다. 취소와 대기열 비우기는 해당 화면의 실행 영역에서 사용합니다. 앱을 종료하면 실행 중인 작업과 대기 요청을 정리합니다.</x:v>
       </x:c>
       <x:c r="D692" s="3" t="str">
-        <x:v>The footer displays status, progress, time remaining and pending count. Cancel training beside the request button. Clear requests that have not started from the queue in Generate or Train. Closing the app cleans up running and pending work.</x:v>
+        <x:v>Generation, editing, training and asset requests run in order. The footer shows status, progress, estimated training time remaining and pending count. Use cancellation and queue actions in the current screen. Closing the app cleans up active and queued requests.</x:v>
       </x:c>
     </x:row>
     <x:row r="693" ht="118.80000305175781" hidden="0" customHeight="1">
@@ -13388,10 +13405,10 @@
         <x:v>EidolonText196</x:v>
       </x:c>
       <x:c r="C693" s="3" t="str">
-        <x:v>오류가 발생하면 앱 로그, 설치 폴더의 Logs, 해당 학습 작업의 Training.log를 확인하세요. 모델 등록 해제는 가중치 파일을 삭제하지 않습니다. 설정 파일이 손상되면 사용자 데이터 폴더의 .bak 파일로 복원할 수 있습니다.</x:v>
+        <x:v>오류가 발생하면 앱 로그 폴더를 열어 Eidolon.log를 확인합니다. 엔진 설치 폴더의 Logs와 각 Job의 Codex.log·Training.log에도 실행 내용이 남습니다. 손상된 설정은 사용자 데이터 폴더의 .bak 파일을 확인하세요.</x:v>
       </x:c>
       <x:c r="D693" s="3" t="str">
-        <x:v>If an error occurs, check the app log, the installation folder's Logs, or Training.log in the training job folder. Unregistering a model preserves its weights. Restore a damaged settings file from its .bak backup in the user data folder.</x:v>
+        <x:v>For errors, open the app log folder and check Eidolon.log. Runtime logs are also stored in the engine folder's Logs and each job's Codex.log or Training.log. For damaged settings, check the .bak file in the user data folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="694" ht="16.5" hidden="0" customHeight="1">
@@ -14642,10 +14659,10 @@
         <x:v>EidolonText285</x:v>
       </x:c>
       <x:c r="C782" s="3" t="str">
-        <x:v>ComfyUI 서버 주소는 엔진 설치에서 입력합니다. 기존 서버에 연결하거나 로컬 설치 엔진을 실행합니다. Codex는 ComfyUI 설치와 서버 연결 없이 설치된 Codex의 로그인으로 사용합니다.</x:v>
+        <x:v>ComfyUI 서버 주소도 엔진 설치·연결에서 입력합니다. 기존 서버에 연결하거나 설치한 로컬 엔진을 실행합니다. Codex는 ComfyUI 설치 없이 사용할 수 있습니다.</x:v>
       </x:c>
       <x:c r="D782" s="3" t="str">
-        <x:v>Set the ComfyUI server address in Engine setup. Connect to an existing server or start the installed local engine. Codex uses its own sign-in without ComfyUI setup.</x:v>
+        <x:v>Set the ComfyUI server address in Engine setup and connection. Connect to an existing server or start the installed local engine. Codex can be used without installing ComfyUI.</x:v>
       </x:c>
     </x:row>
     <x:row r="783" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -17320,10 +17337,10 @@
         <x:v>EidolonText476</x:v>
       </x:c>
       <x:c r="C973" s="3" t="str">
-        <x:v>기존 이미지의 그림체 바꾸기</x:v>
+        <x:v>이미지 편집</x:v>
       </x:c>
       <x:c r="D973" s="3" t="str">
-        <x:v>Change an image style</x:v>
+        <x:v>Edit images</x:v>
       </x:c>
     </x:row>
     <x:row r="974">
@@ -17334,10 +17351,14 @@
         <x:v>EidolonText477</x:v>
       </x:c>
       <x:c r="C974" s="3" t="str">
-        <x:v>원본 이미지와 수정 설명을 입력해 편집을 요청합니다. ComfyUI는 선택 모델·LoRA와 변경 강도를 사용하고, Codex는 원본과 수정 설명을 함께 전달합니다. 원본은 보존하고 결과는 새 이미지로 저장합니다.</x:v>
+        <x:v>1. 이미지 편집에서 원본 이미지를 선택합니다. 생성 결과의 이 이미지로 편집으로 가져올 수도 있습니다.
+2. 바꾸고 싶은 그림체나 내용을 설명하고 편집 요청을 추가합니다.
+3. 결과는 새 이미지로 저장합니다. 원본 파일은 보존합니다.</x:v>
       </x:c>
       <x:c r="D974" s="3" t="str">
-        <x:v>Provide a source image and edit instructions. ComfyUI uses the selected model, LoRAs and change strength; Codex receives the image and instructions. The source is preserved and the result is saved as a new image.</x:v>
+        <x:v>1. In Edit, choose a source image, or use Edit this image from Results.
+2. Describe the style or content changes and submit the request.
+3. The result is saved as a new image. The source file is preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="975">
@@ -17348,10 +17369,10 @@
         <x:v>EidolonText479</x:v>
       </x:c>
       <x:c r="C975" s="3" t="str">
-        <x:v>변경 강도가 낮을수록 원본을 더 유지하고, 높을수록 새 그림체와 설명을 더 반영합니다. 형태나 구도를 정확히 고정하지는 않습니다. 원본 파일은 변경하지 않습니다.</x:v>
+        <x:v>ComfyUI는 모델·LoRA와 변경 강도를 사용합니다. 낮은 강도는 원본을 더 유지하고 높은 강도는 수정 설명을 더 반영합니다. Codex에는 원본과 수정 설명을 전달하며 변경 강도·LoRA는 적용하지 않습니다.</x:v>
       </x:c>
       <x:c r="D975" s="3" t="str">
-        <x:v>Lower change strength retains more of the original; higher strength applies more of the new style and description. Exact shape or composition is not guaranteed. The source file is preserved.</x:v>
+        <x:v>ComfyUI uses a model, LoRAs and change strength. Lower strength retains more of the source; higher strength applies more of your edit instructions. Codex receives the image and instructions without change strength or LoRAs.</x:v>
       </x:c>
     </x:row>
     <x:row r="976">
@@ -18706,1506 +18727,1634 @@
         <x:v>Deleted {0} training dataset folders.</x:v>
       </x:c>
     </x:row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1072">
-      <c r="A1072" s="2">
-        <v>3660</v>
-      </c>
-      <c r="B1072" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText581</t>
-        </is>
-      </c>
-      <c r="C1072" s="2" t="inlineStr">
-        <is>
-          <t>생성 환경</t>
-        </is>
-      </c>
-      <c r="D1072" s="2" t="inlineStr">
-        <is>
-          <t>Generation environment</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1073">
-      <c r="A1073" s="2">
-        <v>3661</v>
-      </c>
-      <c r="B1073" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText582</t>
-        </is>
-      </c>
-      <c r="C1073" s="2" t="inlineStr">
-        <is>
-          <t>생성 방식과 사용할 모델, 모든 이미지에 적용할 공통 지침을 관리합니다.</t>
-        </is>
-      </c>
-      <c r="D1073" s="2" t="inlineStr">
-        <is>
-          <t>Manage generation methods, models, and instructions shared by all images.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1074">
-      <c r="A1074" s="2">
-        <v>3662</v>
-      </c>
-      <c r="B1074" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText583</t>
-        </is>
-      </c>
-      <c r="C1074" s="2" t="inlineStr">
-        <is>
-          <t>생성 방식</t>
-        </is>
-      </c>
-      <c r="D1074" s="2" t="inlineStr">
-        <is>
-          <t>Generation methods</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1075">
-      <c r="A1075" s="2">
-        <v>3663</v>
-      </c>
-      <c r="B1075" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText584</t>
-        </is>
-      </c>
-      <c r="C1075" s="2" t="inlineStr">
-        <is>
-          <t>학습 데이터</t>
-        </is>
-      </c>
-      <c r="D1075" s="2" t="inlineStr">
-        <is>
-          <t>Training data</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1076">
-      <c r="A1076" s="2">
-        <v>3664</v>
-      </c>
-      <c r="B1076" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText585</t>
-        </is>
-      </c>
-      <c r="C1076" s="2" t="inlineStr">
-        <is>
-          <t>준비한 학습 데이터로 LoRA를 학습합니다. 데이터 준비와 수정은 설정에서 진행하세요.</t>
-        </is>
-      </c>
-      <c r="D1076" s="2" t="inlineStr">
-        <is>
-          <t>Train a LoRA with the prepared dataset. Prepare and edit training data in Settings.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1077">
-      <c r="A1077" s="2">
-        <v>3665</v>
-      </c>
-      <c r="B1077" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText586</t>
-        </is>
-      </c>
-      <c r="C1077" s="2" t="inlineStr">
-        <is>
-          <t>화면과 저장 위치, 엔진 설치·연결, 학습 데이터 준비를 관리합니다.</t>
-        </is>
-      </c>
-      <c r="D1077" s="2" t="inlineStr">
-        <is>
-          <t>Manage appearance, storage, engine setup and connections, and training data.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1078">
-      <c r="A1078" s="2">
-        <v>3666</v>
-      </c>
-      <c r="B1078" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText587</t>
-        </is>
-      </c>
-      <c r="C1078" s="2" t="inlineStr">
-        <is>
-          <t>학습 데이터가 아직 없습니다. 위의 학습 데이터를 눌러 이미지와 설명을 준비하세요.</t>
-        </is>
-      </c>
-      <c r="D1078" s="2" t="inlineStr">
-        <is>
-          <t>No training data is ready. Select Training data above to prepare images and captions.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1079">
-      <c r="A1079" s="2">
-        <v>3667</v>
-      </c>
-      <c r="B1079" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText588</t>
-        </is>
-      </c>
-      <c r="C1079" s="2" t="inlineStr">
-        <is>
-          <t>설명으로 새로운 이미지를 만듭니다. 참고 이미지를 추가하면 기존 이미지의 구도와 내용을 바탕으로 생성할 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="D1079" s="2" t="inlineStr">
-        <is>
-          <t>Create a new image from a description. Add a reference image to guide its composition and content.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1080">
-      <c r="A1080" s="2">
-        <v>3668</v>
-      </c>
-      <c r="B1080" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText589</t>
-        </is>
-      </c>
-      <c r="C1080" s="2" t="inlineStr">
-        <is>
-          <t>이미지와 원하는 그림체를 지정해 편집합니다. 변경 강도로 기존 이미지가 유지되는 정도를 조절합니다.</t>
-        </is>
-      </c>
-      <c r="D1080" s="2" t="inlineStr">
-        <is>
-          <t>Choose an image and describe the desired style. Change strength controls how much of the original image is preserved.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1081">
-      <c r="A1081" s="2">
-        <v>3669</v>
-      </c>
-      <c r="B1081" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText590</t>
-        </is>
-      </c>
-      <c r="C1081" s="2" t="inlineStr">
-        <is>
-          <t>생성으로 이동</t>
-        </is>
-      </c>
-      <c r="D1081" s="2" t="inlineStr">
-        <is>
-          <t>Open Generate</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1082">
-      <c r="A1082" s="2">
-        <v>3670</v>
-      </c>
-      <c r="B1082" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText591</t>
-        </is>
-      </c>
-      <c r="C1082" s="2" t="inlineStr">
-        <is>
-          <t>편집으로 이동</t>
-        </is>
-      </c>
-      <c r="D1082" s="2" t="inlineStr">
-        <is>
-          <t>Open Edit</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1083">
-      <c r="A1083" s="2">
-        <v>3671</v>
-      </c>
-      <c r="B1083" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText592</t>
-        </is>
-      </c>
-      <c r="C1083" s="2" t="inlineStr">
-        <is>
-          <t>저장 위치</t>
-        </is>
-      </c>
-      <c r="D1083" s="2" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1084">
-      <c r="A1084" s="2">
-        <v>3672</v>
-      </c>
-      <c r="B1084" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText593</t>
-        </is>
-      </c>
-      <c r="C1084" s="2" t="inlineStr">
-        <is>
-          <t>엔진 설치·연결</t>
-        </is>
-      </c>
-      <c r="D1084" s="2" t="inlineStr">
-        <is>
-          <t>Engine setup and connection</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1085">
-      <c r="A1085" s="2">
-        <v>3673</v>
-      </c>
-      <c r="B1085" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText594</t>
-        </is>
-      </c>
-      <c r="C1085" s="2" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="D1085" s="2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1086">
-      <c r="A1086" s="2">
-        <v>3674</v>
-      </c>
-      <c r="B1086" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText595</t>
-        </is>
-      </c>
-      <c r="C1086" s="2" t="inlineStr">
-        <is>
-          <t>MCP 연결</t>
-        </is>
-      </c>
-      <c r="D1086" s="2" t="inlineStr">
-        <is>
-          <t>MCP connection</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1087">
-      <c r="A1087" s="2">
-        <v>3675</v>
-      </c>
-      <c r="B1087" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText596</t>
-        </is>
-      </c>
-      <c r="C1087" s="2" t="inlineStr">
-        <is>
-          <t>외부 AI 도구에서 이미지 생성·편집과 결과 조회를 사용할 수 있습니다. 사용할 때 서버를 켜세요.</t>
-        </is>
-      </c>
-      <c r="D1087" s="2" t="inlineStr">
-        <is>
-          <t>Use image generation, editing and result lookup from external AI tools. Start the server when you need it.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1088">
-      <c r="A1088" s="2">
-        <v>3676</v>
-      </c>
-      <c r="B1088" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText597</t>
-        </is>
-      </c>
-      <c r="C1088" s="2" t="inlineStr">
-        <is>
-          <t>생성 지침은 MCP 요청별로 바꿀 수 있습니다. 저장한 설정은 유지되며 같은 PC에서만 연결합니다.</t>
-        </is>
-      </c>
-      <c r="D1088" s="2" t="inlineStr">
-        <is>
-          <t>Override generation instructions per MCP request. Saved settings are preserved. Connections are limited to this PC.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1089">
-      <c r="A1089" s="2">
-        <v>3677</v>
-      </c>
-      <c r="B1089" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText598</t>
-        </is>
-      </c>
-      <c r="C1089" s="2" t="inlineStr">
-        <is>
-          <t>연결 대기 중</t>
-        </is>
-      </c>
-      <c r="D1089" s="2" t="inlineStr">
-        <is>
-          <t>Listening</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1090">
-      <c r="A1090" s="2">
-        <v>3678</v>
-      </c>
-      <c r="B1090" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText599</t>
-        </is>
-      </c>
-      <c r="C1090" s="2" t="inlineStr">
-        <is>
-          <t>서버 꺼짐</t>
-        </is>
-      </c>
-      <c r="D1090" s="2" t="inlineStr">
-        <is>
-          <t>Server stopped</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1091">
-      <c r="A1091" s="2">
-        <v>3679</v>
-      </c>
-      <c r="B1091" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText600</t>
-        </is>
-      </c>
-      <c r="C1091" s="2" t="inlineStr">
-        <is>
-          <t>서버 켜기</t>
-        </is>
-      </c>
-      <c r="D1091" s="2" t="inlineStr">
-        <is>
-          <t>Start server</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1092">
-      <c r="A1092" s="2">
-        <v>3680</v>
-      </c>
-      <c r="B1092" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText601</t>
-        </is>
-      </c>
-      <c r="C1092" s="2" t="inlineStr">
-        <is>
-          <t>서버 끄기</t>
-        </is>
-      </c>
-      <c r="D1092" s="2" t="inlineStr">
-        <is>
-          <t>Stop server</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1093">
-      <c r="A1093" s="2">
-        <v>3681</v>
-      </c>
-      <c r="B1093" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText602</t>
-        </is>
-      </c>
-      <c r="C1093" s="2" t="inlineStr">
-        <is>
-          <t>MCP 주소의 수신 권한이 없습니다. 사용법 문서의 HTTP URL 예약 안내를 확인하세요.</t>
-        </is>
-      </c>
-      <c r="D1093" s="2" t="inlineStr">
-        <is>
-          <t>The MCP address has no listener permission. See the HTTP URL reservation instructions in the usage document.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1094">
-      <c r="A1094" s="2">
-        <v>3682</v>
-      </c>
-      <c r="B1094" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText603</t>
-        </is>
-      </c>
-      <c r="C1094" s="2" t="inlineStr">
-        <is>
-          <t>에셋 제작</t>
-        </is>
-      </c>
-      <c r="D1094" s="2" t="inlineStr">
-        <is>
-          <t>Asset creation</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1095">
-      <c r="A1095" s="2">
-        <v>3683</v>
-      </c>
-      <c r="B1095" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText604</t>
-        </is>
-      </c>
-      <c r="C1095" s="2" t="inlineStr">
-        <is>
-          <t>기준 이미지로 스프라이트 프레임이나 모델링 참고 이미지를 만듭니다.</t>
-        </is>
-      </c>
-      <c r="D1095" s="2" t="inlineStr">
-        <is>
-          <t>Create sprite frames or modeling-reference views from a reference image.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1096">
-      <c r="A1096" s="2">
-        <v>3684</v>
-      </c>
-      <c r="B1096" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText605</t>
-        </is>
-      </c>
-      <c r="C1096" s="2" t="inlineStr">
-        <is>
-          <t>스프라이트 애니메이션</t>
-        </is>
-      </c>
-      <c r="D1096" s="2" t="inlineStr">
-        <is>
-          <t>Sprite animation</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1097">
-      <c r="A1097" s="2">
-        <v>3685</v>
-      </c>
-      <c r="B1097" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText606</t>
-        </is>
-      </c>
-      <c r="C1097" s="2" t="inlineStr">
-        <is>
-          <t>캐릭터 삼면도</t>
-        </is>
-      </c>
-      <c r="D1097" s="2" t="inlineStr">
-        <is>
-          <t>Character views</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1098">
-      <c r="A1098" s="2">
-        <v>3686</v>
-      </c>
-      <c r="B1098" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText607</t>
-        </is>
-      </c>
-      <c r="C1098" s="2" t="inlineStr">
-        <is>
-          <t>물체 삼면도</t>
-        </is>
-      </c>
-      <c r="D1098" s="2" t="inlineStr">
-        <is>
-          <t>Object views</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1099">
-      <c r="A1099" s="2">
-        <v>3687</v>
-      </c>
-      <c r="B1099" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText608</t>
-        </is>
-      </c>
-      <c r="C1099" s="2" t="inlineStr">
-        <is>
-          <t>1. 기준 이미지</t>
-        </is>
-      </c>
-      <c r="D1099" s="2" t="inlineStr">
-        <is>
-          <t>1. Reference image</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1100">
-      <c r="A1100" s="2">
-        <v>3688</v>
-      </c>
-      <c r="B1100" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText609</t>
-        </is>
-      </c>
-      <c r="C1100" s="2" t="inlineStr">
-        <is>
-          <t>2. 제작 설정</t>
-        </is>
-      </c>
-      <c r="D1100" s="2" t="inlineStr">
-        <is>
-          <t>2. Creation settings</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1101">
-      <c r="A1101" s="2">
-        <v>3689</v>
-      </c>
-      <c r="B1101" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText610</t>
-        </is>
-      </c>
-      <c r="C1101" s="2" t="inlineStr">
-        <is>
-          <t>동작 설명</t>
-        </is>
-      </c>
-      <c r="D1101" s="2" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1102">
-      <c r="A1102" s="2">
-        <v>3690</v>
-      </c>
-      <c r="B1102" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText611</t>
-        </is>
-      </c>
-      <c r="C1102" s="2" t="inlineStr">
-        <is>
-          <t>프레임 수</t>
-        </is>
-      </c>
-      <c r="D1102" s="2" t="inlineStr">
-        <is>
-          <t>Frame count</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1103">
-      <c r="A1103" s="2">
-        <v>3691</v>
-      </c>
-      <c r="B1103" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText612</t>
-        </is>
-      </c>
-      <c r="C1103" s="2" t="inlineStr">
-        <is>
-          <t>재생 속도 (FPS)</t>
-        </is>
-      </c>
-      <c r="D1103" s="2" t="inlineStr">
-        <is>
-          <t>Playback speed (FPS)</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1104">
-      <c r="A1104" s="2">
-        <v>3692</v>
-      </c>
-      <c r="B1104" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText613</t>
-        </is>
-      </c>
-      <c r="C1104" s="2" t="inlineStr">
-        <is>
-          <t>참고 이미지 변경 강도</t>
-        </is>
-      </c>
-      <c r="D1104" s="2" t="inlineStr">
-        <is>
-          <t>Reference change strength</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1105">
-      <c r="A1105" s="2">
-        <v>3693</v>
-      </c>
-      <c r="B1105" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText614</t>
-        </is>
-      </c>
-      <c r="C1105" s="2" t="inlineStr">
-        <is>
-          <t>픽셀 아트</t>
-        </is>
-      </c>
-      <c r="D1105" s="2" t="inlineStr">
-        <is>
-          <t>Pixel art</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1106">
-      <c r="A1106" s="2">
-        <v>3694</v>
-      </c>
-      <c r="B1106" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText615</t>
-        </is>
-      </c>
-      <c r="C1106" s="2" t="inlineStr">
-        <is>
-          <t>출력 프레임 크기 (px)</t>
-        </is>
-      </c>
-      <c r="D1106" s="2" t="inlineStr">
-        <is>
-          <t>Export frame size (px)</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1107">
-      <c r="A1107" s="2">
-        <v>3695</v>
-      </c>
-      <c r="B1107" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText616</t>
-        </is>
-      </c>
-      <c r="C1107" s="2" t="inlineStr">
-        <is>
-          <t>시트 열 수</t>
-        </is>
-      </c>
-      <c r="D1107" s="2" t="inlineStr">
-        <is>
-          <t>Sheet columns</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1108">
-      <c r="A1108" s="2">
-        <v>3696</v>
-      </c>
-      <c r="B1108" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText617</t>
-        </is>
-      </c>
-      <c r="C1108" s="2" t="inlineStr">
-        <is>
-          <t>묶음 만들기</t>
-        </is>
-      </c>
-      <c r="D1108" s="2" t="inlineStr">
-        <is>
-          <t>Create collection</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1109">
-      <c r="A1109" s="2">
-        <v>3697</v>
-      </c>
-      <c r="B1109" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText618</t>
-        </is>
-      </c>
-      <c r="C1109" s="2" t="inlineStr">
-        <is>
-          <t>재생</t>
-        </is>
-      </c>
-      <c r="D1109" s="2" t="inlineStr">
-        <is>
-          <t>Play</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1110">
-      <c r="A1110" s="2">
-        <v>3698</v>
-      </c>
-      <c r="B1110" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText619</t>
-        </is>
-      </c>
-      <c r="C1110" s="2" t="inlineStr">
-        <is>
-          <t>일시 정지</t>
-        </is>
-      </c>
-      <c r="D1110" s="2" t="inlineStr">
-        <is>
-          <t>Pause</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1111">
-      <c r="A1111" s="2">
-        <v>3699</v>
-      </c>
-      <c r="B1111" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText620</t>
-        </is>
-      </c>
-      <c r="C1111" s="2" t="inlineStr">
-        <is>
-          <t>프레임 {0}</t>
-        </is>
-      </c>
-      <c r="D1111" s="2" t="inlineStr">
-        <is>
-          <t>Frame {0}</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1112">
-      <c r="A1112" s="2">
-        <v>3700</v>
-      </c>
-      <c r="B1112" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText621</t>
-        </is>
-      </c>
-      <c r="C1112" s="2" t="inlineStr">
-        <is>
-          <t>기준 이미지를 선택하고 제작 설명을 입력하세요.</t>
-        </is>
-      </c>
-      <c r="D1112" s="2" t="inlineStr">
-        <is>
-          <t>Select a reference image and describe the asset.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1113">
-      <c r="A1113" s="2">
-        <v>3701</v>
-      </c>
-      <c r="B1113" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText622</t>
-        </is>
-      </c>
-      <c r="C1113" s="2" t="inlineStr">
-        <is>
-          <t>3. 결과 확인</t>
-        </is>
-      </c>
-      <c r="D1113" s="2" t="inlineStr">
-        <is>
-          <t>3. Review results</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1114">
-      <c r="A1114" s="2">
-        <v>3702</v>
-      </c>
-      <c r="B1114" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText623</t>
-        </is>
-      </c>
-      <c r="C1114" s="2" t="inlineStr">
-        <is>
-          <t>이전 제작 묶음</t>
-        </is>
-      </c>
-      <c r="D1114" s="2" t="inlineStr">
-        <is>
-          <t>Previous collections</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1115">
-      <c r="A1115" s="2">
-        <v>3703</v>
-      </c>
-      <c r="B1115" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText624</t>
-        </is>
-      </c>
-      <c r="C1115" s="2" t="inlineStr">
-        <is>
-          <t>대기</t>
-        </is>
-      </c>
-      <c r="D1115" s="2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1116">
-      <c r="A1116" s="2">
-        <v>3704</v>
-      </c>
-      <c r="B1116" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText625</t>
-        </is>
-      </c>
-      <c r="C1116" s="2" t="inlineStr">
-        <is>
-          <t>생성 중</t>
-        </is>
-      </c>
-      <c r="D1116" s="2" t="inlineStr">
-        <is>
-          <t>Generating</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1117">
-      <c r="A1117" s="2">
-        <v>3705</v>
-      </c>
-      <c r="B1117" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText626</t>
-        </is>
-      </c>
-      <c r="C1117" s="2" t="inlineStr">
-        <is>
-          <t>다시 만들기 필요</t>
-        </is>
-      </c>
-      <c r="D1117" s="2" t="inlineStr">
-        <is>
-          <t>Needs regeneration</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1118">
-      <c r="A1118" s="2">
-        <v>3706</v>
-      </c>
-      <c r="B1118" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText627</t>
-        </is>
-      </c>
-      <c r="C1118" s="2" t="inlineStr">
-        <is>
-          <t>에셋 내보내기 폴더 선택</t>
-        </is>
-      </c>
-      <c r="D1118" s="2" t="inlineStr">
-        <is>
-          <t>Choose an asset export folder</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1119">
-      <c r="A1119" s="2">
-        <v>3707</v>
-      </c>
-      <c r="B1119" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText628</t>
-        </is>
-      </c>
-      <c r="C1119" s="2" t="inlineStr">
-        <is>
-          <t>선택 항목의 생성 설명</t>
-        </is>
-      </c>
-      <c r="D1119" s="2" t="inlineStr">
-        <is>
-          <t>Selected frame prompt</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1120">
-      <c r="A1120" s="2">
-        <v>3708</v>
-      </c>
-      <c r="B1120" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText629</t>
-        </is>
-      </c>
-      <c r="C1120" s="2" t="inlineStr">
-        <is>
-          <t>참고 생성으로 만드는 초안입니다. 외형·동작·시점의 일관성을 보장하지 않으므로 결과를 확인하고 필요한 항목을 다시 만드세요.</t>
-        </is>
-      </c>
-      <c r="D1120" s="2" t="inlineStr">
-        <is>
-          <t>These are reference-based drafts. Identity, motion and view consistency are not guaranteed. Review the results and regenerate individual items as needed.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1121">
-      <c r="A1121" s="2">
-        <v>3709</v>
-      </c>
-      <c r="B1121" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText630</t>
-        </is>
-      </c>
-      <c r="C1121" s="2" t="inlineStr">
-        <is>
-          <t>선택 항목 다시 만들기</t>
-        </is>
-      </c>
-      <c r="D1121" s="2" t="inlineStr">
-        <is>
-          <t>Regenerate selected</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1122">
-      <c r="A1122" s="2">
-        <v>3710</v>
-      </c>
-      <c r="B1122" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText631</t>
-        </is>
-      </c>
-      <c r="C1122" s="2" t="inlineStr">
-        <is>
-          <t>제작 취소</t>
-        </is>
-      </c>
-      <c r="D1122" s="2" t="inlineStr">
-        <is>
-          <t>Cancel creation</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1123">
-      <c r="A1123" s="2">
-        <v>3711</v>
-      </c>
-      <c r="B1123" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText632</t>
-        </is>
-      </c>
-      <c r="C1123" s="2" t="inlineStr">
-        <is>
-          <t>이미지 교체</t>
-        </is>
-      </c>
-      <c r="D1123" s="2" t="inlineStr">
-        <is>
-          <t>Replace image</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1124">
-      <c r="A1124" s="2">
-        <v>3712</v>
-      </c>
-      <c r="B1124" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText633</t>
-        </is>
-      </c>
-      <c r="C1124" s="2" t="inlineStr">
-        <is>
-          <t>미완성 이어 만들기</t>
-        </is>
-      </c>
-      <c r="D1124" s="2" t="inlineStr">
-        <is>
-          <t>Resume unfinished</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1125">
-      <c r="A1125" s="2">
-        <v>3713</v>
-      </c>
-      <c r="B1125" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText634</t>
-        </is>
-      </c>
-      <c r="C1125" s="2" t="inlineStr">
-        <is>
-          <t>에셋 제작 입력이나 묶음 기록이 올바르지 않습니다.</t>
-        </is>
-      </c>
-      <c r="D1125" s="2" t="inlineStr">
-        <is>
-          <t>The asset creation input or collection record is invalid.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1126">
-      <c r="A1126" s="2">
-        <v>3714</v>
-      </c>
-      <c r="B1126" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText635</t>
-        </is>
-      </c>
-      <c r="C1126" s="2" t="inlineStr">
-        <is>
-          <t>{0}/{1} 항목 생성 중</t>
-        </is>
-      </c>
-      <c r="D1126" s="2" t="inlineStr">
-        <is>
-          <t>Generating item {0}/{1}</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1127">
-      <c r="A1127" s="2">
-        <v>3715</v>
-      </c>
-      <c r="B1127" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText636</t>
-        </is>
-      </c>
-      <c r="C1127" s="2" t="inlineStr">
-        <is>
-          <t>에셋 제작에 실패했습니다. 완성된 이미지는 유지됩니다.</t>
-        </is>
-      </c>
-      <c r="D1127" s="2" t="inlineStr">
-        <is>
-          <t>Asset creation failed. Completed images are preserved.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1128">
-      <c r="A1128" s="2">
-        <v>3716</v>
-      </c>
-      <c r="B1128" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText637</t>
-        </is>
-      </c>
-      <c r="C1128" s="2" t="inlineStr">
-        <is>
-          <t>정면</t>
-        </is>
-      </c>
-      <c r="D1128" s="2" t="inlineStr">
-        <is>
-          <t>Front</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1129">
-      <c r="A1129" s="2">
-        <v>3717</v>
-      </c>
-      <c r="B1129" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText638</t>
-        </is>
-      </c>
-      <c r="C1129" s="2" t="inlineStr">
-        <is>
-          <t>측면</t>
-        </is>
-      </c>
-      <c r="D1129" s="2" t="inlineStr">
-        <is>
-          <t>Side</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1130">
-      <c r="A1130" s="2">
-        <v>3718</v>
-      </c>
-      <c r="B1130" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText639</t>
-        </is>
-      </c>
-      <c r="C1130" s="2" t="inlineStr">
-        <is>
-          <t>후면</t>
-        </is>
-      </c>
-      <c r="D1130" s="2" t="inlineStr">
-        <is>
-          <t>Back</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1131">
-      <c r="A1131" s="2">
-        <v>3719</v>
-      </c>
-      <c r="B1131" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText640</t>
-        </is>
-      </c>
-      <c r="C1131" s="2" t="inlineStr">
-        <is>
-          <t>윗면</t>
-        </is>
-      </c>
-      <c r="D1131" s="2" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1132">
-      <c r="A1132" s="2">
-        <v>3720</v>
-      </c>
-      <c r="B1132" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText641</t>
-        </is>
-      </c>
-      <c r="C1132" s="2" t="inlineStr">
-        <is>
-          <t>예: 파란 망토를 입은 작은 기사</t>
-        </is>
-      </c>
-      <c r="D1132" s="2" t="inlineStr">
-        <is>
-          <t>e.g. a small knight wearing a blue cape</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1133">
-      <c r="A1133" s="2">
-        <v>3721</v>
-      </c>
-      <c r="B1133" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText642</t>
-        </is>
-      </c>
-      <c r="C1133" s="2" t="inlineStr">
-        <is>
-          <t>예: 오른쪽으로 걷기</t>
-        </is>
-      </c>
-      <c r="D1133" s="2" t="inlineStr">
-        <is>
-          <t>e.g. walking to the right</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1134">
-      <c r="A1134" s="2">
-        <v>3722</v>
-      </c>
-      <c r="B1134" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText643</t>
-        </is>
-      </c>
-      <c r="C1134" s="2" t="inlineStr">
-        <is>
-          <t>프레임별 포즈 설명 (선택)</t>
-        </is>
-      </c>
-      <c r="D1134" s="2" t="inlineStr">
-        <is>
-          <t>Per-frame poses (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1135">
-      <c r="A1135" s="2">
-        <v>3723</v>
-      </c>
-      <c r="B1135" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText644</t>
-        </is>
-      </c>
-      <c r="C1135" s="2" t="inlineStr">
-        <is>
-          <t>프레임 수만큼 한 줄씩 입력합니다. 비우면 공통 동작을 단계별 초안으로 만듭니다.</t>
-        </is>
-      </c>
-      <c r="D1135" s="2" t="inlineStr">
-        <is>
-          <t>Enter one pose per frame, one per line. Leave blank to draft phases of the shared action.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1136">
-      <c r="A1136" s="2">
-        <v>3724</v>
-      </c>
-      <c r="B1136" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText645</t>
-        </is>
-      </c>
-      <c r="C1136" s="2" t="inlineStr">
-        <is>
-          <t>모델·LoRA·출력 설정</t>
-        </is>
-      </c>
-      <c r="D1136" s="2" t="inlineStr">
-        <is>
-          <t>Model, LoRA and output</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1137">
-      <c r="A1137" s="2">
-        <v>3725</v>
-      </c>
-      <c r="B1137" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText646</t>
-        </is>
-      </c>
-      <c r="C1137" s="2" t="inlineStr">
-        <is>
-          <t>앞으로 이동</t>
-        </is>
-      </c>
-      <c r="D1137" s="2" t="inlineStr">
-        <is>
-          <t>Move earlier</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1138">
-      <c r="A1138" s="2">
-        <v>3726</v>
-      </c>
-      <c r="B1138" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText647</t>
-        </is>
-      </c>
-      <c r="C1138" s="2" t="inlineStr">
-        <is>
-          <t>뒤로 이동</t>
-        </is>
-      </c>
-      <c r="D1138" s="2" t="inlineStr">
-        <is>
-          <t>Move later</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1139">
-      <c r="A1139" s="2">
-        <v>3727</v>
-      </c>
-      <c r="B1139" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText648</t>
-        </is>
-      </c>
-      <c r="C1139" s="2" t="inlineStr">
-        <is>
-          <t>4. 공통 크기·하단 중앙 기준점으로 PNG와 시트를 저장합니다.</t>
-        </is>
-      </c>
-      <c r="D1139" s="2" t="inlineStr">
-        <is>
-          <t>4. Export PNG frames and a sheet at a common size with a bottom-center pivot.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1140">
-      <c r="A1140" s="2">
-        <v>3728</v>
-      </c>
-      <c r="B1140" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText649</t>
-        </is>
-      </c>
-      <c r="C1140" s="2" t="inlineStr">
-        <is>
-          <t>시트·PNG 내보내기</t>
-        </is>
-      </c>
-      <c r="D1140" s="2" t="inlineStr">
-        <is>
-          <t>Export sheet and PNGs</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1141">
-      <c r="A1141" s="2">
-        <v>3729</v>
-      </c>
-      <c r="B1141" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText650</t>
-        </is>
-      </c>
-      <c r="C1141" s="2" t="inlineStr">
-        <is>
-          <t>모든 항목에 이미지가 있어야 내보낼 수 있습니다.</t>
-        </is>
-      </c>
-      <c r="D1141" s="2" t="inlineStr">
-        <is>
-          <t>All items need an image before export.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1142">
-      <c r="A1142" s="2">
-        <v>3730</v>
-      </c>
-      <c r="B1142" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText651</t>
-        </is>
-      </c>
-      <c r="C1142" s="2" t="inlineStr">
-        <is>
-          <t>출력 시트가 너무 큽니다. 프레임 크기를 줄이세요.</t>
-        </is>
-      </c>
-      <c r="D1142" s="2" t="inlineStr">
-        <is>
-          <t>The output sheet is too large. Reduce the frame size.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1143">
-      <c r="A1143" s="2">
-        <v>3731</v>
-      </c>
-      <c r="B1143" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText652</t>
-        </is>
-      </c>
-      <c r="C1143" s="2" t="inlineStr">
-        <is>
-          <t>스프라이트·삼면도 제작</t>
-        </is>
-      </c>
-      <c r="D1143" s="2" t="inlineStr">
-        <is>
-          <t>Create sprites and views</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1144">
-      <c r="A1144" s="2">
-        <v>3732</v>
-      </c>
-      <c r="B1144" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText653</t>
-        </is>
-      </c>
-      <c r="C1144" s="2" t="inlineStr">
-        <is>
-          <t>생성 결과의 큰 이미지에서 우클릭 메뉴의 에셋 제작을 선택하면 이미지와 기존 설명을 가져옵니다. 에셋 제작에서 기준 이미지와 대상 설명을 입력하고 스프라이트 또는 삼면도를 선택합니다. 스프라이트는 동작·프레임 수·재생 속도를 지정합니다. 캐릭터는 정면·측면·후면, 물체는 정면·측면·윗면을 만듭니다. 결과에서 항목을 선택해 다시 만들거나 이미지로 교체할 수 있고, 스프라이트는 순서 변경과 반복 재생을 지원합니다. 취소·실패한 묶음은 미완성 이어 만들기로 남은 항목만 생성합니다. 내보내면 새 폴더에 개별 PNG, 시트, 좌표·기준점·FPS JSON과 원본 사본을 저장합니다. 참고 생성 기반 초안이므로 동작 연결이나 삼면도의 형태가 정확히 맞는지 직접 확인하세요.</t>
-        </is>
-      </c>
-      <c r="D1144" s="2" t="inlineStr">
-        <is>
-          <t>Right-click a large result preview and choose Asset creation to use its image and existing description. In Asset creation, select a reference, describe the subject and choose sprites or views. For sprites, enter an action, frame count and playback speed. Character views include front, side and back; object views include front, side and top. Regenerate or replace selected items, and reorder or loop sprite frames. Resume unfinished collections after cancellation or failure. Export creates a new folder with individual PNGs, a sheet, rectangle/pivot/FPS JSON and source copies. These reference-based drafts require review of motion continuity and view consistency.</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1145">
-      <c r="A1145" s="2">
-        <v>3733</v>
-      </c>
-      <c r="B1145" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText654</t>
-        </is>
-      </c>
-      <c r="C1145" s="2" t="inlineStr">
-        <is>
-          <t>공통 시드: {0}</t>
-        </is>
-      </c>
-      <c r="D1145" s="2" t="inlineStr">
-        <is>
-          <t>Common seed: {0}</t>
-        </is>
-      </c>
-    </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="1146">
-      <c r="A1146" s="2">
-        <v>3734</v>
-      </c>
-      <c r="B1146" s="2" t="inlineStr">
-        <is>
-          <t>EidolonText655</t>
-        </is>
-      </c>
-      <c r="C1146" s="2" t="inlineStr">
-        <is>
-          <t>에셋 제작은 ComfyUI 생성 방식에서 사용할 수 있습니다. 생성 환경에서 방식을 변경하세요.</t>
-        </is>
-      </c>
-      <c r="D1146" s="2" t="inlineStr">
-        <is>
-          <t>Asset creation uses ComfyUI. Change the backend in Generation environment to create assets.</t>
-        </is>
-      </c>
-    </row>
+    <x:row r="1072">
+      <x:c r="A1072" s="2">
+        <x:v>3660</x:v>
+      </x:c>
+      <x:c r="B1072" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText581</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1072" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">생성 환경</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1072" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Generation environment</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1073">
+      <x:c r="A1073" s="2">
+        <x:v>3661</x:v>
+      </x:c>
+      <x:c r="B1073" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText582</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1073" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">생성 방식과 사용할 모델, 모든 이미지에 적용할 공통 지침을 관리합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1073" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Manage generation methods, models, and instructions shared by all images.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1074">
+      <x:c r="A1074" s="2">
+        <x:v>3662</x:v>
+      </x:c>
+      <x:c r="B1074" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText583</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1074" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">생성 방식</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1074" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Generation methods</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1075">
+      <x:c r="A1075" s="2">
+        <x:v>3663</x:v>
+      </x:c>
+      <x:c r="B1075" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText584</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1075" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">학습 데이터</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1075" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Training data</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1076">
+      <x:c r="A1076" s="2">
+        <x:v>3664</x:v>
+      </x:c>
+      <x:c r="B1076" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText585</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1076" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">준비한 학습 데이터로 LoRA를 학습합니다. 데이터 준비와 수정은 설정에서 진행하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1076" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Train a LoRA with the prepared dataset. Prepare and edit training data in Settings.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1077">
+      <x:c r="A1077" s="2">
+        <x:v>3665</x:v>
+      </x:c>
+      <x:c r="B1077" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText586</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1077" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">화면과 저장 위치, 엔진 설치·연결, 학습 데이터 준비를 관리합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1077" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Manage appearance, storage, engine setup and connections, and training data.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1078">
+      <x:c r="A1078" s="2">
+        <x:v>3666</x:v>
+      </x:c>
+      <x:c r="B1078" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText587</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1078" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">학습 데이터가 아직 없습니다. 위의 학습 데이터를 눌러 이미지와 설명을 준비하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1078" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No training data is ready. Select Training data above to prepare images and captions.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1079">
+      <x:c r="A1079" s="2">
+        <x:v>3667</x:v>
+      </x:c>
+      <x:c r="B1079" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText588</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1079" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">설명으로 새로운 이미지를 만듭니다. 참고 이미지를 추가하면 기존 이미지의 구도와 내용을 바탕으로 생성할 수 있습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1079" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Create a new image from a description. Add a reference image to guide its composition and content.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1080">
+      <x:c r="A1080" s="2">
+        <x:v>3668</x:v>
+      </x:c>
+      <x:c r="B1080" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText589</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1080" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이미지와 원하는 그림체를 지정해 편집합니다. 변경 강도로 기존 이미지가 유지되는 정도를 조절합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1080" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Choose an image and describe the desired style. Change strength controls how much of the original image is preserved.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1081">
+      <x:c r="A1081" s="2">
+        <x:v>3669</x:v>
+      </x:c>
+      <x:c r="B1081" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText590</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1081" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">생성으로 이동</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1081" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Open Generate</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1082">
+      <x:c r="A1082" s="2">
+        <x:v>3670</x:v>
+      </x:c>
+      <x:c r="B1082" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText591</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1082" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">편집으로 이동</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1082" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Open Edit</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1083">
+      <x:c r="A1083" s="2">
+        <x:v>3671</x:v>
+      </x:c>
+      <x:c r="B1083" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText592</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1083" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">저장 위치</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1083" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Storage</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1084">
+      <x:c r="A1084" s="2">
+        <x:v>3672</x:v>
+      </x:c>
+      <x:c r="B1084" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText593</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1084" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">엔진 설치·연결</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1084" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Engine setup and connection</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1085">
+      <x:c r="A1085" s="2">
+        <x:v>3673</x:v>
+      </x:c>
+      <x:c r="B1085" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText594</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1085" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">일반</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1085" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">General</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1086">
+      <x:c r="A1086" s="2">
+        <x:v>3674</x:v>
+      </x:c>
+      <x:c r="B1086" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText595</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1086" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MCP 연결</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1086" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MCP connection</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1087">
+      <x:c r="A1087" s="2">
+        <x:v>3675</x:v>
+      </x:c>
+      <x:c r="B1087" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText596</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1087" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">외부 AI 도구에서 이미지 생성·편집과 결과 조회를 사용할 수 있습니다. 사용할 때 서버를 켜세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1087" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Use image generation, editing and result lookup from external AI tools. Start the server when you need it.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1088">
+      <x:c r="A1088" s="2">
+        <x:v>3676</x:v>
+      </x:c>
+      <x:c r="B1088" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText597</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1088" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">생성 지침은 MCP 요청별로 바꿀 수 있습니다. 저장한 설정은 유지되며 같은 PC에서만 연결합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1088" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Override generation instructions per MCP request. Saved settings are preserved. Connections are limited to this PC.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1089">
+      <x:c r="A1089" s="2">
+        <x:v>3677</x:v>
+      </x:c>
+      <x:c r="B1089" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText598</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1089" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">연결 대기 중</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1089" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Listening</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1090">
+      <x:c r="A1090" s="2">
+        <x:v>3678</x:v>
+      </x:c>
+      <x:c r="B1090" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText599</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1090" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">서버 꺼짐</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1090" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Server stopped</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1091">
+      <x:c r="A1091" s="2">
+        <x:v>3679</x:v>
+      </x:c>
+      <x:c r="B1091" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText600</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1091" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">서버 켜기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1091" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Start server</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1092">
+      <x:c r="A1092" s="2">
+        <x:v>3680</x:v>
+      </x:c>
+      <x:c r="B1092" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText601</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1092" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">서버 끄기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1092" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Stop server</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1093">
+      <x:c r="A1093" s="2">
+        <x:v>3681</x:v>
+      </x:c>
+      <x:c r="B1093" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText602</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1093" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MCP 주소의 수신 권한이 없습니다. 사용법 문서의 HTTP URL 예약 안내를 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1093" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The MCP address has no listener permission. See the HTTP URL reservation instructions in the usage document.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1094">
+      <x:c r="A1094" s="2">
+        <x:v>3682</x:v>
+      </x:c>
+      <x:c r="B1094" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText603</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1094" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">에셋 제작</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1094" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Asset creation</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1095">
+      <x:c r="A1095" s="2">
+        <x:v>3683</x:v>
+      </x:c>
+      <x:c r="B1095" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText604</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1095" s="2" t="str">
+        <x:v>기준 이미지로 스프라이트 또는 정면·측면·후면·윗면 사면도를 만듭니다.</x:v>
+      </x:c>
+      <x:c r="D1095" s="2" t="str">
+        <x:v>Create sprites or front, side, back and top views from a reference image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1096">
+      <x:c r="A1096" s="2">
+        <x:v>3684</x:v>
+      </x:c>
+      <x:c r="B1096" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText605</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1096" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">스프라이트 애니메이션</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1096" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sprite animation</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1097">
+      <x:c r="A1097" s="2">
+        <x:v>3685</x:v>
+      </x:c>
+      <x:c r="B1097" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText606</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1097" s="2" t="str">
+        <x:v>사면도</x:v>
+      </x:c>
+      <x:c r="D1097" s="2" t="str">
+        <x:v>Four views</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1098">
+      <x:c r="A1098" s="2">
+        <x:v>3686</x:v>
+      </x:c>
+      <x:c r="B1098" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText607</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1098" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">물체 삼면도</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1098" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Object views</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1099">
+      <x:c r="A1099" s="2">
+        <x:v>3687</x:v>
+      </x:c>
+      <x:c r="B1099" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText608</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1099" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 기준 이미지</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1099" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. Reference image</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1100">
+      <x:c r="A1100" s="2">
+        <x:v>3688</x:v>
+      </x:c>
+      <x:c r="B1100" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText609</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1100" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2. 제작 설정</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1100" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2. Creation settings</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1101">
+      <x:c r="A1101" s="2">
+        <x:v>3689</x:v>
+      </x:c>
+      <x:c r="B1101" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText610</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1101" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">동작 설명</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1101" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Action</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1102">
+      <x:c r="A1102" s="2">
+        <x:v>3690</x:v>
+      </x:c>
+      <x:c r="B1102" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText611</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1102" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">프레임 수</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1102" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Frame count</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1103">
+      <x:c r="A1103" s="2">
+        <x:v>3691</x:v>
+      </x:c>
+      <x:c r="B1103" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText612</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1103" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">재생 속도 (FPS)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1103" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Playback speed (FPS)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1104">
+      <x:c r="A1104" s="2">
+        <x:v>3692</x:v>
+      </x:c>
+      <x:c r="B1104" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText613</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1104" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">참고 이미지 변경 강도</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1104" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Reference change strength</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1105">
+      <x:c r="A1105" s="2">
+        <x:v>3693</x:v>
+      </x:c>
+      <x:c r="B1105" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText614</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1105" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">픽셀 아트</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1105" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pixel art</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1106">
+      <x:c r="A1106" s="2">
+        <x:v>3694</x:v>
+      </x:c>
+      <x:c r="B1106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText615</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">출력 프레임 크기 (px)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Export frame size (px)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1107">
+      <x:c r="A1107" s="2">
+        <x:v>3695</x:v>
+      </x:c>
+      <x:c r="B1107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText616</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">시트 열 수</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sheet columns</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1108">
+      <x:c r="A1108" s="2">
+        <x:v>3696</x:v>
+      </x:c>
+      <x:c r="B1108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText617</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">묶음 만들기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Create collection</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1109">
+      <x:c r="A1109" s="2">
+        <x:v>3697</x:v>
+      </x:c>
+      <x:c r="B1109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText618</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">재생</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Play</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1110">
+      <x:c r="A1110" s="2">
+        <x:v>3698</x:v>
+      </x:c>
+      <x:c r="B1110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText619</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">일시 정지</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pause</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1111">
+      <x:c r="A1111" s="2">
+        <x:v>3699</x:v>
+      </x:c>
+      <x:c r="B1111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText620</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">프레임 {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Frame {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1112">
+      <x:c r="A1112" s="2">
+        <x:v>3700</x:v>
+      </x:c>
+      <x:c r="B1112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText621</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">기준 이미지를 선택하고 제작 설명을 입력하세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Select a reference image and describe the asset.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1113">
+      <x:c r="A1113" s="2">
+        <x:v>3701</x:v>
+      </x:c>
+      <x:c r="B1113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText622</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">3. 결과 확인</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">3. Review results</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1114">
+      <x:c r="A1114" s="2">
+        <x:v>3702</x:v>
+      </x:c>
+      <x:c r="B1114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText623</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이전 제작 묶음</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Previous collections</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1115">
+      <x:c r="A1115" s="2">
+        <x:v>3703</x:v>
+      </x:c>
+      <x:c r="B1115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText624</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">대기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pending</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1116">
+      <x:c r="A1116" s="2">
+        <x:v>3704</x:v>
+      </x:c>
+      <x:c r="B1116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText625</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">생성 중</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Generating</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1117">
+      <x:c r="A1117" s="2">
+        <x:v>3705</x:v>
+      </x:c>
+      <x:c r="B1117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText626</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">다시 만들기 필요</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Needs regeneration</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1118">
+      <x:c r="A1118" s="2">
+        <x:v>3706</x:v>
+      </x:c>
+      <x:c r="B1118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText627</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">에셋 내보내기 폴더 선택</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Choose an asset export folder</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1119">
+      <x:c r="A1119" s="2">
+        <x:v>3707</x:v>
+      </x:c>
+      <x:c r="B1119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText628</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">선택 항목의 생성 설명</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Selected frame prompt</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1120">
+      <x:c r="A1120" s="2">
+        <x:v>3708</x:v>
+      </x:c>
+      <x:c r="B1120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText629</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">참고 생성으로 만드는 초안입니다. 외형·동작·시점의 일관성을 보장하지 않으므로 결과를 확인하고 필요한 항목을 다시 만드세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">These are reference-based drafts. Identity, motion and view consistency are not guaranteed. Review the results and regenerate individual items as needed.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1121">
+      <x:c r="A1121" s="2">
+        <x:v>3709</x:v>
+      </x:c>
+      <x:c r="B1121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText630</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">선택 항목 다시 만들기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Regenerate selected</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1122">
+      <x:c r="A1122" s="2">
+        <x:v>3710</x:v>
+      </x:c>
+      <x:c r="B1122" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText631</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1122" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">제작 취소</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1122" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cancel creation</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1123">
+      <x:c r="A1123" s="2">
+        <x:v>3711</x:v>
+      </x:c>
+      <x:c r="B1123" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText632</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1123" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이미지 교체</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1123" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Replace image</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1124">
+      <x:c r="A1124" s="2">
+        <x:v>3712</x:v>
+      </x:c>
+      <x:c r="B1124" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText633</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1124" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">미완성 이어 만들기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1124" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Resume unfinished</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1125">
+      <x:c r="A1125" s="2">
+        <x:v>3713</x:v>
+      </x:c>
+      <x:c r="B1125" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText634</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1125" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">에셋 제작 입력이나 묶음 기록이 올바르지 않습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1125" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The asset creation input or collection record is invalid.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1126">
+      <x:c r="A1126" s="2">
+        <x:v>3714</x:v>
+      </x:c>
+      <x:c r="B1126" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText635</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1126" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0}/{1} 항목 생성 중</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1126" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Generating item {0}/{1}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1127">
+      <x:c r="A1127" s="2">
+        <x:v>3715</x:v>
+      </x:c>
+      <x:c r="B1127" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText636</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1127" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">에셋 제작에 실패했습니다. 완성된 이미지는 유지됩니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1127" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Asset creation failed. Completed images are preserved.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1128">
+      <x:c r="A1128" s="2">
+        <x:v>3716</x:v>
+      </x:c>
+      <x:c r="B1128" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText637</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1128" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">정면</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1128" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Front</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1129">
+      <x:c r="A1129" s="2">
+        <x:v>3717</x:v>
+      </x:c>
+      <x:c r="B1129" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText638</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1129" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">측면</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1129" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Side</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1130">
+      <x:c r="A1130" s="2">
+        <x:v>3718</x:v>
+      </x:c>
+      <x:c r="B1130" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText639</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1130" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">후면</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1130" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Back</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1131">
+      <x:c r="A1131" s="2">
+        <x:v>3719</x:v>
+      </x:c>
+      <x:c r="B1131" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText640</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1131" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">윗면</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1131" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Top</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1132">
+      <x:c r="A1132" s="2">
+        <x:v>3720</x:v>
+      </x:c>
+      <x:c r="B1132" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText641</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1132" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">예: 파란 망토를 입은 작은 기사</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1132" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">e.g. a small knight wearing a blue cape</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1133">
+      <x:c r="A1133" s="2">
+        <x:v>3721</x:v>
+      </x:c>
+      <x:c r="B1133" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText642</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1133" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">예: 오른쪽으로 걷기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1133" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">e.g. walking to the right</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1134">
+      <x:c r="A1134" s="2">
+        <x:v>3722</x:v>
+      </x:c>
+      <x:c r="B1134" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText643</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1134" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">프레임별 포즈 설명 (선택)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1134" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Per-frame poses (optional)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1135">
+      <x:c r="A1135" s="2">
+        <x:v>3723</x:v>
+      </x:c>
+      <x:c r="B1135" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText644</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1135" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">프레임 수만큼 한 줄씩 입력합니다. 비우면 공통 동작을 단계별 초안으로 만듭니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1135" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enter one pose per frame, one per line. Leave blank to draft phases of the shared action.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1136">
+      <x:c r="A1136" s="2">
+        <x:v>3724</x:v>
+      </x:c>
+      <x:c r="B1136" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText645</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1136" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">모델·LoRA·출력 설정</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1136" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Model, LoRA and output</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1137">
+      <x:c r="A1137" s="2">
+        <x:v>3725</x:v>
+      </x:c>
+      <x:c r="B1137" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText646</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1137" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">앞으로 이동</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1137" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Move earlier</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1138">
+      <x:c r="A1138" s="2">
+        <x:v>3726</x:v>
+      </x:c>
+      <x:c r="B1138" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText647</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1138" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">뒤로 이동</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1138" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Move later</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1139">
+      <x:c r="A1139" s="2">
+        <x:v>3727</x:v>
+      </x:c>
+      <x:c r="B1139" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText648</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1139" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4. 공통 크기·하단 중앙 기준점으로 PNG와 시트를 저장합니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1139" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4. Export PNG frames and a sheet at a common size with a bottom-center pivot.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1140">
+      <x:c r="A1140" s="2">
+        <x:v>3728</x:v>
+      </x:c>
+      <x:c r="B1140" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText649</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1140" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">시트·PNG 내보내기</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1140" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Export sheet and PNGs</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1141">
+      <x:c r="A1141" s="2">
+        <x:v>3729</x:v>
+      </x:c>
+      <x:c r="B1141" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText650</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1141" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">모든 항목에 이미지가 있어야 내보낼 수 있습니다.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1141" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">All items need an image before export.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1142">
+      <x:c r="A1142" s="2">
+        <x:v>3730</x:v>
+      </x:c>
+      <x:c r="B1142" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText651</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1142" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">출력 시트가 너무 큽니다. 프레임 크기를 줄이세요.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1142" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The output sheet is too large. Reduce the frame size.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1143">
+      <x:c r="A1143" s="2">
+        <x:v>3731</x:v>
+      </x:c>
+      <x:c r="B1143" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText652</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1143" s="2" t="str">
+        <x:v>스프라이트·사면도 제작</x:v>
+      </x:c>
+      <x:c r="D1143" s="2" t="str">
+        <x:v>Create sprites and four views</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1144">
+      <x:c r="A1144" s="2">
+        <x:v>3732</x:v>
+      </x:c>
+      <x:c r="B1144" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText653</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1144" s="2" t="str">
+        <x:v>1. 에셋 제작에서 기준 이미지와 대상 설명을 입력합니다. 생성 결과의 큰 이미지를 우클릭해 에셋 제작으로 가져올 수도 있습니다.
+2. 스프라이트는 동작·프레임 수·재생 속도를 정하고 사면도는 정면·측면·후면·윗면을 생성합니다.
+3. 생성 후 프레임을 재생·비교하고 필요한 항목만 재생성하거나 교체합니다.
+4. 개별 PNG·시트·좌표와 FPS JSON을 내보냅니다.</x:v>
+      </x:c>
+      <x:c r="D1144" s="2" t="str">
+        <x:v>1. In Asset creation, choose a reference image and describe the subject. You can also right-click the large image in Results and choose Asset creation.
+2. For sprites, set the action, frame count and FPS. Four views generate front, side, back and top.
+3. Play or compare the results, then regenerate or replace individual items.
+4. Export individual PNGs, a sheet, coordinates and FPS JSON.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1145">
+      <x:c r="A1145" s="2">
+        <x:v>3733</x:v>
+      </x:c>
+      <x:c r="B1145" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText654</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1145" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">공통 시드: {0}</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1145" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Common seed: {0}</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="1146">
+      <x:c r="A1146" s="2">
+        <x:v>3734</x:v>
+      </x:c>
+      <x:c r="B1146" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EidolonText655</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1146" s="2" t="str">
+        <x:v>Codex가 기준 이미지와 공통 지침으로 각 프레임·시점을 순서대로 생성합니다. 체크포인트·LoRA·참고 강도·시드는 사용하지 않습니다.</x:v>
+      </x:c>
+      <x:c r="D1146" s="2" t="str">
+        <x:v>Codex generates each frame or view in sequence from the reference and shared guidelines. Checkpoints, LoRAs, reference strength and seeds do not apply.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1147">
+      <x:c r="A1147" s="5" t="n">
+        <x:v>3735</x:v>
+      </x:c>
+      <x:c r="B1147" s="5" t="str">
+        <x:v>EidolonText656</x:v>
+      </x:c>
+      <x:c r="C1147" s="5" t="str">
+        <x:v>묶음 삭제</x:v>
+      </x:c>
+      <x:c r="D1147" s="5" t="str">
+        <x:v>Delete collection</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1148">
+      <x:c r="A1148" s="5" t="n">
+        <x:v>3736</x:v>
+      </x:c>
+      <x:c r="B1148" s="5" t="str">
+        <x:v>EidolonText657</x:v>
+      </x:c>
+      <x:c r="C1148" s="5" t="str">
+        <x:v>{0}
+이 제작 묶음을 삭제할까요? 묶음 기록과 내부 작업 파일을 삭제합니다. 생성된 PNG와 프롬프트 JSON, 원본 생성 작업, 내보낸 파일은 보존합니다.</x:v>
+      </x:c>
+      <x:c r="D1148" s="5" t="str">
+        <x:v>{0}
+Delete this collection and its internal working files? Generated PNGs, prompt JSON, source generation jobs and exported files are preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1149">
+      <x:c r="A1149" s="5" t="n">
+        <x:v>3737</x:v>
+      </x:c>
+      <x:c r="B1149" s="5" t="str">
+        <x:v>EidolonText658</x:v>
+      </x:c>
+      <x:c r="C1149" s="5" t="str">
+        <x:v>{0} 제작 묶음을 삭제했습니다.</x:v>
+      </x:c>
+      <x:c r="D1149" s="5" t="str">
+        <x:v>Deleted collection: {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1150">
+      <x:c r="A1150" s="2" t="n">
+        <x:v>3738</x:v>
+      </x:c>
+      <x:c r="B1150" s="2" t="str">
+        <x:v>EidolonText659</x:v>
+      </x:c>
+      <x:c r="C1150" s="2" t="str">
+        <x:v>프롬프트 JSON의 생성 정보 형식이 올바르지 않습니다.</x:v>
+      </x:c>
+      <x:c r="D1150" s="2" t="str">
+        <x:v>The generation data in the prompt JSON has an invalid format.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1151">
+      <x:c r="A1151" s="2" t="n">
+        <x:v>3739</x:v>
+      </x:c>
+      <x:c r="B1151" s="2" t="str">
+        <x:v>EidolonText660</x:v>
+      </x:c>
+      <x:c r="C1151" s="2" t="str">
+        <x:v>이미지 생성·편집부터 결과 관리, 스프라이트·사면도 제작과 LoRA 학습까지 한곳에서 진행합니다. 아래 순서로 환경을 준비하고 필요한 작업 화면을 여세요.</x:v>
+      </x:c>
+      <x:c r="D1151" s="2" t="str">
+        <x:v>Create and edit images, manage results, make sprites and four views, and train LoRAs in one app. Prepare your environment below, then open the screen for your task.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1152">
+      <x:c r="A1152" s="2" t="n">
+        <x:v>3740</x:v>
+      </x:c>
+      <x:c r="B1152" s="2" t="str">
+        <x:v>EidolonText661</x:v>
+      </x:c>
+      <x:c r="C1152" s="2" t="str">
+        <x:v>생성 결과 관리</x:v>
+      </x:c>
+      <x:c r="D1152" s="2" t="str">
+        <x:v>Manage results</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1153">
+      <x:c r="A1153" s="2" t="n">
+        <x:v>3741</x:v>
+      </x:c>
+      <x:c r="B1153" s="2" t="str">
+        <x:v>EidolonText662</x:v>
+      </x:c>
+      <x:c r="C1153" s="2" t="str">
+        <x:v>생성 결과에서 이미지를 선택하면 생성 조건과 프롬프트를 확인할 수 있습니다. 저장·프롬프트 재사용·이 이미지로 편집·이 결과로 학습으로 다음 작업을 이어갑니다. Ctrl·Shift로 여러 이미지를 선택해 삭제하거나 이미지 폴더를 열 수 있습니다. 이미지 삭제는 PNG와 같은 이름의 프롬프트 JSON을 함께 삭제합니다.</x:v>
+      </x:c>
+      <x:c r="D1153" s="2" t="str">
+        <x:v>Select an image in Results to read its settings and prompt. Save it, reuse the prompt, edit the image or use it for training. Use Ctrl or Shift to select multiple images for deletion, or open the image folder. Deleting an image also removes its matching prompt JSON.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1154">
+      <x:c r="A1154" s="2" t="n">
+        <x:v>3742</x:v>
+      </x:c>
+      <x:c r="B1154" s="2" t="str">
+        <x:v>EidolonText663</x:v>
+      </x:c>
+      <x:c r="C1154" s="2" t="str">
+        <x:v>재생 속도는 초당 보여주는 프레임 수입니다. 미리보기와 내보내기는 같은 크기 보정을 사용합니다. 미완성 묶음은 이어 만들 수 있으며 묶음 삭제는 제작 기록·내부 작업 파일만 삭제하고 생성 이미지·프롬프트 JSON·내보낸 파일은 보존합니다.</x:v>
+      </x:c>
+      <x:c r="D1154" s="2" t="str">
+        <x:v>FPS is the number of frames shown per second. Preview and export use the same size normalization. Resume unfinished collections when needed. Delete collection removes its record and internal working files, while preserving generated images, prompt JSON and exported files.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1155">
+      <x:c r="A1155" s="2" t="n">
+        <x:v>3743</x:v>
+      </x:c>
+      <x:c r="B1155" s="2" t="str">
+        <x:v>EidolonText664</x:v>
+      </x:c>
+      <x:c r="C1155" s="2" t="str">
+        <x:v>설정과 저장 위치</x:v>
+      </x:c>
+      <x:c r="D1155" s="2" t="str">
+        <x:v>Settings and storage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1156">
+      <x:c r="A1156" s="2" t="n">
+        <x:v>3744</x:v>
+      </x:c>
+      <x:c r="B1156" s="2" t="str">
+        <x:v>EidolonText665</x:v>
+      </x:c>
+      <x:c r="C1156" s="2" t="str">
+        <x:v>설정 → 일반에서 이미지 저장 폴더·언어·테마와 MCP 연결을 관리합니다. 기본 이미지 폴더는 %LOCALAPPDATA%\Eidolon\Images이며 PNG와 같은 이름의 프롬프트 JSON을 함께 저장합니다. 원본과 실행 로그는 Jobs 아래에 보존합니다. 학습 데이터는 설정 → 엔진 설치·연결에서 열거나 비울 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D1156" s="2" t="str">
+        <x:v>Manage the image folder, language, theme and MCP connection in Settings &gt; General. The default image folder is %LOCALAPPDATA%\Eidolon\Images; each PNG has a matching prompt JSON. Originals and job logs are preserved under Jobs. Open or clear prepared datasets in Settings &gt; Engine setup and connection.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -20355,6 +20355,468 @@
         <x:v>Manage the image folder, language, theme and MCP connection in Settings &gt; General. The default image folder is %LOCALAPPDATA%\Eidolon\Images; each PNG has a matching prompt JSON. Originals and job logs are preserved under Jobs. Open or clear prepared datasets in Settings &gt; Engine setup and connection.</x:v>
       </x:c>
     </x:row>
+    <x:row r="1157">
+      <x:c r="A1157" s="2" t="n">
+        <x:v>3745</x:v>
+      </x:c>
+      <x:c r="B1157" s="2" t="str">
+        <x:v>EidolonText666</x:v>
+      </x:c>
+      <x:c r="C1157" s="2" t="str">
+        <x:v>앱 업데이트</x:v>
+      </x:c>
+      <x:c r="D1157" s="2" t="str">
+        <x:v>App updates</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1158">
+      <x:c r="A1158" s="2" t="n">
+        <x:v>3746</x:v>
+      </x:c>
+      <x:c r="B1158" s="2" t="str">
+        <x:v>EidolonText667</x:v>
+      </x:c>
+      <x:c r="C1158" s="2" t="str">
+        <x:v>현재 버전 {0}</x:v>
+      </x:c>
+      <x:c r="D1158" s="2" t="str">
+        <x:v>Current version {0}</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1159">
+      <x:c r="A1159" s="2" t="n">
+        <x:v>3747</x:v>
+      </x:c>
+      <x:c r="B1159" s="2" t="str">
+        <x:v>EidolonText668</x:v>
+      </x:c>
+      <x:c r="C1159" s="2" t="str">
+        <x:v>업데이트 확인</x:v>
+      </x:c>
+      <x:c r="D1159" s="2" t="str">
+        <x:v>Check for updates</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1160">
+      <x:c r="A1160" s="2" t="n">
+        <x:v>3748</x:v>
+      </x:c>
+      <x:c r="B1160" s="2" t="str">
+        <x:v>EidolonText669</x:v>
+      </x:c>
+      <x:c r="C1160" s="2" t="str">
+        <x:v>업데이트 후 재시작</x:v>
+      </x:c>
+      <x:c r="D1160" s="2" t="str">
+        <x:v>Update and restart</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1161">
+      <x:c r="A1161" s="2" t="n">
+        <x:v>3749</x:v>
+      </x:c>
+      <x:c r="B1161" s="2" t="str">
+        <x:v>EidolonText670</x:v>
+      </x:c>
+      <x:c r="C1161" s="2" t="str">
+        <x:v>릴리스 내용 보기</x:v>
+      </x:c>
+      <x:c r="D1161" s="2" t="str">
+        <x:v>View release notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1162">
+      <x:c r="A1162" s="2" t="n">
+        <x:v>3750</x:v>
+      </x:c>
+      <x:c r="B1162" s="2" t="str">
+        <x:v>EidolonText671</x:v>
+      </x:c>
+      <x:c r="C1162" s="2" t="str">
+        <x:v>새 버전을 확인하는 중…</x:v>
+      </x:c>
+      <x:c r="D1162" s="2" t="str">
+        <x:v>Checking for updates…</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1163">
+      <x:c r="A1163" s="2" t="n">
+        <x:v>3751</x:v>
+      </x:c>
+      <x:c r="B1163" s="2" t="str">
+        <x:v>EidolonText672</x:v>
+      </x:c>
+      <x:c r="C1163" s="2" t="str">
+        <x:v>업데이트를 확인하지 않았습니다.</x:v>
+      </x:c>
+      <x:c r="D1163" s="2" t="str">
+        <x:v>Updates have not been checked.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1164">
+      <x:c r="A1164" s="2" t="n">
+        <x:v>3752</x:v>
+      </x:c>
+      <x:c r="B1164" s="2" t="str">
+        <x:v>EidolonText673</x:v>
+      </x:c>
+      <x:c r="C1164" s="2" t="str">
+        <x:v>새로운 정식 업데이트가 없습니다.</x:v>
+      </x:c>
+      <x:c r="D1164" s="2" t="str">
+        <x:v>No newer stable update is available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1165">
+      <x:c r="A1165" s="2" t="n">
+        <x:v>3753</x:v>
+      </x:c>
+      <x:c r="B1165" s="2" t="str">
+        <x:v>EidolonText674</x:v>
+      </x:c>
+      <x:c r="C1165" s="2" t="str">
+        <x:v>게시된 정식 릴리스가 아직 없습니다.</x:v>
+      </x:c>
+      <x:c r="D1165" s="2" t="str">
+        <x:v>No stable release has been published yet.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1166">
+      <x:c r="A1166" s="2" t="n">
+        <x:v>3754</x:v>
+      </x:c>
+      <x:c r="B1166" s="2" t="str">
+        <x:v>EidolonText675</x:v>
+      </x:c>
+      <x:c r="C1166" s="2" t="str">
+        <x:v>새 버전 {0}을 사용할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D1166" s="2" t="str">
+        <x:v>Version {0} is available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1167">
+      <x:c r="A1167" s="2" t="n">
+        <x:v>3755</x:v>
+      </x:c>
+      <x:c r="B1167" s="2" t="str">
+        <x:v>EidolonText676</x:v>
+      </x:c>
+      <x:c r="C1167" s="2" t="str">
+        <x:v>공식 릴리스를 확인하고 업데이트합니다. 설치가 끝나면 앱이 다시 시작됩니다.</x:v>
+      </x:c>
+      <x:c r="D1167" s="2" t="str">
+        <x:v>Check official releases and install updates. The app restarts after installation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1168">
+      <x:c r="A1168" s="2" t="n">
+        <x:v>3756</x:v>
+      </x:c>
+      <x:c r="B1168" s="2" t="str">
+        <x:v>EidolonText677</x:v>
+      </x:c>
+      <x:c r="C1168" s="2" t="str">
+        <x:v>취소</x:v>
+      </x:c>
+      <x:c r="D1168" s="2" t="str">
+        <x:v>Cancel</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1169">
+      <x:c r="A1169" s="2" t="n">
+        <x:v>3757</x:v>
+      </x:c>
+      <x:c r="B1169" s="2" t="str">
+        <x:v>EidolonText678</x:v>
+      </x:c>
+      <x:c r="C1169" s="2" t="str">
+        <x:v>앱 업데이트는 Windows x64 단일 실행 파일 배포본에서 사용할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D1169" s="2" t="str">
+        <x:v>App updates require the published Windows x64 single executable.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1170">
+      <x:c r="A1170" s="2" t="n">
+        <x:v>3758</x:v>
+      </x:c>
+      <x:c r="B1170" s="2" t="str">
+        <x:v>EidolonText679</x:v>
+      </x:c>
+      <x:c r="C1170" s="2" t="str">
+        <x:v>현재 앱 버전을 확인할 수 없습니다.</x:v>
+      </x:c>
+      <x:c r="D1170" s="2" t="str">
+        <x:v>The current application version could not be read.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1171">
+      <x:c r="A1171" s="2" t="n">
+        <x:v>3759</x:v>
+      </x:c>
+      <x:c r="B1171" s="2" t="str">
+        <x:v>EidolonText680</x:v>
+      </x:c>
+      <x:c r="C1171" s="2" t="str">
+        <x:v>업데이트 서버 요청에 실패했습니다. (HTTP {0})</x:v>
+      </x:c>
+      <x:c r="D1171" s="2" t="str">
+        <x:v>The update server request failed. (HTTP {0})</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1172">
+      <x:c r="A1172" s="2" t="n">
+        <x:v>3760</x:v>
+      </x:c>
+      <x:c r="B1172" s="2" t="str">
+        <x:v>EidolonText681</x:v>
+      </x:c>
+      <x:c r="C1172" s="2" t="str">
+        <x:v>릴리스 정보를 확인할 수 없습니다. 릴리스 내용을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D1172" s="2" t="str">
+        <x:v>The release information is invalid. Check the release notes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1173">
+      <x:c r="A1173" s="2" t="n">
+        <x:v>3761</x:v>
+      </x:c>
+      <x:c r="B1173" s="2" t="str">
+        <x:v>EidolonText682</x:v>
+      </x:c>
+      <x:c r="C1173" s="2" t="str">
+        <x:v>릴리스에 SHA-256 정보가 없어 자동 설치할 수 없습니다. 릴리스 내용을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D1173" s="2" t="str">
+        <x:v>The release has no SHA-256 digest for automatic installation. Check the release notes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1174">
+      <x:c r="A1174" s="2" t="n">
+        <x:v>3762</x:v>
+      </x:c>
+      <x:c r="B1174" s="2" t="str">
+        <x:v>EidolonText683</x:v>
+      </x:c>
+      <x:c r="C1174" s="2" t="str">
+        <x:v>업데이트를 확인하지 못했습니다. 연결을 확인하고 다시 시도하세요.</x:v>
+      </x:c>
+      <x:c r="D1174" s="2" t="str">
+        <x:v>Updates could not be checked. Check your connection and try again.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1175">
+      <x:c r="A1175" s="2" t="n">
+        <x:v>3763</x:v>
+      </x:c>
+      <x:c r="B1175" s="2" t="str">
+        <x:v>EidolonText684</x:v>
+      </x:c>
+      <x:c r="C1175" s="2" t="str">
+        <x:v>Windows x64 실행 파일을 찾을 수 없습니다. 릴리스 내용을 확인하세요.</x:v>
+      </x:c>
+      <x:c r="D1175" s="2" t="str">
+        <x:v>The Windows x64 executable could not be found. Check the release notes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1176">
+      <x:c r="A1176" s="2" t="n">
+        <x:v>3764</x:v>
+      </x:c>
+      <x:c r="B1176" s="2" t="str">
+        <x:v>EidolonText685</x:v>
+      </x:c>
+      <x:c r="C1176" s="2" t="str">
+        <x:v>다운로드가 완료되지 않았습니다. 다시 시도하세요.</x:v>
+      </x:c>
+      <x:c r="D1176" s="2" t="str">
+        <x:v>The download is incomplete. Please try again.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1177">
+      <x:c r="A1177" s="2" t="n">
+        <x:v>3765</x:v>
+      </x:c>
+      <x:c r="B1177" s="2" t="str">
+        <x:v>EidolonText686</x:v>
+      </x:c>
+      <x:c r="C1177" s="2" t="str">
+        <x:v>업데이트를 다운로드하지 못했습니다. 다시 시도하세요.</x:v>
+      </x:c>
+      <x:c r="D1177" s="2" t="str">
+        <x:v>The update could not be downloaded. Please try again.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1178">
+      <x:c r="A1178" s="2" t="n">
+        <x:v>3766</x:v>
+      </x:c>
+      <x:c r="B1178" s="2" t="str">
+        <x:v>EidolonText687</x:v>
+      </x:c>
+      <x:c r="C1178" s="2" t="str">
+        <x:v>다운로드한 파일의 SHA-256이 일치하지 않습니다. 다시 다운로드하세요.</x:v>
+      </x:c>
+      <x:c r="D1178" s="2" t="str">
+        <x:v>The downloaded file's SHA-256 does not match. Download it again.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1179">
+      <x:c r="A1179" s="2" t="n">
+        <x:v>3767</x:v>
+      </x:c>
+      <x:c r="B1179" s="2" t="str">
+        <x:v>EidolonText688</x:v>
+      </x:c>
+      <x:c r="C1179" s="2" t="str">
+        <x:v>업데이트 설치를 준비하지 못했습니다. 현재 앱은 유지됩니다.</x:v>
+      </x:c>
+      <x:c r="D1179" s="2" t="str">
+        <x:v>The update could not be prepared. The current app is preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1180">
+      <x:c r="A1180" s="2" t="n">
+        <x:v>3768</x:v>
+      </x:c>
+      <x:c r="B1180" s="2" t="str">
+        <x:v>EidolonText689</x:v>
+      </x:c>
+      <x:c r="C1180" s="2" t="str">
+        <x:v>앱 파일을 교체하지 못했습니다. 기존 버전으로 다시 시작했습니다.</x:v>
+      </x:c>
+      <x:c r="D1180" s="2" t="str">
+        <x:v>The app file could not be replaced. The previous version was restarted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1181">
+      <x:c r="A1181" s="2" t="n">
+        <x:v>3769</x:v>
+      </x:c>
+      <x:c r="B1181" s="2" t="str">
+        <x:v>EidolonText690</x:v>
+      </x:c>
+      <x:c r="C1181" s="2" t="str">
+        <x:v>기존 앱 파일을 복원하지 못했습니다. 설치 폴더의 백업 파일을 보존했습니다.</x:v>
+      </x:c>
+      <x:c r="D1181" s="2" t="str">
+        <x:v>The previous app file could not be restored. Its backup has been preserved in the installation folder.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1182">
+      <x:c r="A1182" s="2" t="n">
+        <x:v>3770</x:v>
+      </x:c>
+      <x:c r="B1182" s="2" t="str">
+        <x:v>EidolonText691</x:v>
+      </x:c>
+      <x:c r="C1182" s="2" t="str">
+        <x:v>앱을 정상적으로 종료할 수 없어 업데이트를 중단했습니다.</x:v>
+      </x:c>
+      <x:c r="D1182" s="2" t="str">
+        <x:v>The update was stopped because the app could not close normally.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1183">
+      <x:c r="A1183" s="2" t="n">
+        <x:v>3771</x:v>
+      </x:c>
+      <x:c r="B1183" s="2" t="str">
+        <x:v>EidolonText692</x:v>
+      </x:c>
+      <x:c r="C1183" s="2" t="str">
+        <x:v>업데이트 다운로드 요청에 실패했습니다. (HTTP {0})</x:v>
+      </x:c>
+      <x:c r="D1183" s="2" t="str">
+        <x:v>The update download request failed. (HTTP {0})</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1184">
+      <x:c r="A1184" s="2" t="n">
+        <x:v>3772</x:v>
+      </x:c>
+      <x:c r="B1184" s="2" t="str">
+        <x:v>EidolonText693</x:v>
+      </x:c>
+      <x:c r="C1184" s="2" t="str">
+        <x:v>새 앱을 실행하지 못했습니다. 기존 버전으로 다시 시작했습니다.</x:v>
+      </x:c>
+      <x:c r="D1184" s="2" t="str">
+        <x:v>The new app could not be started. The previous version was restarted.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1185">
+      <x:c r="A1185" s="2" t="n">
+        <x:v>3773</x:v>
+      </x:c>
+      <x:c r="B1185" s="2" t="str">
+        <x:v>EidolonText694</x:v>
+      </x:c>
+      <x:c r="C1185" s="2" t="str">
+        <x:v>생성·학습·대기 작업을 완료한 뒤 업데이트할 수 있습니다.</x:v>
+      </x:c>
+      <x:c r="D1185" s="2" t="str">
+        <x:v>Complete generation, training and queued work before updating.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1186">
+      <x:c r="A1186" s="2" t="n">
+        <x:v>3774</x:v>
+      </x:c>
+      <x:c r="B1186" s="2" t="str">
+        <x:v>EidolonText695</x:v>
+      </x:c>
+      <x:c r="C1186" s="2" t="str">
+        <x:v>업데이트 다운로드 중 · {0:0}%</x:v>
+      </x:c>
+      <x:c r="D1186" s="2" t="str">
+        <x:v>Downloading update · {0:0}%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1187">
+      <x:c r="A1187" s="2" t="n">
+        <x:v>3775</x:v>
+      </x:c>
+      <x:c r="B1187" s="2" t="str">
+        <x:v>EidolonText696</x:v>
+      </x:c>
+      <x:c r="C1187" s="2" t="str">
+        <x:v>다운로드한 파일을 검증하고 재시작을 준비하는 중…</x:v>
+      </x:c>
+      <x:c r="D1187" s="2" t="str">
+        <x:v>Verifying the download and preparing to restart…</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1188">
+      <x:c r="A1188" s="2" t="n">
+        <x:v>3776</x:v>
+      </x:c>
+      <x:c r="B1188" s="2" t="str">
+        <x:v>EidolonText697</x:v>
+      </x:c>
+      <x:c r="C1188" s="2" t="str">
+        <x:v>업데이트를 준비했습니다. 앱을 종료하고 다시 시작합니다.</x:v>
+      </x:c>
+      <x:c r="D1188" s="2" t="str">
+        <x:v>The update is ready. Closing and restarting the app.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1189">
+      <x:c r="A1189" s="2" t="n">
+        <x:v>3777</x:v>
+      </x:c>
+      <x:c r="B1189" s="2" t="str">
+        <x:v>EidolonText698</x:v>
+      </x:c>
+      <x:c r="C1189" s="2" t="str">
+        <x:v>업데이트 작업을 취소했습니다.</x:v>
+      </x:c>
+      <x:c r="D1189" s="2" t="str">
+        <x:v>The update operation was cancelled.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -13250,15 +13250,19 @@
       <ns0:c r="B683" s="2" t="str">
         <ns0:v>EidolonText186</ns0:v>
       </ns0:c>
-      <ns0:c r="C683" s="3" t="str">
-        <ns0:v>1. 생성 환경 → 생성 방식·지침에서 ComfyUI 또는 Codex를 선택합니다.
-2. Codex를 사용하려면 설치된 Codex에서 먼저 로그인하고 실행 모델을 선택합니다. 기본 모델은 Codex의 기본값을 사용합니다.
-3. 공통 생성 지침·제외할 요소와 프리셋을 정하고 생성 환경 저장을 누릅니다.</ns0:v>
-      </ns0:c>
-      <ns0:c r="D683" s="3" t="str">
-        <ns0:v>1. Open Generation environment &gt; Generation method and guidelines and choose ComfyUI or Codex.
-2. For Codex, sign in to your installed Codex and select an execution model. Default model uses the CLI default.
-3. Set shared guidelines, exclusions and presets, then save the generation environment.</ns0:v>
+      <ns0:c r="C683" s="3" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>1. 생성 환경 → 생성 방식에서 ComfyUI 또는 Codex를 선택합니다.
+2. Codex는 설치된 Codex에서 먼저 로그인하고 실행 모델을 선택합니다. 기본 모델은 CLI 기본값을 사용합니다.
+3. 공통 생성 지침 메뉴에서 지침·제외할 요소와 프리셋을 정하고 생성 환경 저장을 누릅니다.</t>
+        </is>
+      </ns0:c>
+      <ns0:c r="D683" s="3" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>1. In Generation environment &gt; Generation methods, choose ComfyUI or Codex.
+2. For Codex, sign in and select an execution model; Default model uses the CLI default.
+3. Open Shared generation instructions, edit guidelines and presets, then save.</t>
+        </is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="684" ht="92.4000015258789" hidden="0" customHeight="1">
@@ -18194,11 +18198,15 @@
       <ns0:c r="B1034" s="2" t="str">
         <ns0:v>EidolonText542</ns0:v>
       </ns0:c>
-      <ns0:c r="C1034" s="3" t="str">
-        <ns0:v>저장하면 다음 생성·편집 요청부터 적용됩니다. 대기 중인 요청은 기존 설정을 사용합니다.</ns0:v>
-      </ns0:c>
-      <ns0:c r="D1034" s="3" t="str">
-        <ns0:v>Saved settings apply to new generation and editing requests. Queued requests keep their original settings.</ns0:v>
+      <ns0:c r="C1034" s="3" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>생성 방식·공통 지침·프리셋을 함께 저장합니다. 다음 생성·편집 요청부터 적용되며 대기 중인 요청은 기존 설정을 사용합니다.</t>
+        </is>
+      </ns0:c>
+      <ns0:c r="D1034" s="3" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>Save the generation method, shared instructions and presets together. Changes apply to new generation and editing requests; queued requests keep their original settings.</t>
+        </is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="1035">
@@ -18757,14 +18765,14 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="C1073" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">생성 방식과 사용할 모델, 모든 이미지에 적용할 공통 지침을 관리합니다.</ns0:t>
-        </ns0:is>
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>왼쪽 메뉴에서 생성 방식, 공통 생성 지침, 모델·LoRA를 선택해 관리합니다.</t>
+        </is>
       </ns0:c>
       <ns0:c r="D1073" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">Manage generation methods, models, and instructions shared by all images.</ns0:t>
-        </ns0:is>
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>Use the left menu to manage generation methods, shared generation instructions, and models and LoRAs.</t>
+        </is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="1074">
@@ -19037,14 +19045,14 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="C1087" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">외부 AI 도구에서 이미지 생성·편집과 결과 조회를 사용할 수 있습니다. 사용할 때 서버를 켜세요.</ns0:t>
-        </ns0:is>
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>외부 AI 도구에서 이미지 생성·편집과 결과 조회를 사용할 수 있습니다. 앱 초기화가 끝나면 서버가 자동으로 시작됩니다.</t>
+        </is>
       </ns0:c>
       <ns0:c r="D1087" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">Use image generation, editing and result lookup from external AI tools. Start the server when you need it.</ns0:t>
-        </ns0:is>
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>Use image generation, editing and result lookup from external AI tools. The server starts automatically after app initialization.</t>
+        </is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="1088">
@@ -19077,14 +19085,14 @@
         </ns0:is>
       </ns0:c>
       <ns0:c r="C1089" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">연결 대기 중</ns0:t>
-        </ns0:is>
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>서버 실행 중</t>
+        </is>
       </ns0:c>
       <ns0:c r="D1089" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">Listening</ns0:t>
-        </ns0:is>
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>Server running</t>
+        </is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="1090">
@@ -20336,11 +20344,15 @@
       <ns0:c r="B1156" s="2" t="str">
         <ns0:v>EidolonText665</ns0:v>
       </ns0:c>
-      <ns0:c r="C1156" s="2" t="str">
-        <ns0:v>설정 → 일반에서 이미지 저장 폴더·언어·테마와 MCP 연결을 관리합니다. 기본 이미지 폴더는 %LOCALAPPDATA%\Eidolon\Images이며 PNG와 같은 이름의 프롬프트 JSON을 함께 저장합니다. 원본과 실행 로그는 Jobs 아래에 보존합니다. 학습 데이터는 설정 → 엔진 설치·연결에서 열거나 비울 수 있습니다.</ns0:v>
-      </ns0:c>
-      <ns0:c r="D1156" s="2" t="str">
-        <ns0:v>Manage the image folder, language, theme and MCP connection in Settings &gt; General. The default image folder is %LOCALAPPDATA%\Eidolon\Images; each PNG has a matching prompt JSON. Originals and job logs are preserved under Jobs. Open or clear prepared datasets in Settings &gt; Engine setup and connection.</ns0:v>
+      <ns0:c r="C1156" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>설정 왼쪽 메뉴에서 일반·엔진 설치·연결·MCP 연결·앱 업데이트를 선택합니다. 일반에서 이미지 저장 폴더·언어·테마를 변경하고 설정 저장을 누릅니다. MCP 연결에서는 서버 상태·주소와 시작·정지를, 앱 업데이트에서는 버전 확인·업데이트를 관리합니다. 기본 이미지 폴더는 %LOCALAPPDATA%\Eidolon\Images이며 PNG와 같은 이름의 프롬프트 JSON을 함께 저장합니다. 학습 데이터는 엔진 설치·연결에서 열거나 비울 수 있습니다.</t>
+        </is>
+      </ns0:c>
+      <ns0:c r="D1156" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>Use the left menu in Settings to select General, Engine setup and connection, MCP connection or App updates. Change the image folder, language and theme in General, then save settings. MCP connection provides server status, address and start/stop controls. App updates provides version checks and updates. The default image folder is %LOCALAPPDATA%\Eidolon\Images; each PNG has a matching prompt JSON. Open or clear prepared training data in Engine setup and connection.</t>
+        </is>
       </ns0:c>
     </ns0:row>
     <ns0:row r="1157">
@@ -20803,6 +20815,66 @@
       </ns0:c>
       <ns0:c r="D1189" s="2" t="str">
         <ns0:v>The update operation was cancelled.</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="1190">
+      <ns0:c r="A1190" s="2">
+        <v xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">3778</v>
+      </ns0:c>
+      <ns0:c r="B1190" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>EidolonText699</t>
+        </is>
+      </ns0:c>
+      <ns0:c r="C1190" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>외곽선 유지 모델을 준비하는 중 · {0}</t>
+        </is>
+      </ns0:c>
+      <ns0:c r="D1190" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>Preparing outline control model · {0}</t>
+        </is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="1191">
+      <ns0:c r="A1191" s="2">
+        <v xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">3779</v>
+      </ns0:c>
+      <ns0:c r="B1191" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>EidolonText700</t>
+        </is>
+      </ns0:c>
+      <ns0:c r="C1191" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>편집에 필요한 {0} 모델이 서버에 없습니다. ComfyUI의 models/controlnet 폴더에 준비해 주세요.</t>
+        </is>
+      </ns0:c>
+      <ns0:c r="D1191" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>The server is missing {0}, required for style editing. Place it in ComfyUI models/controlnet.</t>
+        </is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="1192">
+      <ns0:c r="A1192" s="2">
+        <v xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">3780</v>
+      </ns0:c>
+      <ns0:c r="B1192" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>EidolonText701</t>
+        </is>
+      </ns0:c>
+      <ns0:c r="C1192" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>외곽선 유지에 필요한 {0} 노드가 없습니다. ComfyUI를 설치·복구하거나 외부 서버의 기본 노드를 확인해 주세요.</t>
+        </is>
+      </ns0:c>
+      <ns0:c r="D1192" s="2" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>The {0} node required for outline control is unavailable. Install or repair ComfyUI, or check the external server core nodes.</t>
+        </is>
       </ns0:c>
     </ns0:row>
   </ns0:sheetData>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -21013,6 +21013,248 @@
         </is>
       </c>
     </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>3786</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>EidolonText707</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>프롬프트 변환 모델을 설치하는 중…</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>Installing the prompt conversion model…</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>3787</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>EidolonText708</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>프롬프트 변환 모델이 준비되었습니다.</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>The prompt conversion model is ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>3788</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>EidolonText709</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>입력을 영문 태그로 변환하는 중…</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>Converting the description to English tags…</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>3789</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>EidolonText710</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>프롬프트 변환 모델이 없습니다. 엔진 탭에서 설치해 주세요.</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>The prompt conversion model is unavailable. Install it in the engine tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>3790</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>EidolonText711</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>영문 태그 변환에 실패했습니다. 입력과 로그를 확인해 주세요.</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>English tag conversion failed. Check the input and log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>3791</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>EidolonText712</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>프롬프트 변환 모델</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>Prompt conversion model</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>3792</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>EidolonText713</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>한글·영어 설명을 영문 태그로 정리해 생성합니다. 원문은 유지합니다.</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>Generate with English tags converted from Korean or English input. The original input is preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>3793</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>EidolonText714</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Instruct-2507 · Q4_K_M · 약 2.5 GB</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Qwen3-4B-Instruct-2507 · Q4_K_M · about 2.5 GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>EidolonText715</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>변환 모델 설치</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Install converter</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>3795</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>EidolonText716</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>설치하면 일반·참고 이미지 생성 전에 영문 태그로 자동 변환합니다.</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>Once installed, automatically converts prompts to English tags before standard and reference-image generation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>3796</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>EidolonText717</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>저장된 엔진 경로를 사용합니다. 경로 변경은 엔진 설정에서 적용하세요.</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>Uses the saved engine location. Apply location changes in engine settings.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -21255,6 +21255,78 @@
         </is>
       </c>
     </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>3797</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>EidolonText718</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>변환 모델 삭제</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>Delete converter</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>3798</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>EidolonText719</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>아래의 변환 모델·실행기 폴더와 설치용 압축·부분 다운로드 파일을 영구 삭제합니다.
+{0}
+{1}
+ComfyUI·생성 모델·LoRA는 유지합니다. 삭제 후에는 입력한 설명으로 생성합니다.</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>Permanently delete these converter model/runtime folders and their installer archive and partial downloads:
+{0}
+{1}
+ComfyUI, checkpoints and LoRAs are preserved. Generation then uses your original input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>3799</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>EidolonText720</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>변환 모델을 삭제했습니다. 입력한 설명으로 생성합니다.</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>Converter removed. Generation now uses your original input.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -21158,12 +21158,12 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>한글·영어 설명을 영문 태그로 정리해 생성합니다. 원문은 유지합니다.</t>
+          <t>한글·영어 입력을 선택한 이미지 모델에 맞는 영어 태그나 문장으로 정리합니다. 원문은 유지합니다.</t>
         </is>
       </c>
       <c r="D1204" t="inlineStr">
         <is>
-          <t>Generate with English tags converted from Korean or English input. The original input is preserved.</t>
+          <t>Adapts Korean or English input into English tags or sentences suited to the selected image model. Preserves the original input.</t>
         </is>
       </c>
     </row>
@@ -21224,12 +21224,12 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>설치하면 일반·참고 이미지 생성 전에 영문 태그로 자동 변환합니다.</t>
+          <t>설치하면 앱·MCP의 일반·참고 이미지 생성과 편집에 자동 적용합니다.</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
         <is>
-          <t>Once installed, automatically converts prompts to English tags before standard and reference-image generation.</t>
+          <t>Once installed, applies automatically to standard and reference-image generation and style edits from the app and MCP.</t>
         </is>
       </c>
     </row>
@@ -21324,6 +21324,166 @@
       <c r="D1211" t="inlineStr">
         <is>
           <t>Converter removed. Generation now uses your original input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="n">
+        <v>3800</v>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>EidolonText721</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>부분 고치기</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>Edit area</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="n">
+        <v>3801</v>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>EidolonText722</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>브러시 크기</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>Brush size</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="n">
+        <v>3802</v>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>EidolonText723</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>지우개</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Eraser</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="n">
+        <v>3803</v>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>EidolonText724</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>선택 지우기</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Clear selection</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="n">
+        <v>3804</v>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>EidolonText725</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>고칠 부분을 칠한 뒤 변경할 내용을 입력하세요. 선택하지 않은 부분은 원본을 유지합니다.</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Paint the area to edit, then describe the change. Unselected areas retain the original image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="n">
+        <v>3805</v>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>EidolonText726</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>고칠 부분을 먼저 칠하세요.</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>Paint the area to edit first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="n">
+        <v>3806</v>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>EidolonText727</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>선택한 영역을 어떻게 바꿀지 입력하세요.</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Describe what to change inside the selected area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="n">
+        <v>3807</v>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>EidolonText728</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>영역 선택</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Select area</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -21224,12 +21224,12 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>설치하면 앱·MCP의 일반·참고 이미지 생성과 편집에 자동 적용합니다.</t>
+          <t>설치하면 생성·편집 화면에서 입력을 변환하고 수정할 수 있습니다.</t>
         </is>
       </c>
       <c r="D1207" t="inlineStr">
         <is>
-          <t>Once installed, applies automatically to standard and reference-image generation and style edits from the app and MCP.</t>
+          <t>After installation, you can convert and edit the input on the generation and editing screens.</t>
         </is>
       </c>
     </row>
@@ -21484,6 +21484,66 @@
       <c r="D1219" t="inlineStr">
         <is>
           <t>Select area</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="n">
+        <v>3808</v>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>EidolonText729</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>변환하기</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Convert</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="n">
+        <v>3809</v>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>EidolonText730</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>변환문</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>Converted prompt</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="n">
+        <v>3810</v>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>EidolonText731</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>변환문을 확인하고 필요하면 수정한 뒤 생성하세요.</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>Review and edit the converted prompt before generating.</t>
         </is>
       </c>
     </row>

--- a/Excel/String.xlsx
+++ b/Excel/String.xlsx
@@ -21498,12 +21498,12 @@
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>변환하기</t>
+          <t>tag로 변환</t>
         </is>
       </c>
       <c r="D1220" t="inlineStr">
         <is>
-          <t>Convert</t>
+          <t>Convert to tags</t>
         </is>
       </c>
     </row>
